--- a/data.xlsx
+++ b/data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macos/REPORT FB&amp;STORE/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macos/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE03B486-DC96-B94B-9234-02C3C79EEC6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE85971B-2AC6-514E-A01E-E80A56CC3EA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="80" yWindow="660" windowWidth="29320" windowHeight="18460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="80" yWindow="660" windowWidth="29320" windowHeight="18460" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="📖 ĐỊNH NGHĨA CHỈ SỐ" sheetId="1" r:id="rId1"/>
@@ -4149,16 +4149,18 @@
     <xf numFmtId="0" fontId="34" fillId="136" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -4166,7 +4168,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -4177,7 +4178,6 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="44" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -12782,7 +12782,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="38" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="322" t="s">
+      <c r="A1" s="326" t="s">
         <v>335</v>
       </c>
       <c r="B1" s="323"/>
@@ -12810,7 +12810,7 @@
       <c r="X1" s="323"/>
     </row>
     <row r="2" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="327" t="s">
+      <c r="A2" s="329" t="s">
         <v>336</v>
       </c>
       <c r="B2" s="323"/>
@@ -12912,7 +12912,7 @@
       </c>
     </row>
     <row r="4" spans="1:24" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="333" t="s">
+      <c r="A4" s="334" t="s">
         <v>361</v>
       </c>
       <c r="B4" s="323"/>
@@ -12940,7 +12940,7 @@
       <c r="X4" s="323"/>
     </row>
     <row r="5" spans="1:24" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="324" t="s">
+      <c r="A5" s="327" t="s">
         <v>362</v>
       </c>
       <c r="B5" s="323"/>
@@ -13404,7 +13404,7 @@
       <c r="X12" s="14"/>
     </row>
     <row r="13" spans="1:24" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="324" t="s">
+      <c r="A13" s="327" t="s">
         <v>370</v>
       </c>
       <c r="B13" s="323"/>
@@ -14604,7 +14604,7 @@
       <c r="X32" s="12"/>
     </row>
     <row r="33" spans="1:24" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="330" t="s">
+      <c r="A33" s="331" t="s">
         <v>387</v>
       </c>
       <c r="B33" s="323"/>
@@ -14632,7 +14632,7 @@
       <c r="X33" s="323"/>
     </row>
     <row r="34" spans="1:24" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="332" t="s">
+      <c r="A34" s="333" t="s">
         <v>388</v>
       </c>
       <c r="B34" s="323"/>
@@ -15110,7 +15110,7 @@
       </c>
     </row>
     <row r="41" spans="1:24" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="328"/>
+      <c r="A41" s="330"/>
       <c r="B41" s="323"/>
       <c r="C41" s="323"/>
       <c r="D41" s="323"/>
@@ -15133,10 +15133,10 @@
       <c r="U41" s="323"/>
       <c r="V41" s="323"/>
       <c r="W41" s="323"/>
-      <c r="X41" s="329"/>
+      <c r="X41" s="324"/>
     </row>
     <row r="42" spans="1:24" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="328"/>
+      <c r="A42" s="330"/>
       <c r="B42" s="323"/>
       <c r="C42" s="323"/>
       <c r="D42" s="323"/>
@@ -15159,7 +15159,7 @@
       <c r="U42" s="323"/>
       <c r="V42" s="323"/>
       <c r="W42" s="323"/>
-      <c r="X42" s="329"/>
+      <c r="X42" s="324"/>
     </row>
     <row r="43" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="20"/>
@@ -16584,7 +16584,7 @@
       </c>
     </row>
     <row r="69" spans="1:24" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="331"/>
+      <c r="A69" s="332"/>
       <c r="B69" s="323"/>
       <c r="C69" s="323"/>
       <c r="D69" s="323"/>
@@ -16607,7 +16607,7 @@
       <c r="U69" s="323"/>
       <c r="V69" s="323"/>
       <c r="W69" s="323"/>
-      <c r="X69" s="329"/>
+      <c r="X69" s="324"/>
     </row>
     <row r="70" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="24"/>
@@ -16882,7 +16882,7 @@
       <c r="X73" s="27"/>
     </row>
     <row r="74" spans="1:24" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="326" t="s">
+      <c r="A74" s="328" t="s">
         <v>406</v>
       </c>
       <c r="B74" s="323"/>
@@ -17236,7 +17236,7 @@
       <c r="X80" s="12"/>
     </row>
     <row r="81" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="334"/>
+      <c r="A81" s="322"/>
       <c r="B81" s="323"/>
       <c r="C81" s="323"/>
       <c r="D81" s="323"/>
@@ -17259,7 +17259,7 @@
       <c r="U81" s="323"/>
       <c r="V81" s="323"/>
       <c r="W81" s="323"/>
-      <c r="X81" s="329"/>
+      <c r="X81" s="324"/>
     </row>
     <row r="82" spans="1:24" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="29"/>
@@ -17509,6 +17509,7 @@
     <row r="200" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A4:X4"/>
     <mergeCell ref="A81:X81"/>
     <mergeCell ref="A57:X57"/>
     <mergeCell ref="A47:X47"/>
@@ -17525,7 +17526,6 @@
     <mergeCell ref="A69:X69"/>
     <mergeCell ref="A34:X34"/>
     <mergeCell ref="A29:X29"/>
-    <mergeCell ref="A4:X4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -17737,7 +17737,9 @@
       <c r="D6" s="49">
         <v>97</v>
       </c>
-      <c r="E6" s="49"/>
+      <c r="E6" s="49">
+        <v>274</v>
+      </c>
       <c r="F6" s="49"/>
       <c r="G6" s="49">
         <v>6767007</v>
@@ -17771,9 +17773,9 @@
         <f t="shared" ref="P6:P35" si="3">IFERROR(IF(J6&gt;0,M6/J6,""),"")</f>
         <v>301152.59090909088</v>
       </c>
-      <c r="Q6" s="52" t="str">
+      <c r="Q6" s="52">
         <f t="shared" ref="Q6:Q35" si="4">IFERROR(IF(E6&gt;0,D6/E6,""),"")</f>
-        <v/>
+        <v>0.354014598540146</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -17789,7 +17791,9 @@
       <c r="D7" s="49">
         <v>65</v>
       </c>
-      <c r="E7" s="49"/>
+      <c r="E7" s="49">
+        <v>231</v>
+      </c>
       <c r="F7" s="49"/>
       <c r="G7" s="49">
         <v>4259006</v>
@@ -17823,9 +17827,9 @@
         <f t="shared" si="3"/>
         <v>313523.53488372092</v>
       </c>
-      <c r="Q7" s="52" t="str">
+      <c r="Q7" s="52">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.2813852813852814</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -17841,7 +17845,9 @@
       <c r="D8" s="49">
         <v>87</v>
       </c>
-      <c r="E8" s="49"/>
+      <c r="E8" s="49">
+        <v>230</v>
+      </c>
       <c r="F8" s="49"/>
       <c r="G8" s="49">
         <v>8799511</v>
@@ -17875,9 +17881,9 @@
         <f t="shared" si="3"/>
         <v>300000.3125</v>
       </c>
-      <c r="Q8" s="52" t="str">
+      <c r="Q8" s="52">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.37826086956521737</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -17893,7 +17899,9 @@
       <c r="D9" s="49">
         <v>81</v>
       </c>
-      <c r="E9" s="49"/>
+      <c r="E9" s="49">
+        <v>304</v>
+      </c>
       <c r="F9" s="49"/>
       <c r="G9" s="49">
         <v>9745005</v>
@@ -17925,9 +17933,9 @@
         <f t="shared" si="3"/>
         <v>331025.21666666667</v>
       </c>
-      <c r="Q9" s="52" t="str">
+      <c r="Q9" s="52">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.26644736842105265</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -17943,7 +17951,9 @@
       <c r="D10" s="49">
         <v>76</v>
       </c>
-      <c r="E10" s="49"/>
+      <c r="E10" s="49">
+        <v>467</v>
+      </c>
       <c r="F10" s="49"/>
       <c r="G10" s="49">
         <v>12953499</v>
@@ -17977,9 +17987,9 @@
         <f t="shared" si="3"/>
         <v>310641.30434782611</v>
       </c>
-      <c r="Q10" s="52" t="str">
+      <c r="Q10" s="52">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.16274089935760172</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -17995,7 +18005,9 @@
       <c r="D11" s="49">
         <v>81</v>
       </c>
-      <c r="E11" s="49"/>
+      <c r="E11" s="49">
+        <v>456</v>
+      </c>
       <c r="F11" s="49"/>
       <c r="G11" s="49">
         <v>9757501</v>
@@ -18029,9 +18041,9 @@
         <f t="shared" si="3"/>
         <v>275347.97297297296</v>
       </c>
-      <c r="Q11" s="52" t="str">
+      <c r="Q11" s="52">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.17763157894736842</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -18047,7 +18059,9 @@
       <c r="D12" s="49">
         <v>64</v>
       </c>
-      <c r="E12" s="49"/>
+      <c r="E12" s="49">
+        <v>392</v>
+      </c>
       <c r="F12" s="49"/>
       <c r="G12" s="49">
         <v>10669504</v>
@@ -18081,9 +18095,9 @@
         <f t="shared" si="3"/>
         <v>325365.46376811597</v>
       </c>
-      <c r="Q12" s="52" t="str">
+      <c r="Q12" s="52">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.16326530612244897</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -18099,7 +18113,9 @@
       <c r="D13" s="49">
         <v>74</v>
       </c>
-      <c r="E13" s="49"/>
+      <c r="E13" s="49">
+        <v>284</v>
+      </c>
       <c r="F13" s="49"/>
       <c r="G13" s="49">
         <v>6963251</v>
@@ -18133,9 +18149,9 @@
         <f t="shared" si="3"/>
         <v>407593.75</v>
       </c>
-      <c r="Q13" s="52" t="str">
+      <c r="Q13" s="52">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.26056338028169013</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -18151,7 +18167,9 @@
       <c r="D14" s="49">
         <v>76</v>
       </c>
-      <c r="E14" s="49"/>
+      <c r="E14" s="49">
+        <v>186</v>
+      </c>
       <c r="F14" s="49"/>
       <c r="G14" s="49">
         <v>5794398</v>
@@ -18185,9 +18203,9 @@
         <f t="shared" si="3"/>
         <v>282302.53658536583</v>
       </c>
-      <c r="Q14" s="52" t="str">
+      <c r="Q14" s="52">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.40860215053763443</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -18203,7 +18221,9 @@
       <c r="D15" s="49">
         <v>76</v>
       </c>
-      <c r="E15" s="49"/>
+      <c r="E15" s="49">
+        <v>240</v>
+      </c>
       <c r="F15" s="49"/>
       <c r="G15" s="49">
         <v>5953000</v>
@@ -18235,9 +18255,9 @@
         <f t="shared" si="3"/>
         <v>296194.46296296298</v>
       </c>
-      <c r="Q15" s="52" t="str">
+      <c r="Q15" s="52">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.31666666666666665</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -18253,7 +18273,9 @@
       <c r="D16" s="49">
         <v>90</v>
       </c>
-      <c r="E16" s="49"/>
+      <c r="E16" s="49">
+        <v>261</v>
+      </c>
       <c r="F16" s="49"/>
       <c r="G16" s="49">
         <v>4152001</v>
@@ -18285,9 +18307,9 @@
         <f t="shared" si="3"/>
         <v>370561.02439024393</v>
       </c>
-      <c r="Q16" s="52" t="str">
+      <c r="Q16" s="52">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.34482758620689657</v>
       </c>
     </row>
     <row r="17" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -18303,7 +18325,9 @@
       <c r="D17" s="49">
         <v>88</v>
       </c>
-      <c r="E17" s="49"/>
+      <c r="E17" s="49">
+        <v>285</v>
+      </c>
       <c r="F17" s="49"/>
       <c r="G17" s="49">
         <v>12255008</v>
@@ -18337,9 +18361,9 @@
         <f t="shared" si="3"/>
         <v>286619.62686567166</v>
       </c>
-      <c r="Q17" s="52" t="str">
+      <c r="Q17" s="52">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.30877192982456142</v>
       </c>
     </row>
     <row r="18" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -18355,7 +18379,9 @@
       <c r="D18" s="49">
         <v>82</v>
       </c>
-      <c r="E18" s="49"/>
+      <c r="E18" s="49">
+        <v>262</v>
+      </c>
       <c r="F18" s="49"/>
       <c r="G18" s="49">
         <v>11464504</v>
@@ -18389,9 +18415,9 @@
         <f t="shared" si="3"/>
         <v>268454.01086956525</v>
       </c>
-      <c r="Q18" s="52" t="str">
+      <c r="Q18" s="52">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.31297709923664124</v>
       </c>
     </row>
     <row r="19" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -18407,7 +18433,9 @@
       <c r="D19" s="49">
         <v>63</v>
       </c>
-      <c r="E19" s="49"/>
+      <c r="E19" s="49">
+        <v>275</v>
+      </c>
       <c r="F19" s="49"/>
       <c r="G19" s="49">
         <v>13214251</v>
@@ -18441,9 +18469,9 @@
         <f t="shared" si="3"/>
         <v>354036.32258064515</v>
       </c>
-      <c r="Q19" s="52" t="str">
+      <c r="Q19" s="52">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.2290909090909091</v>
       </c>
     </row>
     <row r="20" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -18459,7 +18487,9 @@
       <c r="D20" s="49">
         <v>104</v>
       </c>
-      <c r="E20" s="49"/>
+      <c r="E20" s="49">
+        <v>358</v>
+      </c>
       <c r="F20" s="49"/>
       <c r="G20" s="49">
         <v>5703750</v>
@@ -18493,9 +18523,9 @@
         <f t="shared" si="3"/>
         <v>367437.58333333331</v>
       </c>
-      <c r="Q20" s="52" t="str">
+      <c r="Q20" s="52">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.29050279329608941</v>
       </c>
     </row>
     <row r="21" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -18511,7 +18541,9 @@
       <c r="D21" s="49">
         <v>108</v>
       </c>
-      <c r="E21" s="49"/>
+      <c r="E21" s="49">
+        <v>379</v>
+      </c>
       <c r="F21" s="49"/>
       <c r="G21" s="49">
         <v>8659502</v>
@@ -18545,9 +18577,9 @@
         <f t="shared" si="3"/>
         <v>309663.69090909092</v>
       </c>
-      <c r="Q21" s="52" t="str">
+      <c r="Q21" s="52">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.28496042216358841</v>
       </c>
     </row>
     <row r="22" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -18563,7 +18595,9 @@
       <c r="D22" s="49">
         <v>99</v>
       </c>
-      <c r="E22" s="49"/>
+      <c r="E22" s="49">
+        <v>432</v>
+      </c>
       <c r="F22" s="49"/>
       <c r="G22" s="49">
         <v>7292002</v>
@@ -18597,9 +18631,9 @@
         <f t="shared" si="3"/>
         <v>274288.27450980392</v>
       </c>
-      <c r="Q22" s="52" t="str">
+      <c r="Q22" s="52">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.22916666666666666</v>
       </c>
     </row>
     <row r="23" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -18615,7 +18649,9 @@
       <c r="D23" s="49">
         <v>114</v>
       </c>
-      <c r="E23" s="49"/>
+      <c r="E23" s="49">
+        <v>403</v>
+      </c>
       <c r="F23" s="49"/>
       <c r="G23" s="49">
         <v>6905755</v>
@@ -18647,9 +18683,9 @@
         <f t="shared" si="3"/>
         <v>361073.68627450982</v>
       </c>
-      <c r="Q23" s="52" t="str">
+      <c r="Q23" s="52">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.28287841191066998</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -18665,7 +18701,9 @@
       <c r="D24" s="49">
         <v>102</v>
       </c>
-      <c r="E24" s="49"/>
+      <c r="E24" s="49">
+        <v>303</v>
+      </c>
       <c r="F24" s="49"/>
       <c r="G24" s="49">
         <v>10739751</v>
@@ -18699,9 +18737,9 @@
         <f t="shared" si="3"/>
         <v>317124.98484848486</v>
       </c>
-      <c r="Q24" s="52" t="str">
+      <c r="Q24" s="52">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.33663366336633666</v>
       </c>
     </row>
     <row r="25" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -18717,7 +18755,9 @@
       <c r="D25" s="49">
         <v>78</v>
       </c>
-      <c r="E25" s="49"/>
+      <c r="E25" s="49">
+        <v>230</v>
+      </c>
       <c r="F25" s="49"/>
       <c r="G25" s="49">
         <v>9487759</v>
@@ -18751,9 +18791,9 @@
         <f t="shared" si="3"/>
         <v>268104.3</v>
       </c>
-      <c r="Q25" s="52" t="str">
+      <c r="Q25" s="52">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.33913043478260868</v>
       </c>
     </row>
     <row r="26" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -18769,7 +18809,9 @@
       <c r="D26" s="49">
         <v>63</v>
       </c>
-      <c r="E26" s="49"/>
+      <c r="E26" s="49">
+        <v>197</v>
+      </c>
       <c r="F26" s="49"/>
       <c r="G26" s="49">
         <v>7185011</v>
@@ -18803,9 +18845,9 @@
         <f t="shared" si="3"/>
         <v>262856.45762711862</v>
       </c>
-      <c r="Q26" s="52" t="str">
+      <c r="Q26" s="52">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.31979695431472083</v>
       </c>
     </row>
     <row r="27" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -18821,7 +18863,9 @@
       <c r="D27" s="49">
         <v>82</v>
       </c>
-      <c r="E27" s="49"/>
+      <c r="E27" s="49">
+        <v>210</v>
+      </c>
       <c r="F27" s="49"/>
       <c r="G27" s="49">
         <v>5823399</v>
@@ -18855,9 +18899,9 @@
         <f t="shared" si="3"/>
         <v>303137.30232558138</v>
       </c>
-      <c r="Q27" s="52" t="str">
+      <c r="Q27" s="52">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.39047619047619048</v>
       </c>
     </row>
     <row r="28" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -18873,7 +18917,9 @@
       <c r="D28" s="49">
         <v>69</v>
       </c>
-      <c r="E28" s="49"/>
+      <c r="E28" s="49">
+        <v>337</v>
+      </c>
       <c r="F28" s="49"/>
       <c r="G28" s="49">
         <v>6753005</v>
@@ -18905,9 +18951,9 @@
         <f t="shared" si="3"/>
         <v>356712.54545454547</v>
       </c>
-      <c r="Q28" s="52" t="str">
+      <c r="Q28" s="52">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.20474777448071216</v>
       </c>
     </row>
     <row r="29" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -18923,7 +18969,9 @@
       <c r="D29" s="49">
         <v>82</v>
       </c>
-      <c r="E29" s="49"/>
+      <c r="E29" s="49">
+        <v>278</v>
+      </c>
       <c r="F29" s="49"/>
       <c r="G29" s="49">
         <v>8755015</v>
@@ -18955,9 +19003,9 @@
         <f t="shared" si="3"/>
         <v>362643.28571428574</v>
       </c>
-      <c r="Q29" s="52" t="str">
+      <c r="Q29" s="52">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.29496402877697842</v>
       </c>
     </row>
     <row r="30" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -18973,7 +19021,9 @@
       <c r="D30" s="49">
         <v>99</v>
       </c>
-      <c r="E30" s="49"/>
+      <c r="E30" s="49">
+        <v>404</v>
+      </c>
       <c r="F30" s="49"/>
       <c r="G30" s="49">
         <v>7045999</v>
@@ -19005,9 +19055,9 @@
         <f t="shared" si="3"/>
         <v>263269.19230769231</v>
       </c>
-      <c r="Q30" s="52" t="str">
+      <c r="Q30" s="52">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.24504950495049505</v>
       </c>
     </row>
     <row r="31" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -19023,7 +19073,9 @@
       <c r="D31" s="49">
         <v>80</v>
       </c>
-      <c r="E31" s="49"/>
+      <c r="E31" s="49">
+        <v>283</v>
+      </c>
       <c r="F31" s="49"/>
       <c r="G31" s="49">
         <v>10419503</v>
@@ -19057,9 +19109,9 @@
         <f t="shared" si="3"/>
         <v>285430.59722222225</v>
       </c>
-      <c r="Q31" s="52" t="str">
+      <c r="Q31" s="52">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.28268551236749118</v>
       </c>
     </row>
     <row r="32" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -19075,7 +19127,9 @@
       <c r="D32" s="49">
         <v>75</v>
       </c>
-      <c r="E32" s="49"/>
+      <c r="E32" s="49">
+        <v>226</v>
+      </c>
       <c r="F32" s="49"/>
       <c r="G32" s="49">
         <v>10394010</v>
@@ -19109,9 +19163,9 @@
         <f t="shared" si="3"/>
         <v>291340.72463768115</v>
       </c>
-      <c r="Q32" s="52" t="str">
+      <c r="Q32" s="52">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.33185840707964603</v>
       </c>
     </row>
     <row r="33" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -19127,7 +19181,9 @@
       <c r="D33" s="49">
         <v>60</v>
       </c>
-      <c r="E33" s="49"/>
+      <c r="E33" s="49">
+        <v>236</v>
+      </c>
       <c r="F33" s="49"/>
       <c r="G33" s="49">
         <v>9633250</v>
@@ -19161,9 +19217,9 @@
         <f t="shared" si="3"/>
         <v>277970.93333333335</v>
       </c>
-      <c r="Q33" s="52" t="str">
+      <c r="Q33" s="52">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.25423728813559321</v>
       </c>
     </row>
     <row r="34" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -19179,7 +19235,9 @@
       <c r="D34" s="49">
         <v>73</v>
       </c>
-      <c r="E34" s="49"/>
+      <c r="E34" s="49">
+        <v>282</v>
+      </c>
       <c r="F34" s="49"/>
       <c r="G34" s="49">
         <v>7841005</v>
@@ -19211,9 +19269,9 @@
         <f t="shared" si="3"/>
         <v>342650.22857142857</v>
       </c>
-      <c r="Q34" s="52" t="str">
+      <c r="Q34" s="52">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.25886524822695034</v>
       </c>
     </row>
     <row r="35" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -19229,7 +19287,9 @@
       <c r="D35" s="49">
         <v>83</v>
       </c>
-      <c r="E35" s="49"/>
+      <c r="E35" s="49">
+        <v>261</v>
+      </c>
       <c r="F35" s="49"/>
       <c r="G35" s="49">
         <v>9861013</v>
@@ -19261,9 +19321,9 @@
         <f t="shared" si="3"/>
         <v>303102.09259259258</v>
       </c>
-      <c r="Q35" s="52" t="str">
+      <c r="Q35" s="52">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.31800766283524906</v>
       </c>
     </row>
     <row r="36" spans="1:17" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -20557,7 +20617,9 @@
       <c r="D6" s="105">
         <v>98</v>
       </c>
-      <c r="E6" s="105"/>
+      <c r="E6" s="105">
+        <v>248</v>
+      </c>
       <c r="F6" s="105"/>
       <c r="G6" s="105">
         <v>5255003</v>
@@ -20591,9 +20653,9 @@
         <f t="shared" ref="P6:P36" si="3">IFERROR(IF(J6&gt;0,M6/J6,""),"")</f>
         <v>345744.14285714284</v>
       </c>
-      <c r="Q6" s="108" t="str">
+      <c r="Q6" s="108">
         <f t="shared" ref="Q6:Q36" si="4">IFERROR(IF(E6&gt;0,D6/E6,""),"")</f>
-        <v/>
+        <v>0.39516129032258063</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -20609,7 +20671,9 @@
       <c r="D7" s="105">
         <v>88</v>
       </c>
-      <c r="E7" s="105"/>
+      <c r="E7" s="105">
+        <v>269</v>
+      </c>
       <c r="F7" s="105"/>
       <c r="G7" s="105">
         <v>9476011</v>
@@ -20643,9 +20707,9 @@
         <f t="shared" si="3"/>
         <v>342105.56140350876</v>
       </c>
-      <c r="Q7" s="108" t="str">
+      <c r="Q7" s="108">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.32713754646840149</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -20661,7 +20725,9 @@
       <c r="D8" s="105">
         <v>117</v>
       </c>
-      <c r="E8" s="105"/>
+      <c r="E8" s="105">
+        <v>271</v>
+      </c>
       <c r="F8" s="105"/>
       <c r="G8" s="105">
         <v>9565500</v>
@@ -20695,9 +20761,9 @@
         <f t="shared" si="3"/>
         <v>305177.80645161291</v>
       </c>
-      <c r="Q8" s="108" t="str">
+      <c r="Q8" s="108">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.43173431734317341</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -20713,7 +20779,9 @@
       <c r="D9" s="105">
         <v>96</v>
       </c>
-      <c r="E9" s="105"/>
+      <c r="E9" s="105">
+        <v>261</v>
+      </c>
       <c r="F9" s="105"/>
       <c r="G9" s="105">
         <v>6833004</v>
@@ -20747,9 +20815,9 @@
         <f t="shared" si="3"/>
         <v>269311.47540983604</v>
       </c>
-      <c r="Q9" s="108" t="str">
+      <c r="Q9" s="108">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.36781609195402298</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -20765,7 +20833,9 @@
       <c r="D10" s="105">
         <v>66</v>
       </c>
-      <c r="E10" s="105"/>
+      <c r="E10" s="105">
+        <v>260</v>
+      </c>
       <c r="F10" s="105"/>
       <c r="G10" s="105">
         <v>6461003</v>
@@ -20799,9 +20869,9 @@
         <f t="shared" si="3"/>
         <v>351030.68421052629</v>
       </c>
-      <c r="Q10" s="108" t="str">
+      <c r="Q10" s="108">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.25384615384615383</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macos/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE85971B-2AC6-514E-A01E-E80A56CC3EA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82F46BE3-3B3D-A94C-AD83-AC28F03C88D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="80" yWindow="660" windowWidth="29320" windowHeight="18460" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="80" yWindow="660" windowWidth="29320" windowHeight="18460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="📖 ĐỊNH NGHĨA CHỈ SỐ" sheetId="1" r:id="rId1"/>
@@ -4149,8 +4149,42 @@
     <xf numFmtId="0" fontId="34" fillId="136" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="39" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="43" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="46" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="44" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="40" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="40" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="42" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="41" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="146" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -4175,16 +4209,6 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="43" fillId="146" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4224,30 +4248,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="26" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="39" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="43" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="46" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="44" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="40" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="40" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="42" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="41" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="54" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4687,26 +4687,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="337" t="s">
+      <c r="A1" s="333" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="336"/>
-      <c r="C1" s="336"/>
-      <c r="D1" s="336"/>
-      <c r="E1" s="336"/>
-      <c r="F1" s="336"/>
-      <c r="G1" s="336"/>
+      <c r="B1" s="332"/>
+      <c r="C1" s="332"/>
+      <c r="D1" s="332"/>
+      <c r="E1" s="332"/>
+      <c r="F1" s="332"/>
+      <c r="G1" s="332"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="335" t="s">
+      <c r="A2" s="331" t="s">
         <v>57</v>
       </c>
-      <c r="B2" s="336"/>
-      <c r="C2" s="336"/>
-      <c r="D2" s="336"/>
-      <c r="E2" s="336"/>
-      <c r="F2" s="336"/>
-      <c r="G2" s="336"/>
+      <c r="B2" s="332"/>
+      <c r="C2" s="332"/>
+      <c r="D2" s="332"/>
+      <c r="E2" s="332"/>
+      <c r="F2" s="332"/>
+      <c r="G2" s="332"/>
     </row>
     <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="289" t="s">
@@ -7034,37 +7034,37 @@
       <c r="A1" s="396" t="s">
         <v>519</v>
       </c>
-      <c r="B1" s="336"/>
-      <c r="C1" s="336"/>
-      <c r="D1" s="336"/>
-      <c r="E1" s="336"/>
-      <c r="F1" s="336"/>
-      <c r="G1" s="336"/>
-      <c r="H1" s="336"/>
-      <c r="I1" s="336"/>
-      <c r="J1" s="336"/>
-      <c r="K1" s="336"/>
-      <c r="L1" s="336"/>
-      <c r="M1" s="336"/>
-      <c r="N1" s="336"/>
+      <c r="B1" s="332"/>
+      <c r="C1" s="332"/>
+      <c r="D1" s="332"/>
+      <c r="E1" s="332"/>
+      <c r="F1" s="332"/>
+      <c r="G1" s="332"/>
+      <c r="H1" s="332"/>
+      <c r="I1" s="332"/>
+      <c r="J1" s="332"/>
+      <c r="K1" s="332"/>
+      <c r="L1" s="332"/>
+      <c r="M1" s="332"/>
+      <c r="N1" s="332"/>
     </row>
     <row r="2" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="394" t="s">
         <v>520</v>
       </c>
-      <c r="B2" s="336"/>
-      <c r="C2" s="336"/>
-      <c r="D2" s="336"/>
-      <c r="E2" s="336"/>
-      <c r="F2" s="336"/>
-      <c r="G2" s="336"/>
-      <c r="H2" s="336"/>
-      <c r="I2" s="336"/>
-      <c r="J2" s="336"/>
-      <c r="K2" s="336"/>
-      <c r="L2" s="336"/>
-      <c r="M2" s="336"/>
-      <c r="N2" s="336"/>
+      <c r="B2" s="332"/>
+      <c r="C2" s="332"/>
+      <c r="D2" s="332"/>
+      <c r="E2" s="332"/>
+      <c r="F2" s="332"/>
+      <c r="G2" s="332"/>
+      <c r="H2" s="332"/>
+      <c r="I2" s="332"/>
+      <c r="J2" s="332"/>
+      <c r="K2" s="332"/>
+      <c r="L2" s="332"/>
+      <c r="M2" s="332"/>
+      <c r="N2" s="332"/>
     </row>
     <row r="3" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="272" t="s">
@@ -7114,19 +7114,19 @@
       <c r="A4" s="393" t="s">
         <v>535</v>
       </c>
-      <c r="B4" s="336"/>
-      <c r="C4" s="336"/>
-      <c r="D4" s="336"/>
-      <c r="E4" s="336"/>
-      <c r="F4" s="336"/>
-      <c r="G4" s="336"/>
-      <c r="H4" s="336"/>
-      <c r="I4" s="336"/>
-      <c r="J4" s="336"/>
-      <c r="K4" s="336"/>
-      <c r="L4" s="336"/>
-      <c r="M4" s="336"/>
-      <c r="N4" s="336"/>
+      <c r="B4" s="332"/>
+      <c r="C4" s="332"/>
+      <c r="D4" s="332"/>
+      <c r="E4" s="332"/>
+      <c r="F4" s="332"/>
+      <c r="G4" s="332"/>
+      <c r="H4" s="332"/>
+      <c r="I4" s="332"/>
+      <c r="J4" s="332"/>
+      <c r="K4" s="332"/>
+      <c r="L4" s="332"/>
+      <c r="M4" s="332"/>
+      <c r="N4" s="332"/>
     </row>
     <row r="5" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="273" t="s">
@@ -9944,19 +9944,19 @@
       <c r="A81" s="395" t="s">
         <v>557</v>
       </c>
-      <c r="B81" s="336"/>
-      <c r="C81" s="336"/>
-      <c r="D81" s="336"/>
-      <c r="E81" s="336"/>
-      <c r="F81" s="336"/>
-      <c r="G81" s="336"/>
-      <c r="H81" s="336"/>
-      <c r="I81" s="336"/>
-      <c r="J81" s="336"/>
-      <c r="K81" s="336"/>
-      <c r="L81" s="336"/>
-      <c r="M81" s="336"/>
-      <c r="N81" s="336"/>
+      <c r="B81" s="332"/>
+      <c r="C81" s="332"/>
+      <c r="D81" s="332"/>
+      <c r="E81" s="332"/>
+      <c r="F81" s="332"/>
+      <c r="G81" s="332"/>
+      <c r="H81" s="332"/>
+      <c r="I81" s="332"/>
+      <c r="J81" s="332"/>
+      <c r="K81" s="332"/>
+      <c r="L81" s="332"/>
+      <c r="M81" s="332"/>
+      <c r="N81" s="332"/>
     </row>
     <row r="82" spans="1:14" ht="5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="273" t="s">
@@ -12782,7 +12782,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="38" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="326" t="s">
+      <c r="A1" s="338" t="s">
         <v>335</v>
       </c>
       <c r="B1" s="323"/>
@@ -12810,7 +12810,7 @@
       <c r="X1" s="323"/>
     </row>
     <row r="2" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="329" t="s">
+      <c r="A2" s="341" t="s">
         <v>336</v>
       </c>
       <c r="B2" s="323"/>
@@ -12940,7 +12940,7 @@
       <c r="X4" s="323"/>
     </row>
     <row r="5" spans="1:24" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="327" t="s">
+      <c r="A5" s="339" t="s">
         <v>362</v>
       </c>
       <c r="B5" s="323"/>
@@ -13252,10 +13252,10 @@
         <v>5231</v>
       </c>
       <c r="U9" s="12">
-        <v>5518</v>
+        <v>5789</v>
       </c>
       <c r="V9" s="12">
-        <v>1309</v>
+        <v>969</v>
       </c>
       <c r="W9" s="12"/>
       <c r="X9" s="12"/>
@@ -13366,11 +13366,11 @@
       </c>
       <c r="U11" s="288">
         <f t="shared" si="0"/>
-        <v>0.44780717651322943</v>
+        <v>0.42684401451027809</v>
       </c>
       <c r="V11" s="288">
         <f t="shared" si="0"/>
-        <v>0.35523300229182581</v>
+        <v>0.47987616099071206</v>
       </c>
       <c r="W11" s="13"/>
       <c r="X11" s="13"/>
@@ -13404,7 +13404,7 @@
       <c r="X12" s="14"/>
     </row>
     <row r="13" spans="1:24" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="327" t="s">
+      <c r="A13" s="339" t="s">
         <v>370</v>
       </c>
       <c r="B13" s="323"/>
@@ -13432,7 +13432,7 @@
       <c r="X13" s="323"/>
     </row>
     <row r="14" spans="1:24" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="325" t="s">
+      <c r="A14" s="337" t="s">
         <v>371</v>
       </c>
       <c r="B14" s="323"/>
@@ -13732,7 +13732,7 @@
       <c r="X18" s="13"/>
     </row>
     <row r="19" spans="1:24" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="325" t="s">
+      <c r="A19" s="337" t="s">
         <v>376</v>
       </c>
       <c r="B19" s="323"/>
@@ -14372,7 +14372,7 @@
       <c r="X28" s="12"/>
     </row>
     <row r="29" spans="1:24" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="325" t="s">
+      <c r="A29" s="337" t="s">
         <v>383</v>
       </c>
       <c r="B29" s="323"/>
@@ -14604,7 +14604,7 @@
       <c r="X32" s="12"/>
     </row>
     <row r="33" spans="1:24" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="331" t="s">
+      <c r="A33" s="343" t="s">
         <v>387</v>
       </c>
       <c r="B33" s="323"/>
@@ -14632,7 +14632,7 @@
       <c r="X33" s="323"/>
     </row>
     <row r="34" spans="1:24" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="333" t="s">
+      <c r="A34" s="345" t="s">
         <v>388</v>
       </c>
       <c r="B34" s="323"/>
@@ -15110,7 +15110,7 @@
       </c>
     </row>
     <row r="41" spans="1:24" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="330"/>
+      <c r="A41" s="342"/>
       <c r="B41" s="323"/>
       <c r="C41" s="323"/>
       <c r="D41" s="323"/>
@@ -15133,10 +15133,10 @@
       <c r="U41" s="323"/>
       <c r="V41" s="323"/>
       <c r="W41" s="323"/>
-      <c r="X41" s="324"/>
+      <c r="X41" s="336"/>
     </row>
     <row r="42" spans="1:24" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="330"/>
+      <c r="A42" s="342"/>
       <c r="B42" s="323"/>
       <c r="C42" s="323"/>
       <c r="D42" s="323"/>
@@ -15159,7 +15159,7 @@
       <c r="U42" s="323"/>
       <c r="V42" s="323"/>
       <c r="W42" s="323"/>
-      <c r="X42" s="324"/>
+      <c r="X42" s="336"/>
     </row>
     <row r="43" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="20"/>
@@ -15434,7 +15434,7 @@
       <c r="X46" s="13"/>
     </row>
     <row r="47" spans="1:24" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="325" t="s">
+      <c r="A47" s="337" t="s">
         <v>376</v>
       </c>
       <c r="B47" s="323"/>
@@ -16074,7 +16074,7 @@
       <c r="X56" s="12"/>
     </row>
     <row r="57" spans="1:24" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="325" t="s">
+      <c r="A57" s="337" t="s">
         <v>383</v>
       </c>
       <c r="B57" s="323"/>
@@ -16584,7 +16584,7 @@
       </c>
     </row>
     <row r="69" spans="1:24" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="332"/>
+      <c r="A69" s="344"/>
       <c r="B69" s="323"/>
       <c r="C69" s="323"/>
       <c r="D69" s="323"/>
@@ -16607,7 +16607,7 @@
       <c r="U69" s="323"/>
       <c r="V69" s="323"/>
       <c r="W69" s="323"/>
-      <c r="X69" s="324"/>
+      <c r="X69" s="336"/>
     </row>
     <row r="70" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="24"/>
@@ -16882,7 +16882,7 @@
       <c r="X73" s="27"/>
     </row>
     <row r="74" spans="1:24" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="328" t="s">
+      <c r="A74" s="340" t="s">
         <v>406</v>
       </c>
       <c r="B74" s="323"/>
@@ -17236,7 +17236,7 @@
       <c r="X80" s="12"/>
     </row>
     <row r="81" spans="1:24" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="322"/>
+      <c r="A81" s="335"/>
       <c r="B81" s="323"/>
       <c r="C81" s="323"/>
       <c r="D81" s="323"/>
@@ -17259,7 +17259,7 @@
       <c r="U81" s="323"/>
       <c r="V81" s="323"/>
       <c r="W81" s="323"/>
-      <c r="X81" s="324"/>
+      <c r="X81" s="336"/>
     </row>
     <row r="82" spans="1:24" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="29"/>
@@ -17509,6 +17509,7 @@
     <row r="200" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A29:X29"/>
     <mergeCell ref="A4:X4"/>
     <mergeCell ref="A81:X81"/>
     <mergeCell ref="A57:X57"/>
@@ -17525,7 +17526,6 @@
     <mergeCell ref="A33:X33"/>
     <mergeCell ref="A69:X69"/>
     <mergeCell ref="A34:X34"/>
-    <mergeCell ref="A29:X29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -17556,7 +17556,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="338" t="s">
+      <c r="A1" s="346" t="s">
         <v>413</v>
       </c>
       <c r="B1" s="323"/>
@@ -17577,7 +17577,7 @@
       <c r="Q1" s="323"/>
     </row>
     <row r="2" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="343" t="s">
+      <c r="A2" s="351" t="s">
         <v>414</v>
       </c>
       <c r="B2" s="323"/>
@@ -17598,19 +17598,19 @@
       <c r="Q2" s="323"/>
     </row>
     <row r="3" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="345" t="s">
+      <c r="A3" s="353" t="s">
         <v>415</v>
       </c>
       <c r="B3" s="323"/>
-      <c r="C3" s="344" t="s">
+      <c r="C3" s="352" t="s">
         <v>416</v>
       </c>
       <c r="D3" s="323"/>
-      <c r="E3" s="339" t="s">
+      <c r="E3" s="347" t="s">
         <v>417</v>
       </c>
       <c r="F3" s="323"/>
-      <c r="G3" s="341" t="s">
+      <c r="G3" s="349" t="s">
         <v>418</v>
       </c>
       <c r="H3" s="323"/>
@@ -17622,11 +17622,11 @@
       <c r="L3" s="32" t="s">
         <v>420</v>
       </c>
-      <c r="M3" s="340" t="s">
+      <c r="M3" s="348" t="s">
         <v>421</v>
       </c>
       <c r="N3" s="323"/>
-      <c r="O3" s="340" t="s">
+      <c r="O3" s="348" t="s">
         <v>421</v>
       </c>
       <c r="P3" s="323"/>
@@ -17688,7 +17688,7 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="342" t="s">
+      <c r="A5" s="350" t="s">
         <v>435</v>
       </c>
       <c r="B5" s="323"/>
@@ -17734,12 +17734,8 @@
       <c r="C6" s="49">
         <v>44886805</v>
       </c>
-      <c r="D6" s="49">
-        <v>97</v>
-      </c>
-      <c r="E6" s="49">
-        <v>274</v>
-      </c>
+      <c r="D6" s="49"/>
+      <c r="E6" s="49"/>
       <c r="F6" s="49"/>
       <c r="G6" s="49">
         <v>6767007</v>
@@ -17765,17 +17761,17 @@
         <f t="shared" ref="N6:N35" si="1">IF(N(C6)+N(M6)&gt;0,N(C6)+N(M6),"")</f>
         <v>58137519</v>
       </c>
-      <c r="O6" s="51">
+      <c r="O6" s="51" t="str">
         <f t="shared" ref="O6:O35" si="2">IFERROR(IF(D6&gt;0,C6/D6,""),"")</f>
-        <v>462750.56701030926</v>
+        <v/>
       </c>
       <c r="P6" s="51">
         <f t="shared" ref="P6:P35" si="3">IFERROR(IF(J6&gt;0,M6/J6,""),"")</f>
         <v>301152.59090909088</v>
       </c>
-      <c r="Q6" s="52">
+      <c r="Q6" s="52" t="str">
         <f t="shared" ref="Q6:Q35" si="4">IFERROR(IF(E6&gt;0,D6/E6,""),"")</f>
-        <v>0.354014598540146</v>
+        <v/>
       </c>
     </row>
     <row r="7" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -17788,12 +17784,8 @@
       <c r="C7" s="49">
         <v>32214802</v>
       </c>
-      <c r="D7" s="49">
-        <v>65</v>
-      </c>
-      <c r="E7" s="49">
-        <v>231</v>
-      </c>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
       <c r="F7" s="49"/>
       <c r="G7" s="49">
         <v>4259006</v>
@@ -17819,17 +17811,17 @@
         <f t="shared" si="1"/>
         <v>45696314</v>
       </c>
-      <c r="O7" s="51">
+      <c r="O7" s="51" t="str">
         <f t="shared" si="2"/>
-        <v>495612.33846153849</v>
+        <v/>
       </c>
       <c r="P7" s="51">
         <f t="shared" si="3"/>
         <v>313523.53488372092</v>
       </c>
-      <c r="Q7" s="52">
+      <c r="Q7" s="52" t="str">
         <f t="shared" si="4"/>
-        <v>0.2813852813852814</v>
+        <v/>
       </c>
     </row>
     <row r="8" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -17842,12 +17834,8 @@
       <c r="C8" s="49">
         <v>36473477</v>
       </c>
-      <c r="D8" s="49">
-        <v>87</v>
-      </c>
-      <c r="E8" s="49">
-        <v>230</v>
-      </c>
+      <c r="D8" s="49"/>
+      <c r="E8" s="49"/>
       <c r="F8" s="49"/>
       <c r="G8" s="49">
         <v>8799511</v>
@@ -17873,17 +17861,17 @@
         <f t="shared" si="1"/>
         <v>50873492</v>
       </c>
-      <c r="O8" s="51">
+      <c r="O8" s="51" t="str">
         <f t="shared" si="2"/>
-        <v>419235.36781609198</v>
+        <v/>
       </c>
       <c r="P8" s="51">
         <f t="shared" si="3"/>
         <v>300000.3125</v>
       </c>
-      <c r="Q8" s="52">
+      <c r="Q8" s="52" t="str">
         <f t="shared" si="4"/>
-        <v>0.37826086956521737</v>
+        <v/>
       </c>
     </row>
     <row r="9" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -17896,12 +17884,8 @@
       <c r="C9" s="49">
         <v>35472516</v>
       </c>
-      <c r="D9" s="49">
-        <v>81</v>
-      </c>
-      <c r="E9" s="49">
-        <v>304</v>
-      </c>
+      <c r="D9" s="49"/>
+      <c r="E9" s="49"/>
       <c r="F9" s="49"/>
       <c r="G9" s="49">
         <v>9745005</v>
@@ -17925,17 +17909,17 @@
         <f t="shared" si="1"/>
         <v>55334029</v>
       </c>
-      <c r="O9" s="51">
+      <c r="O9" s="51" t="str">
         <f t="shared" si="2"/>
-        <v>437932.29629629629</v>
+        <v/>
       </c>
       <c r="P9" s="51">
         <f t="shared" si="3"/>
         <v>331025.21666666667</v>
       </c>
-      <c r="Q9" s="52">
+      <c r="Q9" s="52" t="str">
         <f t="shared" si="4"/>
-        <v>0.26644736842105265</v>
+        <v/>
       </c>
     </row>
     <row r="10" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -17948,12 +17932,8 @@
       <c r="C10" s="49">
         <v>31950186</v>
       </c>
-      <c r="D10" s="49">
-        <v>76</v>
-      </c>
-      <c r="E10" s="49">
-        <v>467</v>
-      </c>
+      <c r="D10" s="49"/>
+      <c r="E10" s="49"/>
       <c r="F10" s="49"/>
       <c r="G10" s="49">
         <v>12953499</v>
@@ -17979,17 +17959,17 @@
         <f t="shared" si="1"/>
         <v>53384436</v>
       </c>
-      <c r="O10" s="51">
+      <c r="O10" s="51" t="str">
         <f t="shared" si="2"/>
-        <v>420397.18421052629</v>
+        <v/>
       </c>
       <c r="P10" s="51">
         <f t="shared" si="3"/>
         <v>310641.30434782611</v>
       </c>
-      <c r="Q10" s="52">
+      <c r="Q10" s="52" t="str">
         <f t="shared" si="4"/>
-        <v>0.16274089935760172</v>
+        <v/>
       </c>
     </row>
     <row r="11" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -18002,12 +17982,8 @@
       <c r="C11" s="49">
         <v>35754690</v>
       </c>
-      <c r="D11" s="49">
-        <v>81</v>
-      </c>
-      <c r="E11" s="49">
-        <v>456</v>
-      </c>
+      <c r="D11" s="49"/>
+      <c r="E11" s="49"/>
       <c r="F11" s="49"/>
       <c r="G11" s="49">
         <v>9757501</v>
@@ -18033,17 +18009,17 @@
         <f t="shared" si="1"/>
         <v>56130440</v>
       </c>
-      <c r="O11" s="51">
+      <c r="O11" s="51" t="str">
         <f t="shared" si="2"/>
-        <v>441415.9259259259</v>
+        <v/>
       </c>
       <c r="P11" s="51">
         <f t="shared" si="3"/>
         <v>275347.97297297296</v>
       </c>
-      <c r="Q11" s="52">
+      <c r="Q11" s="52" t="str">
         <f t="shared" si="4"/>
-        <v>0.17763157894736842</v>
+        <v/>
       </c>
     </row>
     <row r="12" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -18056,12 +18032,8 @@
       <c r="C12" s="49">
         <v>26345035</v>
       </c>
-      <c r="D12" s="49">
-        <v>64</v>
-      </c>
-      <c r="E12" s="49">
-        <v>392</v>
-      </c>
+      <c r="D12" s="49"/>
+      <c r="E12" s="49"/>
       <c r="F12" s="49"/>
       <c r="G12" s="49">
         <v>10669504</v>
@@ -18087,17 +18059,17 @@
         <f t="shared" si="1"/>
         <v>48795252</v>
       </c>
-      <c r="O12" s="51">
+      <c r="O12" s="51" t="str">
         <f t="shared" si="2"/>
-        <v>411641.171875</v>
+        <v/>
       </c>
       <c r="P12" s="51">
         <f t="shared" si="3"/>
         <v>325365.46376811597</v>
       </c>
-      <c r="Q12" s="52">
+      <c r="Q12" s="52" t="str">
         <f t="shared" si="4"/>
-        <v>0.16326530612244897</v>
+        <v/>
       </c>
     </row>
     <row r="13" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -18110,12 +18082,8 @@
       <c r="C13" s="49">
         <v>36505043</v>
       </c>
-      <c r="D13" s="49">
-        <v>74</v>
-      </c>
-      <c r="E13" s="49">
-        <v>284</v>
-      </c>
+      <c r="D13" s="49"/>
+      <c r="E13" s="49"/>
       <c r="F13" s="49"/>
       <c r="G13" s="49">
         <v>6963251</v>
@@ -18141,17 +18109,17 @@
         <f t="shared" si="1"/>
         <v>52808793</v>
       </c>
-      <c r="O13" s="51">
+      <c r="O13" s="51" t="str">
         <f t="shared" si="2"/>
-        <v>493311.39189189189</v>
+        <v/>
       </c>
       <c r="P13" s="51">
         <f t="shared" si="3"/>
         <v>407593.75</v>
       </c>
-      <c r="Q13" s="52">
+      <c r="Q13" s="52" t="str">
         <f t="shared" si="4"/>
-        <v>0.26056338028169013</v>
+        <v/>
       </c>
     </row>
     <row r="14" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -18164,12 +18132,8 @@
       <c r="C14" s="49">
         <v>31831101</v>
       </c>
-      <c r="D14" s="49">
-        <v>76</v>
-      </c>
-      <c r="E14" s="49">
-        <v>186</v>
-      </c>
+      <c r="D14" s="49"/>
+      <c r="E14" s="49"/>
       <c r="F14" s="49"/>
       <c r="G14" s="49">
         <v>5794398</v>
@@ -18195,17 +18159,17 @@
         <f t="shared" si="1"/>
         <v>43405505</v>
       </c>
-      <c r="O14" s="51">
+      <c r="O14" s="51" t="str">
         <f t="shared" si="2"/>
-        <v>418830.2763157895</v>
+        <v/>
       </c>
       <c r="P14" s="51">
         <f t="shared" si="3"/>
         <v>282302.53658536583</v>
       </c>
-      <c r="Q14" s="52">
+      <c r="Q14" s="52" t="str">
         <f t="shared" si="4"/>
-        <v>0.40860215053763443</v>
+        <v/>
       </c>
     </row>
     <row r="15" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -18218,12 +18182,8 @@
       <c r="C15" s="49">
         <v>32966537</v>
       </c>
-      <c r="D15" s="49">
-        <v>76</v>
-      </c>
-      <c r="E15" s="49">
-        <v>240</v>
-      </c>
+      <c r="D15" s="49"/>
+      <c r="E15" s="49"/>
       <c r="F15" s="49"/>
       <c r="G15" s="49">
         <v>5953000</v>
@@ -18247,17 +18207,17 @@
         <f t="shared" si="1"/>
         <v>48961038</v>
       </c>
-      <c r="O15" s="51">
+      <c r="O15" s="51" t="str">
         <f t="shared" si="2"/>
-        <v>433770.2236842105</v>
+        <v/>
       </c>
       <c r="P15" s="51">
         <f t="shared" si="3"/>
         <v>296194.46296296298</v>
       </c>
-      <c r="Q15" s="52">
+      <c r="Q15" s="52" t="str">
         <f t="shared" si="4"/>
-        <v>0.31666666666666665</v>
+        <v/>
       </c>
     </row>
     <row r="16" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -18270,12 +18230,8 @@
       <c r="C16" s="49">
         <v>38207669</v>
       </c>
-      <c r="D16" s="49">
-        <v>90</v>
-      </c>
-      <c r="E16" s="49">
-        <v>261</v>
-      </c>
+      <c r="D16" s="49"/>
+      <c r="E16" s="49"/>
       <c r="F16" s="49"/>
       <c r="G16" s="49">
         <v>4152001</v>
@@ -18299,17 +18255,17 @@
         <f t="shared" si="1"/>
         <v>53400671</v>
       </c>
-      <c r="O16" s="51">
+      <c r="O16" s="51" t="str">
         <f t="shared" si="2"/>
-        <v>424529.65555555554</v>
+        <v/>
       </c>
       <c r="P16" s="51">
         <f t="shared" si="3"/>
         <v>370561.02439024393</v>
       </c>
-      <c r="Q16" s="52">
+      <c r="Q16" s="52" t="str">
         <f t="shared" si="4"/>
-        <v>0.34482758620689657</v>
+        <v/>
       </c>
     </row>
     <row r="17" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -18322,12 +18278,8 @@
       <c r="C17" s="49">
         <v>37803177</v>
       </c>
-      <c r="D17" s="49">
-        <v>88</v>
-      </c>
-      <c r="E17" s="49">
-        <v>285</v>
-      </c>
+      <c r="D17" s="49"/>
+      <c r="E17" s="49"/>
       <c r="F17" s="49"/>
       <c r="G17" s="49">
         <v>12255008</v>
@@ -18353,17 +18305,17 @@
         <f t="shared" si="1"/>
         <v>57006692</v>
       </c>
-      <c r="O17" s="51">
+      <c r="O17" s="51" t="str">
         <f t="shared" si="2"/>
-        <v>429581.55681818182</v>
+        <v/>
       </c>
       <c r="P17" s="51">
         <f t="shared" si="3"/>
         <v>286619.62686567166</v>
       </c>
-      <c r="Q17" s="52">
+      <c r="Q17" s="52" t="str">
         <f t="shared" si="4"/>
-        <v>0.30877192982456142</v>
+        <v/>
       </c>
     </row>
     <row r="18" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -18376,12 +18328,8 @@
       <c r="C18" s="49">
         <v>31450293</v>
       </c>
-      <c r="D18" s="49">
-        <v>82</v>
-      </c>
-      <c r="E18" s="49">
-        <v>262</v>
-      </c>
+      <c r="D18" s="49"/>
+      <c r="E18" s="49"/>
       <c r="F18" s="49"/>
       <c r="G18" s="49">
         <v>11464504</v>
@@ -18407,17 +18355,17 @@
         <f t="shared" si="1"/>
         <v>56148062</v>
       </c>
-      <c r="O18" s="51">
+      <c r="O18" s="51" t="str">
         <f t="shared" si="2"/>
-        <v>383540.15853658534</v>
+        <v/>
       </c>
       <c r="P18" s="51">
         <f t="shared" si="3"/>
         <v>268454.01086956525</v>
       </c>
-      <c r="Q18" s="52">
+      <c r="Q18" s="52" t="str">
         <f t="shared" si="4"/>
-        <v>0.31297709923664124</v>
+        <v/>
       </c>
     </row>
     <row r="19" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -18430,12 +18378,8 @@
       <c r="C19" s="49">
         <v>27933793</v>
       </c>
-      <c r="D19" s="49">
-        <v>63</v>
-      </c>
-      <c r="E19" s="49">
-        <v>275</v>
-      </c>
+      <c r="D19" s="49"/>
+      <c r="E19" s="49"/>
       <c r="F19" s="49"/>
       <c r="G19" s="49">
         <v>13214251</v>
@@ -18461,17 +18405,17 @@
         <f t="shared" si="1"/>
         <v>49884045</v>
       </c>
-      <c r="O19" s="51">
+      <c r="O19" s="51" t="str">
         <f t="shared" si="2"/>
-        <v>443393.5396825397</v>
+        <v/>
       </c>
       <c r="P19" s="51">
         <f t="shared" si="3"/>
         <v>354036.32258064515</v>
       </c>
-      <c r="Q19" s="52">
+      <c r="Q19" s="52" t="str">
         <f t="shared" si="4"/>
-        <v>0.2290909090909091</v>
+        <v/>
       </c>
     </row>
     <row r="20" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -18484,12 +18428,8 @@
       <c r="C20" s="49">
         <v>42226288</v>
       </c>
-      <c r="D20" s="49">
-        <v>104</v>
-      </c>
-      <c r="E20" s="49">
-        <v>358</v>
-      </c>
+      <c r="D20" s="49"/>
+      <c r="E20" s="49"/>
       <c r="F20" s="49"/>
       <c r="G20" s="49">
         <v>5703750</v>
@@ -18515,17 +18455,17 @@
         <f t="shared" si="1"/>
         <v>55454041</v>
       </c>
-      <c r="O20" s="51">
+      <c r="O20" s="51" t="str">
         <f t="shared" si="2"/>
-        <v>406022</v>
+        <v/>
       </c>
       <c r="P20" s="51">
         <f t="shared" si="3"/>
         <v>367437.58333333331</v>
       </c>
-      <c r="Q20" s="52">
+      <c r="Q20" s="52" t="str">
         <f t="shared" si="4"/>
-        <v>0.29050279329608941</v>
+        <v/>
       </c>
     </row>
     <row r="21" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -18538,12 +18478,8 @@
       <c r="C21" s="49">
         <v>44253287</v>
       </c>
-      <c r="D21" s="49">
-        <v>108</v>
-      </c>
-      <c r="E21" s="49">
-        <v>379</v>
-      </c>
+      <c r="D21" s="49"/>
+      <c r="E21" s="49"/>
       <c r="F21" s="49"/>
       <c r="G21" s="49">
         <v>8659502</v>
@@ -18569,17 +18505,17 @@
         <f t="shared" si="1"/>
         <v>61284790</v>
       </c>
-      <c r="O21" s="51">
+      <c r="O21" s="51" t="str">
         <f t="shared" si="2"/>
-        <v>409752.65740740742</v>
+        <v/>
       </c>
       <c r="P21" s="51">
         <f t="shared" si="3"/>
         <v>309663.69090909092</v>
       </c>
-      <c r="Q21" s="52">
+      <c r="Q21" s="52" t="str">
         <f t="shared" si="4"/>
-        <v>0.28496042216358841</v>
+        <v/>
       </c>
     </row>
     <row r="22" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -18592,12 +18528,8 @@
       <c r="C22" s="49">
         <v>43337858</v>
       </c>
-      <c r="D22" s="49">
-        <v>99</v>
-      </c>
-      <c r="E22" s="49">
-        <v>432</v>
-      </c>
+      <c r="D22" s="49"/>
+      <c r="E22" s="49"/>
       <c r="F22" s="49"/>
       <c r="G22" s="49">
         <v>7292002</v>
@@ -18623,17 +18555,17 @@
         <f t="shared" si="1"/>
         <v>57326560</v>
       </c>
-      <c r="O22" s="51">
+      <c r="O22" s="51" t="str">
         <f t="shared" si="2"/>
-        <v>437756.1414141414</v>
+        <v/>
       </c>
       <c r="P22" s="51">
         <f t="shared" si="3"/>
         <v>274288.27450980392</v>
       </c>
-      <c r="Q22" s="52">
+      <c r="Q22" s="52" t="str">
         <f t="shared" si="4"/>
-        <v>0.22916666666666666</v>
+        <v/>
       </c>
     </row>
     <row r="23" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -18646,12 +18578,8 @@
       <c r="C23" s="49">
         <v>49976088</v>
       </c>
-      <c r="D23" s="49">
-        <v>114</v>
-      </c>
-      <c r="E23" s="49">
-        <v>403</v>
-      </c>
+      <c r="D23" s="49"/>
+      <c r="E23" s="49"/>
       <c r="F23" s="49"/>
       <c r="G23" s="49">
         <v>6905755</v>
@@ -18675,17 +18603,17 @@
         <f t="shared" si="1"/>
         <v>68390846</v>
       </c>
-      <c r="O23" s="51">
+      <c r="O23" s="51" t="str">
         <f t="shared" si="2"/>
-        <v>438386.73684210528</v>
+        <v/>
       </c>
       <c r="P23" s="51">
         <f t="shared" si="3"/>
         <v>361073.68627450982</v>
       </c>
-      <c r="Q23" s="52">
+      <c r="Q23" s="52" t="str">
         <f t="shared" si="4"/>
-        <v>0.28287841191066998</v>
+        <v/>
       </c>
     </row>
     <row r="24" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -18698,12 +18626,8 @@
       <c r="C24" s="49">
         <v>45923314</v>
       </c>
-      <c r="D24" s="49">
-        <v>102</v>
-      </c>
-      <c r="E24" s="49">
-        <v>303</v>
-      </c>
+      <c r="D24" s="49"/>
+      <c r="E24" s="49"/>
       <c r="F24" s="49"/>
       <c r="G24" s="49">
         <v>10739751</v>
@@ -18729,17 +18653,17 @@
         <f t="shared" si="1"/>
         <v>66853563</v>
       </c>
-      <c r="O24" s="51">
+      <c r="O24" s="51" t="str">
         <f t="shared" si="2"/>
-        <v>450228.56862745096</v>
+        <v/>
       </c>
       <c r="P24" s="51">
         <f t="shared" si="3"/>
         <v>317124.98484848486</v>
       </c>
-      <c r="Q24" s="52">
+      <c r="Q24" s="52" t="str">
         <f t="shared" si="4"/>
-        <v>0.33663366336633666</v>
+        <v/>
       </c>
     </row>
     <row r="25" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -18752,12 +18676,8 @@
       <c r="C25" s="49">
         <v>34642065</v>
       </c>
-      <c r="D25" s="49">
-        <v>78</v>
-      </c>
-      <c r="E25" s="49">
-        <v>230</v>
-      </c>
+      <c r="D25" s="49"/>
+      <c r="E25" s="49"/>
       <c r="F25" s="49"/>
       <c r="G25" s="49">
         <v>9487759</v>
@@ -18783,17 +18703,17 @@
         <f t="shared" si="1"/>
         <v>50728323</v>
       </c>
-      <c r="O25" s="51">
+      <c r="O25" s="51" t="str">
         <f t="shared" si="2"/>
-        <v>444129.03846153844</v>
+        <v/>
       </c>
       <c r="P25" s="51">
         <f t="shared" si="3"/>
         <v>268104.3</v>
       </c>
-      <c r="Q25" s="52">
+      <c r="Q25" s="52" t="str">
         <f t="shared" si="4"/>
-        <v>0.33913043478260868</v>
+        <v/>
       </c>
     </row>
     <row r="26" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -18806,12 +18726,8 @@
       <c r="C26" s="49">
         <v>34371552</v>
       </c>
-      <c r="D26" s="49">
-        <v>63</v>
-      </c>
-      <c r="E26" s="49">
-        <v>197</v>
-      </c>
+      <c r="D26" s="49"/>
+      <c r="E26" s="49"/>
       <c r="F26" s="49"/>
       <c r="G26" s="49">
         <v>7185011</v>
@@ -18837,17 +18753,17 @@
         <f t="shared" si="1"/>
         <v>49880083</v>
       </c>
-      <c r="O26" s="51">
+      <c r="O26" s="51" t="str">
         <f t="shared" si="2"/>
-        <v>545580.19047619053</v>
+        <v/>
       </c>
       <c r="P26" s="51">
         <f t="shared" si="3"/>
         <v>262856.45762711862</v>
       </c>
-      <c r="Q26" s="52">
+      <c r="Q26" s="52" t="str">
         <f t="shared" si="4"/>
-        <v>0.31979695431472083</v>
+        <v/>
       </c>
     </row>
     <row r="27" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -18860,12 +18776,8 @@
       <c r="C27" s="49">
         <v>45116287</v>
       </c>
-      <c r="D27" s="49">
-        <v>82</v>
-      </c>
-      <c r="E27" s="49">
-        <v>210</v>
-      </c>
+      <c r="D27" s="49"/>
+      <c r="E27" s="49"/>
       <c r="F27" s="49"/>
       <c r="G27" s="49">
         <v>5823399</v>
@@ -18891,17 +18803,17 @@
         <f t="shared" si="1"/>
         <v>58151191</v>
       </c>
-      <c r="O27" s="51">
+      <c r="O27" s="51" t="str">
         <f t="shared" si="2"/>
-        <v>550198.62195121951</v>
+        <v/>
       </c>
       <c r="P27" s="51">
         <f t="shared" si="3"/>
         <v>303137.30232558138</v>
       </c>
-      <c r="Q27" s="52">
+      <c r="Q27" s="52" t="str">
         <f t="shared" si="4"/>
-        <v>0.39047619047619048</v>
+        <v/>
       </c>
     </row>
     <row r="28" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -18914,12 +18826,8 @@
       <c r="C28" s="49">
         <v>32312408</v>
       </c>
-      <c r="D28" s="49">
-        <v>69</v>
-      </c>
-      <c r="E28" s="49">
-        <v>337</v>
-      </c>
+      <c r="D28" s="49"/>
+      <c r="E28" s="49"/>
       <c r="F28" s="49"/>
       <c r="G28" s="49">
         <v>6753005</v>
@@ -18943,17 +18851,17 @@
         <f t="shared" si="1"/>
         <v>44083922</v>
       </c>
-      <c r="O28" s="51">
+      <c r="O28" s="51" t="str">
         <f t="shared" si="2"/>
-        <v>468295.76811594202</v>
+        <v/>
       </c>
       <c r="P28" s="51">
         <f t="shared" si="3"/>
         <v>356712.54545454547</v>
       </c>
-      <c r="Q28" s="52">
+      <c r="Q28" s="52" t="str">
         <f t="shared" si="4"/>
-        <v>0.20474777448071216</v>
+        <v/>
       </c>
     </row>
     <row r="29" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -18966,12 +18874,8 @@
       <c r="C29" s="49">
         <v>32701796</v>
       </c>
-      <c r="D29" s="49">
-        <v>82</v>
-      </c>
-      <c r="E29" s="49">
-        <v>278</v>
-      </c>
+      <c r="D29" s="49"/>
+      <c r="E29" s="49"/>
       <c r="F29" s="49"/>
       <c r="G29" s="49">
         <v>8755015</v>
@@ -18995,17 +18899,17 @@
         <f t="shared" si="1"/>
         <v>47932814</v>
       </c>
-      <c r="O29" s="51">
+      <c r="O29" s="51" t="str">
         <f t="shared" si="2"/>
-        <v>398802.39024390245</v>
+        <v/>
       </c>
       <c r="P29" s="51">
         <f t="shared" si="3"/>
         <v>362643.28571428574</v>
       </c>
-      <c r="Q29" s="52">
+      <c r="Q29" s="52" t="str">
         <f t="shared" si="4"/>
-        <v>0.29496402877697842</v>
+        <v/>
       </c>
     </row>
     <row r="30" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -19018,12 +18922,8 @@
       <c r="C30" s="49">
         <v>39556390</v>
       </c>
-      <c r="D30" s="49">
-        <v>99</v>
-      </c>
-      <c r="E30" s="49">
-        <v>404</v>
-      </c>
+      <c r="D30" s="49"/>
+      <c r="E30" s="49"/>
       <c r="F30" s="49"/>
       <c r="G30" s="49">
         <v>7045999</v>
@@ -19047,17 +18947,17 @@
         <f t="shared" si="1"/>
         <v>53246388</v>
       </c>
-      <c r="O30" s="51">
+      <c r="O30" s="51" t="str">
         <f t="shared" si="2"/>
-        <v>399559.49494949495</v>
+        <v/>
       </c>
       <c r="P30" s="51">
         <f t="shared" si="3"/>
         <v>263269.19230769231</v>
       </c>
-      <c r="Q30" s="52">
+      <c r="Q30" s="52" t="str">
         <f t="shared" si="4"/>
-        <v>0.24504950495049505</v>
+        <v/>
       </c>
     </row>
     <row r="31" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -19070,12 +18970,8 @@
       <c r="C31" s="49">
         <v>34245263</v>
       </c>
-      <c r="D31" s="49">
-        <v>80</v>
-      </c>
-      <c r="E31" s="49">
-        <v>283</v>
-      </c>
+      <c r="D31" s="49"/>
+      <c r="E31" s="49"/>
       <c r="F31" s="49"/>
       <c r="G31" s="49">
         <v>10419503</v>
@@ -19101,17 +18997,17 @@
         <f t="shared" si="1"/>
         <v>54796266</v>
       </c>
-      <c r="O31" s="51">
+      <c r="O31" s="51" t="str">
         <f t="shared" si="2"/>
-        <v>428065.78749999998</v>
+        <v/>
       </c>
       <c r="P31" s="51">
         <f t="shared" si="3"/>
         <v>285430.59722222225</v>
       </c>
-      <c r="Q31" s="52">
+      <c r="Q31" s="52" t="str">
         <f t="shared" si="4"/>
-        <v>0.28268551236749118</v>
+        <v/>
       </c>
     </row>
     <row r="32" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -19124,12 +19020,8 @@
       <c r="C32" s="49">
         <v>31660032</v>
       </c>
-      <c r="D32" s="49">
-        <v>75</v>
-      </c>
-      <c r="E32" s="49">
-        <v>226</v>
-      </c>
+      <c r="D32" s="49"/>
+      <c r="E32" s="49"/>
       <c r="F32" s="49"/>
       <c r="G32" s="49">
         <v>10394010</v>
@@ -19155,17 +19047,17 @@
         <f t="shared" si="1"/>
         <v>51762542</v>
       </c>
-      <c r="O32" s="51">
+      <c r="O32" s="51" t="str">
         <f t="shared" si="2"/>
-        <v>422133.76000000001</v>
+        <v/>
       </c>
       <c r="P32" s="51">
         <f t="shared" si="3"/>
         <v>291340.72463768115</v>
       </c>
-      <c r="Q32" s="52">
+      <c r="Q32" s="52" t="str">
         <f t="shared" si="4"/>
-        <v>0.33185840707964603</v>
+        <v/>
       </c>
     </row>
     <row r="33" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -19178,12 +19070,8 @@
       <c r="C33" s="49">
         <v>28009525</v>
       </c>
-      <c r="D33" s="49">
-        <v>60</v>
-      </c>
-      <c r="E33" s="49">
-        <v>236</v>
-      </c>
+      <c r="D33" s="49"/>
+      <c r="E33" s="49"/>
       <c r="F33" s="49"/>
       <c r="G33" s="49">
         <v>9633250</v>
@@ -19209,17 +19097,17 @@
         <f t="shared" si="1"/>
         <v>44687781</v>
       </c>
-      <c r="O33" s="51">
+      <c r="O33" s="51" t="str">
         <f t="shared" si="2"/>
-        <v>466825.41666666669</v>
+        <v/>
       </c>
       <c r="P33" s="51">
         <f t="shared" si="3"/>
         <v>277970.93333333335</v>
       </c>
-      <c r="Q33" s="52">
+      <c r="Q33" s="52" t="str">
         <f t="shared" si="4"/>
-        <v>0.25423728813559321</v>
+        <v/>
       </c>
     </row>
     <row r="34" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -19232,12 +19120,8 @@
       <c r="C34" s="49">
         <v>35600022</v>
       </c>
-      <c r="D34" s="49">
-        <v>73</v>
-      </c>
-      <c r="E34" s="49">
-        <v>282</v>
-      </c>
+      <c r="D34" s="49"/>
+      <c r="E34" s="49"/>
       <c r="F34" s="49"/>
       <c r="G34" s="49">
         <v>7841005</v>
@@ -19261,17 +19145,17 @@
         <f t="shared" si="1"/>
         <v>47592780</v>
       </c>
-      <c r="O34" s="51">
+      <c r="O34" s="51" t="str">
         <f t="shared" si="2"/>
-        <v>487671.53424657532</v>
+        <v/>
       </c>
       <c r="P34" s="51">
         <f t="shared" si="3"/>
         <v>342650.22857142857</v>
       </c>
-      <c r="Q34" s="52">
+      <c r="Q34" s="52" t="str">
         <f t="shared" si="4"/>
-        <v>0.25886524822695034</v>
+        <v/>
       </c>
     </row>
     <row r="35" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -19284,12 +19168,8 @@
       <c r="C35" s="49">
         <v>35013903</v>
       </c>
-      <c r="D35" s="49">
-        <v>83</v>
-      </c>
-      <c r="E35" s="49">
-        <v>261</v>
-      </c>
+      <c r="D35" s="49"/>
+      <c r="E35" s="49"/>
       <c r="F35" s="49"/>
       <c r="G35" s="49">
         <v>9861013</v>
@@ -19313,17 +19193,17 @@
         <f t="shared" si="1"/>
         <v>51381416</v>
       </c>
-      <c r="O35" s="51">
+      <c r="O35" s="51" t="str">
         <f t="shared" si="2"/>
-        <v>421854.2530120482</v>
+        <v/>
       </c>
       <c r="P35" s="51">
         <f t="shared" si="3"/>
         <v>303102.09259259258</v>
       </c>
-      <c r="Q35" s="52">
+      <c r="Q35" s="52" t="str">
         <f t="shared" si="4"/>
-        <v>0.31800766283524906</v>
+        <v/>
       </c>
     </row>
     <row r="36" spans="1:17" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -19528,7 +19408,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="350" t="s">
+      <c r="A1" s="358" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="323"/>
@@ -19544,7 +19424,7 @@
       <c r="L1" s="323"/>
     </row>
     <row r="2" spans="1:12" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="348" t="s">
+      <c r="A2" s="356" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="323"/>
@@ -19827,7 +19707,7 @@
     </row>
     <row r="22" spans="1:20" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="23" spans="1:20" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="351" t="s">
+      <c r="A23" s="359" t="s">
         <v>26</v>
       </c>
       <c r="B23" s="323"/>
@@ -19850,7 +19730,7 @@
     </row>
     <row r="24" spans="1:20" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="25" spans="1:20" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="349" t="s">
+      <c r="A25" s="357" t="s">
         <v>27</v>
       </c>
       <c r="B25" s="323"/>
@@ -19867,7 +19747,7 @@
     </row>
     <row r="26" spans="1:20" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="27" spans="1:20" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="346" t="s">
+      <c r="A27" s="354" t="s">
         <v>28</v>
       </c>
       <c r="B27" s="323"/>
@@ -19880,7 +19760,7 @@
       <c r="I27" s="323"/>
       <c r="J27" s="323"/>
       <c r="K27" s="323"/>
-      <c r="L27" s="347"/>
+      <c r="L27" s="355"/>
       <c r="M27" s="281"/>
       <c r="N27" s="281"/>
       <c r="O27" s="281"/>
@@ -20113,7 +19993,7 @@
       <c r="T34" s="285"/>
     </row>
     <row r="35" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="346" t="s">
+      <c r="A35" s="354" t="s">
         <v>52</v>
       </c>
       <c r="B35" s="323"/>
@@ -20126,7 +20006,7 @@
       <c r="I35" s="323"/>
       <c r="J35" s="323"/>
       <c r="K35" s="323"/>
-      <c r="L35" s="347"/>
+      <c r="L35" s="355"/>
       <c r="M35" s="285"/>
       <c r="N35" s="285"/>
       <c r="O35" s="285"/>
@@ -20436,7 +20316,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="352" t="s">
+      <c r="A1" s="322" t="s">
         <v>443</v>
       </c>
       <c r="B1" s="323"/>
@@ -20457,7 +20337,7 @@
       <c r="Q1" s="323"/>
     </row>
     <row r="2" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="357" t="s">
+      <c r="A2" s="328" t="s">
         <v>414</v>
       </c>
       <c r="B2" s="323"/>
@@ -20478,19 +20358,19 @@
       <c r="Q2" s="323"/>
     </row>
     <row r="3" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="359" t="s">
+      <c r="A3" s="330" t="s">
         <v>415</v>
       </c>
       <c r="B3" s="323"/>
-      <c r="C3" s="358" t="s">
+      <c r="C3" s="329" t="s">
         <v>416</v>
       </c>
       <c r="D3" s="323"/>
-      <c r="E3" s="353" t="s">
+      <c r="E3" s="324" t="s">
         <v>417</v>
       </c>
       <c r="F3" s="323"/>
-      <c r="G3" s="355" t="s">
+      <c r="G3" s="326" t="s">
         <v>418</v>
       </c>
       <c r="H3" s="323"/>
@@ -20502,11 +20382,11 @@
       <c r="L3" s="88" t="s">
         <v>420</v>
       </c>
-      <c r="M3" s="354" t="s">
+      <c r="M3" s="325" t="s">
         <v>421</v>
       </c>
       <c r="N3" s="323"/>
-      <c r="O3" s="354" t="s">
+      <c r="O3" s="325" t="s">
         <v>421</v>
       </c>
       <c r="P3" s="323"/>
@@ -20568,7 +20448,7 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="356" t="s">
+      <c r="A5" s="327" t="s">
         <v>435</v>
       </c>
       <c r="B5" s="323"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -7785,40 +7785,40 @@
         </is>
       </c>
       <c r="C77" s="128" t="n">
-        <v>337</v>
+        <v>440</v>
       </c>
       <c r="D77" s="129" t="n">
-        <v>133</v>
+        <v>170</v>
       </c>
       <c r="E77" s="129" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="F77" s="129" t="n">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="G77" s="129" t="n">
+        <v>10</v>
+      </c>
+      <c r="H77" s="129" t="n">
+        <v>47</v>
+      </c>
+      <c r="I77" s="129" t="n">
+        <v>35</v>
+      </c>
+      <c r="J77" s="129" t="n">
+        <v>17</v>
+      </c>
+      <c r="K77" s="131" t="n">
         <v>8</v>
       </c>
-      <c r="H77" s="129" t="n">
-        <v>39</v>
-      </c>
-      <c r="I77" s="129" t="n">
-        <v>26</v>
-      </c>
-      <c r="J77" s="129" t="n">
-        <v>13</v>
-      </c>
-      <c r="K77" s="131" t="n">
+      <c r="L77" s="131" t="n">
+        <v>130</v>
+      </c>
+      <c r="M77" s="131" t="n">
         <v>7</v>
       </c>
-      <c r="L77" s="131" t="n">
-        <v>101</v>
-      </c>
-      <c r="M77" s="131" t="n">
-        <v>5</v>
-      </c>
       <c r="N77" s="131" t="n">
-        <v>153</v>
+        <v>200</v>
       </c>
     </row>
     <row r="78" ht="19.5" customHeight="1" s="149">
@@ -7833,22 +7833,22 @@
         </is>
       </c>
       <c r="C78" s="128" t="n">
-        <v>572</v>
+        <v>710</v>
       </c>
       <c r="D78" s="129" t="n">
-        <v>442</v>
+        <v>546</v>
       </c>
       <c r="E78" s="129" t="n">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="F78" s="129" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="G78" s="129" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H78" s="129" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I78" s="129" t="n">
         <v>0</v>
@@ -7857,16 +7857,16 @@
         <v>0</v>
       </c>
       <c r="K78" s="131" t="n">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="L78" s="131" t="n">
+        <v>112</v>
+      </c>
+      <c r="M78" s="131" t="n">
+        <v>115</v>
+      </c>
+      <c r="N78" s="131" t="n">
         <v>83</v>
-      </c>
-      <c r="M78" s="131" t="n">
-        <v>93</v>
-      </c>
-      <c r="N78" s="131" t="n">
-        <v>68</v>
       </c>
     </row>
     <row r="79" ht="15.75" customHeight="1" s="149">
@@ -7881,19 +7881,19 @@
         </is>
       </c>
       <c r="C79" s="128" t="n">
-        <v>361</v>
+        <v>459</v>
       </c>
       <c r="D79" s="129" t="n">
-        <v>289</v>
+        <v>372</v>
       </c>
       <c r="E79" s="129" t="n">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="F79" s="129" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G79" s="129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H79" s="129" t="n">
         <v>1</v>
@@ -7905,16 +7905,16 @@
         <v>0</v>
       </c>
       <c r="K79" s="131" t="n">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="L79" s="131" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="M79" s="131" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="N79" s="131" t="n">
-        <v>60</v>
+        <v>73</v>
       </c>
     </row>
     <row r="80" ht="15.75" customHeight="1" s="149">
@@ -10832,40 +10832,40 @@
         </is>
       </c>
       <c r="C154" s="128" t="n">
-        <v>349</v>
+        <v>468</v>
       </c>
       <c r="D154" s="129" t="n">
-        <v>204</v>
+        <v>268</v>
       </c>
       <c r="E154" s="129" t="n">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="F154" s="129" t="n">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="G154" s="129" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H154" s="129" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="I154" s="129" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J154" s="129" t="n">
         <v>2</v>
       </c>
       <c r="K154" s="131" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L154" s="131" t="n">
-        <v>117</v>
+        <v>158</v>
       </c>
       <c r="M154" s="131" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N154" s="131" t="n">
-        <v>134</v>
+        <v>179</v>
       </c>
     </row>
     <row r="155" ht="13.5" customHeight="1" s="149">
@@ -10880,16 +10880,16 @@
         </is>
       </c>
       <c r="C155" s="128" t="n">
-        <v>297</v>
+        <v>378</v>
       </c>
       <c r="D155" s="129" t="n">
-        <v>258</v>
+        <v>332</v>
       </c>
       <c r="E155" s="129" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F155" s="129" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G155" s="129" t="n">
         <v>3</v>
@@ -10904,16 +10904,16 @@
         <v>0</v>
       </c>
       <c r="K155" s="131" t="n">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="L155" s="131" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="M155" s="131" t="n">
+        <v>87</v>
+      </c>
+      <c r="N155" s="131" t="n">
         <v>66</v>
-      </c>
-      <c r="N155" s="131" t="n">
-        <v>58</v>
       </c>
     </row>
     <row r="156" ht="13.5" customHeight="1" s="149">
@@ -10928,19 +10928,19 @@
         </is>
       </c>
       <c r="C156" s="128" t="n">
-        <v>156</v>
+        <v>198</v>
       </c>
       <c r="D156" s="129" t="n">
-        <v>141</v>
+        <v>178</v>
       </c>
       <c r="E156" s="129" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F156" s="129" t="n">
         <v>5</v>
       </c>
       <c r="G156" s="130" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H156" s="129" t="n">
         <v>0</v>
@@ -10952,16 +10952,16 @@
         <v>0</v>
       </c>
       <c r="K156" s="131" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="L156" s="131" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="M156" s="131" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="N156" s="131" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -11302,7 +11302,7 @@
         <v>1088741202</v>
       </c>
       <c r="V6" s="33" t="n">
-        <v>562148118</v>
+        <v>713359006</v>
       </c>
       <c r="W6" s="33">
         <f>IFERROR(SUM('📅 DAILY T8'!C$6:C$36),0)</f>
@@ -11380,7 +11380,7 @@
         <v>2471</v>
       </c>
       <c r="V7" s="33" t="n">
-        <v>1346</v>
+        <v>1708</v>
       </c>
       <c r="W7" s="33">
         <f>IFERROR(SUM('📅 DAILY T8'!D$6:D$36),0)</f>
@@ -11458,7 +11458,7 @@
         <v>440607</v>
       </c>
       <c r="V8" s="33" t="n">
-        <v>417643</v>
+        <v>417657</v>
       </c>
       <c r="W8" s="33">
         <f>IFERROR(SUM('📅 DAILY T8'!C$6:C$36)/SUM('📅 DAILY T8'!D$6:D$36),"")</f>
@@ -11819,7 +11819,7 @@
         <v>676</v>
       </c>
       <c r="V15" s="36" t="n">
-        <v>404</v>
+        <v>522</v>
       </c>
       <c r="W15" s="36" t="n"/>
       <c r="X15" s="36" t="n"/>
@@ -11891,7 +11891,7 @@
         <v>410341</v>
       </c>
       <c r="V16" s="36" t="n">
-        <v>368826</v>
+        <v>366461</v>
       </c>
       <c r="W16" s="36" t="n"/>
       <c r="X16" s="36" t="n"/>
@@ -11963,7 +11963,7 @@
         <v>0.1676</v>
       </c>
       <c r="V17" s="38" t="n">
-        <v>0.1394</v>
+        <v>0.1434</v>
       </c>
       <c r="W17" s="38" t="n"/>
       <c r="X17" s="38" t="n"/>
@@ -12035,7 +12035,7 @@
         <v>0.0819</v>
       </c>
       <c r="V18" s="38" t="n">
-        <v>0.0488</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="W18" s="38" t="n"/>
       <c r="X18" s="38" t="n"/>
@@ -12137,7 +12137,7 @@
         <v>1584</v>
       </c>
       <c r="V20" s="36" t="n">
-        <v>945</v>
+        <v>1192</v>
       </c>
       <c r="W20" s="36" t="n"/>
       <c r="X20" s="36" t="n"/>
@@ -12209,7 +12209,7 @@
         <v>438668</v>
       </c>
       <c r="V21" s="36" t="n">
-        <v>437188</v>
+        <v>437975</v>
       </c>
       <c r="W21" s="36" t="n"/>
       <c r="X21" s="36" t="n"/>
@@ -12281,7 +12281,7 @@
         <v>0.7009</v>
       </c>
       <c r="V22" s="38" t="n">
-        <v>0.7005</v>
+        <v>0.6954</v>
       </c>
       <c r="W22" s="38" t="n"/>
       <c r="X22" s="38" t="n"/>
@@ -12353,7 +12353,7 @@
         <v>395</v>
       </c>
       <c r="V23" s="36" t="n">
-        <v>250</v>
+        <v>328</v>
       </c>
       <c r="W23" s="36" t="n"/>
       <c r="X23" s="36" t="n"/>
@@ -12425,7 +12425,7 @@
         <v>427919</v>
       </c>
       <c r="V24" s="36" t="n">
-        <v>369416</v>
+        <v>373504</v>
       </c>
       <c r="W24" s="36" t="n"/>
       <c r="X24" s="36" t="n"/>
@@ -12497,7 +12497,7 @@
         <v>491</v>
       </c>
       <c r="V25" s="36" t="n">
-        <v>277</v>
+        <v>347</v>
       </c>
       <c r="W25" s="36" t="n"/>
       <c r="X25" s="36" t="n"/>
@@ -12569,7 +12569,7 @@
         <v>450680</v>
       </c>
       <c r="V26" s="36" t="n">
-        <v>447478</v>
+        <v>456387</v>
       </c>
       <c r="W26" s="36" t="n"/>
       <c r="X26" s="36" t="n"/>
@@ -12641,7 +12641,7 @@
         <v>698</v>
       </c>
       <c r="V27" s="36" t="n">
-        <v>418</v>
+        <v>517</v>
       </c>
       <c r="W27" s="36" t="n"/>
       <c r="X27" s="36" t="n"/>
@@ -12713,7 +12713,7 @@
         <v>436911</v>
       </c>
       <c r="V28" s="36" t="n">
-        <v>470902</v>
+        <v>466520</v>
       </c>
       <c r="W28" s="36" t="n"/>
       <c r="X28" s="36" t="n"/>
@@ -12815,7 +12815,7 @@
         <v>1258</v>
       </c>
       <c r="V30" s="36" t="n">
-        <v>735</v>
+        <v>927</v>
       </c>
       <c r="W30" s="36" t="n"/>
       <c r="X30" s="36" t="n"/>
@@ -12887,7 +12887,7 @@
         <v>443642</v>
       </c>
       <c r="V31" s="36" t="n">
-        <v>445056</v>
+        <v>450093</v>
       </c>
       <c r="W31" s="36" t="n"/>
       <c r="X31" s="36" t="n"/>
@@ -12959,7 +12959,7 @@
         <v>804514</v>
       </c>
       <c r="V32" s="36" t="n">
-        <v>797668</v>
+        <v>799867</v>
       </c>
       <c r="W32" s="36" t="n"/>
       <c r="X32" s="36" t="n"/>
@@ -13091,7 +13091,7 @@
         <v>504778392</v>
       </c>
       <c r="V35" s="33" t="n">
-        <v>259550554</v>
+        <v>329558569</v>
       </c>
       <c r="W35" s="33">
         <f>IFERROR(SUM('📅 DAILY T8'!G$6:I$36),0)</f>
@@ -13169,7 +13169,7 @@
         <v>255247175</v>
       </c>
       <c r="V36" s="33" t="n">
-        <v>124556657</v>
+        <v>160710803</v>
       </c>
       <c r="W36" s="33">
         <f>IFERROR(SUM('📅 DAILY T8'!G$6:G$36),0)</f>
@@ -13247,7 +13247,7 @@
         <v>125740056</v>
       </c>
       <c r="V37" s="33" t="n">
-        <v>73270539</v>
+        <v>86806275</v>
       </c>
       <c r="W37" s="33">
         <f>IFERROR(SUM('📅 DAILY T8'!H$6:H$36),0)</f>
@@ -13325,7 +13325,7 @@
         <v>123791161</v>
       </c>
       <c r="V38" s="33" t="n">
-        <v>61723358</v>
+        <v>82041491</v>
       </c>
       <c r="W38" s="33">
         <f>IFERROR(SUM('📅 DAILY T8'!I$6:I$36),0)</f>
@@ -13403,7 +13403,7 @@
         <v>1642</v>
       </c>
       <c r="V39" s="33" t="n">
-        <v>832</v>
+        <v>1071</v>
       </c>
       <c r="W39" s="33">
         <f>IFERROR(SUM('📅 DAILY T8'!J$6:J$36),0)</f>
@@ -13481,7 +13481,7 @@
         <v>307417</v>
       </c>
       <c r="V40" s="33" t="n">
-        <v>311960</v>
+        <v>307711</v>
       </c>
       <c r="W40" s="33">
         <f>IFERROR(SUM('📅 DAILY T8'!M$6:M$36)/SUM('📅 DAILY T8'!J$6:J$36),"")</f>
@@ -13611,7 +13611,7 @@
         <v>576</v>
       </c>
       <c r="V43" s="36" t="n">
-        <v>383</v>
+        <v>489</v>
       </c>
       <c r="W43" s="36" t="n"/>
       <c r="X43" s="36" t="n"/>
@@ -13683,7 +13683,7 @@
         <v>345626</v>
       </c>
       <c r="V44" s="36" t="n">
-        <v>297717</v>
+        <v>290265</v>
       </c>
       <c r="W44" s="36" t="n"/>
       <c r="X44" s="36" t="n"/>
@@ -13755,7 +13755,7 @@
         <v>0.1766</v>
       </c>
       <c r="V45" s="38" t="n">
-        <v>0.1419</v>
+        <v>0.1474</v>
       </c>
       <c r="W45" s="38" t="n"/>
       <c r="X45" s="38" t="n"/>
@@ -13827,7 +13827,7 @@
         <v>0.0644</v>
       </c>
       <c r="V46" s="38" t="n">
-        <v>0.0347</v>
+        <v>0.0451</v>
       </c>
       <c r="W46" s="38" t="n"/>
       <c r="X46" s="38" t="n"/>
@@ -13929,7 +13929,7 @@
         <v>818</v>
       </c>
       <c r="V48" s="36" t="n">
-        <v>451</v>
+        <v>588</v>
       </c>
       <c r="W48" s="36" t="n"/>
       <c r="X48" s="36" t="n"/>
@@ -14001,7 +14001,7 @@
         <v>327838</v>
       </c>
       <c r="V49" s="36" t="n">
-        <v>322671</v>
+        <v>319080</v>
       </c>
       <c r="W49" s="36" t="n"/>
       <c r="X49" s="36" t="n"/>
@@ -14073,7 +14073,7 @@
         <v>0.5868</v>
       </c>
       <c r="V50" s="38" t="n">
-        <v>0.5407999999999999</v>
+        <v>0.546</v>
       </c>
       <c r="W50" s="38" t="n"/>
       <c r="X50" s="38" t="n"/>
@@ -14145,7 +14145,7 @@
         <v>168</v>
       </c>
       <c r="V51" s="36" t="n">
-        <v>96</v>
+        <v>131</v>
       </c>
       <c r="W51" s="36" t="n"/>
       <c r="X51" s="36" t="n"/>
@@ -14217,7 +14217,7 @@
         <v>306908</v>
       </c>
       <c r="V52" s="36" t="n">
-        <v>304027</v>
+        <v>300144</v>
       </c>
       <c r="W52" s="36" t="n"/>
       <c r="X52" s="36" t="n"/>
@@ -14289,7 +14289,7 @@
         <v>252</v>
       </c>
       <c r="V53" s="36" t="n">
-        <v>124</v>
+        <v>162</v>
       </c>
       <c r="W53" s="36" t="n"/>
       <c r="X53" s="36" t="n"/>
@@ -14361,7 +14361,7 @@
         <v>329485</v>
       </c>
       <c r="V54" s="36" t="n">
-        <v>315742</v>
+        <v>306888</v>
       </c>
       <c r="W54" s="36" t="n"/>
       <c r="X54" s="36" t="n"/>
@@ -14433,7 +14433,7 @@
         <v>398</v>
       </c>
       <c r="V55" s="36" t="n">
-        <v>231</v>
+        <v>295</v>
       </c>
       <c r="W55" s="36" t="n"/>
       <c r="X55" s="36" t="n"/>
@@ -14505,7 +14505,7 @@
         <v>336422</v>
       </c>
       <c r="V56" s="36" t="n">
-        <v>334140</v>
+        <v>334185</v>
       </c>
       <c r="W56" s="36" t="n"/>
       <c r="X56" s="36" t="n"/>
@@ -14607,7 +14607,7 @@
         <v>579</v>
       </c>
       <c r="V58" s="36" t="n">
-        <v>310</v>
+        <v>404</v>
       </c>
       <c r="W58" s="36" t="n"/>
       <c r="X58" s="36" t="n"/>
@@ -14679,7 +14679,7 @@
         <v>331118</v>
       </c>
       <c r="V59" s="36" t="n">
-        <v>326240</v>
+        <v>321708</v>
       </c>
       <c r="W59" s="36" t="n"/>
       <c r="X59" s="36" t="n"/>
@@ -14751,7 +14751,7 @@
         <v>496795</v>
       </c>
       <c r="V60" s="36" t="n">
-        <v>490586</v>
+        <v>492225</v>
       </c>
       <c r="W60" s="36" t="n"/>
       <c r="X60" s="36" t="n"/>
@@ -14837,7 +14837,7 @@
         <v>27162334</v>
       </c>
       <c r="V63" s="33" t="n">
-        <v>20656391</v>
+        <v>23871091</v>
       </c>
       <c r="W63" s="33" t="n"/>
       <c r="X63" s="33" t="n"/>
@@ -14909,7 +14909,7 @@
         <v>0.017</v>
       </c>
       <c r="V64" s="46" t="n">
-        <v>0.0251</v>
+        <v>0.0229</v>
       </c>
       <c r="W64" s="33" t="n"/>
       <c r="X64" s="33" t="n"/>
@@ -15042,7 +15042,7 @@
         <v>1593519594</v>
       </c>
       <c r="V68" s="33" t="n">
-        <v>821698672</v>
+        <v>1042917575</v>
       </c>
       <c r="W68" s="33">
         <f>IFERROR(SUM('📅 DAILY T8'!C$6:C$36)+SUM('📅 DAILY T8'!G$6:I$36),0)</f>
@@ -15146,7 +15146,7 @@
         <v>1.13</v>
       </c>
       <c r="V70" s="39" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W70" s="39" t="n"/>
       <c r="X70" s="39" t="n"/>
@@ -15218,7 +15218,7 @@
         <v>19281</v>
       </c>
       <c r="V71" s="36" t="n">
-        <v>17701</v>
+        <v>17935</v>
       </c>
       <c r="W71" s="36" t="n"/>
       <c r="X71" s="36" t="n"/>
@@ -15290,7 +15290,7 @@
         <v>984</v>
       </c>
       <c r="V72" s="36" t="n">
-        <v>755</v>
+        <v>946</v>
       </c>
       <c r="W72" s="36" t="n"/>
       <c r="X72" s="36" t="n"/>
@@ -15464,7 +15464,7 @@
         <v>1014219</v>
       </c>
       <c r="V75" s="36" t="n">
-        <v>1018889</v>
+        <v>1019759</v>
       </c>
       <c r="W75" s="36" t="n"/>
       <c r="X75" s="36" t="n"/>
@@ -15536,7 +15536,7 @@
         <v>647229</v>
       </c>
       <c r="V76" s="36" t="n">
-        <v>649550</v>
+        <v>650099</v>
       </c>
       <c r="W76" s="36" t="n"/>
       <c r="X76" s="36" t="n"/>
@@ -15608,7 +15608,7 @@
         <v>804514</v>
       </c>
       <c r="V77" s="36" t="n">
-        <v>797668</v>
+        <v>799867</v>
       </c>
       <c r="W77" s="36" t="n"/>
       <c r="X77" s="36" t="n"/>
@@ -15680,7 +15680,7 @@
         <v>496795</v>
       </c>
       <c r="V78" s="36" t="n">
-        <v>490586</v>
+        <v>492225</v>
       </c>
       <c r="W78" s="36" t="n"/>
       <c r="X78" s="36" t="n"/>
@@ -20157,10 +20157,10 @@
         </is>
       </c>
       <c r="C20" s="75" t="n">
-        <v>37830798</v>
+        <v>38150799</v>
       </c>
       <c r="D20" s="75" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E20" s="75" t="n"/>
       <c r="F20" s="75" t="n"/>
@@ -20208,15 +20208,29 @@
           <t>T5</t>
         </is>
       </c>
-      <c r="C21" s="75" t="n"/>
-      <c r="D21" s="75" t="n"/>
+      <c r="C21" s="75" t="n">
+        <v>39385519</v>
+      </c>
+      <c r="D21" s="75" t="n">
+        <v>88</v>
+      </c>
       <c r="E21" s="75" t="n"/>
       <c r="F21" s="75" t="n"/>
-      <c r="G21" s="75" t="n"/>
-      <c r="H21" s="75" t="n"/>
-      <c r="I21" s="75" t="n"/>
-      <c r="J21" s="75" t="n"/>
-      <c r="K21" s="75" t="n"/>
+      <c r="G21" s="75" t="n">
+        <v>10004741</v>
+      </c>
+      <c r="H21" s="75" t="n">
+        <v>2615001</v>
+      </c>
+      <c r="I21" s="75" t="n">
+        <v>4320000</v>
+      </c>
+      <c r="J21" s="75" t="n">
+        <v>58</v>
+      </c>
+      <c r="K21" s="75" t="n">
+        <v>1028800</v>
+      </c>
       <c r="L21" s="76" t="n"/>
       <c r="M21" s="33">
         <f>IF(SUM(G21:I21)&gt;0,SUM(G21:I21),"")</f>
@@ -20248,15 +20262,29 @@
           <t>T6</t>
         </is>
       </c>
-      <c r="C22" s="75" t="n"/>
-      <c r="D22" s="75" t="n"/>
+      <c r="C22" s="75" t="n">
+        <v>46753158</v>
+      </c>
+      <c r="D22" s="75" t="n">
+        <v>103</v>
+      </c>
       <c r="E22" s="75" t="n"/>
       <c r="F22" s="75" t="n"/>
-      <c r="G22" s="75" t="n"/>
-      <c r="H22" s="75" t="n"/>
-      <c r="I22" s="75" t="n"/>
-      <c r="J22" s="75" t="n"/>
-      <c r="K22" s="75" t="n"/>
+      <c r="G22" s="75" t="n">
+        <v>8923000</v>
+      </c>
+      <c r="H22" s="75" t="n">
+        <v>2255001</v>
+      </c>
+      <c r="I22" s="75" t="n">
+        <v>5365199</v>
+      </c>
+      <c r="J22" s="75" t="n">
+        <v>63</v>
+      </c>
+      <c r="K22" s="75" t="n">
+        <v>1043500</v>
+      </c>
       <c r="L22" s="76" t="n"/>
       <c r="M22" s="33">
         <f>IF(SUM(G22:I22)&gt;0,SUM(G22:I22),"")</f>
@@ -20288,15 +20316,29 @@
           <t>T7</t>
         </is>
       </c>
-      <c r="C23" s="75" t="n"/>
-      <c r="D23" s="75" t="n"/>
+      <c r="C23" s="75" t="n">
+        <v>40097175</v>
+      </c>
+      <c r="D23" s="75" t="n">
+        <v>102</v>
+      </c>
       <c r="E23" s="75" t="n"/>
       <c r="F23" s="75" t="n"/>
-      <c r="G23" s="75" t="n"/>
-      <c r="H23" s="75" t="n"/>
-      <c r="I23" s="75" t="n"/>
-      <c r="J23" s="75" t="n"/>
-      <c r="K23" s="75" t="n"/>
+      <c r="G23" s="75" t="n">
+        <v>5977296</v>
+      </c>
+      <c r="H23" s="75" t="n">
+        <v>5832004</v>
+      </c>
+      <c r="I23" s="75" t="n">
+        <v>7530007</v>
+      </c>
+      <c r="J23" s="75" t="n">
+        <v>66</v>
+      </c>
+      <c r="K23" s="75" t="n">
+        <v>1142400</v>
+      </c>
       <c r="L23" s="76" t="n"/>
       <c r="M23" s="33">
         <f>IF(SUM(G23:I23)&gt;0,SUM(G23:I23),"")</f>
@@ -20328,14 +20370,26 @@
           <t>CN</t>
         </is>
       </c>
-      <c r="C24" s="75" t="n"/>
-      <c r="D24" s="75" t="n"/>
+      <c r="C24" s="75" t="n">
+        <v>24655035</v>
+      </c>
+      <c r="D24" s="75" t="n">
+        <v>68</v>
+      </c>
       <c r="E24" s="75" t="n"/>
       <c r="F24" s="75" t="n"/>
-      <c r="G24" s="75" t="n"/>
-      <c r="H24" s="75" t="n"/>
-      <c r="I24" s="75" t="n"/>
-      <c r="J24" s="75" t="n"/>
+      <c r="G24" s="75" t="n">
+        <v>11550771</v>
+      </c>
+      <c r="H24" s="75" t="n">
+        <v>2669997</v>
+      </c>
+      <c r="I24" s="75" t="n">
+        <v>2964998</v>
+      </c>
+      <c r="J24" s="75" t="n">
+        <v>52</v>
+      </c>
       <c r="K24" s="75" t="n"/>
       <c r="L24" s="76" t="n"/>
       <c r="M24" s="33">

--- a/data.xlsx
+++ b/data.xlsx
@@ -21208,43 +21208,43 @@
       </c>
       <c r="B4" s="80" t="inlineStr">
         <is>
-          <t>1/7–7/7</t>
+          <t>1/7–5/7</t>
         </is>
       </c>
       <c r="C4" s="81">
-        <f>IFERROR(SUM('📅 DAILY T7'!C6:C12),0)</f>
+        <f>IFERROR(SUM('📅 DAILY T7'!C6:C10),0)</f>
         <v/>
       </c>
       <c r="D4" s="81">
-        <f>IFERROR(SUM('📅 DAILY T7'!D6:D12),0)</f>
+        <f>IFERROR(SUM('📅 DAILY T7'!D6:D10),0)</f>
         <v/>
       </c>
       <c r="E4" s="81">
-        <f>IFERROR(SUM('📅 DAILY T7'!C6:C12)/SUM('📅 DAILY T7'!D6:D12),"")</f>
+        <f>IFERROR(SUM('📅 DAILY T7'!C6:C10)/SUM('📅 DAILY T7'!D6:D10),"")</f>
         <v/>
       </c>
       <c r="F4" s="82">
-        <f>IFERROR(SUM('📅 DAILY T7'!F6:F12),0)</f>
+        <f>IFERROR(SUM('📅 DAILY T7'!F6:F10),0)</f>
         <v/>
       </c>
       <c r="G4" s="83">
-        <f>IFERROR(SUM('📅 DAILY T7'!C6:C12)/SUM('📅 DAILY T7'!F6:F12),"")</f>
+        <f>IFERROR(SUM('📅 DAILY T7'!C6:C10)/SUM('📅 DAILY T7'!F6:F10),"")</f>
         <v/>
       </c>
       <c r="H4" s="84">
-        <f>IFERROR(SUM('📅 DAILY T7'!M6:M12),0)</f>
+        <f>IFERROR(SUM('📅 DAILY T7'!M6:M10),0)</f>
         <v/>
       </c>
       <c r="I4" s="85">
-        <f>IFERROR(SUM('📅 DAILY T7'!N6:N12),0)</f>
+        <f>IFERROR(SUM('📅 DAILY T7'!N6:N10),0)</f>
         <v/>
       </c>
       <c r="J4" s="86">
-        <f>IFERROR(SUM('📅 DAILY T7'!C6:C12)/1277560078,"")</f>
+        <f>IFERROR(SUM('📅 DAILY T7'!C6:C10)/1277560078,"")</f>
         <v/>
       </c>
       <c r="K4" s="86">
-        <f>IFERROR(SUM('📅 DAILY T7'!M6:M12)/721910506,"")</f>
+        <f>IFERROR(SUM('📅 DAILY T7'!M6:M10)/721910506,"")</f>
         <v/>
       </c>
       <c r="L4" s="87" t="n"/>
@@ -21257,43 +21257,43 @@
       </c>
       <c r="B5" s="89" t="inlineStr">
         <is>
-          <t>8/7–14/7</t>
+          <t>6/7–12/7</t>
         </is>
       </c>
       <c r="C5" s="81">
-        <f>IFERROR(SUM('📅 DAILY T7'!C13:C19),0)</f>
+        <f>IFERROR(SUM('📅 DAILY T7'!C11:C17),0)</f>
         <v/>
       </c>
       <c r="D5" s="81">
-        <f>IFERROR(SUM('📅 DAILY T7'!D13:D19),0)</f>
+        <f>IFERROR(SUM('📅 DAILY T7'!D11:D17),0)</f>
         <v/>
       </c>
       <c r="E5" s="81">
-        <f>IFERROR(SUM('📅 DAILY T7'!C13:C19)/SUM('📅 DAILY T7'!D13:D19),"")</f>
+        <f>IFERROR(SUM('📅 DAILY T7'!C11:C17)/SUM('📅 DAILY T7'!D11:D17),"")</f>
         <v/>
       </c>
       <c r="F5" s="82">
-        <f>IFERROR(SUM('📅 DAILY T7'!F13:F19),0)</f>
+        <f>IFERROR(SUM('📅 DAILY T7'!F11:F17),0)</f>
         <v/>
       </c>
       <c r="G5" s="83">
-        <f>IFERROR(SUM('📅 DAILY T7'!C13:C19)/SUM('📅 DAILY T7'!F13:F19),"")</f>
+        <f>IFERROR(SUM('📅 DAILY T7'!C11:C17)/SUM('📅 DAILY T7'!F11:F17),"")</f>
         <v/>
       </c>
       <c r="H5" s="84">
-        <f>IFERROR(SUM('📅 DAILY T7'!M13:M19),0)</f>
+        <f>IFERROR(SUM('📅 DAILY T7'!M11:M17),0)</f>
         <v/>
       </c>
       <c r="I5" s="85">
-        <f>IFERROR(SUM('📅 DAILY T7'!N13:N19),0)</f>
+        <f>IFERROR(SUM('📅 DAILY T7'!N11:N17),0)</f>
         <v/>
       </c>
       <c r="J5" s="86">
-        <f>IFERROR(SUM('📅 DAILY T7'!C6:C19)/1277560078,"")</f>
+        <f>IFERROR(SUM('📅 DAILY T7'!C6:C17)/1277560078,"")</f>
         <v/>
       </c>
       <c r="K5" s="86">
-        <f>IFERROR(SUM('📅 DAILY T7'!M6:M19)/721910506,"")</f>
+        <f>IFERROR(SUM('📅 DAILY T7'!M6:M17)/721910506,"")</f>
         <v/>
       </c>
       <c r="L5" s="87" t="n"/>
@@ -21306,43 +21306,43 @@
       </c>
       <c r="B6" s="91" t="inlineStr">
         <is>
-          <t>15/7–21/7</t>
+          <t>13/7–19/7</t>
         </is>
       </c>
       <c r="C6" s="81">
-        <f>IFERROR(SUM('📅 DAILY T7'!C20:C26),0)</f>
+        <f>IFERROR(SUM('📅 DAILY T7'!C18:C24),0)</f>
         <v/>
       </c>
       <c r="D6" s="81">
-        <f>IFERROR(SUM('📅 DAILY T7'!D20:D26),0)</f>
+        <f>IFERROR(SUM('📅 DAILY T7'!D18:D24),0)</f>
         <v/>
       </c>
       <c r="E6" s="81">
-        <f>IFERROR(SUM('📅 DAILY T7'!C20:C26)/SUM('📅 DAILY T7'!D20:D26),"")</f>
+        <f>IFERROR(SUM('📅 DAILY T7'!C18:C24)/SUM('📅 DAILY T7'!D18:D24),"")</f>
         <v/>
       </c>
       <c r="F6" s="82">
-        <f>IFERROR(SUM('📅 DAILY T7'!F20:F26),0)</f>
+        <f>IFERROR(SUM('📅 DAILY T7'!F18:F24),0)</f>
         <v/>
       </c>
       <c r="G6" s="83">
-        <f>IFERROR(SUM('📅 DAILY T7'!C20:C26)/SUM('📅 DAILY T7'!F20:F26),"")</f>
+        <f>IFERROR(SUM('📅 DAILY T7'!C18:C24)/SUM('📅 DAILY T7'!F18:F24),"")</f>
         <v/>
       </c>
       <c r="H6" s="84">
-        <f>IFERROR(SUM('📅 DAILY T7'!M20:M26),0)</f>
+        <f>IFERROR(SUM('📅 DAILY T7'!M18:M24),0)</f>
         <v/>
       </c>
       <c r="I6" s="85">
-        <f>IFERROR(SUM('📅 DAILY T7'!N20:N26),0)</f>
+        <f>IFERROR(SUM('📅 DAILY T7'!N18:N24),0)</f>
         <v/>
       </c>
       <c r="J6" s="86">
-        <f>IFERROR(SUM('📅 DAILY T7'!C6:C26)/1277560078,"")</f>
+        <f>IFERROR(SUM('📅 DAILY T7'!C6:C24)/1277560078,"")</f>
         <v/>
       </c>
       <c r="K6" s="86">
-        <f>IFERROR(SUM('📅 DAILY T7'!M6:M26)/721910506,"")</f>
+        <f>IFERROR(SUM('📅 DAILY T7'!M6:M24)/721910506,"")</f>
         <v/>
       </c>
       <c r="L6" s="87" t="n"/>
@@ -21355,43 +21355,43 @@
       </c>
       <c r="B7" s="93" t="inlineStr">
         <is>
-          <t>22/7–28/7</t>
+          <t>20/7–26/7</t>
         </is>
       </c>
       <c r="C7" s="81">
-        <f>IFERROR(SUM('📅 DAILY T7'!C27:C33),0)</f>
+        <f>IFERROR(SUM('📅 DAILY T7'!C25:C31),0)</f>
         <v/>
       </c>
       <c r="D7" s="81">
-        <f>IFERROR(SUM('📅 DAILY T7'!D27:D33),0)</f>
+        <f>IFERROR(SUM('📅 DAILY T7'!D25:D31),0)</f>
         <v/>
       </c>
       <c r="E7" s="81">
-        <f>IFERROR(SUM('📅 DAILY T7'!C27:C33)/SUM('📅 DAILY T7'!D27:D33),"")</f>
+        <f>IFERROR(SUM('📅 DAILY T7'!C25:C31)/SUM('📅 DAILY T7'!D25:D31),"")</f>
         <v/>
       </c>
       <c r="F7" s="82">
-        <f>IFERROR(SUM('📅 DAILY T7'!F27:F33),0)</f>
+        <f>IFERROR(SUM('📅 DAILY T7'!F25:F31),0)</f>
         <v/>
       </c>
       <c r="G7" s="83">
-        <f>IFERROR(SUM('📅 DAILY T7'!C27:C33)/SUM('📅 DAILY T7'!F27:F33),"")</f>
+        <f>IFERROR(SUM('📅 DAILY T7'!C25:C31)/SUM('📅 DAILY T7'!F25:F31),"")</f>
         <v/>
       </c>
       <c r="H7" s="84">
-        <f>IFERROR(SUM('📅 DAILY T7'!M27:M33),0)</f>
+        <f>IFERROR(SUM('📅 DAILY T7'!M25:M31),0)</f>
         <v/>
       </c>
       <c r="I7" s="85">
-        <f>IFERROR(SUM('📅 DAILY T7'!N27:N33),0)</f>
+        <f>IFERROR(SUM('📅 DAILY T7'!N25:N31),0)</f>
         <v/>
       </c>
       <c r="J7" s="86">
-        <f>IFERROR(SUM('📅 DAILY T7'!C6:C33)/1277560078,"")</f>
+        <f>IFERROR(SUM('📅 DAILY T7'!C6:C31)/1277560078,"")</f>
         <v/>
       </c>
       <c r="K7" s="86">
-        <f>IFERROR(SUM('📅 DAILY T7'!M6:M33)/721910506,"")</f>
+        <f>IFERROR(SUM('📅 DAILY T7'!M6:M31)/721910506,"")</f>
         <v/>
       </c>
       <c r="L7" s="87" t="n"/>
@@ -21404,35 +21404,35 @@
       </c>
       <c r="B8" s="95" t="inlineStr">
         <is>
-          <t>29/7–31/7</t>
+          <t>27/7–31/7</t>
         </is>
       </c>
       <c r="C8" s="81">
-        <f>IFERROR(SUM('📅 DAILY T7'!C34:C36),0)</f>
+        <f>IFERROR(SUM('📅 DAILY T7'!C32:C36),0)</f>
         <v/>
       </c>
       <c r="D8" s="81">
-        <f>IFERROR(SUM('📅 DAILY T7'!D34:D36),0)</f>
+        <f>IFERROR(SUM('📅 DAILY T7'!D32:D36),0)</f>
         <v/>
       </c>
       <c r="E8" s="81">
-        <f>IFERROR(SUM('📅 DAILY T7'!C34:C36)/SUM('📅 DAILY T7'!D34:D36),"")</f>
+        <f>IFERROR(SUM('📅 DAILY T7'!C32:C36)/SUM('📅 DAILY T7'!D32:D36),"")</f>
         <v/>
       </c>
       <c r="F8" s="82">
-        <f>IFERROR(SUM('📅 DAILY T7'!F34:F36),0)</f>
+        <f>IFERROR(SUM('📅 DAILY T7'!F32:F36),0)</f>
         <v/>
       </c>
       <c r="G8" s="83">
-        <f>IFERROR(SUM('📅 DAILY T7'!C34:C36)/SUM('📅 DAILY T7'!F34:F36),"")</f>
+        <f>IFERROR(SUM('📅 DAILY T7'!C32:C36)/SUM('📅 DAILY T7'!F32:F36),"")</f>
         <v/>
       </c>
       <c r="H8" s="84">
-        <f>IFERROR(SUM('📅 DAILY T7'!M34:M36),0)</f>
+        <f>IFERROR(SUM('📅 DAILY T7'!M32:M36),0)</f>
         <v/>
       </c>
       <c r="I8" s="85">
-        <f>IFERROR(SUM('📅 DAILY T7'!N34:N36),0)</f>
+        <f>IFERROR(SUM('📅 DAILY T7'!N32:N36),0)</f>
         <v/>
       </c>
       <c r="J8" s="86">

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macos/REPORT FB&amp;STORE/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33C452F8-6CB5-5B47-91DB-96F507F418E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D312025F-A105-BA4A-8D98-FD5D6B8BF88B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2884,12 +2884,12 @@
     <xf numFmtId="16" fontId="14" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2904,11 +2904,11 @@
     <xf numFmtId="0" fontId="3" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2941,16 +2941,16 @@
     <xf numFmtId="0" fontId="19" fillId="19" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="36" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -4896,7 +4896,7 @@
     </row>
     <row r="22" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="23" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="160" t="s">
+      <c r="A23" s="162" t="s">
         <v>413</v>
       </c>
       <c r="B23" s="137"/>
@@ -4919,7 +4919,7 @@
     </row>
     <row r="24" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="25" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="159" t="s">
+      <c r="A25" s="161" t="s">
         <v>414</v>
       </c>
       <c r="B25" s="137"/>
@@ -8364,40 +8364,40 @@
         <v>538</v>
       </c>
       <c r="C77" s="128">
-        <v>618</v>
+        <v>665</v>
       </c>
       <c r="D77" s="129">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="E77" s="129">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="F77" s="129">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="G77" s="129">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H77" s="129">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I77" s="129">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="J77" s="129">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K77" s="131">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L77" s="131">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="M77" s="131">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N77" s="131">
-        <v>276</v>
+        <v>308</v>
       </c>
     </row>
     <row r="78" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -8408,40 +8408,40 @@
         <v>539</v>
       </c>
       <c r="C78" s="128">
-        <v>961</v>
+        <v>1037</v>
       </c>
       <c r="D78" s="129">
-        <v>728</v>
+        <v>788</v>
       </c>
       <c r="E78" s="129">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="F78" s="129">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G78" s="129">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H78" s="129">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I78" s="129">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J78" s="130">
         <v>0</v>
       </c>
       <c r="K78" s="131">
+        <v>189</v>
+      </c>
+      <c r="L78" s="131">
         <v>175</v>
       </c>
-      <c r="L78" s="131">
-        <v>159</v>
-      </c>
       <c r="M78" s="131">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="N78" s="131">
-        <v>121</v>
+        <v>131</v>
       </c>
     </row>
     <row r="79" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8452,19 +8452,19 @@
         <v>540</v>
       </c>
       <c r="C79" s="128">
-        <v>618</v>
+        <v>665</v>
       </c>
       <c r="D79" s="129">
-        <v>499</v>
+        <v>537</v>
       </c>
       <c r="E79" s="129">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="F79" s="129">
         <v>13</v>
       </c>
       <c r="G79" s="129">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H79" s="129">
         <v>3</v>
@@ -8476,16 +8476,16 @@
         <v>0</v>
       </c>
       <c r="K79" s="131">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="L79" s="131">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="M79" s="131">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="N79" s="131">
-        <v>101</v>
+        <v>112</v>
       </c>
     </row>
     <row r="80" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -11194,22 +11194,22 @@
         <v>538</v>
       </c>
       <c r="C154" s="128">
-        <v>615</v>
+        <v>659</v>
       </c>
       <c r="D154" s="129">
-        <v>357</v>
+        <v>380</v>
       </c>
       <c r="E154" s="129">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F154" s="129">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="G154" s="129">
         <v>8</v>
       </c>
       <c r="H154" s="129">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I154" s="129">
         <v>11</v>
@@ -11218,16 +11218,16 @@
         <v>2</v>
       </c>
       <c r="K154" s="131">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L154" s="131">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="M154" s="131">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N154" s="131">
-        <v>229</v>
+        <v>245</v>
       </c>
     </row>
     <row r="155" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -11238,16 +11238,16 @@
         <v>539</v>
       </c>
       <c r="C155" s="128">
-        <v>502</v>
+        <v>534</v>
       </c>
       <c r="D155" s="129">
-        <v>436</v>
+        <v>463</v>
       </c>
       <c r="E155" s="129">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F155" s="129">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G155" s="129">
         <v>3</v>
@@ -11262,16 +11262,16 @@
         <v>0</v>
       </c>
       <c r="K155" s="131">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="L155" s="131">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="M155" s="131">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="N155" s="131">
-        <v>94</v>
+        <v>99</v>
       </c>
     </row>
     <row r="156" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -11282,13 +11282,13 @@
         <v>540</v>
       </c>
       <c r="C156" s="128">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="D156" s="129">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="E156" s="129">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F156" s="129">
         <v>6</v>
@@ -11306,16 +11306,16 @@
         <v>0</v>
       </c>
       <c r="K156" s="131">
+        <v>58</v>
+      </c>
+      <c r="L156" s="131">
+        <v>26</v>
+      </c>
+      <c r="M156" s="131">
         <v>55</v>
       </c>
-      <c r="L156" s="131">
-        <v>25</v>
-      </c>
-      <c r="M156" s="131">
-        <v>52</v>
-      </c>
       <c r="N156" s="131">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -11347,7 +11347,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="147" t="s">
+      <c r="A1" s="146" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="137"/>
@@ -11505,7 +11505,7 @@
       <c r="X4" s="137"/>
     </row>
     <row r="5" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="146" t="s">
+      <c r="A5" s="147" t="s">
         <v>27</v>
       </c>
       <c r="B5" s="137"/>
@@ -11595,7 +11595,7 @@
         <v>1088741202</v>
       </c>
       <c r="V6" s="33">
-        <v>980866532</v>
+        <v>1060858865</v>
       </c>
       <c r="W6" s="33">
         <f>IFERROR(SUM('📅 DAILY T8'!C$6:C$36),0)</f>
@@ -11669,7 +11669,7 @@
         <v>2471</v>
       </c>
       <c r="V7" s="33">
-        <v>2351</v>
+        <v>2432</v>
       </c>
       <c r="W7" s="33">
         <f>IFERROR(SUM('📅 DAILY T8'!D$6:D$36),0)</f>
@@ -11743,7 +11743,7 @@
         <v>440607</v>
       </c>
       <c r="V8" s="33">
-        <v>417212</v>
+        <v>436208</v>
       </c>
       <c r="W8" s="33" t="str">
         <f>IFERROR(SUM('📅 DAILY T8'!C$6:C$36)/SUM('📅 DAILY T8'!D$6:D$36),"")</f>
@@ -11817,7 +11817,7 @@
         <v>5789</v>
       </c>
       <c r="V9" s="36">
-        <v>4100</v>
+        <v>4554</v>
       </c>
       <c r="W9" s="36"/>
       <c r="X9" s="36"/>
@@ -11932,7 +11932,7 @@
       </c>
       <c r="V11" s="37">
         <f t="shared" si="0"/>
-        <v>0.57341463414634142</v>
+        <v>0.53403601229688191</v>
       </c>
       <c r="W11" s="38"/>
       <c r="X11" s="38"/>
@@ -11966,7 +11966,7 @@
       <c r="X12" s="39"/>
     </row>
     <row r="13" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="146" t="s">
+      <c r="A13" s="147" t="s">
         <v>39</v>
       </c>
       <c r="B13" s="137"/>
@@ -12084,7 +12084,7 @@
         <v>676</v>
       </c>
       <c r="V15" s="36">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="W15" s="36"/>
       <c r="X15" s="36"/>
@@ -12152,7 +12152,7 @@
         <v>410341</v>
       </c>
       <c r="V16" s="36">
-        <v>380459</v>
+        <v>395297</v>
       </c>
       <c r="W16" s="36"/>
       <c r="X16" s="36"/>
@@ -12220,7 +12220,7 @@
         <v>0.1676</v>
       </c>
       <c r="V17" s="38">
-        <v>0.189</v>
+        <v>0.1394</v>
       </c>
       <c r="W17" s="38"/>
       <c r="X17" s="38"/>
@@ -12384,7 +12384,7 @@
         <v>1584</v>
       </c>
       <c r="V20" s="36">
-        <v>1626</v>
+        <v>1573</v>
       </c>
       <c r="W20" s="36"/>
       <c r="X20" s="36"/>
@@ -12452,7 +12452,7 @@
         <v>438668</v>
       </c>
       <c r="V21" s="36">
-        <v>433600</v>
+        <v>454451</v>
       </c>
       <c r="W21" s="36"/>
       <c r="X21" s="36"/>
@@ -12520,7 +12520,7 @@
         <v>0.70089999999999997</v>
       </c>
       <c r="V22" s="38">
-        <v>0.69159999999999999</v>
+        <v>0.68210000000000004</v>
       </c>
       <c r="W22" s="38"/>
       <c r="X22" s="38"/>
@@ -12588,7 +12588,7 @@
         <v>395</v>
       </c>
       <c r="V23" s="36">
-        <v>466</v>
+        <v>417</v>
       </c>
       <c r="W23" s="36"/>
       <c r="X23" s="36"/>
@@ -12656,7 +12656,7 @@
         <v>427919</v>
       </c>
       <c r="V24" s="36">
-        <v>377650</v>
+        <v>410757</v>
       </c>
       <c r="W24" s="36"/>
       <c r="X24" s="36"/>
@@ -12724,7 +12724,7 @@
         <v>491</v>
       </c>
       <c r="V25" s="36">
-        <v>476</v>
+        <v>467</v>
       </c>
       <c r="W25" s="36"/>
       <c r="X25" s="36"/>
@@ -12792,7 +12792,7 @@
         <v>450680</v>
       </c>
       <c r="V26" s="36">
-        <v>448856</v>
+        <v>465513</v>
       </c>
       <c r="W26" s="36"/>
       <c r="X26" s="36"/>
@@ -12860,7 +12860,7 @@
         <v>698</v>
       </c>
       <c r="V27" s="36">
-        <v>684</v>
+        <v>689</v>
       </c>
       <c r="W27" s="36"/>
       <c r="X27" s="36"/>
@@ -12928,7 +12928,7 @@
         <v>436911</v>
       </c>
       <c r="V28" s="36">
-        <v>461102</v>
+        <v>474970</v>
       </c>
       <c r="W28" s="36"/>
       <c r="X28" s="36"/>
@@ -13024,7 +13024,7 @@
         <v>1258</v>
       </c>
       <c r="V30" s="36">
-        <v>1280</v>
+        <v>1612</v>
       </c>
       <c r="W30" s="36"/>
       <c r="X30" s="36"/>
@@ -13092,7 +13092,7 @@
         <v>443642</v>
       </c>
       <c r="V31" s="36">
-        <v>440961</v>
+        <v>450270</v>
       </c>
       <c r="W31" s="36"/>
       <c r="X31" s="36"/>
@@ -13160,7 +13160,7 @@
         <v>804514</v>
       </c>
       <c r="V32" s="36">
-        <v>804884</v>
+        <v>964719</v>
       </c>
       <c r="W32" s="36"/>
       <c r="X32" s="36"/>
@@ -13194,7 +13194,7 @@
       <c r="X33" s="137"/>
     </row>
     <row r="34" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="139" t="s">
+      <c r="A34" s="136" t="s">
         <v>60</v>
       </c>
       <c r="B34" s="137"/>
@@ -13284,7 +13284,7 @@
         <v>504778392</v>
       </c>
       <c r="V35" s="33">
-        <v>451501662</v>
+        <v>478274678</v>
       </c>
       <c r="W35" s="33">
         <f>IFERROR(SUM('📅 DAILY T8'!G$6:I$36),0)</f>
@@ -13358,7 +13358,7 @@
         <v>255247175</v>
       </c>
       <c r="V36" s="33">
-        <v>228769573</v>
+        <v>241526587</v>
       </c>
       <c r="W36" s="33">
         <f>IFERROR(SUM('📅 DAILY T8'!G$6:G$36),0)</f>
@@ -13432,7 +13432,7 @@
         <v>125740056</v>
       </c>
       <c r="V37" s="33">
-        <v>114081091</v>
+        <v>120353091</v>
       </c>
       <c r="W37" s="33">
         <f>IFERROR(SUM('📅 DAILY T8'!H$6:H$36),0)</f>
@@ -13506,7 +13506,7 @@
         <v>123791161</v>
       </c>
       <c r="V38" s="33">
-        <v>108650998</v>
+        <v>116395000</v>
       </c>
       <c r="W38" s="33">
         <f>IFERROR(SUM('📅 DAILY T8'!I$6:I$36),0)</f>
@@ -13580,7 +13580,7 @@
         <v>1642</v>
       </c>
       <c r="V39" s="33">
-        <v>1465</v>
+        <v>1504</v>
       </c>
       <c r="W39" s="33">
         <f>IFERROR(SUM('📅 DAILY T8'!J$6:J$36),0)</f>
@@ -13654,7 +13654,7 @@
         <v>307417</v>
       </c>
       <c r="V40" s="33">
-        <v>308192</v>
+        <v>318002</v>
       </c>
       <c r="W40" s="33" t="str">
         <f>IFERROR(SUM('📅 DAILY T8'!M$6:M$36)/SUM('📅 DAILY T8'!J$6:J$36),"")</f>
@@ -13689,7 +13689,7 @@
       <c r="U41" s="137"/>
       <c r="V41" s="137"/>
       <c r="W41" s="137"/>
-      <c r="X41" s="138"/>
+      <c r="X41" s="139"/>
     </row>
     <row r="42" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="144"/>
@@ -13715,7 +13715,7 @@
       <c r="U42" s="137"/>
       <c r="V42" s="137"/>
       <c r="W42" s="137"/>
-      <c r="X42" s="138"/>
+      <c r="X42" s="139"/>
     </row>
     <row r="43" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="45"/>
@@ -13780,7 +13780,7 @@
         <v>576</v>
       </c>
       <c r="V43" s="36">
-        <v>682</v>
+        <v>556</v>
       </c>
       <c r="W43" s="36"/>
       <c r="X43" s="36"/>
@@ -13848,7 +13848,7 @@
         <v>345626</v>
       </c>
       <c r="V44" s="36">
-        <v>290440</v>
+        <v>299551</v>
       </c>
       <c r="W44" s="36"/>
       <c r="X44" s="36"/>
@@ -13916,7 +13916,7 @@
         <v>0.17660000000000001</v>
       </c>
       <c r="V45" s="38">
-        <v>0.18870000000000001</v>
+        <v>0.14330000000000001</v>
       </c>
       <c r="W45" s="38"/>
       <c r="X45" s="38"/>
@@ -13984,7 +13984,7 @@
         <v>6.4399999999999999E-2</v>
       </c>
       <c r="V46" s="38">
-        <v>5.5599999999999997E-2</v>
+        <v>5.7299999999999997E-2</v>
       </c>
       <c r="W46" s="38"/>
       <c r="X46" s="38"/>
@@ -14080,7 +14080,7 @@
         <v>818</v>
       </c>
       <c r="V48" s="36">
-        <v>783</v>
+        <v>745</v>
       </c>
       <c r="W48" s="36"/>
       <c r="X48" s="36"/>
@@ -14148,7 +14148,7 @@
         <v>327838</v>
       </c>
       <c r="V49" s="36">
-        <v>323655</v>
+        <v>334109</v>
       </c>
       <c r="W49" s="36"/>
       <c r="X49" s="36"/>
@@ -14216,7 +14216,7 @@
         <v>0.58679999999999999</v>
       </c>
       <c r="V50" s="38">
-        <v>0.53449999999999998</v>
+        <v>0.5726</v>
       </c>
       <c r="W50" s="38"/>
       <c r="X50" s="38"/>
@@ -14284,7 +14284,7 @@
         <v>168</v>
       </c>
       <c r="V51" s="36">
-        <v>188</v>
+        <v>167</v>
       </c>
       <c r="W51" s="36"/>
       <c r="X51" s="36"/>
@@ -14352,7 +14352,7 @@
         <v>306908</v>
       </c>
       <c r="V52" s="36">
-        <v>297145</v>
+        <v>305722</v>
       </c>
       <c r="W52" s="36"/>
       <c r="X52" s="36"/>
@@ -14420,7 +14420,7 @@
         <v>252</v>
       </c>
       <c r="V53" s="36">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="W53" s="36"/>
       <c r="X53" s="36"/>
@@ -14488,7 +14488,7 @@
         <v>329485</v>
       </c>
       <c r="V54" s="36">
-        <v>312768</v>
+        <v>323838</v>
       </c>
       <c r="W54" s="36"/>
       <c r="X54" s="36"/>
@@ -14556,7 +14556,7 @@
         <v>398</v>
       </c>
       <c r="V55" s="36">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="W55" s="36"/>
       <c r="X55" s="36"/>
@@ -14624,7 +14624,7 @@
         <v>336422</v>
       </c>
       <c r="V56" s="36">
-        <v>343662</v>
+        <v>354695</v>
       </c>
       <c r="W56" s="36"/>
       <c r="X56" s="36"/>
@@ -14720,7 +14720,7 @@
         <v>579</v>
       </c>
       <c r="V58" s="36">
-        <v>548</v>
+        <v>769</v>
       </c>
       <c r="W58" s="36"/>
       <c r="X58" s="36"/>
@@ -14788,7 +14788,7 @@
         <v>331118</v>
       </c>
       <c r="V59" s="36">
-        <v>319550</v>
+        <v>318634</v>
       </c>
       <c r="W59" s="36"/>
       <c r="X59" s="36"/>
@@ -14856,7 +14856,7 @@
         <v>496795</v>
       </c>
       <c r="V60" s="36">
-        <v>495113</v>
+        <v>511208</v>
       </c>
       <c r="W60" s="36"/>
       <c r="X60" s="36"/>
@@ -14934,7 +14934,7 @@
         <v>27162334</v>
       </c>
       <c r="V63" s="33">
-        <v>34646799</v>
+        <v>30661564</v>
       </c>
       <c r="W63" s="33"/>
       <c r="X63" s="33"/>
@@ -15002,7 +15002,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
       <c r="V64" s="46">
-        <v>2.4199999999999999E-2</v>
+        <v>1.9900000000000001E-2</v>
       </c>
       <c r="W64" s="33"/>
       <c r="X64" s="33"/>
@@ -15127,7 +15127,7 @@
         <v>1593519594</v>
       </c>
       <c r="V68" s="33">
-        <v>1432368194</v>
+        <v>1539133543</v>
       </c>
       <c r="W68" s="33">
         <f>IFERROR(SUM('📅 DAILY T8'!C$6:C$36)+SUM('📅 DAILY T8'!G$6:I$36),0)</f>
@@ -15139,7 +15139,7 @@
       </c>
     </row>
     <row r="69" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="136"/>
+      <c r="A69" s="138"/>
       <c r="B69" s="137"/>
       <c r="C69" s="137"/>
       <c r="D69" s="137"/>
@@ -15162,7 +15162,7 @@
       <c r="U69" s="137"/>
       <c r="V69" s="137"/>
       <c r="W69" s="137"/>
-      <c r="X69" s="138"/>
+      <c r="X69" s="139"/>
     </row>
     <row r="70" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="50"/>
@@ -15227,7 +15227,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="V70" s="39">
-        <v>1.1399999999999999</v>
+        <v>2.12</v>
       </c>
       <c r="W70" s="39"/>
       <c r="X70" s="39"/>
@@ -15295,7 +15295,7 @@
         <v>19281</v>
       </c>
       <c r="V71" s="36">
-        <v>18356</v>
+        <v>19676</v>
       </c>
       <c r="W71" s="36"/>
       <c r="X71" s="36"/>
@@ -15363,7 +15363,7 @@
         <v>984</v>
       </c>
       <c r="V72" s="36">
-        <v>1320</v>
+        <v>1316</v>
       </c>
       <c r="W72" s="36"/>
       <c r="X72" s="36"/>
@@ -15527,7 +15527,7 @@
         <v>1014219</v>
       </c>
       <c r="V75" s="36">
-        <v>1021853</v>
+        <v>976666</v>
       </c>
       <c r="W75" s="36"/>
       <c r="X75" s="36"/>
@@ -15595,7 +15595,7 @@
         <v>647229</v>
       </c>
       <c r="V76" s="36">
-        <v>651168</v>
+        <v>564021</v>
       </c>
       <c r="W76" s="36"/>
       <c r="X76" s="36"/>
@@ -15663,7 +15663,7 @@
         <v>804514</v>
       </c>
       <c r="V77" s="36">
-        <v>804884</v>
+        <v>964719</v>
       </c>
       <c r="W77" s="36"/>
       <c r="X77" s="36"/>
@@ -15731,7 +15731,7 @@
         <v>496795</v>
       </c>
       <c r="V78" s="36">
-        <v>495113</v>
+        <v>511208</v>
       </c>
       <c r="W78" s="36"/>
       <c r="X78" s="36"/>
@@ -15814,7 +15814,7 @@
       <c r="U81" s="137"/>
       <c r="V81" s="137"/>
       <c r="W81" s="137"/>
-      <c r="X81" s="138"/>
+      <c r="X81" s="139"/>
     </row>
     <row r="82" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="55"/>
@@ -16065,6 +16065,7 @@
   </sheetData>
   <mergeCells count="17">
     <mergeCell ref="A1:X1"/>
+    <mergeCell ref="A5:X5"/>
     <mergeCell ref="A13:X13"/>
     <mergeCell ref="A14:X14"/>
     <mergeCell ref="A74:X74"/>
@@ -16073,9 +16074,8 @@
     <mergeCell ref="A41:X41"/>
     <mergeCell ref="A19:X19"/>
     <mergeCell ref="A33:X33"/>
-    <mergeCell ref="A5:X5"/>
+    <mergeCell ref="A34:X34"/>
     <mergeCell ref="A69:X69"/>
-    <mergeCell ref="A34:X34"/>
     <mergeCell ref="A29:X29"/>
     <mergeCell ref="A4:X4"/>
     <mergeCell ref="A81:X81"/>
@@ -18323,7 +18323,7 @@
     </row>
     <row r="22" spans="1:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="23" spans="1:20" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="160" t="s">
+      <c r="A23" s="162" t="s">
         <v>413</v>
       </c>
       <c r="B23" s="137"/>
@@ -18346,7 +18346,7 @@
     </row>
     <row r="24" spans="1:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="25" spans="1:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="159" t="s">
+      <c r="A25" s="161" t="s">
         <v>414</v>
       </c>
       <c r="B25" s="137"/>
@@ -18363,7 +18363,7 @@
     </row>
     <row r="26" spans="1:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="27" spans="1:20" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="161" t="s">
+      <c r="A27" s="159" t="s">
         <v>415</v>
       </c>
       <c r="B27" s="137"/>
@@ -18376,7 +18376,7 @@
       <c r="I27" s="137"/>
       <c r="J27" s="137"/>
       <c r="K27" s="137"/>
-      <c r="L27" s="162"/>
+      <c r="L27" s="160"/>
       <c r="M27" s="105"/>
       <c r="N27" s="105"/>
       <c r="O27" s="105"/>
@@ -18609,7 +18609,7 @@
       <c r="T34" s="110"/>
     </row>
     <row r="35" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="161" t="s">
+      <c r="A35" s="159" t="s">
         <v>439</v>
       </c>
       <c r="B35" s="137"/>
@@ -18622,7 +18622,7 @@
       <c r="I35" s="137"/>
       <c r="J35" s="137"/>
       <c r="K35" s="137"/>
-      <c r="L35" s="162"/>
+      <c r="L35" s="160"/>
       <c r="M35" s="110"/>
       <c r="N35" s="110"/>
       <c r="O35" s="110"/>
@@ -18898,11 +18898,11 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A35:L35"/>
+    <mergeCell ref="A27:L27"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A25:L25"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A27:L27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -20448,31 +20448,43 @@
       <c r="B32" s="74" t="s">
         <v>385</v>
       </c>
-      <c r="C32" s="75"/>
-      <c r="D32" s="75"/>
+      <c r="C32" s="75">
+        <v>47494789</v>
+      </c>
+      <c r="D32" s="75">
+        <v>103</v>
+      </c>
       <c r="E32" s="75"/>
       <c r="F32" s="75"/>
-      <c r="G32" s="75"/>
-      <c r="H32" s="75"/>
-      <c r="I32" s="75"/>
-      <c r="J32" s="75"/>
+      <c r="G32" s="75">
+        <v>6449508</v>
+      </c>
+      <c r="H32" s="75">
+        <v>2398499</v>
+      </c>
+      <c r="I32" s="75">
+        <v>1480003</v>
+      </c>
+      <c r="J32" s="75">
+        <v>39</v>
+      </c>
       <c r="K32" s="75"/>
       <c r="L32" s="76"/>
-      <c r="M32" s="33" t="str">
+      <c r="M32" s="33">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N32" s="33" t="str">
+        <v>10328010</v>
+      </c>
+      <c r="N32" s="33">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O32" s="33" t="str">
+        <v>57822799</v>
+      </c>
+      <c r="O32" s="33">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="P32" s="33" t="str">
+        <v>461114.45631067961</v>
+      </c>
+      <c r="P32" s="33">
         <f t="shared" si="3"/>
-        <v/>
+        <v>264820.76923076925</v>
       </c>
       <c r="Q32" s="46" t="str">
         <f t="shared" si="4"/>
@@ -20486,31 +20498,45 @@
       <c r="B33" s="74" t="s">
         <v>386</v>
       </c>
-      <c r="C33" s="75"/>
-      <c r="D33" s="75"/>
+      <c r="C33" s="75">
+        <v>32497544</v>
+      </c>
+      <c r="D33" s="75">
+        <v>78</v>
+      </c>
       <c r="E33" s="75"/>
       <c r="F33" s="75"/>
-      <c r="G33" s="75"/>
-      <c r="H33" s="75"/>
-      <c r="I33" s="75"/>
-      <c r="J33" s="75"/>
-      <c r="K33" s="75"/>
+      <c r="G33" s="75">
+        <v>6307506</v>
+      </c>
+      <c r="H33" s="75">
+        <v>3873501</v>
+      </c>
+      <c r="I33" s="75">
+        <v>6263999</v>
+      </c>
+      <c r="J33" s="75">
+        <v>50</v>
+      </c>
+      <c r="K33" s="75">
+        <v>774073</v>
+      </c>
       <c r="L33" s="76"/>
-      <c r="M33" s="33" t="str">
+      <c r="M33" s="33">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N33" s="33" t="str">
+        <v>16445006</v>
+      </c>
+      <c r="N33" s="33">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O33" s="33" t="str">
+        <v>48942550</v>
+      </c>
+      <c r="O33" s="33">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="P33" s="33" t="str">
+        <v>416635.1794871795</v>
+      </c>
+      <c r="P33" s="33">
         <f t="shared" si="3"/>
-        <v/>
+        <v>328900.12</v>
       </c>
       <c r="Q33" s="46" t="str">
         <f t="shared" si="4"/>
@@ -21091,15 +21117,15 @@
       </c>
       <c r="C8" s="81">
         <f>IFERROR(SUM('📅 DAILY T7'!C32:C36),0)</f>
-        <v>0</v>
+        <v>79992333</v>
       </c>
       <c r="D8" s="81">
         <f>IFERROR(SUM('📅 DAILY T7'!D32:D36),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E8" s="81" t="str">
+        <v>181</v>
+      </c>
+      <c r="E8" s="81">
         <f>IFERROR(SUM('📅 DAILY T7'!C32:C36)/SUM('📅 DAILY T7'!D32:D36),"")</f>
-        <v/>
+        <v>441946.59116022097</v>
       </c>
       <c r="F8" s="82">
         <f>IFERROR(SUM('📅 DAILY T7'!F32:F36),0)</f>
@@ -21111,19 +21137,19 @@
       </c>
       <c r="H8" s="84">
         <f>IFERROR(SUM('📅 DAILY T7'!M32:M36),0)</f>
-        <v>0</v>
+        <v>26773016</v>
       </c>
       <c r="I8" s="85">
         <f>IFERROR(SUM('📅 DAILY T7'!N32:N36),0)</f>
-        <v>0</v>
+        <v>106765349</v>
       </c>
       <c r="J8" s="86">
         <f>IFERROR(SUM('📅 DAILY T7'!C6:C36)/1277560078,"")</f>
-        <v>0.76776548429372571</v>
+        <v>0.83037884735781486</v>
       </c>
       <c r="K8" s="86">
         <f>IFERROR(SUM('📅 DAILY T7'!M6:M36)/721910506,"")</f>
-        <v>0.62542608570929981</v>
+        <v>0.66251242228077512</v>
       </c>
       <c r="L8" s="87"/>
     </row>
@@ -21172,15 +21198,15 @@
       </c>
       <c r="C21" s="99">
         <f>IFERROR(SUM('📅 DAILY T7'!C6:C36),0)</f>
-        <v>980866532</v>
+        <v>1060858865</v>
       </c>
       <c r="D21" s="99">
         <f>IFERROR(SUM('📅 DAILY T7'!D6:D36),0)</f>
-        <v>2343</v>
+        <v>2524</v>
       </c>
       <c r="E21" s="99">
         <f>IFERROR(SUM('📅 DAILY T7'!C6:C36)/SUM('📅 DAILY T7'!D6:D36),"")</f>
-        <v>418637.01749893301</v>
+        <v>420308.58359746437</v>
       </c>
       <c r="F21" s="99">
         <f>IFERROR(SUM('📅 DAILY T7'!F6:F36),0)</f>
@@ -21192,25 +21218,25 @@
       </c>
       <c r="H21" s="99">
         <f>IFERROR(SUM('📅 DAILY T7'!M6:M36),0)</f>
-        <v>451501662</v>
+        <v>478274678</v>
       </c>
       <c r="I21" s="99">
         <f>IFERROR(SUM('📅 DAILY T7'!N6:N36),0)</f>
-        <v>1432368194</v>
+        <v>1539133543</v>
       </c>
       <c r="J21" s="101">
         <f>IFERROR(SUM('📅 DAILY T7'!C6:C36)/1277560078,"")</f>
-        <v>0.76776548429372571</v>
+        <v>0.83037884735781486</v>
       </c>
       <c r="K21" s="101">
         <f>IFERROR(SUM('📅 DAILY T7'!M6:M36)/721910506,"")</f>
-        <v>0.62542608570929981</v>
+        <v>0.66251242228077512</v>
       </c>
       <c r="L21" s="96"/>
     </row>
     <row r="22" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="23" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="160" t="s">
+      <c r="A23" s="162" t="s">
         <v>413</v>
       </c>
       <c r="B23" s="137"/>
@@ -21233,7 +21259,7 @@
     </row>
     <row r="24" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="25" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="159" t="s">
+      <c r="A25" s="161" t="s">
         <v>414</v>
       </c>
       <c r="B25" s="137"/>
@@ -23423,7 +23449,7 @@
     </row>
     <row r="23" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="24" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="160" t="s">
+      <c r="A24" s="162" t="s">
         <v>413</v>
       </c>
       <c r="B24" s="137"/>
@@ -23446,7 +23472,7 @@
     </row>
     <row r="25" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="26" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="159" t="s">
+      <c r="A26" s="161" t="s">
         <v>414</v>
       </c>
       <c r="B26" s="137"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macos/REPORT FB&amp;STORE/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D312025F-A105-BA4A-8D98-FD5D6B8BF88B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2596E68D-938F-D445-BE85-1E28EA0905A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="80" yWindow="580" windowWidth="25520" windowHeight="16060" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="📖 ĐỊNH NGHĨA CHỈ SỐ" sheetId="1" r:id="rId1"/>
@@ -2884,12 +2884,12 @@
     <xf numFmtId="16" fontId="14" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2904,11 +2904,11 @@
     <xf numFmtId="0" fontId="3" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2941,16 +2941,16 @@
     <xf numFmtId="0" fontId="19" fillId="19" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="36" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -4896,7 +4896,7 @@
     </row>
     <row r="22" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="23" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="162" t="s">
+      <c r="A23" s="160" t="s">
         <v>413</v>
       </c>
       <c r="B23" s="137"/>
@@ -4919,7 +4919,7 @@
     </row>
     <row r="24" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="25" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="161" t="s">
+      <c r="A25" s="159" t="s">
         <v>414</v>
       </c>
       <c r="B25" s="137"/>
@@ -8364,40 +8364,40 @@
         <v>538</v>
       </c>
       <c r="C77" s="128">
-        <v>665</v>
+        <v>766</v>
       </c>
       <c r="D77" s="129">
-        <v>259</v>
+        <v>300</v>
       </c>
       <c r="E77" s="129">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="F77" s="129">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="G77" s="129">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H77" s="129">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="I77" s="129">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="J77" s="129">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K77" s="131">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L77" s="131">
-        <v>194</v>
+        <v>221</v>
       </c>
       <c r="M77" s="131">
         <v>9</v>
       </c>
       <c r="N77" s="131">
-        <v>308</v>
+        <v>357</v>
       </c>
     </row>
     <row r="78" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -8408,22 +8408,22 @@
         <v>539</v>
       </c>
       <c r="C78" s="128">
-        <v>1037</v>
+        <v>1154</v>
       </c>
       <c r="D78" s="129">
-        <v>788</v>
+        <v>873</v>
       </c>
       <c r="E78" s="129">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="F78" s="129">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="G78" s="129">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H78" s="129">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I78" s="129">
         <v>2</v>
@@ -8432,16 +8432,16 @@
         <v>0</v>
       </c>
       <c r="K78" s="131">
-        <v>189</v>
+        <v>216</v>
       </c>
       <c r="L78" s="131">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="M78" s="131">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="N78" s="131">
-        <v>131</v>
+        <v>150</v>
       </c>
     </row>
     <row r="79" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8452,22 +8452,22 @@
         <v>540</v>
       </c>
       <c r="C79" s="128">
-        <v>665</v>
+        <v>735</v>
       </c>
       <c r="D79" s="129">
-        <v>537</v>
+        <v>592</v>
       </c>
       <c r="E79" s="129">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="F79" s="129">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G79" s="129">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H79" s="129">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I79" s="130">
         <v>0</v>
@@ -8476,16 +8476,16 @@
         <v>0</v>
       </c>
       <c r="K79" s="131">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="L79" s="131">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="M79" s="131">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="N79" s="131">
-        <v>112</v>
+        <v>131</v>
       </c>
     </row>
     <row r="80" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -11194,40 +11194,40 @@
         <v>538</v>
       </c>
       <c r="C154" s="128">
-        <v>659</v>
+        <v>740</v>
       </c>
       <c r="D154" s="129">
-        <v>380</v>
+        <v>415</v>
       </c>
       <c r="E154" s="129">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="F154" s="129">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="G154" s="129">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H154" s="129">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="I154" s="129">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J154" s="129">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K154" s="131">
         <v>13</v>
       </c>
       <c r="L154" s="131">
-        <v>229</v>
+        <v>263</v>
       </c>
       <c r="M154" s="131">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N154" s="131">
-        <v>245</v>
+        <v>278</v>
       </c>
     </row>
     <row r="155" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -11238,16 +11238,16 @@
         <v>539</v>
       </c>
       <c r="C155" s="128">
-        <v>534</v>
+        <v>581</v>
       </c>
       <c r="D155" s="129">
-        <v>463</v>
+        <v>505</v>
       </c>
       <c r="E155" s="129">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F155" s="129">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G155" s="129">
         <v>3</v>
@@ -11262,16 +11262,16 @@
         <v>0</v>
       </c>
       <c r="K155" s="131">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="L155" s="131">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="M155" s="131">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="N155" s="131">
-        <v>99</v>
+        <v>109</v>
       </c>
     </row>
     <row r="156" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -11282,22 +11282,22 @@
         <v>540</v>
       </c>
       <c r="C156" s="128">
-        <v>263</v>
+        <v>281</v>
       </c>
       <c r="D156" s="129">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="E156" s="129">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F156" s="129">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G156" s="130">
         <v>2</v>
       </c>
       <c r="H156" s="129">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I156" s="130">
         <v>0</v>
@@ -11306,16 +11306,16 @@
         <v>0</v>
       </c>
       <c r="K156" s="131">
+        <v>61</v>
+      </c>
+      <c r="L156" s="131">
+        <v>30</v>
+      </c>
+      <c r="M156" s="131">
         <v>58</v>
       </c>
-      <c r="L156" s="131">
-        <v>26</v>
-      </c>
-      <c r="M156" s="131">
+      <c r="N156" s="131">
         <v>55</v>
-      </c>
-      <c r="N156" s="131">
-        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -11347,7 +11347,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="146" t="s">
+      <c r="A1" s="147" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="137"/>
@@ -11505,7 +11505,7 @@
       <c r="X4" s="137"/>
     </row>
     <row r="5" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="147" t="s">
+      <c r="A5" s="146" t="s">
         <v>27</v>
       </c>
       <c r="B5" s="137"/>
@@ -11595,7 +11595,7 @@
         <v>1088741202</v>
       </c>
       <c r="V6" s="33">
-        <v>1060858865</v>
+        <v>1192707123</v>
       </c>
       <c r="W6" s="33">
         <f>IFERROR(SUM('📅 DAILY T8'!C$6:C$36),0)</f>
@@ -11669,7 +11669,7 @@
         <v>2471</v>
       </c>
       <c r="V7" s="33">
-        <v>2432</v>
+        <v>2726</v>
       </c>
       <c r="W7" s="33">
         <f>IFERROR(SUM('📅 DAILY T8'!D$6:D$36),0)</f>
@@ -11743,7 +11743,7 @@
         <v>440607</v>
       </c>
       <c r="V8" s="33">
-        <v>436208</v>
+        <v>437530</v>
       </c>
       <c r="W8" s="33" t="str">
         <f>IFERROR(SUM('📅 DAILY T8'!C$6:C$36)/SUM('📅 DAILY T8'!D$6:D$36),"")</f>
@@ -11817,7 +11817,7 @@
         <v>5789</v>
       </c>
       <c r="V9" s="36">
-        <v>4554</v>
+        <v>5129</v>
       </c>
       <c r="W9" s="36"/>
       <c r="X9" s="36"/>
@@ -11932,7 +11932,7 @@
       </c>
       <c r="V11" s="37">
         <f t="shared" si="0"/>
-        <v>0.53403601229688191</v>
+        <v>0.53148761941899003</v>
       </c>
       <c r="W11" s="38"/>
       <c r="X11" s="38"/>
@@ -11966,7 +11966,7 @@
       <c r="X12" s="39"/>
     </row>
     <row r="13" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="147" t="s">
+      <c r="A13" s="146" t="s">
         <v>39</v>
       </c>
       <c r="B13" s="137"/>
@@ -12084,7 +12084,7 @@
         <v>676</v>
       </c>
       <c r="V15" s="36">
-        <v>733</v>
+        <v>824</v>
       </c>
       <c r="W15" s="36"/>
       <c r="X15" s="36"/>
@@ -12152,7 +12152,7 @@
         <v>410341</v>
       </c>
       <c r="V16" s="36">
-        <v>395297</v>
+        <v>393944</v>
       </c>
       <c r="W16" s="36"/>
       <c r="X16" s="36"/>
@@ -12288,7 +12288,7 @@
         <v>8.1900000000000001E-2</v>
       </c>
       <c r="V18" s="38">
-        <v>8.8800000000000004E-2</v>
+        <v>0.1021</v>
       </c>
       <c r="W18" s="38"/>
       <c r="X18" s="38"/>
@@ -12384,7 +12384,7 @@
         <v>1584</v>
       </c>
       <c r="V20" s="36">
-        <v>1573</v>
+        <v>1739</v>
       </c>
       <c r="W20" s="36"/>
       <c r="X20" s="36"/>
@@ -12452,7 +12452,7 @@
         <v>438668</v>
       </c>
       <c r="V21" s="36">
-        <v>454451</v>
+        <v>457245</v>
       </c>
       <c r="W21" s="36"/>
       <c r="X21" s="36"/>
@@ -12520,7 +12520,7 @@
         <v>0.70089999999999997</v>
       </c>
       <c r="V22" s="38">
-        <v>0.68210000000000004</v>
+        <v>0.67849999999999999</v>
       </c>
       <c r="W22" s="38"/>
       <c r="X22" s="38"/>
@@ -12588,7 +12588,7 @@
         <v>395</v>
       </c>
       <c r="V23" s="36">
-        <v>417</v>
+        <v>458</v>
       </c>
       <c r="W23" s="36"/>
       <c r="X23" s="36"/>
@@ -12656,7 +12656,7 @@
         <v>427919</v>
       </c>
       <c r="V24" s="36">
-        <v>410757</v>
+        <v>410866</v>
       </c>
       <c r="W24" s="36"/>
       <c r="X24" s="36"/>
@@ -12724,7 +12724,7 @@
         <v>491</v>
       </c>
       <c r="V25" s="36">
-        <v>467</v>
+        <v>520</v>
       </c>
       <c r="W25" s="36"/>
       <c r="X25" s="36"/>
@@ -12792,7 +12792,7 @@
         <v>450680</v>
       </c>
       <c r="V26" s="36">
-        <v>465513</v>
+        <v>472067</v>
       </c>
       <c r="W26" s="36"/>
       <c r="X26" s="36"/>
@@ -12860,7 +12860,7 @@
         <v>698</v>
       </c>
       <c r="V27" s="36">
-        <v>689</v>
+        <v>761</v>
       </c>
       <c r="W27" s="36"/>
       <c r="X27" s="36"/>
@@ -12928,7 +12928,7 @@
         <v>436911</v>
       </c>
       <c r="V28" s="36">
-        <v>474970</v>
+        <v>476924</v>
       </c>
       <c r="W28" s="36"/>
       <c r="X28" s="36"/>
@@ -13024,7 +13024,7 @@
         <v>1258</v>
       </c>
       <c r="V30" s="36">
-        <v>1612</v>
+        <v>1788</v>
       </c>
       <c r="W30" s="36"/>
       <c r="X30" s="36"/>
@@ -13092,7 +13092,7 @@
         <v>443642</v>
       </c>
       <c r="V31" s="36">
-        <v>450270</v>
+        <v>452381</v>
       </c>
       <c r="W31" s="36"/>
       <c r="X31" s="36"/>
@@ -13160,7 +13160,7 @@
         <v>804514</v>
       </c>
       <c r="V32" s="36">
-        <v>964719</v>
+        <v>988687</v>
       </c>
       <c r="W32" s="36"/>
       <c r="X32" s="36"/>
@@ -13194,7 +13194,7 @@
       <c r="X33" s="137"/>
     </row>
     <row r="34" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="136" t="s">
+      <c r="A34" s="139" t="s">
         <v>60</v>
       </c>
       <c r="B34" s="137"/>
@@ -13284,7 +13284,7 @@
         <v>504778392</v>
       </c>
       <c r="V35" s="33">
-        <v>478274678</v>
+        <v>530083436</v>
       </c>
       <c r="W35" s="33">
         <f>IFERROR(SUM('📅 DAILY T8'!G$6:I$36),0)</f>
@@ -13358,7 +13358,7 @@
         <v>255247175</v>
       </c>
       <c r="V36" s="33">
-        <v>241526587</v>
+        <v>272494091</v>
       </c>
       <c r="W36" s="33">
         <f>IFERROR(SUM('📅 DAILY T8'!G$6:G$36),0)</f>
@@ -13432,7 +13432,7 @@
         <v>125740056</v>
       </c>
       <c r="V37" s="33">
-        <v>120353091</v>
+        <v>129188093</v>
       </c>
       <c r="W37" s="33">
         <f>IFERROR(SUM('📅 DAILY T8'!H$6:H$36),0)</f>
@@ -13506,7 +13506,7 @@
         <v>123791161</v>
       </c>
       <c r="V38" s="33">
-        <v>116395000</v>
+        <v>128401252</v>
       </c>
       <c r="W38" s="33">
         <f>IFERROR(SUM('📅 DAILY T8'!I$6:I$36),0)</f>
@@ -13580,7 +13580,7 @@
         <v>1642</v>
       </c>
       <c r="V39" s="33">
-        <v>1504</v>
+        <v>1653</v>
       </c>
       <c r="W39" s="33">
         <f>IFERROR(SUM('📅 DAILY T8'!J$6:J$36),0)</f>
@@ -13654,7 +13654,7 @@
         <v>307417</v>
       </c>
       <c r="V40" s="33">
-        <v>318002</v>
+        <v>320680</v>
       </c>
       <c r="W40" s="33" t="str">
         <f>IFERROR(SUM('📅 DAILY T8'!M$6:M$36)/SUM('📅 DAILY T8'!J$6:J$36),"")</f>
@@ -13689,7 +13689,7 @@
       <c r="U41" s="137"/>
       <c r="V41" s="137"/>
       <c r="W41" s="137"/>
-      <c r="X41" s="139"/>
+      <c r="X41" s="138"/>
     </row>
     <row r="42" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="144"/>
@@ -13715,7 +13715,7 @@
       <c r="U42" s="137"/>
       <c r="V42" s="137"/>
       <c r="W42" s="137"/>
-      <c r="X42" s="139"/>
+      <c r="X42" s="138"/>
     </row>
     <row r="43" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="45"/>
@@ -13780,7 +13780,7 @@
         <v>576</v>
       </c>
       <c r="V43" s="36">
-        <v>556</v>
+        <v>613</v>
       </c>
       <c r="W43" s="36"/>
       <c r="X43" s="36"/>
@@ -13848,7 +13848,7 @@
         <v>345626</v>
       </c>
       <c r="V44" s="36">
-        <v>299551</v>
+        <v>301500</v>
       </c>
       <c r="W44" s="36"/>
       <c r="X44" s="36"/>
@@ -13984,7 +13984,7 @@
         <v>6.4399999999999999E-2</v>
       </c>
       <c r="V46" s="38">
-        <v>5.7299999999999997E-2</v>
+        <v>5.8999999999999997E-2</v>
       </c>
       <c r="W46" s="38"/>
       <c r="X46" s="38"/>
@@ -14080,7 +14080,7 @@
         <v>818</v>
       </c>
       <c r="V48" s="36">
-        <v>745</v>
+        <v>801</v>
       </c>
       <c r="W48" s="36"/>
       <c r="X48" s="36"/>
@@ -14148,7 +14148,7 @@
         <v>327838</v>
       </c>
       <c r="V49" s="36">
-        <v>334109</v>
+        <v>337816</v>
       </c>
       <c r="W49" s="36"/>
       <c r="X49" s="36"/>
@@ -14216,7 +14216,7 @@
         <v>0.58679999999999999</v>
       </c>
       <c r="V50" s="38">
-        <v>0.5726</v>
+        <v>0.5665</v>
       </c>
       <c r="W50" s="38"/>
       <c r="X50" s="38"/>
@@ -14284,7 +14284,7 @@
         <v>168</v>
       </c>
       <c r="V51" s="36">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="W51" s="36"/>
       <c r="X51" s="36"/>
@@ -14352,7 +14352,7 @@
         <v>306908</v>
       </c>
       <c r="V52" s="36">
-        <v>305722</v>
+        <v>314399</v>
       </c>
       <c r="W52" s="36"/>
       <c r="X52" s="36"/>
@@ -14420,7 +14420,7 @@
         <v>252</v>
       </c>
       <c r="V53" s="36">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="W53" s="36"/>
       <c r="X53" s="36"/>
@@ -14488,7 +14488,7 @@
         <v>329485</v>
       </c>
       <c r="V54" s="36">
-        <v>323838</v>
+        <v>330301</v>
       </c>
       <c r="W54" s="36"/>
       <c r="X54" s="36"/>
@@ -14556,7 +14556,7 @@
         <v>398</v>
       </c>
       <c r="V55" s="36">
-        <v>368</v>
+        <v>391</v>
       </c>
       <c r="W55" s="36"/>
       <c r="X55" s="36"/>
@@ -14624,7 +14624,7 @@
         <v>336422</v>
       </c>
       <c r="V56" s="36">
-        <v>354695</v>
+        <v>354566</v>
       </c>
       <c r="W56" s="36"/>
       <c r="X56" s="36"/>
@@ -14720,7 +14720,7 @@
         <v>579</v>
       </c>
       <c r="V58" s="36">
-        <v>769</v>
+        <v>832</v>
       </c>
       <c r="W58" s="36"/>
       <c r="X58" s="36"/>
@@ -14788,7 +14788,7 @@
         <v>331118</v>
       </c>
       <c r="V59" s="36">
-        <v>318634</v>
+        <v>320520</v>
       </c>
       <c r="W59" s="36"/>
       <c r="X59" s="36"/>
@@ -14856,7 +14856,7 @@
         <v>496795</v>
       </c>
       <c r="V60" s="36">
-        <v>511208</v>
+        <v>516026</v>
       </c>
       <c r="W60" s="36"/>
       <c r="X60" s="36"/>
@@ -14934,7 +14934,7 @@
         <v>27162334</v>
       </c>
       <c r="V63" s="33">
-        <v>30661564</v>
+        <v>35625949</v>
       </c>
       <c r="W63" s="33"/>
       <c r="X63" s="33"/>
@@ -15002,7 +15002,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
       <c r="V64" s="46">
-        <v>1.9900000000000001E-2</v>
+        <v>2.07E-2</v>
       </c>
       <c r="W64" s="33"/>
       <c r="X64" s="33"/>
@@ -15127,7 +15127,7 @@
         <v>1593519594</v>
       </c>
       <c r="V68" s="33">
-        <v>1539133543</v>
+        <v>1722790559</v>
       </c>
       <c r="W68" s="33">
         <f>IFERROR(SUM('📅 DAILY T8'!C$6:C$36)+SUM('📅 DAILY T8'!G$6:I$36),0)</f>
@@ -15139,7 +15139,7 @@
       </c>
     </row>
     <row r="69" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="138"/>
+      <c r="A69" s="136"/>
       <c r="B69" s="137"/>
       <c r="C69" s="137"/>
       <c r="D69" s="137"/>
@@ -15162,7 +15162,7 @@
       <c r="U69" s="137"/>
       <c r="V69" s="137"/>
       <c r="W69" s="137"/>
-      <c r="X69" s="139"/>
+      <c r="X69" s="138"/>
     </row>
     <row r="70" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="50"/>
@@ -15295,7 +15295,7 @@
         <v>19281</v>
       </c>
       <c r="V71" s="36">
-        <v>19676</v>
+        <v>19927</v>
       </c>
       <c r="W71" s="36"/>
       <c r="X71" s="36"/>
@@ -15363,7 +15363,7 @@
         <v>984</v>
       </c>
       <c r="V72" s="36">
-        <v>1316</v>
+        <v>1493</v>
       </c>
       <c r="W72" s="36"/>
       <c r="X72" s="36"/>
@@ -15527,7 +15527,7 @@
         <v>1014219</v>
       </c>
       <c r="V75" s="36">
-        <v>976666</v>
+        <v>990553</v>
       </c>
       <c r="W75" s="36"/>
       <c r="X75" s="36"/>
@@ -15595,7 +15595,7 @@
         <v>647229</v>
       </c>
       <c r="V76" s="36">
-        <v>564021</v>
+        <v>569362</v>
       </c>
       <c r="W76" s="36"/>
       <c r="X76" s="36"/>
@@ -15663,7 +15663,7 @@
         <v>804514</v>
       </c>
       <c r="V77" s="36">
-        <v>964719</v>
+        <v>988687</v>
       </c>
       <c r="W77" s="36"/>
       <c r="X77" s="36"/>
@@ -15731,7 +15731,7 @@
         <v>496795</v>
       </c>
       <c r="V78" s="36">
-        <v>511208</v>
+        <v>516026</v>
       </c>
       <c r="W78" s="36"/>
       <c r="X78" s="36"/>
@@ -15814,7 +15814,7 @@
       <c r="U81" s="137"/>
       <c r="V81" s="137"/>
       <c r="W81" s="137"/>
-      <c r="X81" s="139"/>
+      <c r="X81" s="138"/>
     </row>
     <row r="82" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="55"/>
@@ -16065,7 +16065,6 @@
   </sheetData>
   <mergeCells count="17">
     <mergeCell ref="A1:X1"/>
-    <mergeCell ref="A5:X5"/>
     <mergeCell ref="A13:X13"/>
     <mergeCell ref="A14:X14"/>
     <mergeCell ref="A74:X74"/>
@@ -16074,8 +16073,9 @@
     <mergeCell ref="A41:X41"/>
     <mergeCell ref="A19:X19"/>
     <mergeCell ref="A33:X33"/>
+    <mergeCell ref="A5:X5"/>
+    <mergeCell ref="A69:X69"/>
     <mergeCell ref="A34:X34"/>
-    <mergeCell ref="A69:X69"/>
     <mergeCell ref="A29:X29"/>
     <mergeCell ref="A4:X4"/>
     <mergeCell ref="A81:X81"/>
@@ -18323,7 +18323,7 @@
     </row>
     <row r="22" spans="1:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="23" spans="1:20" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="162" t="s">
+      <c r="A23" s="160" t="s">
         <v>413</v>
       </c>
       <c r="B23" s="137"/>
@@ -18346,7 +18346,7 @@
     </row>
     <row r="24" spans="1:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="25" spans="1:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="161" t="s">
+      <c r="A25" s="159" t="s">
         <v>414</v>
       </c>
       <c r="B25" s="137"/>
@@ -18363,7 +18363,7 @@
     </row>
     <row r="26" spans="1:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="27" spans="1:20" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="159" t="s">
+      <c r="A27" s="161" t="s">
         <v>415</v>
       </c>
       <c r="B27" s="137"/>
@@ -18376,7 +18376,7 @@
       <c r="I27" s="137"/>
       <c r="J27" s="137"/>
       <c r="K27" s="137"/>
-      <c r="L27" s="160"/>
+      <c r="L27" s="162"/>
       <c r="M27" s="105"/>
       <c r="N27" s="105"/>
       <c r="O27" s="105"/>
@@ -18609,7 +18609,7 @@
       <c r="T34" s="110"/>
     </row>
     <row r="35" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="159" t="s">
+      <c r="A35" s="161" t="s">
         <v>439</v>
       </c>
       <c r="B35" s="137"/>
@@ -18622,7 +18622,7 @@
       <c r="I35" s="137"/>
       <c r="J35" s="137"/>
       <c r="K35" s="137"/>
-      <c r="L35" s="160"/>
+      <c r="L35" s="162"/>
       <c r="M35" s="110"/>
       <c r="N35" s="110"/>
       <c r="O35" s="110"/>
@@ -18898,11 +18898,11 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A35:L35"/>
-    <mergeCell ref="A27:L27"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A25:L25"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A27:L27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -19265,10 +19265,10 @@
         <v>390</v>
       </c>
       <c r="C9" s="75">
-        <v>39025533</v>
+        <v>39340033</v>
       </c>
       <c r="D9" s="75">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E9" s="75"/>
       <c r="F9" s="75"/>
@@ -19294,11 +19294,11 @@
       </c>
       <c r="N9" s="33">
         <f t="shared" si="1"/>
-        <v>55453533</v>
+        <v>55768033</v>
       </c>
       <c r="O9" s="33">
         <f t="shared" si="2"/>
-        <v>406515.96875</v>
+        <v>405567.35051546391</v>
       </c>
       <c r="P9" s="33">
         <f t="shared" si="3"/>
@@ -20550,31 +20550,43 @@
       <c r="B34" s="74" t="s">
         <v>387</v>
       </c>
-      <c r="C34" s="75"/>
-      <c r="D34" s="75"/>
+      <c r="C34" s="75">
+        <v>28567538</v>
+      </c>
+      <c r="D34" s="75">
+        <v>75</v>
+      </c>
       <c r="E34" s="75"/>
       <c r="F34" s="75"/>
-      <c r="G34" s="75"/>
-      <c r="H34" s="75"/>
-      <c r="I34" s="75"/>
-      <c r="J34" s="75"/>
+      <c r="G34" s="75">
+        <v>12056503</v>
+      </c>
+      <c r="H34" s="75">
+        <v>1149000</v>
+      </c>
+      <c r="I34" s="75">
+        <v>2322503</v>
+      </c>
+      <c r="J34" s="75">
+        <v>46</v>
+      </c>
       <c r="K34" s="75"/>
       <c r="L34" s="76"/>
-      <c r="M34" s="33" t="str">
+      <c r="M34" s="33">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N34" s="33" t="str">
+        <v>15528006</v>
+      </c>
+      <c r="N34" s="33">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O34" s="33" t="str">
+        <v>44095544</v>
+      </c>
+      <c r="O34" s="33">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="P34" s="33" t="str">
+        <v>380900.50666666665</v>
+      </c>
+      <c r="P34" s="33">
         <f t="shared" si="3"/>
-        <v/>
+        <v>337565.34782608697</v>
       </c>
       <c r="Q34" s="46" t="str">
         <f t="shared" si="4"/>
@@ -20588,31 +20600,45 @@
       <c r="B35" s="74" t="s">
         <v>388</v>
       </c>
-      <c r="C35" s="75"/>
-      <c r="D35" s="75"/>
+      <c r="C35" s="75">
+        <v>48417154</v>
+      </c>
+      <c r="D35" s="75">
+        <v>113</v>
+      </c>
       <c r="E35" s="75"/>
       <c r="F35" s="75"/>
-      <c r="G35" s="75"/>
-      <c r="H35" s="75"/>
-      <c r="I35" s="75"/>
-      <c r="J35" s="75"/>
-      <c r="K35" s="75"/>
+      <c r="G35" s="75">
+        <v>7681005</v>
+      </c>
+      <c r="H35" s="75">
+        <v>3645499</v>
+      </c>
+      <c r="I35" s="75">
+        <v>4691997</v>
+      </c>
+      <c r="J35" s="75">
+        <v>52</v>
+      </c>
+      <c r="K35" s="75">
+        <v>1772000</v>
+      </c>
       <c r="L35" s="76"/>
-      <c r="M35" s="33" t="str">
+      <c r="M35" s="33">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N35" s="33" t="str">
+        <v>16018501</v>
+      </c>
+      <c r="N35" s="33">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O35" s="33" t="str">
+        <v>64435655</v>
+      </c>
+      <c r="O35" s="33">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="P35" s="33" t="str">
+        <v>428470.38938053098</v>
+      </c>
+      <c r="P35" s="33">
         <f t="shared" si="3"/>
-        <v/>
+        <v>308048.09615384613</v>
       </c>
       <c r="Q35" s="46" t="str">
         <f t="shared" si="4"/>
@@ -20626,31 +20652,45 @@
       <c r="B36" s="74" t="s">
         <v>389</v>
       </c>
-      <c r="C36" s="75"/>
-      <c r="D36" s="75"/>
+      <c r="C36" s="75">
+        <v>54549066</v>
+      </c>
+      <c r="D36" s="75">
+        <v>110</v>
+      </c>
       <c r="E36" s="75"/>
       <c r="F36" s="75"/>
-      <c r="G36" s="75"/>
-      <c r="H36" s="75"/>
-      <c r="I36" s="75"/>
-      <c r="J36" s="75"/>
-      <c r="K36" s="75"/>
+      <c r="G36" s="75">
+        <v>11229996</v>
+      </c>
+      <c r="H36" s="75">
+        <v>4040503</v>
+      </c>
+      <c r="I36" s="75">
+        <v>4991752</v>
+      </c>
+      <c r="J36" s="75">
+        <v>72</v>
+      </c>
+      <c r="K36" s="75">
+        <v>2971200</v>
+      </c>
       <c r="L36" s="76"/>
-      <c r="M36" s="33" t="str">
+      <c r="M36" s="33">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N36" s="33" t="str">
+        <v>20262251</v>
+      </c>
+      <c r="N36" s="33">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O36" s="33" t="str">
+        <v>74811317</v>
+      </c>
+      <c r="O36" s="33">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="P36" s="33" t="str">
+        <v>495900.6</v>
+      </c>
+      <c r="P36" s="33">
         <f t="shared" si="3"/>
-        <v/>
+        <v>281420.15277777775</v>
       </c>
       <c r="Q36" s="46" t="str">
         <f t="shared" si="4"/>
@@ -20937,15 +20977,15 @@
       </c>
       <c r="C4" s="81">
         <f>IFERROR(SUM('📅 DAILY T7'!C6:C10),0)</f>
-        <v>196045598</v>
+        <v>196360098</v>
       </c>
       <c r="D4" s="81">
         <f>IFERROR(SUM('📅 DAILY T7'!D6:D10),0)</f>
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E4" s="81">
         <f>IFERROR(SUM('📅 DAILY T7'!C6:C10)/SUM('📅 DAILY T7'!D6:D10),"")</f>
-        <v>421603.43655913981</v>
+        <v>421373.60085836909</v>
       </c>
       <c r="F4" s="82">
         <f>IFERROR(SUM('📅 DAILY T7'!F6:F10),0)</f>
@@ -20961,11 +21001,11 @@
       </c>
       <c r="I4" s="85">
         <f>IFERROR(SUM('📅 DAILY T7'!N6:N10),0)</f>
-        <v>285424642</v>
+        <v>285739142</v>
       </c>
       <c r="J4" s="86">
         <f>IFERROR(SUM('📅 DAILY T7'!C6:C10)/1277560078,"")</f>
-        <v>0.15345313412337233</v>
+        <v>0.15369930649946312</v>
       </c>
       <c r="K4" s="86">
         <f>IFERROR(SUM('📅 DAILY T7'!M6:M10)/721910506,"")</f>
@@ -21010,7 +21050,7 @@
       </c>
       <c r="J5" s="86">
         <f>IFERROR(SUM('📅 DAILY T7'!C6:C17)/1277560078,"")</f>
-        <v>0.35007610499237907</v>
+        <v>0.35032227736846988</v>
       </c>
       <c r="K5" s="86">
         <f>IFERROR(SUM('📅 DAILY T7'!M6:M17)/721910506,"")</f>
@@ -21055,7 +21095,7 @@
       </c>
       <c r="J6" s="86">
         <f>IFERROR(SUM('📅 DAILY T7'!C6:C24)/1277560078,"")</f>
-        <v>0.55837609384033993</v>
+        <v>0.55862226621643074</v>
       </c>
       <c r="K6" s="86">
         <f>IFERROR(SUM('📅 DAILY T7'!M6:M24)/721910506,"")</f>
@@ -21100,7 +21140,7 @@
       </c>
       <c r="J7" s="86">
         <f>IFERROR(SUM('📅 DAILY T7'!C6:C31)/1277560078,"")</f>
-        <v>0.76776548429372571</v>
+        <v>0.76801165666981652</v>
       </c>
       <c r="K7" s="86">
         <f>IFERROR(SUM('📅 DAILY T7'!M6:M31)/721910506,"")</f>
@@ -21117,15 +21157,15 @@
       </c>
       <c r="C8" s="81">
         <f>IFERROR(SUM('📅 DAILY T7'!C32:C36),0)</f>
-        <v>79992333</v>
+        <v>211526091</v>
       </c>
       <c r="D8" s="81">
         <f>IFERROR(SUM('📅 DAILY T7'!D32:D36),0)</f>
-        <v>181</v>
+        <v>479</v>
       </c>
       <c r="E8" s="81">
         <f>IFERROR(SUM('📅 DAILY T7'!C32:C36)/SUM('📅 DAILY T7'!D32:D36),"")</f>
-        <v>441946.59116022097</v>
+        <v>441599.35490605427</v>
       </c>
       <c r="F8" s="82">
         <f>IFERROR(SUM('📅 DAILY T7'!F32:F36),0)</f>
@@ -21137,19 +21177,19 @@
       </c>
       <c r="H8" s="84">
         <f>IFERROR(SUM('📅 DAILY T7'!M32:M36),0)</f>
-        <v>26773016</v>
+        <v>78581774</v>
       </c>
       <c r="I8" s="85">
         <f>IFERROR(SUM('📅 DAILY T7'!N32:N36),0)</f>
-        <v>106765349</v>
+        <v>290107865</v>
       </c>
       <c r="J8" s="86">
         <f>IFERROR(SUM('📅 DAILY T7'!C6:C36)/1277560078,"")</f>
-        <v>0.83037884735781486</v>
+        <v>0.93358202368624732</v>
       </c>
       <c r="K8" s="86">
         <f>IFERROR(SUM('📅 DAILY T7'!M6:M36)/721910506,"")</f>
-        <v>0.66251242228077512</v>
+        <v>0.73427860045577453</v>
       </c>
       <c r="L8" s="87"/>
     </row>
@@ -21198,15 +21238,15 @@
       </c>
       <c r="C21" s="99">
         <f>IFERROR(SUM('📅 DAILY T7'!C6:C36),0)</f>
-        <v>1060858865</v>
+        <v>1192707123</v>
       </c>
       <c r="D21" s="99">
         <f>IFERROR(SUM('📅 DAILY T7'!D6:D36),0)</f>
-        <v>2524</v>
+        <v>2823</v>
       </c>
       <c r="E21" s="99">
         <f>IFERROR(SUM('📅 DAILY T7'!C6:C36)/SUM('📅 DAILY T7'!D6:D36),"")</f>
-        <v>420308.58359746437</v>
+        <v>422496.32412327314</v>
       </c>
       <c r="F21" s="99">
         <f>IFERROR(SUM('📅 DAILY T7'!F6:F36),0)</f>
@@ -21218,25 +21258,25 @@
       </c>
       <c r="H21" s="99">
         <f>IFERROR(SUM('📅 DAILY T7'!M6:M36),0)</f>
-        <v>478274678</v>
+        <v>530083436</v>
       </c>
       <c r="I21" s="99">
         <f>IFERROR(SUM('📅 DAILY T7'!N6:N36),0)</f>
-        <v>1539133543</v>
+        <v>1722790559</v>
       </c>
       <c r="J21" s="101">
         <f>IFERROR(SUM('📅 DAILY T7'!C6:C36)/1277560078,"")</f>
-        <v>0.83037884735781486</v>
+        <v>0.93358202368624732</v>
       </c>
       <c r="K21" s="101">
         <f>IFERROR(SUM('📅 DAILY T7'!M6:M36)/721910506,"")</f>
-        <v>0.66251242228077512</v>
+        <v>0.73427860045577453</v>
       </c>
       <c r="L21" s="96"/>
     </row>
     <row r="22" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="23" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="162" t="s">
+      <c r="A23" s="160" t="s">
         <v>413</v>
       </c>
       <c r="B23" s="137"/>
@@ -21259,7 +21299,7 @@
     </row>
     <row r="24" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="25" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="161" t="s">
+      <c r="A25" s="159" t="s">
         <v>414</v>
       </c>
       <c r="B25" s="137"/>
@@ -23449,7 +23489,7 @@
     </row>
     <row r="23" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="24" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="162" t="s">
+      <c r="A24" s="160" t="s">
         <v>413</v>
       </c>
       <c r="B24" s="137"/>
@@ -23472,7 +23512,7 @@
     </row>
     <row r="25" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="26" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="161" t="s">
+      <c r="A26" s="159" t="s">
         <v>414</v>
       </c>
       <c r="B26" s="137"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -14048,7 +14048,7 @@
         <v>2891501</v>
       </c>
       <c r="J7" s="74" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K7" s="74" t="n"/>
       <c r="L7" s="75" t="n"/>
@@ -14100,7 +14100,7 @@
         <v>3587501</v>
       </c>
       <c r="J8" s="74" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K8" s="74" t="n">
         <v>2150459</v>
@@ -14154,7 +14154,7 @@
         <v>2450001</v>
       </c>
       <c r="J9" s="74" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K9" s="74" t="n">
         <v>601852</v>
@@ -14370,7 +14370,7 @@
         <v>4499002</v>
       </c>
       <c r="J13" s="74" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K13" s="74" t="n">
         <v>1888518</v>
@@ -14460,17 +14460,25 @@
           <t>T2</t>
         </is>
       </c>
-      <c r="C15" s="74" t="n"/>
-      <c r="D15" s="74" t="n"/>
+      <c r="C15" s="74" t="n">
+        <v>38639566</v>
+      </c>
+      <c r="D15" s="74" t="n">
+        <v>93</v>
+      </c>
       <c r="E15" s="74" t="n"/>
       <c r="F15" s="74" t="n"/>
       <c r="G15" s="74" t="n">
-        <v>737000</v>
-      </c>
-      <c r="H15" s="74" t="n"/>
-      <c r="I15" s="74" t="n"/>
+        <v>6749999</v>
+      </c>
+      <c r="H15" s="74" t="n">
+        <v>3985503</v>
+      </c>
+      <c r="I15" s="74" t="n">
+        <v>1597251</v>
+      </c>
       <c r="J15" s="74" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="K15" s="74" t="n"/>
       <c r="L15" s="75" t="n"/>
@@ -18621,7 +18629,7 @@
         <v>1192707123</v>
       </c>
       <c r="W6" s="33" t="n">
-        <v>327143980</v>
+        <v>365783546</v>
       </c>
       <c r="X6" s="33">
         <f>IFERROR(SUM('📅 DAILY T9'!C$6:C$35),0)</f>
@@ -18698,7 +18706,7 @@
         <v>2823</v>
       </c>
       <c r="W7" s="33" t="n">
-        <v>797</v>
+        <v>890</v>
       </c>
       <c r="X7" s="33">
         <f>IFERROR(SUM('📅 DAILY T9'!D$6:D$35),0)</f>
@@ -18775,7 +18783,7 @@
         <v>422496</v>
       </c>
       <c r="W8" s="33" t="n">
-        <v>410469</v>
+        <v>410993</v>
       </c>
       <c r="X8" s="33">
         <f>IFERROR(SUM('📅 DAILY T9'!C$6:C$35)/SUM('📅 DAILY T9'!D$6:D$35),"")</f>
@@ -19140,7 +19148,7 @@
         <v>824</v>
       </c>
       <c r="W15" s="36" t="n">
-        <v>238</v>
+        <v>259</v>
       </c>
       <c r="X15" s="36" t="n"/>
     </row>
@@ -19214,7 +19222,7 @@
         <v>393944</v>
       </c>
       <c r="W16" s="36" t="n">
-        <v>387026</v>
+        <v>386245</v>
       </c>
       <c r="X16" s="36" t="n"/>
     </row>
@@ -19288,7 +19296,7 @@
         <v>0.1394</v>
       </c>
       <c r="W17" s="38" t="n">
-        <v>0.1442</v>
+        <v>0.1472</v>
       </c>
       <c r="X17" s="38" t="n"/>
     </row>
@@ -19362,7 +19370,7 @@
         <v>0.1021</v>
       </c>
       <c r="W18" s="38" t="n">
-        <v>0.0212</v>
+        <v>0.0288</v>
       </c>
       <c r="X18" s="38" t="n"/>
     </row>
@@ -19466,7 +19474,7 @@
         <v>1739</v>
       </c>
       <c r="W20" s="36" t="n">
-        <v>534</v>
+        <v>597</v>
       </c>
       <c r="X20" s="36" t="n"/>
     </row>
@@ -19540,7 +19548,7 @@
         <v>457245</v>
       </c>
       <c r="W21" s="36" t="n">
-        <v>421055</v>
+        <v>421761</v>
       </c>
       <c r="X21" s="36" t="n"/>
     </row>
@@ -19614,7 +19622,7 @@
         <v>0.6785</v>
       </c>
       <c r="W22" s="38" t="n">
-        <v>0.6917</v>
+        <v>0.6974</v>
       </c>
       <c r="X22" s="38" t="n"/>
     </row>
@@ -19688,7 +19696,7 @@
         <v>458</v>
       </c>
       <c r="W23" s="36" t="n">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="X23" s="36" t="n"/>
     </row>
@@ -19762,7 +19770,7 @@
         <v>410866</v>
       </c>
       <c r="W24" s="36" t="n">
-        <v>366769</v>
+        <v>357023</v>
       </c>
       <c r="X24" s="36" t="n"/>
     </row>
@@ -19836,7 +19844,7 @@
         <v>520</v>
       </c>
       <c r="W25" s="36" t="n">
-        <v>173</v>
+        <v>195</v>
       </c>
       <c r="X25" s="36" t="n"/>
     </row>
@@ -19910,7 +19918,7 @@
         <v>472067</v>
       </c>
       <c r="W26" s="36" t="n">
-        <v>435167</v>
+        <v>447045</v>
       </c>
       <c r="X26" s="36" t="n"/>
     </row>
@@ -19984,7 +19992,7 @@
         <v>761</v>
       </c>
       <c r="W27" s="36" t="n">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="X27" s="36" t="n"/>
     </row>
@@ -20058,7 +20066,7 @@
         <v>476924</v>
       </c>
       <c r="W28" s="36" t="n">
-        <v>444827</v>
+        <v>447307</v>
       </c>
       <c r="X28" s="36" t="n"/>
     </row>
@@ -20162,7 +20170,7 @@
         <v>1788</v>
       </c>
       <c r="W30" s="36" t="n">
-        <v>459</v>
+        <v>522</v>
       </c>
       <c r="X30" s="36" t="n"/>
     </row>
@@ -20236,7 +20244,7 @@
         <v>452381</v>
       </c>
       <c r="W31" s="36" t="n">
-        <v>441343</v>
+        <v>438959</v>
       </c>
       <c r="X31" s="36" t="n"/>
     </row>
@@ -20310,7 +20318,7 @@
         <v>988687</v>
       </c>
       <c r="W32" s="36" t="n">
-        <v>808755</v>
+        <v>809418</v>
       </c>
       <c r="X32" s="36" t="n"/>
     </row>
@@ -20444,7 +20452,7 @@
         <v>530083436</v>
       </c>
       <c r="W35" s="33" t="n">
-        <v>155777891</v>
+        <v>168110644</v>
       </c>
       <c r="X35" s="33">
         <f>IFERROR(SUM('📅 DAILY T9'!G$6:I$35),0)</f>
@@ -20521,7 +20529,7 @@
         <v>272494091</v>
       </c>
       <c r="W36" s="33" t="n">
-        <v>77313044</v>
+        <v>84063043</v>
       </c>
       <c r="X36" s="33">
         <f>IFERROR(SUM('📅 DAILY T9'!G$6:G$35),0)</f>
@@ -20598,7 +20606,7 @@
         <v>129188093</v>
       </c>
       <c r="W37" s="33" t="n">
-        <v>38489096</v>
+        <v>42474599</v>
       </c>
       <c r="X37" s="33">
         <f>IFERROR(SUM('📅 DAILY T9'!H$6:H$35),0)</f>
@@ -20675,7 +20683,7 @@
         <v>128401252</v>
       </c>
       <c r="W38" s="33" t="n">
-        <v>39975751</v>
+        <v>41573002</v>
       </c>
       <c r="X38" s="33">
         <f>IFERROR(SUM('📅 DAILY T9'!I$6:I$35),0)</f>
@@ -20752,7 +20760,7 @@
         <v>1717</v>
       </c>
       <c r="W39" s="33" t="n">
-        <v>513</v>
+        <v>559</v>
       </c>
       <c r="X39" s="33">
         <f>IFERROR(SUM('📅 DAILY T9'!J$6:J$35),0)</f>
@@ -20829,7 +20837,7 @@
         <v>308727</v>
       </c>
       <c r="W40" s="33" t="n">
-        <v>303661</v>
+        <v>300735</v>
       </c>
       <c r="X40" s="33">
         <f>IFERROR(SUM('📅 DAILY T9'!M$6:M$35)/SUM('📅 DAILY T9'!J$6:J$35),"")</f>
@@ -20958,7 +20966,7 @@
         <v>613</v>
       </c>
       <c r="W43" s="36" t="n">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="X43" s="36" t="n"/>
     </row>
@@ -21032,7 +21040,7 @@
         <v>301500</v>
       </c>
       <c r="W44" s="36" t="n">
-        <v>327939</v>
+        <v>326501</v>
       </c>
       <c r="X44" s="36" t="n"/>
     </row>
@@ -21284,7 +21292,7 @@
         <v>801</v>
       </c>
       <c r="W48" s="36" t="n">
-        <v>296</v>
+        <v>314</v>
       </c>
       <c r="X48" s="36" t="n"/>
     </row>
@@ -21358,7 +21366,7 @@
         <v>337816</v>
       </c>
       <c r="W49" s="36" t="n">
-        <v>287817</v>
+        <v>286798</v>
       </c>
       <c r="X49" s="36" t="n"/>
     </row>
@@ -21432,7 +21440,7 @@
         <v>0.5665</v>
       </c>
       <c r="W50" s="38" t="n">
-        <v>0.6421</v>
+        <v>0.6343</v>
       </c>
       <c r="X50" s="38" t="n"/>
     </row>
@@ -21506,7 +21514,7 @@
         <v>181</v>
       </c>
       <c r="W51" s="36" t="n">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="X51" s="36" t="n"/>
     </row>
@@ -21580,7 +21588,7 @@
         <v>314399</v>
       </c>
       <c r="W52" s="36" t="n">
-        <v>225862</v>
+        <v>222415</v>
       </c>
       <c r="X52" s="36" t="n"/>
     </row>
@@ -21654,7 +21662,7 @@
         <v>229</v>
       </c>
       <c r="W53" s="36" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="X53" s="36" t="n"/>
     </row>
@@ -21728,7 +21736,7 @@
         <v>330301</v>
       </c>
       <c r="W54" s="36" t="n">
-        <v>334469</v>
+        <v>333222</v>
       </c>
       <c r="X54" s="36" t="n"/>
     </row>
@@ -21802,7 +21810,7 @@
         <v>391</v>
       </c>
       <c r="W55" s="36" t="n">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="X55" s="36" t="n"/>
     </row>
@@ -21876,7 +21884,7 @@
         <v>354566</v>
       </c>
       <c r="W56" s="36" t="n">
-        <v>307156</v>
+        <v>308382</v>
       </c>
       <c r="X56" s="36" t="n"/>
     </row>
@@ -21980,7 +21988,7 @@
         <v>832</v>
       </c>
       <c r="W58" s="36" t="n">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="X58" s="36" t="n"/>
     </row>
@@ -22054,7 +22062,7 @@
         <v>320520</v>
       </c>
       <c r="W59" s="36" t="n">
-        <v>293135</v>
+        <v>291087</v>
       </c>
       <c r="X59" s="36" t="n"/>
     </row>
@@ -22128,7 +22136,7 @@
         <v>516026</v>
       </c>
       <c r="W60" s="36" t="n">
-        <v>497863</v>
+        <v>496488</v>
       </c>
       <c r="X60" s="36" t="n"/>
     </row>
@@ -22290,7 +22298,7 @@
         <v>0.02331338060229061</v>
       </c>
       <c r="W64" s="33" t="n">
-        <v>0.01776856157338958</v>
+        <v>0.0161</v>
       </c>
       <c r="X64" s="33" t="n"/>
     </row>
@@ -22425,7 +22433,7 @@
         <v>1722790559</v>
       </c>
       <c r="W68" s="33" t="n">
-        <v>482921871</v>
+        <v>533894190</v>
       </c>
       <c r="X68" s="33">
         <f>IFERROR(SUM('📅 DAILY T9'!C$6:C$35)+SUM('📅 DAILY T9'!G$6:I$35),0)</f>
@@ -22602,7 +22610,7 @@
         <v>19927</v>
       </c>
       <c r="W71" s="36" t="n">
-        <v>18942</v>
+        <v>18999</v>
       </c>
       <c r="X71" s="36" t="n"/>
     </row>
@@ -22676,7 +22684,7 @@
         <v>1493</v>
       </c>
       <c r="W72" s="36" t="n">
-        <v>423</v>
+        <v>461</v>
       </c>
       <c r="X72" s="36" t="n"/>
     </row>
@@ -22988,7 +22996,7 @@
         <v>990553</v>
       </c>
       <c r="W77" s="36" t="n">
-        <v>1025870</v>
+        <v>1026314</v>
       </c>
       <c r="X77" s="36" t="n"/>
     </row>
@@ -23062,7 +23070,7 @@
         <v>569362</v>
       </c>
       <c r="W78" s="36" t="n">
-        <v>653561</v>
+        <v>651848</v>
       </c>
       <c r="X78" s="36" t="n"/>
     </row>
@@ -23136,7 +23144,7 @@
         <v>988687</v>
       </c>
       <c r="W79" s="36" t="n">
-        <v>808755</v>
+        <v>809418</v>
       </c>
       <c r="X79" s="36" t="n"/>
     </row>
@@ -23210,7 +23218,7 @@
         <v>516026</v>
       </c>
       <c r="W80" s="36" t="n">
-        <v>497863</v>
+        <v>496488</v>
       </c>
       <c r="X80" s="36" t="n"/>
     </row>
@@ -33543,79 +33551,79 @@
     <row r="80" ht="15.75" customHeight="1" s="167">
       <c r="A80" s="133" t="inlineStr">
         <is>
-          <t>T8/26</t>
+          <t>T8/2026</t>
         </is>
       </c>
       <c r="B80" s="133" t="inlineStr">
         <is>
-          <t>1N</t>
+          <t>Lens 1 Ngày</t>
         </is>
       </c>
       <c r="C80" s="133" t="n">
-        <v>277</v>
+        <v>295</v>
       </c>
       <c r="D80" s="133" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E80" s="133" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F80" s="133" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="G80" s="133" t="n">
         <v>11</v>
       </c>
       <c r="H80" s="133" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I80" s="133" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J80" s="133" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K80" s="133" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L80" s="133" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="M80" s="133" t="n">
         <v>4</v>
       </c>
       <c r="N80" s="133" t="n">
-        <v>104</v>
+        <v>142</v>
       </c>
     </row>
     <row r="81" ht="15.75" customHeight="1" s="167">
       <c r="A81" s="137" t="inlineStr">
         <is>
-          <t>T8/26</t>
+          <t>T8/2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1M</t>
+          <t>Lens 1 Tháng</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>324</v>
+        <v>373</v>
       </c>
       <c r="D81" t="n">
-        <v>245</v>
+        <v>277</v>
       </c>
       <c r="E81" t="n">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="F81" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G81" t="n">
         <v>1</v>
       </c>
       <c r="H81" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I81" t="n">
         <v>0</v>
@@ -33624,40 +33632,40 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="L81" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="M81" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="N81" t="n">
-        <v>23</v>
+        <v>64</v>
       </c>
     </row>
     <row r="82" ht="4.5" customHeight="1" s="167">
       <c r="A82" s="125" t="inlineStr">
         <is>
-          <t>T8/26</t>
+          <t>T8/2026</t>
         </is>
       </c>
       <c r="B82" s="126" t="inlineStr">
         <is>
-          <t>3M</t>
+          <t>Lens 3 Tháng</t>
         </is>
       </c>
       <c r="C82" s="127" t="n">
-        <v>183</v>
+        <v>206</v>
       </c>
       <c r="D82" s="128" t="n">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="E82" s="128" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F82" s="128" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G82" s="128" t="n">
         <v>1</v>
@@ -33672,16 +33680,16 @@
         <v>0</v>
       </c>
       <c r="K82" s="130" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="L82" s="130" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M82" s="130" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N82" s="130" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
     </row>
     <row r="83" ht="15.75" customHeight="1" s="167">
@@ -36663,34 +36671,34 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>T8/26</t>
+          <t>T8/2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>1N</t>
+          <t>Lens 1 Ngày</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>238</v>
+        <v>261</v>
       </c>
       <c r="D157" t="n">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="E157" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F157" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G157" t="n">
+        <v>8</v>
+      </c>
+      <c r="H157" t="n">
+        <v>23</v>
+      </c>
+      <c r="I157" t="n">
         <v>7</v>
-      </c>
-      <c r="H157" t="n">
-        <v>21</v>
-      </c>
-      <c r="I157" t="n">
-        <v>6</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -36699,34 +36707,34 @@
         <v>11</v>
       </c>
       <c r="L157" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M157" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N157" t="n">
-        <v>80</v>
+        <v>108</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>T8/26</t>
+          <t>T8/2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>1M</t>
+          <t>Lens 1 Tháng</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="D158" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="E158" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F158" t="n">
         <v>8</v>
@@ -36744,34 +36752,34 @@
         <v>0</v>
       </c>
       <c r="K158" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L158" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M158" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="N158" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>T8/26</t>
+          <t>T8/2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>3M</t>
+          <t>Lens 3 Tháng</t>
         </is>
       </c>
       <c r="C159" t="n">
+        <v>97</v>
+      </c>
+      <c r="D159" t="n">
         <v>89</v>
-      </c>
-      <c r="D159" t="n">
-        <v>81</v>
       </c>
       <c r="E159" t="n">
         <v>7</v>
@@ -36792,16 +36800,16 @@
         <v>0</v>
       </c>
       <c r="K159" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L159" t="n">
         <v>7</v>
       </c>
       <c r="M159" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N159" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -19370,7 +19370,7 @@
         <v>0.1021</v>
       </c>
       <c r="W18" s="38" t="n">
-        <v>0.0288</v>
+        <v>0.034</v>
       </c>
       <c r="X18" s="38" t="n"/>
     </row>
@@ -19548,7 +19548,7 @@
         <v>457245</v>
       </c>
       <c r="W21" s="36" t="n">
-        <v>421761</v>
+        <v>440835</v>
       </c>
       <c r="X21" s="36" t="n"/>
     </row>
@@ -19696,7 +19696,7 @@
         <v>458</v>
       </c>
       <c r="W23" s="36" t="n">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="X23" s="36" t="n"/>
     </row>
@@ -19770,7 +19770,7 @@
         <v>410866</v>
       </c>
       <c r="W24" s="36" t="n">
-        <v>357023</v>
+        <v>390286</v>
       </c>
       <c r="X24" s="36" t="n"/>
     </row>
@@ -19844,7 +19844,7 @@
         <v>520</v>
       </c>
       <c r="W25" s="36" t="n">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="X25" s="36" t="n"/>
     </row>
@@ -19918,7 +19918,7 @@
         <v>472067</v>
       </c>
       <c r="W26" s="36" t="n">
-        <v>447045</v>
+        <v>471210</v>
       </c>
       <c r="X26" s="36" t="n"/>
     </row>
@@ -19992,7 +19992,7 @@
         <v>761</v>
       </c>
       <c r="W27" s="36" t="n">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="X27" s="36" t="n"/>
     </row>
@@ -20066,7 +20066,7 @@
         <v>476924</v>
       </c>
       <c r="W28" s="36" t="n">
-        <v>447307</v>
+        <v>450871</v>
       </c>
       <c r="X28" s="36" t="n"/>
     </row>
@@ -21188,7 +21188,7 @@
         <v>0.059</v>
       </c>
       <c r="W46" s="38" t="n">
-        <v>0.0141</v>
+        <v>0.0233</v>
       </c>
       <c r="X46" s="38" t="n"/>
     </row>
@@ -21366,7 +21366,7 @@
         <v>337816</v>
       </c>
       <c r="W49" s="36" t="n">
-        <v>286798</v>
+        <v>339787</v>
       </c>
       <c r="X49" s="36" t="n"/>
     </row>
@@ -21514,7 +21514,7 @@
         <v>181</v>
       </c>
       <c r="W51" s="36" t="n">
-        <v>118</v>
+        <v>68</v>
       </c>
       <c r="X51" s="36" t="n"/>
     </row>
@@ -21588,7 +21588,7 @@
         <v>314399</v>
       </c>
       <c r="W52" s="36" t="n">
-        <v>222415</v>
+        <v>387013</v>
       </c>
       <c r="X52" s="36" t="n"/>
     </row>
@@ -21662,7 +21662,7 @@
         <v>229</v>
       </c>
       <c r="W53" s="36" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="X53" s="36" t="n"/>
     </row>
@@ -21736,7 +21736,7 @@
         <v>330301</v>
       </c>
       <c r="W54" s="36" t="n">
-        <v>333222</v>
+        <v>342089</v>
       </c>
       <c r="X54" s="36" t="n"/>
     </row>
@@ -21810,7 +21810,7 @@
         <v>391</v>
       </c>
       <c r="W55" s="36" t="n">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="X55" s="36" t="n"/>
     </row>
@@ -21884,7 +21884,7 @@
         <v>354566</v>
       </c>
       <c r="W56" s="36" t="n">
-        <v>308382</v>
+        <v>318770</v>
       </c>
       <c r="X56" s="36" t="n"/>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macos/REPORT FB&amp;STORE/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{431767CA-F0CF-F44A-9F83-8D72806129AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{778580AE-FB05-1245-9195-BA5938EAB9DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2757,7 +2757,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="53" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="53" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="193">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -3209,12 +3209,15 @@
     <xf numFmtId="49" fontId="52" fillId="51" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="14" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3231,11 +3234,11 @@
     <xf numFmtId="0" fontId="3" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3265,16 +3268,16 @@
     <xf numFmtId="0" fontId="19" fillId="19" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="49" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3301,9 +3304,6 @@
     </xf>
     <xf numFmtId="0" fontId="38" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="14" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3579,26 +3579,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="171" t="s">
+      <c r="A1" s="172" t="s">
         <v>95</v>
       </c>
-      <c r="B1" s="170"/>
-      <c r="C1" s="170"/>
-      <c r="D1" s="170"/>
-      <c r="E1" s="170"/>
-      <c r="F1" s="170"/>
-      <c r="G1" s="170"/>
+      <c r="B1" s="171"/>
+      <c r="C1" s="171"/>
+      <c r="D1" s="171"/>
+      <c r="E1" s="171"/>
+      <c r="F1" s="171"/>
+      <c r="G1" s="171"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="169" t="s">
+      <c r="A2" s="170" t="s">
         <v>96</v>
       </c>
-      <c r="B2" s="170"/>
-      <c r="C2" s="170"/>
-      <c r="D2" s="170"/>
-      <c r="E2" s="170"/>
-      <c r="F2" s="170"/>
-      <c r="G2" s="170"/>
+      <c r="B2" s="171"/>
+      <c r="C2" s="171"/>
+      <c r="D2" s="171"/>
+      <c r="E2" s="171"/>
+      <c r="F2" s="171"/>
+      <c r="G2" s="171"/>
     </row>
     <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -4853,80 +4853,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="177" t="s">
+      <c r="A1" s="178" t="s">
         <v>400</v>
       </c>
-      <c r="B1" s="158"/>
-      <c r="C1" s="158"/>
-      <c r="D1" s="158"/>
-      <c r="E1" s="158"/>
-      <c r="F1" s="158"/>
-      <c r="G1" s="158"/>
-      <c r="H1" s="158"/>
-      <c r="I1" s="158"/>
-      <c r="J1" s="158"/>
-      <c r="K1" s="158"/>
-      <c r="L1" s="158"/>
-      <c r="M1" s="158"/>
-      <c r="N1" s="158"/>
-      <c r="O1" s="158"/>
-      <c r="P1" s="158"/>
-      <c r="Q1" s="158"/>
+      <c r="B1" s="159"/>
+      <c r="C1" s="159"/>
+      <c r="D1" s="159"/>
+      <c r="E1" s="159"/>
+      <c r="F1" s="159"/>
+      <c r="G1" s="159"/>
+      <c r="H1" s="159"/>
+      <c r="I1" s="159"/>
+      <c r="J1" s="159"/>
+      <c r="K1" s="159"/>
+      <c r="L1" s="159"/>
+      <c r="M1" s="159"/>
+      <c r="N1" s="159"/>
+      <c r="O1" s="159"/>
+      <c r="P1" s="159"/>
+      <c r="Q1" s="159"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="164" t="s">
+      <c r="A2" s="165" t="s">
         <v>360</v>
       </c>
-      <c r="B2" s="158"/>
-      <c r="C2" s="158"/>
-      <c r="D2" s="158"/>
-      <c r="E2" s="158"/>
-      <c r="F2" s="158"/>
-      <c r="G2" s="158"/>
-      <c r="H2" s="158"/>
-      <c r="I2" s="158"/>
-      <c r="J2" s="158"/>
-      <c r="K2" s="158"/>
-      <c r="L2" s="158"/>
-      <c r="M2" s="158"/>
-      <c r="N2" s="158"/>
-      <c r="O2" s="158"/>
-      <c r="P2" s="158"/>
-      <c r="Q2" s="158"/>
+      <c r="B2" s="159"/>
+      <c r="C2" s="159"/>
+      <c r="D2" s="159"/>
+      <c r="E2" s="159"/>
+      <c r="F2" s="159"/>
+      <c r="G2" s="159"/>
+      <c r="H2" s="159"/>
+      <c r="I2" s="159"/>
+      <c r="J2" s="159"/>
+      <c r="K2" s="159"/>
+      <c r="L2" s="159"/>
+      <c r="M2" s="159"/>
+      <c r="N2" s="159"/>
+      <c r="O2" s="159"/>
+      <c r="P2" s="159"/>
+      <c r="Q2" s="159"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="176" t="s">
+      <c r="A3" s="177" t="s">
         <v>361</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="175" t="s">
+      <c r="B3" s="159"/>
+      <c r="C3" s="176" t="s">
         <v>362</v>
       </c>
-      <c r="D3" s="158"/>
-      <c r="E3" s="178" t="s">
+      <c r="D3" s="159"/>
+      <c r="E3" s="179" t="s">
         <v>363</v>
       </c>
-      <c r="F3" s="158"/>
-      <c r="G3" s="173" t="s">
+      <c r="F3" s="159"/>
+      <c r="G3" s="174" t="s">
         <v>364</v>
       </c>
-      <c r="H3" s="158"/>
-      <c r="I3" s="158"/>
-      <c r="J3" s="158"/>
+      <c r="H3" s="159"/>
+      <c r="I3" s="159"/>
+      <c r="J3" s="159"/>
       <c r="K3" s="56" t="s">
         <v>365</v>
       </c>
       <c r="L3" s="57" t="s">
         <v>366</v>
       </c>
-      <c r="M3" s="172" t="s">
+      <c r="M3" s="173" t="s">
         <v>367</v>
       </c>
-      <c r="N3" s="158"/>
-      <c r="O3" s="172" t="s">
+      <c r="N3" s="159"/>
+      <c r="O3" s="173" t="s">
         <v>367</v>
       </c>
-      <c r="P3" s="158"/>
+      <c r="P3" s="159"/>
       <c r="Q3" s="58" t="s">
         <v>368</v>
       </c>
@@ -4985,10 +4985,10 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="174" t="s">
+      <c r="A5" s="175" t="s">
         <v>386</v>
       </c>
-      <c r="B5" s="158"/>
+      <c r="B5" s="159"/>
       <c r="C5" s="66"/>
       <c r="D5" s="67"/>
       <c r="E5" s="67"/>
@@ -6751,80 +6751,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="177" t="s">
+      <c r="A1" s="178" t="s">
         <v>401</v>
       </c>
-      <c r="B1" s="158"/>
-      <c r="C1" s="158"/>
-      <c r="D1" s="158"/>
-      <c r="E1" s="158"/>
-      <c r="F1" s="158"/>
-      <c r="G1" s="158"/>
-      <c r="H1" s="158"/>
-      <c r="I1" s="158"/>
-      <c r="J1" s="158"/>
-      <c r="K1" s="158"/>
-      <c r="L1" s="158"/>
-      <c r="M1" s="158"/>
-      <c r="N1" s="158"/>
-      <c r="O1" s="158"/>
-      <c r="P1" s="158"/>
-      <c r="Q1" s="158"/>
+      <c r="B1" s="159"/>
+      <c r="C1" s="159"/>
+      <c r="D1" s="159"/>
+      <c r="E1" s="159"/>
+      <c r="F1" s="159"/>
+      <c r="G1" s="159"/>
+      <c r="H1" s="159"/>
+      <c r="I1" s="159"/>
+      <c r="J1" s="159"/>
+      <c r="K1" s="159"/>
+      <c r="L1" s="159"/>
+      <c r="M1" s="159"/>
+      <c r="N1" s="159"/>
+      <c r="O1" s="159"/>
+      <c r="P1" s="159"/>
+      <c r="Q1" s="159"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="164" t="s">
+      <c r="A2" s="165" t="s">
         <v>360</v>
       </c>
-      <c r="B2" s="158"/>
-      <c r="C2" s="158"/>
-      <c r="D2" s="158"/>
-      <c r="E2" s="158"/>
-      <c r="F2" s="158"/>
-      <c r="G2" s="158"/>
-      <c r="H2" s="158"/>
-      <c r="I2" s="158"/>
-      <c r="J2" s="158"/>
-      <c r="K2" s="158"/>
-      <c r="L2" s="158"/>
-      <c r="M2" s="158"/>
-      <c r="N2" s="158"/>
-      <c r="O2" s="158"/>
-      <c r="P2" s="158"/>
-      <c r="Q2" s="158"/>
+      <c r="B2" s="159"/>
+      <c r="C2" s="159"/>
+      <c r="D2" s="159"/>
+      <c r="E2" s="159"/>
+      <c r="F2" s="159"/>
+      <c r="G2" s="159"/>
+      <c r="H2" s="159"/>
+      <c r="I2" s="159"/>
+      <c r="J2" s="159"/>
+      <c r="K2" s="159"/>
+      <c r="L2" s="159"/>
+      <c r="M2" s="159"/>
+      <c r="N2" s="159"/>
+      <c r="O2" s="159"/>
+      <c r="P2" s="159"/>
+      <c r="Q2" s="159"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="176" t="s">
+      <c r="A3" s="177" t="s">
         <v>361</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="175" t="s">
+      <c r="B3" s="159"/>
+      <c r="C3" s="176" t="s">
         <v>362</v>
       </c>
-      <c r="D3" s="158"/>
-      <c r="E3" s="178" t="s">
+      <c r="D3" s="159"/>
+      <c r="E3" s="179" t="s">
         <v>363</v>
       </c>
-      <c r="F3" s="158"/>
-      <c r="G3" s="173" t="s">
+      <c r="F3" s="159"/>
+      <c r="G3" s="174" t="s">
         <v>364</v>
       </c>
-      <c r="H3" s="158"/>
-      <c r="I3" s="158"/>
-      <c r="J3" s="158"/>
+      <c r="H3" s="159"/>
+      <c r="I3" s="159"/>
+      <c r="J3" s="159"/>
       <c r="K3" s="56" t="s">
         <v>365</v>
       </c>
       <c r="L3" s="57" t="s">
         <v>366</v>
       </c>
-      <c r="M3" s="172" t="s">
+      <c r="M3" s="173" t="s">
         <v>367</v>
       </c>
-      <c r="N3" s="158"/>
-      <c r="O3" s="172" t="s">
+      <c r="N3" s="159"/>
+      <c r="O3" s="173" t="s">
         <v>367</v>
       </c>
-      <c r="P3" s="158"/>
+      <c r="P3" s="159"/>
       <c r="Q3" s="58" t="s">
         <v>368</v>
       </c>
@@ -6883,10 +6883,10 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="174" t="s">
+      <c r="A5" s="175" t="s">
         <v>386</v>
       </c>
-      <c r="B5" s="158"/>
+      <c r="B5" s="159"/>
       <c r="C5" s="66"/>
       <c r="D5" s="67"/>
       <c r="E5" s="67"/>
@@ -8690,80 +8690,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="177" t="s">
+      <c r="A1" s="178" t="s">
         <v>402</v>
       </c>
-      <c r="B1" s="158"/>
-      <c r="C1" s="158"/>
-      <c r="D1" s="158"/>
-      <c r="E1" s="158"/>
-      <c r="F1" s="158"/>
-      <c r="G1" s="158"/>
-      <c r="H1" s="158"/>
-      <c r="I1" s="158"/>
-      <c r="J1" s="158"/>
-      <c r="K1" s="158"/>
-      <c r="L1" s="158"/>
-      <c r="M1" s="158"/>
-      <c r="N1" s="158"/>
-      <c r="O1" s="158"/>
-      <c r="P1" s="158"/>
-      <c r="Q1" s="158"/>
+      <c r="B1" s="159"/>
+      <c r="C1" s="159"/>
+      <c r="D1" s="159"/>
+      <c r="E1" s="159"/>
+      <c r="F1" s="159"/>
+      <c r="G1" s="159"/>
+      <c r="H1" s="159"/>
+      <c r="I1" s="159"/>
+      <c r="J1" s="159"/>
+      <c r="K1" s="159"/>
+      <c r="L1" s="159"/>
+      <c r="M1" s="159"/>
+      <c r="N1" s="159"/>
+      <c r="O1" s="159"/>
+      <c r="P1" s="159"/>
+      <c r="Q1" s="159"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="164" t="s">
+      <c r="A2" s="165" t="s">
         <v>360</v>
       </c>
-      <c r="B2" s="158"/>
-      <c r="C2" s="158"/>
-      <c r="D2" s="158"/>
-      <c r="E2" s="158"/>
-      <c r="F2" s="158"/>
-      <c r="G2" s="158"/>
-      <c r="H2" s="158"/>
-      <c r="I2" s="158"/>
-      <c r="J2" s="158"/>
-      <c r="K2" s="158"/>
-      <c r="L2" s="158"/>
-      <c r="M2" s="158"/>
-      <c r="N2" s="158"/>
-      <c r="O2" s="158"/>
-      <c r="P2" s="158"/>
-      <c r="Q2" s="158"/>
+      <c r="B2" s="159"/>
+      <c r="C2" s="159"/>
+      <c r="D2" s="159"/>
+      <c r="E2" s="159"/>
+      <c r="F2" s="159"/>
+      <c r="G2" s="159"/>
+      <c r="H2" s="159"/>
+      <c r="I2" s="159"/>
+      <c r="J2" s="159"/>
+      <c r="K2" s="159"/>
+      <c r="L2" s="159"/>
+      <c r="M2" s="159"/>
+      <c r="N2" s="159"/>
+      <c r="O2" s="159"/>
+      <c r="P2" s="159"/>
+      <c r="Q2" s="159"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="176" t="s">
+      <c r="A3" s="177" t="s">
         <v>361</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="175" t="s">
+      <c r="B3" s="159"/>
+      <c r="C3" s="176" t="s">
         <v>362</v>
       </c>
-      <c r="D3" s="158"/>
-      <c r="E3" s="178" t="s">
+      <c r="D3" s="159"/>
+      <c r="E3" s="179" t="s">
         <v>363</v>
       </c>
-      <c r="F3" s="158"/>
-      <c r="G3" s="173" t="s">
+      <c r="F3" s="159"/>
+      <c r="G3" s="174" t="s">
         <v>364</v>
       </c>
-      <c r="H3" s="158"/>
-      <c r="I3" s="158"/>
-      <c r="J3" s="158"/>
+      <c r="H3" s="159"/>
+      <c r="I3" s="159"/>
+      <c r="J3" s="159"/>
       <c r="K3" s="56" t="s">
         <v>365</v>
       </c>
       <c r="L3" s="57" t="s">
         <v>366</v>
       </c>
-      <c r="M3" s="172" t="s">
+      <c r="M3" s="173" t="s">
         <v>367</v>
       </c>
-      <c r="N3" s="158"/>
-      <c r="O3" s="172" t="s">
+      <c r="N3" s="159"/>
+      <c r="O3" s="173" t="s">
         <v>367</v>
       </c>
-      <c r="P3" s="158"/>
+      <c r="P3" s="159"/>
       <c r="Q3" s="58" t="s">
         <v>368</v>
       </c>
@@ -8822,10 +8822,10 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="174" t="s">
+      <c r="A5" s="175" t="s">
         <v>386</v>
       </c>
-      <c r="B5" s="158"/>
+      <c r="B5" s="159"/>
       <c r="C5" s="66">
         <v>1149763530</v>
       </c>
@@ -10603,36 +10603,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="177" t="s">
+      <c r="A1" s="178" t="s">
         <v>403</v>
       </c>
-      <c r="B1" s="158"/>
-      <c r="C1" s="158"/>
-      <c r="D1" s="158"/>
-      <c r="E1" s="158"/>
-      <c r="F1" s="158"/>
-      <c r="G1" s="158"/>
-      <c r="H1" s="158"/>
-      <c r="I1" s="158"/>
-      <c r="J1" s="158"/>
-      <c r="K1" s="158"/>
-      <c r="L1" s="158"/>
+      <c r="B1" s="159"/>
+      <c r="C1" s="159"/>
+      <c r="D1" s="159"/>
+      <c r="E1" s="159"/>
+      <c r="F1" s="159"/>
+      <c r="G1" s="159"/>
+      <c r="H1" s="159"/>
+      <c r="I1" s="159"/>
+      <c r="J1" s="159"/>
+      <c r="K1" s="159"/>
+      <c r="L1" s="159"/>
     </row>
     <row r="2" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="164" t="s">
+      <c r="A2" s="165" t="s">
         <v>404</v>
       </c>
-      <c r="B2" s="158"/>
-      <c r="C2" s="158"/>
-      <c r="D2" s="158"/>
-      <c r="E2" s="158"/>
-      <c r="F2" s="158"/>
-      <c r="G2" s="158"/>
-      <c r="H2" s="158"/>
-      <c r="I2" s="158"/>
-      <c r="J2" s="158"/>
-      <c r="K2" s="158"/>
-      <c r="L2" s="158"/>
+      <c r="B2" s="159"/>
+      <c r="C2" s="159"/>
+      <c r="D2" s="159"/>
+      <c r="E2" s="159"/>
+      <c r="F2" s="159"/>
+      <c r="G2" s="159"/>
+      <c r="H2" s="159"/>
+      <c r="I2" s="159"/>
+      <c r="J2" s="159"/>
+      <c r="K2" s="159"/>
+      <c r="L2" s="159"/>
     </row>
     <row r="3" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="60" t="s">
@@ -10902,10 +10902,10 @@
     </row>
     <row r="22" spans="1:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="23" spans="1:20" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="180" t="s">
+      <c r="A23" s="183" t="s">
         <v>424</v>
       </c>
-      <c r="B23" s="158"/>
+      <c r="B23" s="159"/>
       <c r="C23" s="101">
         <v>1221140305</v>
       </c>
@@ -10925,37 +10925,37 @@
     </row>
     <row r="24" spans="1:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="25" spans="1:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="179" t="s">
+      <c r="A25" s="182" t="s">
         <v>425</v>
       </c>
-      <c r="B25" s="158"/>
-      <c r="C25" s="158"/>
-      <c r="D25" s="158"/>
-      <c r="E25" s="158"/>
-      <c r="F25" s="158"/>
-      <c r="G25" s="158"/>
-      <c r="H25" s="158"/>
-      <c r="I25" s="158"/>
-      <c r="J25" s="158"/>
-      <c r="K25" s="158"/>
-      <c r="L25" s="158"/>
+      <c r="B25" s="159"/>
+      <c r="C25" s="159"/>
+      <c r="D25" s="159"/>
+      <c r="E25" s="159"/>
+      <c r="F25" s="159"/>
+      <c r="G25" s="159"/>
+      <c r="H25" s="159"/>
+      <c r="I25" s="159"/>
+      <c r="J25" s="159"/>
+      <c r="K25" s="159"/>
+      <c r="L25" s="159"/>
     </row>
     <row r="26" spans="1:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="27" spans="1:20" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="181" t="s">
+      <c r="A27" s="180" t="s">
         <v>426</v>
       </c>
-      <c r="B27" s="158"/>
-      <c r="C27" s="158"/>
-      <c r="D27" s="158"/>
-      <c r="E27" s="158"/>
-      <c r="F27" s="158"/>
-      <c r="G27" s="158"/>
-      <c r="H27" s="158"/>
-      <c r="I27" s="158"/>
-      <c r="J27" s="158"/>
-      <c r="K27" s="158"/>
-      <c r="L27" s="182"/>
+      <c r="B27" s="159"/>
+      <c r="C27" s="159"/>
+      <c r="D27" s="159"/>
+      <c r="E27" s="159"/>
+      <c r="F27" s="159"/>
+      <c r="G27" s="159"/>
+      <c r="H27" s="159"/>
+      <c r="I27" s="159"/>
+      <c r="J27" s="159"/>
+      <c r="K27" s="159"/>
+      <c r="L27" s="181"/>
       <c r="M27" s="104"/>
       <c r="N27" s="104"/>
       <c r="O27" s="104"/>
@@ -11188,20 +11188,20 @@
       <c r="T34" s="109"/>
     </row>
     <row r="35" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="181" t="s">
+      <c r="A35" s="180" t="s">
         <v>450</v>
       </c>
-      <c r="B35" s="158"/>
-      <c r="C35" s="158"/>
-      <c r="D35" s="158"/>
-      <c r="E35" s="158"/>
-      <c r="F35" s="158"/>
-      <c r="G35" s="158"/>
-      <c r="H35" s="158"/>
-      <c r="I35" s="158"/>
-      <c r="J35" s="158"/>
-      <c r="K35" s="158"/>
-      <c r="L35" s="182"/>
+      <c r="B35" s="159"/>
+      <c r="C35" s="159"/>
+      <c r="D35" s="159"/>
+      <c r="E35" s="159"/>
+      <c r="F35" s="159"/>
+      <c r="G35" s="159"/>
+      <c r="H35" s="159"/>
+      <c r="I35" s="159"/>
+      <c r="J35" s="159"/>
+      <c r="K35" s="159"/>
+      <c r="L35" s="181"/>
       <c r="M35" s="109"/>
       <c r="N35" s="109"/>
       <c r="O35" s="109"/>
@@ -11477,11 +11477,11 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A35:L35"/>
+    <mergeCell ref="A27:L27"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A25:L25"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A27:L27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -11512,80 +11512,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="177" t="s">
+      <c r="A1" s="178" t="s">
         <v>454</v>
       </c>
-      <c r="B1" s="158"/>
-      <c r="C1" s="158"/>
-      <c r="D1" s="158"/>
-      <c r="E1" s="158"/>
-      <c r="F1" s="158"/>
-      <c r="G1" s="158"/>
-      <c r="H1" s="158"/>
-      <c r="I1" s="158"/>
-      <c r="J1" s="158"/>
-      <c r="K1" s="158"/>
-      <c r="L1" s="158"/>
-      <c r="M1" s="158"/>
-      <c r="N1" s="158"/>
-      <c r="O1" s="158"/>
-      <c r="P1" s="158"/>
-      <c r="Q1" s="158"/>
+      <c r="B1" s="159"/>
+      <c r="C1" s="159"/>
+      <c r="D1" s="159"/>
+      <c r="E1" s="159"/>
+      <c r="F1" s="159"/>
+      <c r="G1" s="159"/>
+      <c r="H1" s="159"/>
+      <c r="I1" s="159"/>
+      <c r="J1" s="159"/>
+      <c r="K1" s="159"/>
+      <c r="L1" s="159"/>
+      <c r="M1" s="159"/>
+      <c r="N1" s="159"/>
+      <c r="O1" s="159"/>
+      <c r="P1" s="159"/>
+      <c r="Q1" s="159"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="164" t="s">
+      <c r="A2" s="165" t="s">
         <v>360</v>
       </c>
-      <c r="B2" s="158"/>
-      <c r="C2" s="158"/>
-      <c r="D2" s="158"/>
-      <c r="E2" s="158"/>
-      <c r="F2" s="158"/>
-      <c r="G2" s="158"/>
-      <c r="H2" s="158"/>
-      <c r="I2" s="158"/>
-      <c r="J2" s="158"/>
-      <c r="K2" s="158"/>
-      <c r="L2" s="158"/>
-      <c r="M2" s="158"/>
-      <c r="N2" s="158"/>
-      <c r="O2" s="158"/>
-      <c r="P2" s="158"/>
-      <c r="Q2" s="158"/>
+      <c r="B2" s="159"/>
+      <c r="C2" s="159"/>
+      <c r="D2" s="159"/>
+      <c r="E2" s="159"/>
+      <c r="F2" s="159"/>
+      <c r="G2" s="159"/>
+      <c r="H2" s="159"/>
+      <c r="I2" s="159"/>
+      <c r="J2" s="159"/>
+      <c r="K2" s="159"/>
+      <c r="L2" s="159"/>
+      <c r="M2" s="159"/>
+      <c r="N2" s="159"/>
+      <c r="O2" s="159"/>
+      <c r="P2" s="159"/>
+      <c r="Q2" s="159"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="176" t="s">
+      <c r="A3" s="177" t="s">
         <v>361</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="175" t="s">
+      <c r="B3" s="159"/>
+      <c r="C3" s="176" t="s">
         <v>362</v>
       </c>
-      <c r="D3" s="158"/>
-      <c r="E3" s="178" t="s">
+      <c r="D3" s="159"/>
+      <c r="E3" s="179" t="s">
         <v>363</v>
       </c>
-      <c r="F3" s="158"/>
-      <c r="G3" s="173" t="s">
+      <c r="F3" s="159"/>
+      <c r="G3" s="174" t="s">
         <v>364</v>
       </c>
-      <c r="H3" s="158"/>
-      <c r="I3" s="158"/>
-      <c r="J3" s="158"/>
+      <c r="H3" s="159"/>
+      <c r="I3" s="159"/>
+      <c r="J3" s="159"/>
       <c r="K3" s="56" t="s">
         <v>365</v>
       </c>
       <c r="L3" s="57" t="s">
         <v>366</v>
       </c>
-      <c r="M3" s="172" t="s">
+      <c r="M3" s="173" t="s">
         <v>367</v>
       </c>
-      <c r="N3" s="158"/>
-      <c r="O3" s="172" t="s">
+      <c r="N3" s="159"/>
+      <c r="O3" s="173" t="s">
         <v>367</v>
       </c>
-      <c r="P3" s="158"/>
+      <c r="P3" s="159"/>
       <c r="Q3" s="58" t="s">
         <v>368</v>
       </c>
@@ -11644,10 +11644,10 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="174" t="s">
+      <c r="A5" s="175" t="s">
         <v>386</v>
       </c>
-      <c r="B5" s="158"/>
+      <c r="B5" s="159"/>
       <c r="C5" s="66">
         <v>1214990084</v>
       </c>
@@ -13478,36 +13478,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="177" t="s">
+      <c r="A1" s="178" t="s">
         <v>455</v>
       </c>
-      <c r="B1" s="158"/>
-      <c r="C1" s="158"/>
-      <c r="D1" s="158"/>
-      <c r="E1" s="158"/>
-      <c r="F1" s="158"/>
-      <c r="G1" s="158"/>
-      <c r="H1" s="158"/>
-      <c r="I1" s="158"/>
-      <c r="J1" s="158"/>
-      <c r="K1" s="158"/>
-      <c r="L1" s="158"/>
+      <c r="B1" s="159"/>
+      <c r="C1" s="159"/>
+      <c r="D1" s="159"/>
+      <c r="E1" s="159"/>
+      <c r="F1" s="159"/>
+      <c r="G1" s="159"/>
+      <c r="H1" s="159"/>
+      <c r="I1" s="159"/>
+      <c r="J1" s="159"/>
+      <c r="K1" s="159"/>
+      <c r="L1" s="159"/>
     </row>
     <row r="2" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="164" t="s">
+      <c r="A2" s="165" t="s">
         <v>404</v>
       </c>
-      <c r="B2" s="158"/>
-      <c r="C2" s="158"/>
-      <c r="D2" s="158"/>
-      <c r="E2" s="158"/>
-      <c r="F2" s="158"/>
-      <c r="G2" s="158"/>
-      <c r="H2" s="158"/>
-      <c r="I2" s="158"/>
-      <c r="J2" s="158"/>
-      <c r="K2" s="158"/>
-      <c r="L2" s="158"/>
+      <c r="B2" s="159"/>
+      <c r="C2" s="159"/>
+      <c r="D2" s="159"/>
+      <c r="E2" s="159"/>
+      <c r="F2" s="159"/>
+      <c r="G2" s="159"/>
+      <c r="H2" s="159"/>
+      <c r="I2" s="159"/>
+      <c r="J2" s="159"/>
+      <c r="K2" s="159"/>
+      <c r="L2" s="159"/>
     </row>
     <row r="3" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="60" t="s">
@@ -13855,10 +13855,10 @@
     </row>
     <row r="22" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="23" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="180" t="s">
+      <c r="A23" s="183" t="s">
         <v>424</v>
       </c>
-      <c r="B23" s="158"/>
+      <c r="B23" s="159"/>
       <c r="C23" s="101">
         <v>1214990084</v>
       </c>
@@ -13878,20 +13878,20 @@
     </row>
     <row r="24" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="25" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="179" t="s">
+      <c r="A25" s="182" t="s">
         <v>425</v>
       </c>
-      <c r="B25" s="158"/>
-      <c r="C25" s="158"/>
-      <c r="D25" s="158"/>
-      <c r="E25" s="158"/>
-      <c r="F25" s="158"/>
-      <c r="G25" s="158"/>
-      <c r="H25" s="158"/>
-      <c r="I25" s="158"/>
-      <c r="J25" s="158"/>
-      <c r="K25" s="158"/>
-      <c r="L25" s="158"/>
+      <c r="B25" s="159"/>
+      <c r="C25" s="159"/>
+      <c r="D25" s="159"/>
+      <c r="E25" s="159"/>
+      <c r="F25" s="159"/>
+      <c r="G25" s="159"/>
+      <c r="H25" s="159"/>
+      <c r="I25" s="159"/>
+      <c r="J25" s="159"/>
+      <c r="K25" s="159"/>
+      <c r="L25" s="159"/>
     </row>
     <row r="26" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="27" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -14104,80 +14104,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="177" t="s">
+      <c r="A1" s="178" t="s">
         <v>462</v>
       </c>
-      <c r="B1" s="158"/>
-      <c r="C1" s="158"/>
-      <c r="D1" s="158"/>
-      <c r="E1" s="158"/>
-      <c r="F1" s="158"/>
-      <c r="G1" s="158"/>
-      <c r="H1" s="158"/>
-      <c r="I1" s="158"/>
-      <c r="J1" s="158"/>
-      <c r="K1" s="158"/>
-      <c r="L1" s="158"/>
-      <c r="M1" s="158"/>
-      <c r="N1" s="158"/>
-      <c r="O1" s="158"/>
-      <c r="P1" s="158"/>
-      <c r="Q1" s="158"/>
+      <c r="B1" s="159"/>
+      <c r="C1" s="159"/>
+      <c r="D1" s="159"/>
+      <c r="E1" s="159"/>
+      <c r="F1" s="159"/>
+      <c r="G1" s="159"/>
+      <c r="H1" s="159"/>
+      <c r="I1" s="159"/>
+      <c r="J1" s="159"/>
+      <c r="K1" s="159"/>
+      <c r="L1" s="159"/>
+      <c r="M1" s="159"/>
+      <c r="N1" s="159"/>
+      <c r="O1" s="159"/>
+      <c r="P1" s="159"/>
+      <c r="Q1" s="159"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="164" t="s">
+      <c r="A2" s="165" t="s">
         <v>360</v>
       </c>
-      <c r="B2" s="158"/>
-      <c r="C2" s="158"/>
-      <c r="D2" s="158"/>
-      <c r="E2" s="158"/>
-      <c r="F2" s="158"/>
-      <c r="G2" s="158"/>
-      <c r="H2" s="158"/>
-      <c r="I2" s="158"/>
-      <c r="J2" s="158"/>
-      <c r="K2" s="158"/>
-      <c r="L2" s="158"/>
-      <c r="M2" s="158"/>
-      <c r="N2" s="158"/>
-      <c r="O2" s="158"/>
-      <c r="P2" s="158"/>
-      <c r="Q2" s="158"/>
+      <c r="B2" s="159"/>
+      <c r="C2" s="159"/>
+      <c r="D2" s="159"/>
+      <c r="E2" s="159"/>
+      <c r="F2" s="159"/>
+      <c r="G2" s="159"/>
+      <c r="H2" s="159"/>
+      <c r="I2" s="159"/>
+      <c r="J2" s="159"/>
+      <c r="K2" s="159"/>
+      <c r="L2" s="159"/>
+      <c r="M2" s="159"/>
+      <c r="N2" s="159"/>
+      <c r="O2" s="159"/>
+      <c r="P2" s="159"/>
+      <c r="Q2" s="159"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="176" t="s">
+      <c r="A3" s="177" t="s">
         <v>361</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="175" t="s">
+      <c r="B3" s="159"/>
+      <c r="C3" s="176" t="s">
         <v>362</v>
       </c>
-      <c r="D3" s="158"/>
-      <c r="E3" s="178" t="s">
+      <c r="D3" s="159"/>
+      <c r="E3" s="179" t="s">
         <v>363</v>
       </c>
-      <c r="F3" s="158"/>
-      <c r="G3" s="173" t="s">
+      <c r="F3" s="159"/>
+      <c r="G3" s="174" t="s">
         <v>364</v>
       </c>
-      <c r="H3" s="158"/>
-      <c r="I3" s="158"/>
-      <c r="J3" s="158"/>
+      <c r="H3" s="159"/>
+      <c r="I3" s="159"/>
+      <c r="J3" s="159"/>
       <c r="K3" s="56" t="s">
         <v>365</v>
       </c>
       <c r="L3" s="57" t="s">
         <v>366</v>
       </c>
-      <c r="M3" s="172" t="s">
+      <c r="M3" s="173" t="s">
         <v>367</v>
       </c>
-      <c r="N3" s="158"/>
-      <c r="O3" s="172" t="s">
+      <c r="N3" s="159"/>
+      <c r="O3" s="173" t="s">
         <v>367</v>
       </c>
-      <c r="P3" s="158"/>
+      <c r="P3" s="159"/>
       <c r="Q3" s="58" t="s">
         <v>368</v>
       </c>
@@ -14236,10 +14236,10 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="174" t="s">
+      <c r="A5" s="175" t="s">
         <v>386</v>
       </c>
-      <c r="B5" s="158"/>
+      <c r="B5" s="159"/>
       <c r="C5" s="66">
         <v>1221751028</v>
       </c>
@@ -14947,31 +14947,45 @@
       <c r="B19" s="73" t="s">
         <v>391</v>
       </c>
-      <c r="C19" s="74"/>
-      <c r="D19" s="74"/>
+      <c r="C19" s="74">
+        <v>37336658</v>
+      </c>
+      <c r="D19" s="74">
+        <v>89</v>
+      </c>
       <c r="E19" s="74"/>
       <c r="F19" s="74"/>
-      <c r="G19" s="74"/>
-      <c r="H19" s="74"/>
-      <c r="I19" s="74"/>
-      <c r="J19" s="74"/>
-      <c r="K19" s="74"/>
+      <c r="G19" s="74">
+        <v>5734001</v>
+      </c>
+      <c r="H19" s="74">
+        <v>4229001</v>
+      </c>
+      <c r="I19" s="74">
+        <v>3262999</v>
+      </c>
+      <c r="J19" s="74">
+        <v>50</v>
+      </c>
+      <c r="K19" s="74">
+        <v>1520800</v>
+      </c>
       <c r="L19" s="75"/>
-      <c r="M19" s="33" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N19" s="33" t="str">
+      <c r="M19" s="33">
+        <f t="shared" si="0"/>
+        <v>13226001</v>
+      </c>
+      <c r="N19" s="33">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O19" s="33" t="str">
+        <v>50562659</v>
+      </c>
+      <c r="O19" s="33">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="P19" s="33" t="str">
+        <v>419513.01123595505</v>
+      </c>
+      <c r="P19" s="33">
         <f t="shared" si="3"/>
-        <v/>
+        <v>264520.02</v>
       </c>
       <c r="Q19" s="46" t="str">
         <f t="shared" si="4"/>
@@ -14985,31 +14999,45 @@
       <c r="B20" s="77" t="s">
         <v>392</v>
       </c>
-      <c r="C20" s="74"/>
-      <c r="D20" s="74"/>
+      <c r="C20" s="74">
+        <v>38739110</v>
+      </c>
+      <c r="D20" s="74">
+        <v>84</v>
+      </c>
       <c r="E20" s="74"/>
       <c r="F20" s="74"/>
-      <c r="G20" s="74"/>
-      <c r="H20" s="74"/>
-      <c r="I20" s="74"/>
-      <c r="J20" s="74"/>
-      <c r="K20" s="74"/>
+      <c r="G20" s="74">
+        <v>9644005</v>
+      </c>
+      <c r="H20" s="74">
+        <v>3936252</v>
+      </c>
+      <c r="I20" s="74">
+        <v>6010506</v>
+      </c>
+      <c r="J20" s="74">
+        <v>60</v>
+      </c>
+      <c r="K20" s="74">
+        <v>1256000</v>
+      </c>
       <c r="L20" s="75"/>
-      <c r="M20" s="33" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N20" s="33" t="str">
+      <c r="M20" s="33">
+        <f t="shared" si="0"/>
+        <v>19590763</v>
+      </c>
+      <c r="N20" s="33">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O20" s="33" t="str">
+        <v>58329873</v>
+      </c>
+      <c r="O20" s="33">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="P20" s="33" t="str">
+        <v>461179.88095238095</v>
+      </c>
+      <c r="P20" s="33">
         <f t="shared" si="3"/>
-        <v/>
+        <v>326512.71666666667</v>
       </c>
       <c r="Q20" s="46" t="str">
         <f t="shared" si="4"/>
@@ -15023,31 +15051,43 @@
       <c r="B21" s="77" t="s">
         <v>393</v>
       </c>
-      <c r="C21" s="74"/>
-      <c r="D21" s="74"/>
+      <c r="C21" s="74">
+        <v>28614523</v>
+      </c>
+      <c r="D21" s="74">
+        <v>67</v>
+      </c>
       <c r="E21" s="74"/>
       <c r="F21" s="74"/>
-      <c r="G21" s="74"/>
-      <c r="H21" s="74"/>
-      <c r="I21" s="74"/>
-      <c r="J21" s="74"/>
+      <c r="G21" s="74">
+        <v>7116500</v>
+      </c>
+      <c r="H21" s="74">
+        <v>4767255</v>
+      </c>
+      <c r="I21" s="74">
+        <v>1694004</v>
+      </c>
+      <c r="J21" s="74">
+        <v>45</v>
+      </c>
       <c r="K21" s="74"/>
       <c r="L21" s="75"/>
-      <c r="M21" s="33" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N21" s="33" t="str">
+      <c r="M21" s="33">
+        <f t="shared" si="0"/>
+        <v>13577759</v>
+      </c>
+      <c r="N21" s="33">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O21" s="33" t="str">
+        <v>42192282</v>
+      </c>
+      <c r="O21" s="33">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="P21" s="33" t="str">
+        <v>427082.43283582089</v>
+      </c>
+      <c r="P21" s="33">
         <f t="shared" si="3"/>
-        <v/>
+        <v>301727.97777777776</v>
       </c>
       <c r="Q21" s="46" t="str">
         <f t="shared" si="4"/>
@@ -15826,36 +15866,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="177" t="s">
+      <c r="A1" s="178" t="s">
         <v>463</v>
       </c>
-      <c r="B1" s="158"/>
-      <c r="C1" s="158"/>
-      <c r="D1" s="158"/>
-      <c r="E1" s="158"/>
-      <c r="F1" s="158"/>
-      <c r="G1" s="158"/>
-      <c r="H1" s="158"/>
-      <c r="I1" s="158"/>
-      <c r="J1" s="158"/>
-      <c r="K1" s="158"/>
-      <c r="L1" s="158"/>
+      <c r="B1" s="159"/>
+      <c r="C1" s="159"/>
+      <c r="D1" s="159"/>
+      <c r="E1" s="159"/>
+      <c r="F1" s="159"/>
+      <c r="G1" s="159"/>
+      <c r="H1" s="159"/>
+      <c r="I1" s="159"/>
+      <c r="J1" s="159"/>
+      <c r="K1" s="159"/>
+      <c r="L1" s="159"/>
     </row>
     <row r="2" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="164" t="s">
+      <c r="A2" s="165" t="s">
         <v>404</v>
       </c>
-      <c r="B2" s="158"/>
-      <c r="C2" s="158"/>
-      <c r="D2" s="158"/>
-      <c r="E2" s="158"/>
-      <c r="F2" s="158"/>
-      <c r="G2" s="158"/>
-      <c r="H2" s="158"/>
-      <c r="I2" s="158"/>
-      <c r="J2" s="158"/>
-      <c r="K2" s="158"/>
-      <c r="L2" s="158"/>
+      <c r="B2" s="159"/>
+      <c r="C2" s="159"/>
+      <c r="D2" s="159"/>
+      <c r="E2" s="159"/>
+      <c r="F2" s="159"/>
+      <c r="G2" s="159"/>
+      <c r="H2" s="159"/>
+      <c r="I2" s="159"/>
+      <c r="J2" s="159"/>
+      <c r="K2" s="159"/>
+      <c r="L2" s="159"/>
     </row>
     <row r="3" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="60" t="s">
@@ -15949,15 +15989,15 @@
       </c>
       <c r="C5" s="80">
         <f>IFERROR(SUM('📅 DAILY T8'!C13:C19),0)</f>
-        <v>229515916</v>
+        <v>266852574</v>
       </c>
       <c r="D5" s="80">
         <f>IFERROR(SUM('📅 DAILY T8'!D13:D19),0)</f>
-        <v>540</v>
+        <v>629</v>
       </c>
       <c r="E5" s="80">
         <f>IFERROR(SUM('📅 DAILY T8'!C13:C19)/SUM('📅 DAILY T8'!D13:D19),"")</f>
-        <v>425029.47407407407</v>
+        <v>424248.92527821939</v>
       </c>
       <c r="F5" s="81">
         <f>IFERROR(SUM('📅 DAILY T8'!F13:F19),0)</f>
@@ -15969,19 +16009,19 @@
       </c>
       <c r="H5" s="83">
         <f>IFERROR(SUM('📅 DAILY T8'!M13:M19),0)</f>
-        <v>83810410</v>
+        <v>97036411</v>
       </c>
       <c r="I5" s="84">
         <f>IFERROR(SUM('📅 DAILY T8'!N13:N19),0)</f>
-        <v>313326326</v>
+        <v>363888985</v>
       </c>
       <c r="J5" s="85">
         <f>IFERROR(SUM('📅 DAILY T8'!C6:C19)/1292244677,"")</f>
-        <v>0.37315901437448906</v>
+        <v>0.40205188479178389</v>
       </c>
       <c r="K5" s="85">
         <f>IFERROR(SUM('📅 DAILY T8'!M6:M19)/730208327,"")</f>
-        <v>0.2884612366245996</v>
+        <v>0.30657387723818713</v>
       </c>
       <c r="L5" s="86"/>
     </row>
@@ -15994,15 +16034,15 @@
       </c>
       <c r="C6" s="80">
         <f>IFERROR(SUM('📅 DAILY T8'!C20:C26),0)</f>
-        <v>0</v>
+        <v>67353633</v>
       </c>
       <c r="D6" s="80">
         <f>IFERROR(SUM('📅 DAILY T8'!D20:D26),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E6" s="80" t="str">
+        <v>151</v>
+      </c>
+      <c r="E6" s="80">
         <f>IFERROR(SUM('📅 DAILY T8'!C20:C26)/SUM('📅 DAILY T8'!D20:D26),"")</f>
-        <v/>
+        <v>446050.54966887418</v>
       </c>
       <c r="F6" s="81">
         <f>IFERROR(SUM('📅 DAILY T8'!F20:F26),0)</f>
@@ -16014,19 +16054,19 @@
       </c>
       <c r="H6" s="83">
         <f>IFERROR(SUM('📅 DAILY T8'!M20:M26),0)</f>
-        <v>0</v>
+        <v>33168522</v>
       </c>
       <c r="I6" s="84">
         <f>IFERROR(SUM('📅 DAILY T8'!N20:N26),0)</f>
-        <v>0</v>
+        <v>100522155</v>
       </c>
       <c r="J6" s="85">
         <f>IFERROR(SUM('📅 DAILY T8'!C6:C26)/1292244677,"")</f>
-        <v>0.37315901437448906</v>
+        <v>0.45417330900717651</v>
       </c>
       <c r="K6" s="85">
         <f>IFERROR(SUM('📅 DAILY T8'!M6:M26)/730208327,"")</f>
-        <v>0.2884612366245996</v>
+        <v>0.35199724584899178</v>
       </c>
       <c r="L6" s="86"/>
     </row>
@@ -16067,11 +16107,11 @@
       </c>
       <c r="J7" s="85">
         <f>IFERROR(SUM('📅 DAILY T8'!C6:C33)/1292244677,"")</f>
-        <v>0.37315901437448906</v>
+        <v>0.45417330900717651</v>
       </c>
       <c r="K7" s="85">
         <f>IFERROR(SUM('📅 DAILY T8'!M6:M33)/730208327,"")</f>
-        <v>0.2884612366245996</v>
+        <v>0.35199724584899178</v>
       </c>
       <c r="L7" s="86"/>
     </row>
@@ -16106,11 +16146,11 @@
       </c>
       <c r="J8" s="85">
         <f>IFERROR(SUM('📅 DAILY T8'!C7:C34)/1292244677,"")</f>
-        <v>0.34278354315093845</v>
+        <v>0.42379783778362584</v>
       </c>
       <c r="K8" s="85">
         <f>IFERROR(SUM('📅 DAILY T8'!M7:M34)/730208327,"")</f>
-        <v>0.25438840414647862</v>
+        <v>0.3179244133708708</v>
       </c>
       <c r="L8" s="86"/>
     </row>
@@ -16151,11 +16191,11 @@
       </c>
       <c r="J9" s="85">
         <f>IFERROR(SUM('📅 DAILY T8'!C6:C36)/1292244677,"")</f>
-        <v>0.37315901437448906</v>
+        <v>0.45417330900717651</v>
       </c>
       <c r="K9" s="85">
         <f>IFERROR(SUM('📅 DAILY T8'!M6:M36)/730208327,"")</f>
-        <v>0.2884612366245996</v>
+        <v>0.35199724584899178</v>
       </c>
       <c r="L9" s="86"/>
     </row>
@@ -16204,15 +16244,15 @@
       </c>
       <c r="C22" s="98">
         <f>IFERROR(SUM('📅 DAILY T8'!C6:C36),0)</f>
-        <v>482212750</v>
+        <v>586903041</v>
       </c>
       <c r="D22" s="98">
         <f>IFERROR(SUM('📅 DAILY T8'!D6:D36),0)</f>
-        <v>1152</v>
+        <v>1392</v>
       </c>
       <c r="E22" s="98">
         <f>IFERROR(SUM('📅 DAILY T8'!C6:C36)/SUM('📅 DAILY T8'!D6:D36),"")</f>
-        <v>418587.45659722225</v>
+        <v>421625.74784482759</v>
       </c>
       <c r="F22" s="98">
         <f>IFERROR(SUM('📅 DAILY T8'!F6:F36),0)</f>
@@ -16224,28 +16264,28 @@
       </c>
       <c r="H22" s="98">
         <f>IFERROR(SUM('📅 DAILY T8'!M6:M36),0)</f>
-        <v>210636797</v>
+        <v>257031320</v>
       </c>
       <c r="I22" s="98">
         <f>IFERROR(SUM('📅 DAILY T8'!N6:N36),0)</f>
-        <v>692849547</v>
+        <v>843934361</v>
       </c>
       <c r="J22" s="100">
         <f>IFERROR(SUM('📅 DAILY T8'!C6:C36)/1292244677,"")</f>
-        <v>0.37315901437448906</v>
+        <v>0.45417330900717651</v>
       </c>
       <c r="K22" s="100">
         <f>IFERROR(SUM('📅 DAILY T8'!M6:M36)/730208327,"")</f>
-        <v>0.2884612366245996</v>
+        <v>0.35199724584899178</v>
       </c>
       <c r="L22" s="95"/>
     </row>
     <row r="23" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="24" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="180" t="s">
+      <c r="A24" s="183" t="s">
         <v>424</v>
       </c>
-      <c r="B24" s="158"/>
+      <c r="B24" s="159"/>
       <c r="C24" s="101">
         <v>1221751028</v>
       </c>
@@ -16265,20 +16305,20 @@
     </row>
     <row r="25" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="26" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="179" t="s">
+      <c r="A26" s="182" t="s">
         <v>425</v>
       </c>
-      <c r="B26" s="158"/>
-      <c r="C26" s="158"/>
-      <c r="D26" s="158"/>
-      <c r="E26" s="158"/>
-      <c r="F26" s="158"/>
-      <c r="G26" s="158"/>
-      <c r="H26" s="158"/>
-      <c r="I26" s="158"/>
-      <c r="J26" s="158"/>
-      <c r="K26" s="158"/>
-      <c r="L26" s="158"/>
+      <c r="B26" s="159"/>
+      <c r="C26" s="159"/>
+      <c r="D26" s="159"/>
+      <c r="E26" s="159"/>
+      <c r="F26" s="159"/>
+      <c r="G26" s="159"/>
+      <c r="H26" s="159"/>
+      <c r="I26" s="159"/>
+      <c r="J26" s="159"/>
+      <c r="K26" s="159"/>
+      <c r="L26" s="159"/>
     </row>
     <row r="27" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="28" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -16491,80 +16531,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="177" t="s">
+      <c r="A1" s="178" t="s">
         <v>471</v>
       </c>
-      <c r="B1" s="158"/>
-      <c r="C1" s="158"/>
-      <c r="D1" s="158"/>
-      <c r="E1" s="158"/>
-      <c r="F1" s="158"/>
-      <c r="G1" s="158"/>
-      <c r="H1" s="158"/>
-      <c r="I1" s="158"/>
-      <c r="J1" s="158"/>
-      <c r="K1" s="158"/>
-      <c r="L1" s="158"/>
-      <c r="M1" s="158"/>
-      <c r="N1" s="158"/>
-      <c r="O1" s="158"/>
-      <c r="P1" s="158"/>
-      <c r="Q1" s="158"/>
+      <c r="B1" s="159"/>
+      <c r="C1" s="159"/>
+      <c r="D1" s="159"/>
+      <c r="E1" s="159"/>
+      <c r="F1" s="159"/>
+      <c r="G1" s="159"/>
+      <c r="H1" s="159"/>
+      <c r="I1" s="159"/>
+      <c r="J1" s="159"/>
+      <c r="K1" s="159"/>
+      <c r="L1" s="159"/>
+      <c r="M1" s="159"/>
+      <c r="N1" s="159"/>
+      <c r="O1" s="159"/>
+      <c r="P1" s="159"/>
+      <c r="Q1" s="159"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="164" t="s">
+      <c r="A2" s="165" t="s">
         <v>360</v>
       </c>
-      <c r="B2" s="158"/>
-      <c r="C2" s="158"/>
-      <c r="D2" s="158"/>
-      <c r="E2" s="158"/>
-      <c r="F2" s="158"/>
-      <c r="G2" s="158"/>
-      <c r="H2" s="158"/>
-      <c r="I2" s="158"/>
-      <c r="J2" s="158"/>
-      <c r="K2" s="158"/>
-      <c r="L2" s="158"/>
-      <c r="M2" s="158"/>
-      <c r="N2" s="158"/>
-      <c r="O2" s="158"/>
-      <c r="P2" s="158"/>
-      <c r="Q2" s="158"/>
+      <c r="B2" s="159"/>
+      <c r="C2" s="159"/>
+      <c r="D2" s="159"/>
+      <c r="E2" s="159"/>
+      <c r="F2" s="159"/>
+      <c r="G2" s="159"/>
+      <c r="H2" s="159"/>
+      <c r="I2" s="159"/>
+      <c r="J2" s="159"/>
+      <c r="K2" s="159"/>
+      <c r="L2" s="159"/>
+      <c r="M2" s="159"/>
+      <c r="N2" s="159"/>
+      <c r="O2" s="159"/>
+      <c r="P2" s="159"/>
+      <c r="Q2" s="159"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="176" t="s">
+      <c r="A3" s="177" t="s">
         <v>361</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="175" t="s">
+      <c r="B3" s="159"/>
+      <c r="C3" s="176" t="s">
         <v>362</v>
       </c>
-      <c r="D3" s="158"/>
-      <c r="E3" s="178" t="s">
+      <c r="D3" s="159"/>
+      <c r="E3" s="179" t="s">
         <v>363</v>
       </c>
-      <c r="F3" s="158"/>
-      <c r="G3" s="173" t="s">
+      <c r="F3" s="159"/>
+      <c r="G3" s="174" t="s">
         <v>364</v>
       </c>
-      <c r="H3" s="158"/>
-      <c r="I3" s="158"/>
-      <c r="J3" s="158"/>
+      <c r="H3" s="159"/>
+      <c r="I3" s="159"/>
+      <c r="J3" s="159"/>
       <c r="K3" s="56" t="s">
         <v>365</v>
       </c>
       <c r="L3" s="57" t="s">
         <v>366</v>
       </c>
-      <c r="M3" s="172" t="s">
+      <c r="M3" s="173" t="s">
         <v>367</v>
       </c>
-      <c r="N3" s="158"/>
-      <c r="O3" s="172" t="s">
+      <c r="N3" s="159"/>
+      <c r="O3" s="173" t="s">
         <v>367</v>
       </c>
-      <c r="P3" s="158"/>
+      <c r="P3" s="159"/>
       <c r="Q3" s="58" t="s">
         <v>368</v>
       </c>
@@ -16623,10 +16663,10 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="174" t="s">
+      <c r="A5" s="175" t="s">
         <v>386</v>
       </c>
-      <c r="B5" s="158"/>
+      <c r="B5" s="159"/>
       <c r="C5" s="66">
         <v>1009097583</v>
       </c>
@@ -18001,40 +18041,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="185" t="s">
         <v>472</v>
       </c>
-      <c r="B1" s="170"/>
-      <c r="C1" s="170"/>
-      <c r="D1" s="170"/>
-      <c r="E1" s="170"/>
-      <c r="F1" s="170"/>
-      <c r="G1" s="170"/>
-      <c r="H1" s="170"/>
-      <c r="I1" s="170"/>
-      <c r="J1" s="170"/>
-      <c r="K1" s="170"/>
-      <c r="L1" s="170"/>
-      <c r="M1" s="170"/>
-      <c r="N1" s="170"/>
+      <c r="B1" s="171"/>
+      <c r="C1" s="171"/>
+      <c r="D1" s="171"/>
+      <c r="E1" s="171"/>
+      <c r="F1" s="171"/>
+      <c r="G1" s="171"/>
+      <c r="H1" s="171"/>
+      <c r="I1" s="171"/>
+      <c r="J1" s="171"/>
+      <c r="K1" s="171"/>
+      <c r="L1" s="171"/>
+      <c r="M1" s="171"/>
+      <c r="N1" s="171"/>
     </row>
     <row r="2" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="183" t="s">
+      <c r="A2" s="184" t="s">
         <v>404</v>
       </c>
-      <c r="B2" s="170"/>
-      <c r="C2" s="170"/>
-      <c r="D2" s="170"/>
-      <c r="E2" s="170"/>
-      <c r="F2" s="170"/>
-      <c r="G2" s="170"/>
-      <c r="H2" s="170"/>
-      <c r="I2" s="170"/>
-      <c r="J2" s="170"/>
-      <c r="K2" s="170"/>
-      <c r="L2" s="170"/>
-      <c r="M2" s="170"/>
-      <c r="N2" s="170"/>
+      <c r="B2" s="171"/>
+      <c r="C2" s="171"/>
+      <c r="D2" s="171"/>
+      <c r="E2" s="171"/>
+      <c r="F2" s="171"/>
+      <c r="G2" s="171"/>
+      <c r="H2" s="171"/>
+      <c r="I2" s="171"/>
+      <c r="J2" s="171"/>
+      <c r="K2" s="171"/>
+      <c r="L2" s="171"/>
+      <c r="M2" s="171"/>
+      <c r="N2" s="171"/>
     </row>
     <row r="3" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="141" t="s">
@@ -18364,57 +18404,57 @@
       <c r="A1" s="168" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="158"/>
-      <c r="C1" s="158"/>
-      <c r="D1" s="158"/>
-      <c r="E1" s="158"/>
-      <c r="F1" s="158"/>
-      <c r="G1" s="158"/>
-      <c r="H1" s="158"/>
-      <c r="I1" s="158"/>
-      <c r="J1" s="158"/>
-      <c r="K1" s="158"/>
-      <c r="L1" s="158"/>
-      <c r="M1" s="158"/>
-      <c r="N1" s="158"/>
-      <c r="O1" s="158"/>
-      <c r="P1" s="158"/>
-      <c r="Q1" s="158"/>
-      <c r="R1" s="158"/>
-      <c r="S1" s="158"/>
-      <c r="T1" s="158"/>
-      <c r="U1" s="158"/>
-      <c r="V1" s="158"/>
-      <c r="W1" s="158"/>
-      <c r="X1" s="158"/>
+      <c r="B1" s="159"/>
+      <c r="C1" s="159"/>
+      <c r="D1" s="159"/>
+      <c r="E1" s="159"/>
+      <c r="F1" s="159"/>
+      <c r="G1" s="159"/>
+      <c r="H1" s="159"/>
+      <c r="I1" s="159"/>
+      <c r="J1" s="159"/>
+      <c r="K1" s="159"/>
+      <c r="L1" s="159"/>
+      <c r="M1" s="159"/>
+      <c r="N1" s="159"/>
+      <c r="O1" s="159"/>
+      <c r="P1" s="159"/>
+      <c r="Q1" s="159"/>
+      <c r="R1" s="159"/>
+      <c r="S1" s="159"/>
+      <c r="T1" s="159"/>
+      <c r="U1" s="159"/>
+      <c r="V1" s="159"/>
+      <c r="W1" s="159"/>
+      <c r="X1" s="159"/>
     </row>
     <row r="2" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="164" t="s">
+      <c r="A2" s="165" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="158"/>
-      <c r="C2" s="158"/>
-      <c r="D2" s="158"/>
-      <c r="E2" s="158"/>
-      <c r="F2" s="158"/>
-      <c r="G2" s="158"/>
-      <c r="H2" s="158"/>
-      <c r="I2" s="158"/>
-      <c r="J2" s="158"/>
-      <c r="K2" s="158"/>
-      <c r="L2" s="158"/>
-      <c r="M2" s="158"/>
-      <c r="N2" s="158"/>
-      <c r="O2" s="158"/>
-      <c r="P2" s="158"/>
-      <c r="Q2" s="158"/>
-      <c r="R2" s="158"/>
-      <c r="S2" s="158"/>
-      <c r="T2" s="158"/>
-      <c r="U2" s="158"/>
-      <c r="V2" s="158"/>
-      <c r="W2" s="158"/>
-      <c r="X2" s="158"/>
+      <c r="B2" s="159"/>
+      <c r="C2" s="159"/>
+      <c r="D2" s="159"/>
+      <c r="E2" s="159"/>
+      <c r="F2" s="159"/>
+      <c r="G2" s="159"/>
+      <c r="H2" s="159"/>
+      <c r="I2" s="159"/>
+      <c r="J2" s="159"/>
+      <c r="K2" s="159"/>
+      <c r="L2" s="159"/>
+      <c r="M2" s="159"/>
+      <c r="N2" s="159"/>
+      <c r="O2" s="159"/>
+      <c r="P2" s="159"/>
+      <c r="Q2" s="159"/>
+      <c r="R2" s="159"/>
+      <c r="S2" s="159"/>
+      <c r="T2" s="159"/>
+      <c r="U2" s="159"/>
+      <c r="V2" s="159"/>
+      <c r="W2" s="159"/>
+      <c r="X2" s="159"/>
     </row>
     <row r="3" spans="1:24" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="26" t="s">
@@ -18491,60 +18531,60 @@
       </c>
     </row>
     <row r="4" spans="1:24" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="162" t="s">
+      <c r="A4" s="163" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="158"/>
-      <c r="C4" s="158"/>
-      <c r="D4" s="158"/>
-      <c r="E4" s="158"/>
-      <c r="F4" s="158"/>
-      <c r="G4" s="158"/>
-      <c r="H4" s="158"/>
-      <c r="I4" s="158"/>
-      <c r="J4" s="158"/>
-      <c r="K4" s="158"/>
-      <c r="L4" s="158"/>
-      <c r="M4" s="158"/>
-      <c r="N4" s="158"/>
-      <c r="O4" s="158"/>
-      <c r="P4" s="158"/>
-      <c r="Q4" s="158"/>
-      <c r="R4" s="158"/>
-      <c r="S4" s="158"/>
-      <c r="T4" s="158"/>
-      <c r="U4" s="158"/>
-      <c r="V4" s="158"/>
-      <c r="W4" s="158"/>
-      <c r="X4" s="158"/>
+      <c r="B4" s="159"/>
+      <c r="C4" s="159"/>
+      <c r="D4" s="159"/>
+      <c r="E4" s="159"/>
+      <c r="F4" s="159"/>
+      <c r="G4" s="159"/>
+      <c r="H4" s="159"/>
+      <c r="I4" s="159"/>
+      <c r="J4" s="159"/>
+      <c r="K4" s="159"/>
+      <c r="L4" s="159"/>
+      <c r="M4" s="159"/>
+      <c r="N4" s="159"/>
+      <c r="O4" s="159"/>
+      <c r="P4" s="159"/>
+      <c r="Q4" s="159"/>
+      <c r="R4" s="159"/>
+      <c r="S4" s="159"/>
+      <c r="T4" s="159"/>
+      <c r="U4" s="159"/>
+      <c r="V4" s="159"/>
+      <c r="W4" s="159"/>
+      <c r="X4" s="159"/>
     </row>
     <row r="5" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="167" t="s">
+      <c r="A5" s="169" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="158"/>
-      <c r="C5" s="158"/>
-      <c r="D5" s="158"/>
-      <c r="E5" s="158"/>
-      <c r="F5" s="158"/>
-      <c r="G5" s="158"/>
-      <c r="H5" s="158"/>
-      <c r="I5" s="158"/>
-      <c r="J5" s="158"/>
-      <c r="K5" s="158"/>
-      <c r="L5" s="158"/>
-      <c r="M5" s="158"/>
-      <c r="N5" s="158"/>
-      <c r="O5" s="158"/>
-      <c r="P5" s="158"/>
-      <c r="Q5" s="158"/>
-      <c r="R5" s="158"/>
-      <c r="S5" s="158"/>
-      <c r="T5" s="158"/>
-      <c r="U5" s="158"/>
-      <c r="V5" s="158"/>
-      <c r="W5" s="158"/>
-      <c r="X5" s="158"/>
+      <c r="B5" s="159"/>
+      <c r="C5" s="159"/>
+      <c r="D5" s="159"/>
+      <c r="E5" s="159"/>
+      <c r="F5" s="159"/>
+      <c r="G5" s="159"/>
+      <c r="H5" s="159"/>
+      <c r="I5" s="159"/>
+      <c r="J5" s="159"/>
+      <c r="K5" s="159"/>
+      <c r="L5" s="159"/>
+      <c r="M5" s="159"/>
+      <c r="N5" s="159"/>
+      <c r="O5" s="159"/>
+      <c r="P5" s="159"/>
+      <c r="Q5" s="159"/>
+      <c r="R5" s="159"/>
+      <c r="S5" s="159"/>
+      <c r="T5" s="159"/>
+      <c r="U5" s="159"/>
+      <c r="V5" s="159"/>
+      <c r="W5" s="159"/>
+      <c r="X5" s="159"/>
     </row>
     <row r="6" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="29"/>
@@ -18612,7 +18652,7 @@
         <v>1192707123</v>
       </c>
       <c r="W6" s="33">
-        <v>482212750</v>
+        <v>586903041</v>
       </c>
       <c r="X6" s="33">
         <f>IFERROR(SUM('📅 DAILY T9'!C$6:C$35),0)</f>
@@ -18685,7 +18725,7 @@
         <v>2823</v>
       </c>
       <c r="W7" s="33">
-        <v>1152</v>
+        <v>1392</v>
       </c>
       <c r="X7" s="33">
         <f>IFERROR(SUM('📅 DAILY T9'!D$6:D$35),0)</f>
@@ -18758,7 +18798,7 @@
         <v>422496</v>
       </c>
       <c r="W8" s="33">
-        <v>418587</v>
+        <v>421626</v>
       </c>
       <c r="X8" s="33" t="str">
         <f>IFERROR(SUM('📅 DAILY T9'!C$6:C$35)/SUM('📅 DAILY T9'!D$6:D$35),"")</f>
@@ -18831,7 +18871,7 @@
         <v>5129</v>
       </c>
       <c r="W9" s="36">
-        <v>2381</v>
+        <v>2474</v>
       </c>
       <c r="X9" s="36"/>
     </row>
@@ -18949,7 +18989,7 @@
       </c>
       <c r="W11" s="37">
         <f t="shared" si="0"/>
-        <v>0.4838303233935321</v>
+        <v>0.56265157639450281</v>
       </c>
       <c r="X11" s="38"/>
     </row>
@@ -18982,60 +19022,60 @@
       <c r="X12" s="39"/>
     </row>
     <row r="13" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="167" t="s">
+      <c r="A13" s="169" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="158"/>
-      <c r="C13" s="158"/>
-      <c r="D13" s="158"/>
-      <c r="E13" s="158"/>
-      <c r="F13" s="158"/>
-      <c r="G13" s="158"/>
-      <c r="H13" s="158"/>
-      <c r="I13" s="158"/>
-      <c r="J13" s="158"/>
-      <c r="K13" s="158"/>
-      <c r="L13" s="158"/>
-      <c r="M13" s="158"/>
-      <c r="N13" s="158"/>
-      <c r="O13" s="158"/>
-      <c r="P13" s="158"/>
-      <c r="Q13" s="158"/>
-      <c r="R13" s="158"/>
-      <c r="S13" s="158"/>
-      <c r="T13" s="158"/>
-      <c r="U13" s="158"/>
-      <c r="V13" s="158"/>
-      <c r="W13" s="158"/>
-      <c r="X13" s="158"/>
+      <c r="B13" s="159"/>
+      <c r="C13" s="159"/>
+      <c r="D13" s="159"/>
+      <c r="E13" s="159"/>
+      <c r="F13" s="159"/>
+      <c r="G13" s="159"/>
+      <c r="H13" s="159"/>
+      <c r="I13" s="159"/>
+      <c r="J13" s="159"/>
+      <c r="K13" s="159"/>
+      <c r="L13" s="159"/>
+      <c r="M13" s="159"/>
+      <c r="N13" s="159"/>
+      <c r="O13" s="159"/>
+      <c r="P13" s="159"/>
+      <c r="Q13" s="159"/>
+      <c r="R13" s="159"/>
+      <c r="S13" s="159"/>
+      <c r="T13" s="159"/>
+      <c r="U13" s="159"/>
+      <c r="V13" s="159"/>
+      <c r="W13" s="159"/>
+      <c r="X13" s="159"/>
     </row>
     <row r="14" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="161" t="s">
+      <c r="A14" s="162" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="158"/>
-      <c r="C14" s="158"/>
-      <c r="D14" s="158"/>
-      <c r="E14" s="158"/>
-      <c r="F14" s="158"/>
-      <c r="G14" s="158"/>
-      <c r="H14" s="158"/>
-      <c r="I14" s="158"/>
-      <c r="J14" s="158"/>
-      <c r="K14" s="158"/>
-      <c r="L14" s="158"/>
-      <c r="M14" s="158"/>
-      <c r="N14" s="158"/>
-      <c r="O14" s="158"/>
-      <c r="P14" s="158"/>
-      <c r="Q14" s="158"/>
-      <c r="R14" s="158"/>
-      <c r="S14" s="158"/>
-      <c r="T14" s="158"/>
-      <c r="U14" s="158"/>
-      <c r="V14" s="158"/>
-      <c r="W14" s="158"/>
-      <c r="X14" s="158"/>
+      <c r="B14" s="159"/>
+      <c r="C14" s="159"/>
+      <c r="D14" s="159"/>
+      <c r="E14" s="159"/>
+      <c r="F14" s="159"/>
+      <c r="G14" s="159"/>
+      <c r="H14" s="159"/>
+      <c r="I14" s="159"/>
+      <c r="J14" s="159"/>
+      <c r="K14" s="159"/>
+      <c r="L14" s="159"/>
+      <c r="M14" s="159"/>
+      <c r="N14" s="159"/>
+      <c r="O14" s="159"/>
+      <c r="P14" s="159"/>
+      <c r="Q14" s="159"/>
+      <c r="R14" s="159"/>
+      <c r="S14" s="159"/>
+      <c r="T14" s="159"/>
+      <c r="U14" s="159"/>
+      <c r="V14" s="159"/>
+      <c r="W14" s="159"/>
+      <c r="X14" s="159"/>
     </row>
     <row r="15" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="29"/>
@@ -19103,7 +19143,7 @@
         <v>824</v>
       </c>
       <c r="W15" s="36">
-        <v>328</v>
+        <v>403</v>
       </c>
       <c r="X15" s="36"/>
     </row>
@@ -19173,7 +19213,7 @@
         <v>393944</v>
       </c>
       <c r="W16" s="36">
-        <v>424940</v>
+        <v>430758</v>
       </c>
       <c r="X16" s="36"/>
     </row>
@@ -19243,7 +19283,7 @@
         <v>0.1394</v>
       </c>
       <c r="W17" s="38">
-        <v>0.1502</v>
+        <v>4.87E-2</v>
       </c>
       <c r="X17" s="38"/>
     </row>
@@ -19313,37 +19353,37 @@
         <v>0.1021</v>
       </c>
       <c r="W18" s="38">
-        <v>4.6199999999999998E-2</v>
+        <v>5.3499999999999999E-2</v>
       </c>
       <c r="X18" s="38"/>
     </row>
     <row r="19" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="161" t="s">
+      <c r="A19" s="162" t="s">
         <v>46</v>
       </c>
-      <c r="B19" s="158"/>
-      <c r="C19" s="158"/>
-      <c r="D19" s="158"/>
-      <c r="E19" s="158"/>
-      <c r="F19" s="158"/>
-      <c r="G19" s="158"/>
-      <c r="H19" s="158"/>
-      <c r="I19" s="158"/>
-      <c r="J19" s="158"/>
-      <c r="K19" s="158"/>
-      <c r="L19" s="158"/>
-      <c r="M19" s="158"/>
-      <c r="N19" s="158"/>
-      <c r="O19" s="158"/>
-      <c r="P19" s="158"/>
-      <c r="Q19" s="158"/>
-      <c r="R19" s="158"/>
-      <c r="S19" s="158"/>
-      <c r="T19" s="158"/>
-      <c r="U19" s="158"/>
-      <c r="V19" s="158"/>
-      <c r="W19" s="158"/>
-      <c r="X19" s="158"/>
+      <c r="B19" s="159"/>
+      <c r="C19" s="159"/>
+      <c r="D19" s="159"/>
+      <c r="E19" s="159"/>
+      <c r="F19" s="159"/>
+      <c r="G19" s="159"/>
+      <c r="H19" s="159"/>
+      <c r="I19" s="159"/>
+      <c r="J19" s="159"/>
+      <c r="K19" s="159"/>
+      <c r="L19" s="159"/>
+      <c r="M19" s="159"/>
+      <c r="N19" s="159"/>
+      <c r="O19" s="159"/>
+      <c r="P19" s="159"/>
+      <c r="Q19" s="159"/>
+      <c r="R19" s="159"/>
+      <c r="S19" s="159"/>
+      <c r="T19" s="159"/>
+      <c r="U19" s="159"/>
+      <c r="V19" s="159"/>
+      <c r="W19" s="159"/>
+      <c r="X19" s="159"/>
     </row>
     <row r="20" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="29"/>
@@ -19411,7 +19451,7 @@
         <v>1739</v>
       </c>
       <c r="W20" s="36">
-        <v>773</v>
+        <v>916</v>
       </c>
       <c r="X20" s="36"/>
     </row>
@@ -19481,7 +19521,7 @@
         <v>457245</v>
       </c>
       <c r="W21" s="36">
-        <v>445462</v>
+        <v>454269</v>
       </c>
       <c r="X21" s="36"/>
     </row>
@@ -19551,7 +19591,7 @@
         <v>0.67849999999999999</v>
       </c>
       <c r="W22" s="38">
-        <v>0.70209999999999995</v>
+        <v>0.69450000000000001</v>
       </c>
       <c r="X22" s="38"/>
     </row>
@@ -19621,7 +19661,7 @@
         <v>458</v>
       </c>
       <c r="W23" s="36">
-        <v>217</v>
+        <v>273</v>
       </c>
       <c r="X23" s="36"/>
     </row>
@@ -19691,7 +19731,7 @@
         <v>410866</v>
       </c>
       <c r="W24" s="36">
-        <v>404949</v>
+        <v>417935</v>
       </c>
       <c r="X24" s="36"/>
     </row>
@@ -19761,7 +19801,7 @@
         <v>520</v>
       </c>
       <c r="W25" s="36">
-        <v>233</v>
+        <v>266</v>
       </c>
       <c r="X25" s="36"/>
     </row>
@@ -19831,7 +19871,7 @@
         <v>472067</v>
       </c>
       <c r="W26" s="36">
-        <v>470164</v>
+        <v>486224</v>
       </c>
       <c r="X26" s="36"/>
     </row>
@@ -19901,7 +19941,7 @@
         <v>761</v>
       </c>
       <c r="W27" s="36">
-        <v>323</v>
+        <v>377</v>
       </c>
       <c r="X27" s="36"/>
     </row>
@@ -19971,37 +20011,37 @@
         <v>476924</v>
       </c>
       <c r="W28" s="36">
-        <v>454862</v>
+        <v>458033</v>
       </c>
       <c r="X28" s="36"/>
     </row>
     <row r="29" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="161" t="s">
+      <c r="A29" s="162" t="s">
         <v>54</v>
       </c>
-      <c r="B29" s="158"/>
-      <c r="C29" s="158"/>
-      <c r="D29" s="158"/>
-      <c r="E29" s="158"/>
-      <c r="F29" s="158"/>
-      <c r="G29" s="158"/>
-      <c r="H29" s="158"/>
-      <c r="I29" s="158"/>
-      <c r="J29" s="158"/>
-      <c r="K29" s="158"/>
-      <c r="L29" s="158"/>
-      <c r="M29" s="158"/>
-      <c r="N29" s="158"/>
-      <c r="O29" s="158"/>
-      <c r="P29" s="158"/>
-      <c r="Q29" s="158"/>
-      <c r="R29" s="158"/>
-      <c r="S29" s="158"/>
-      <c r="T29" s="158"/>
-      <c r="U29" s="158"/>
-      <c r="V29" s="158"/>
-      <c r="W29" s="158"/>
-      <c r="X29" s="158"/>
+      <c r="B29" s="159"/>
+      <c r="C29" s="159"/>
+      <c r="D29" s="159"/>
+      <c r="E29" s="159"/>
+      <c r="F29" s="159"/>
+      <c r="G29" s="159"/>
+      <c r="H29" s="159"/>
+      <c r="I29" s="159"/>
+      <c r="J29" s="159"/>
+      <c r="K29" s="159"/>
+      <c r="L29" s="159"/>
+      <c r="M29" s="159"/>
+      <c r="N29" s="159"/>
+      <c r="O29" s="159"/>
+      <c r="P29" s="159"/>
+      <c r="Q29" s="159"/>
+      <c r="R29" s="159"/>
+      <c r="S29" s="159"/>
+      <c r="T29" s="159"/>
+      <c r="U29" s="159"/>
+      <c r="V29" s="159"/>
+      <c r="W29" s="159"/>
+      <c r="X29" s="159"/>
     </row>
     <row r="30" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="29"/>
@@ -20069,7 +20109,7 @@
         <v>1788</v>
       </c>
       <c r="W30" s="36">
-        <v>635</v>
+        <v>743</v>
       </c>
       <c r="X30" s="36"/>
     </row>
@@ -20139,7 +20179,7 @@
         <v>452381</v>
       </c>
       <c r="W31" s="36">
-        <v>471638</v>
+        <v>477771</v>
       </c>
       <c r="X31" s="36"/>
     </row>
@@ -20152,122 +20192,122 @@
         <v>58</v>
       </c>
       <c r="D32" s="32">
-        <v>720380</v>
+        <v>2063244</v>
       </c>
       <c r="E32" s="32">
-        <v>736036</v>
+        <v>2082315</v>
       </c>
       <c r="F32" s="32">
-        <v>755899</v>
+        <v>2020803</v>
       </c>
       <c r="G32" s="32">
-        <v>767863</v>
+        <v>1950883</v>
       </c>
       <c r="H32" s="32">
-        <v>780860</v>
+        <v>1922893</v>
       </c>
       <c r="I32" s="32">
-        <v>773057</v>
+        <v>1843000</v>
       </c>
       <c r="J32" s="32">
-        <v>767234</v>
+        <v>1913799</v>
       </c>
       <c r="K32" s="32">
-        <v>758348</v>
+        <v>1787450</v>
       </c>
       <c r="L32" s="32">
-        <v>751369</v>
+        <v>1737007</v>
       </c>
       <c r="M32" s="32">
-        <v>745530</v>
+        <v>1699589</v>
       </c>
       <c r="N32" s="32">
-        <v>746054</v>
+        <v>1677293</v>
       </c>
       <c r="O32" s="32">
-        <v>751135</v>
+        <v>1757426</v>
       </c>
       <c r="P32" s="32">
-        <v>748857</v>
+        <v>1820648</v>
       </c>
       <c r="Q32" s="32">
-        <v>748498</v>
+        <v>1799499</v>
       </c>
       <c r="R32" s="32">
-        <v>745025</v>
+        <v>1776990</v>
       </c>
       <c r="S32" s="32">
-        <v>751102</v>
+        <v>1827510</v>
       </c>
       <c r="T32" s="32">
-        <v>756186</v>
+        <v>1794170</v>
       </c>
       <c r="U32" s="36">
-        <v>804514</v>
+        <v>1524894</v>
       </c>
       <c r="V32" s="36">
-        <v>988687</v>
+        <v>1589471</v>
       </c>
       <c r="W32" s="36">
-        <v>810188</v>
+        <v>1579126</v>
       </c>
       <c r="X32" s="36"/>
     </row>
     <row r="33" spans="1:24" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="166" t="s">
+      <c r="A33" s="167" t="s">
         <v>59</v>
       </c>
-      <c r="B33" s="158"/>
-      <c r="C33" s="158"/>
-      <c r="D33" s="158"/>
-      <c r="E33" s="158"/>
-      <c r="F33" s="158"/>
-      <c r="G33" s="158"/>
-      <c r="H33" s="158"/>
-      <c r="I33" s="158"/>
-      <c r="J33" s="158"/>
-      <c r="K33" s="158"/>
-      <c r="L33" s="158"/>
-      <c r="M33" s="158"/>
-      <c r="N33" s="158"/>
-      <c r="O33" s="158"/>
-      <c r="P33" s="158"/>
-      <c r="Q33" s="158"/>
-      <c r="R33" s="158"/>
-      <c r="S33" s="158"/>
-      <c r="T33" s="158"/>
-      <c r="U33" s="158"/>
-      <c r="V33" s="158"/>
-      <c r="W33" s="158"/>
-      <c r="X33" s="158"/>
+      <c r="B33" s="159"/>
+      <c r="C33" s="159"/>
+      <c r="D33" s="159"/>
+      <c r="E33" s="159"/>
+      <c r="F33" s="159"/>
+      <c r="G33" s="159"/>
+      <c r="H33" s="159"/>
+      <c r="I33" s="159"/>
+      <c r="J33" s="159"/>
+      <c r="K33" s="159"/>
+      <c r="L33" s="159"/>
+      <c r="M33" s="159"/>
+      <c r="N33" s="159"/>
+      <c r="O33" s="159"/>
+      <c r="P33" s="159"/>
+      <c r="Q33" s="159"/>
+      <c r="R33" s="159"/>
+      <c r="S33" s="159"/>
+      <c r="T33" s="159"/>
+      <c r="U33" s="159"/>
+      <c r="V33" s="159"/>
+      <c r="W33" s="159"/>
+      <c r="X33" s="159"/>
     </row>
     <row r="34" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="160" t="s">
+      <c r="A34" s="158" t="s">
         <v>60</v>
       </c>
-      <c r="B34" s="158"/>
-      <c r="C34" s="158"/>
-      <c r="D34" s="158"/>
-      <c r="E34" s="158"/>
-      <c r="F34" s="158"/>
-      <c r="G34" s="158"/>
-      <c r="H34" s="158"/>
-      <c r="I34" s="158"/>
-      <c r="J34" s="158"/>
-      <c r="K34" s="158"/>
-      <c r="L34" s="158"/>
-      <c r="M34" s="158"/>
-      <c r="N34" s="158"/>
-      <c r="O34" s="158"/>
-      <c r="P34" s="158"/>
-      <c r="Q34" s="158"/>
-      <c r="R34" s="158"/>
-      <c r="S34" s="158"/>
-      <c r="T34" s="158"/>
-      <c r="U34" s="158"/>
-      <c r="V34" s="158"/>
-      <c r="W34" s="158"/>
-      <c r="X34" s="158"/>
+      <c r="B34" s="159"/>
+      <c r="C34" s="159"/>
+      <c r="D34" s="159"/>
+      <c r="E34" s="159"/>
+      <c r="F34" s="159"/>
+      <c r="G34" s="159"/>
+      <c r="H34" s="159"/>
+      <c r="I34" s="159"/>
+      <c r="J34" s="159"/>
+      <c r="K34" s="159"/>
+      <c r="L34" s="159"/>
+      <c r="M34" s="159"/>
+      <c r="N34" s="159"/>
+      <c r="O34" s="159"/>
+      <c r="P34" s="159"/>
+      <c r="Q34" s="159"/>
+      <c r="R34" s="159"/>
+      <c r="S34" s="159"/>
+      <c r="T34" s="159"/>
+      <c r="U34" s="159"/>
+      <c r="V34" s="159"/>
+      <c r="W34" s="159"/>
+      <c r="X34" s="159"/>
     </row>
     <row r="35" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="45"/>
@@ -20335,7 +20375,7 @@
         <v>530083436</v>
       </c>
       <c r="W35" s="33">
-        <v>210636797</v>
+        <v>257031320</v>
       </c>
       <c r="X35" s="33">
         <f>IFERROR(SUM('📅 DAILY T9'!G$6:I$35),0)</f>
@@ -20408,7 +20448,7 @@
         <v>272494091</v>
       </c>
       <c r="W36" s="33">
-        <v>101386187</v>
+        <v>123880693</v>
       </c>
       <c r="X36" s="33">
         <f>IFERROR(SUM('📅 DAILY T9'!G$6:G$35),0)</f>
@@ -20481,7 +20521,7 @@
         <v>129188093</v>
       </c>
       <c r="W37" s="33">
-        <v>56268354</v>
+        <v>69200862</v>
       </c>
       <c r="X37" s="33">
         <f>IFERROR(SUM('📅 DAILY T9'!H$6:H$35),0)</f>
@@ -20554,7 +20594,7 @@
         <v>128401252</v>
       </c>
       <c r="W38" s="33">
-        <v>52982256</v>
+        <v>63949765</v>
       </c>
       <c r="X38" s="33">
         <f>IFERROR(SUM('📅 DAILY T9'!I$6:I$35),0)</f>
@@ -20627,7 +20667,7 @@
         <v>1717</v>
       </c>
       <c r="W39" s="33">
-        <v>693</v>
+        <v>848</v>
       </c>
       <c r="X39" s="33">
         <f>IFERROR(SUM('📅 DAILY T9'!J$6:J$35),0)</f>
@@ -20700,7 +20740,7 @@
         <v>308727</v>
       </c>
       <c r="W40" s="33">
-        <v>303949</v>
+        <v>303103</v>
       </c>
       <c r="X40" s="33" t="str">
         <f>IFERROR(SUM('📅 DAILY T9'!M$6:M$35)/SUM('📅 DAILY T9'!J$6:J$35),"")</f>
@@ -20708,56 +20748,56 @@
       </c>
     </row>
     <row r="41" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="165"/>
-      <c r="B41" s="158"/>
-      <c r="C41" s="158"/>
-      <c r="D41" s="158"/>
-      <c r="E41" s="158"/>
-      <c r="F41" s="158"/>
-      <c r="G41" s="158"/>
-      <c r="H41" s="158"/>
-      <c r="I41" s="158"/>
-      <c r="J41" s="158"/>
-      <c r="K41" s="158"/>
-      <c r="L41" s="158"/>
-      <c r="M41" s="158"/>
-      <c r="N41" s="158"/>
-      <c r="O41" s="158"/>
-      <c r="P41" s="158"/>
-      <c r="Q41" s="158"/>
-      <c r="R41" s="158"/>
-      <c r="S41" s="158"/>
-      <c r="T41" s="158"/>
-      <c r="U41" s="158"/>
-      <c r="V41" s="158"/>
-      <c r="W41" s="158"/>
-      <c r="X41" s="159"/>
+      <c r="A41" s="166"/>
+      <c r="B41" s="159"/>
+      <c r="C41" s="159"/>
+      <c r="D41" s="159"/>
+      <c r="E41" s="159"/>
+      <c r="F41" s="159"/>
+      <c r="G41" s="159"/>
+      <c r="H41" s="159"/>
+      <c r="I41" s="159"/>
+      <c r="J41" s="159"/>
+      <c r="K41" s="159"/>
+      <c r="L41" s="159"/>
+      <c r="M41" s="159"/>
+      <c r="N41" s="159"/>
+      <c r="O41" s="159"/>
+      <c r="P41" s="159"/>
+      <c r="Q41" s="159"/>
+      <c r="R41" s="159"/>
+      <c r="S41" s="159"/>
+      <c r="T41" s="159"/>
+      <c r="U41" s="159"/>
+      <c r="V41" s="159"/>
+      <c r="W41" s="159"/>
+      <c r="X41" s="161"/>
     </row>
     <row r="42" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="165"/>
-      <c r="B42" s="158"/>
-      <c r="C42" s="158"/>
-      <c r="D42" s="158"/>
-      <c r="E42" s="158"/>
-      <c r="F42" s="158"/>
-      <c r="G42" s="158"/>
-      <c r="H42" s="158"/>
-      <c r="I42" s="158"/>
-      <c r="J42" s="158"/>
-      <c r="K42" s="158"/>
-      <c r="L42" s="158"/>
-      <c r="M42" s="158"/>
-      <c r="N42" s="158"/>
-      <c r="O42" s="158"/>
-      <c r="P42" s="158"/>
-      <c r="Q42" s="158"/>
-      <c r="R42" s="158"/>
-      <c r="S42" s="158"/>
-      <c r="T42" s="158"/>
-      <c r="U42" s="158"/>
-      <c r="V42" s="158"/>
-      <c r="W42" s="158"/>
-      <c r="X42" s="159"/>
+      <c r="A42" s="166"/>
+      <c r="B42" s="159"/>
+      <c r="C42" s="159"/>
+      <c r="D42" s="159"/>
+      <c r="E42" s="159"/>
+      <c r="F42" s="159"/>
+      <c r="G42" s="159"/>
+      <c r="H42" s="159"/>
+      <c r="I42" s="159"/>
+      <c r="J42" s="159"/>
+      <c r="K42" s="159"/>
+      <c r="L42" s="159"/>
+      <c r="M42" s="159"/>
+      <c r="N42" s="159"/>
+      <c r="O42" s="159"/>
+      <c r="P42" s="159"/>
+      <c r="Q42" s="159"/>
+      <c r="R42" s="159"/>
+      <c r="S42" s="159"/>
+      <c r="T42" s="159"/>
+      <c r="U42" s="159"/>
+      <c r="V42" s="159"/>
+      <c r="W42" s="159"/>
+      <c r="X42" s="161"/>
     </row>
     <row r="43" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="45"/>
@@ -20825,7 +20865,7 @@
         <v>613</v>
       </c>
       <c r="W43" s="36">
-        <v>225</v>
+        <v>275</v>
       </c>
       <c r="X43" s="36"/>
     </row>
@@ -20895,7 +20935,7 @@
         <v>301500</v>
       </c>
       <c r="W44" s="36">
-        <v>340228</v>
+        <v>343147</v>
       </c>
       <c r="X44" s="36"/>
     </row>
@@ -20965,7 +21005,7 @@
         <v>0.14330000000000001</v>
       </c>
       <c r="W45" s="38">
-        <v>0.14219999999999999</v>
+        <v>2.8000000000000001E-2</v>
       </c>
       <c r="X45" s="38"/>
     </row>
@@ -21035,37 +21075,37 @@
         <v>5.8999999999999997E-2</v>
       </c>
       <c r="W46" s="38">
-        <v>3.27E-2</v>
+        <v>3.5799999999999998E-2</v>
       </c>
       <c r="X46" s="38"/>
     </row>
     <row r="47" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="161" t="s">
+      <c r="A47" s="162" t="s">
         <v>46</v>
       </c>
-      <c r="B47" s="158"/>
-      <c r="C47" s="158"/>
-      <c r="D47" s="158"/>
-      <c r="E47" s="158"/>
-      <c r="F47" s="158"/>
-      <c r="G47" s="158"/>
-      <c r="H47" s="158"/>
-      <c r="I47" s="158"/>
-      <c r="J47" s="158"/>
-      <c r="K47" s="158"/>
-      <c r="L47" s="158"/>
-      <c r="M47" s="158"/>
-      <c r="N47" s="158"/>
-      <c r="O47" s="158"/>
-      <c r="P47" s="158"/>
-      <c r="Q47" s="158"/>
-      <c r="R47" s="158"/>
-      <c r="S47" s="158"/>
-      <c r="T47" s="158"/>
-      <c r="U47" s="158"/>
-      <c r="V47" s="158"/>
-      <c r="W47" s="158"/>
-      <c r="X47" s="158"/>
+      <c r="B47" s="159"/>
+      <c r="C47" s="159"/>
+      <c r="D47" s="159"/>
+      <c r="E47" s="159"/>
+      <c r="F47" s="159"/>
+      <c r="G47" s="159"/>
+      <c r="H47" s="159"/>
+      <c r="I47" s="159"/>
+      <c r="J47" s="159"/>
+      <c r="K47" s="159"/>
+      <c r="L47" s="159"/>
+      <c r="M47" s="159"/>
+      <c r="N47" s="159"/>
+      <c r="O47" s="159"/>
+      <c r="P47" s="159"/>
+      <c r="Q47" s="159"/>
+      <c r="R47" s="159"/>
+      <c r="S47" s="159"/>
+      <c r="T47" s="159"/>
+      <c r="U47" s="159"/>
+      <c r="V47" s="159"/>
+      <c r="W47" s="159"/>
+      <c r="X47" s="159"/>
     </row>
     <row r="48" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="45"/>
@@ -21133,7 +21173,7 @@
         <v>801</v>
       </c>
       <c r="W48" s="36">
-        <v>391</v>
+        <v>474</v>
       </c>
       <c r="X48" s="36"/>
     </row>
@@ -21203,7 +21243,7 @@
         <v>337816</v>
       </c>
       <c r="W49" s="36">
-        <v>342929</v>
+        <v>343177</v>
       </c>
       <c r="X49" s="36"/>
     </row>
@@ -21273,7 +21313,7 @@
         <v>0.5665</v>
       </c>
       <c r="W50" s="38">
-        <v>0.63470000000000004</v>
+        <v>0.63280000000000003</v>
       </c>
       <c r="X50" s="38"/>
     </row>
@@ -21343,7 +21383,7 @@
         <v>181</v>
       </c>
       <c r="W51" s="36">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="X51" s="36"/>
     </row>
@@ -21413,7 +21453,7 @@
         <v>314399</v>
       </c>
       <c r="W52" s="36">
-        <v>383750</v>
+        <v>381782</v>
       </c>
       <c r="X52" s="36"/>
     </row>
@@ -21483,7 +21523,7 @@
         <v>229</v>
       </c>
       <c r="W53" s="36">
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="X53" s="36"/>
     </row>
@@ -21553,7 +21593,7 @@
         <v>330301</v>
       </c>
       <c r="W54" s="36">
-        <v>347853</v>
+        <v>350200</v>
       </c>
       <c r="X54" s="36"/>
     </row>
@@ -21623,7 +21663,7 @@
         <v>391</v>
       </c>
       <c r="W55" s="36">
-        <v>195</v>
+        <v>231</v>
       </c>
       <c r="X55" s="36"/>
     </row>
@@ -21693,37 +21733,37 @@
         <v>354566</v>
       </c>
       <c r="W56" s="36">
-        <v>322333</v>
+        <v>321981</v>
       </c>
       <c r="X56" s="36"/>
     </row>
     <row r="57" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="161" t="s">
+      <c r="A57" s="162" t="s">
         <v>54</v>
       </c>
-      <c r="B57" s="158"/>
-      <c r="C57" s="158"/>
-      <c r="D57" s="158"/>
-      <c r="E57" s="158"/>
-      <c r="F57" s="158"/>
-      <c r="G57" s="158"/>
-      <c r="H57" s="158"/>
-      <c r="I57" s="158"/>
-      <c r="J57" s="158"/>
-      <c r="K57" s="158"/>
-      <c r="L57" s="158"/>
-      <c r="M57" s="158"/>
-      <c r="N57" s="158"/>
-      <c r="O57" s="158"/>
-      <c r="P57" s="158"/>
-      <c r="Q57" s="158"/>
-      <c r="R57" s="158"/>
-      <c r="S57" s="158"/>
-      <c r="T57" s="158"/>
-      <c r="U57" s="158"/>
-      <c r="V57" s="158"/>
-      <c r="W57" s="158"/>
-      <c r="X57" s="158"/>
+      <c r="B57" s="159"/>
+      <c r="C57" s="159"/>
+      <c r="D57" s="159"/>
+      <c r="E57" s="159"/>
+      <c r="F57" s="159"/>
+      <c r="G57" s="159"/>
+      <c r="H57" s="159"/>
+      <c r="I57" s="159"/>
+      <c r="J57" s="159"/>
+      <c r="K57" s="159"/>
+      <c r="L57" s="159"/>
+      <c r="M57" s="159"/>
+      <c r="N57" s="159"/>
+      <c r="O57" s="159"/>
+      <c r="P57" s="159"/>
+      <c r="Q57" s="159"/>
+      <c r="R57" s="159"/>
+      <c r="S57" s="159"/>
+      <c r="T57" s="159"/>
+      <c r="U57" s="159"/>
+      <c r="V57" s="159"/>
+      <c r="W57" s="159"/>
+      <c r="X57" s="159"/>
     </row>
     <row r="58" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="45"/>
@@ -21791,7 +21831,7 @@
         <v>832</v>
       </c>
       <c r="W58" s="36">
-        <v>279</v>
+        <v>338</v>
       </c>
       <c r="X58" s="36"/>
     </row>
@@ -21861,7 +21901,7 @@
         <v>320520</v>
       </c>
       <c r="W59" s="36">
-        <v>367454</v>
+        <v>363938</v>
       </c>
       <c r="X59" s="36"/>
     </row>
@@ -21874,64 +21914,64 @@
         <v>58</v>
       </c>
       <c r="D60" s="32">
-        <v>641895</v>
+        <v>1834742</v>
       </c>
       <c r="E60" s="32">
-        <v>643908</v>
+        <v>1803049</v>
       </c>
       <c r="F60" s="32">
-        <v>646403</v>
+        <v>1785182</v>
       </c>
       <c r="G60" s="32">
-        <v>646525</v>
+        <v>1657418</v>
       </c>
       <c r="H60" s="32">
-        <v>643954</v>
+        <v>1576315</v>
       </c>
       <c r="I60" s="32">
-        <v>625594</v>
+        <v>1515221</v>
       </c>
       <c r="J60" s="32">
-        <v>609044</v>
+        <v>1533526</v>
       </c>
       <c r="K60" s="32">
-        <v>592216</v>
+        <v>1396439</v>
       </c>
       <c r="L60" s="32">
-        <v>577597</v>
+        <v>1424256</v>
       </c>
       <c r="M60" s="32">
-        <v>560469</v>
+        <v>1291060</v>
       </c>
       <c r="N60" s="32">
-        <v>543210</v>
+        <v>1236730</v>
       </c>
       <c r="O60" s="32">
-        <v>533502</v>
+        <v>1375236</v>
       </c>
       <c r="P60" s="32">
-        <v>518249</v>
+        <v>1429464</v>
       </c>
       <c r="Q60" s="32">
-        <v>518879</v>
+        <v>1469344</v>
       </c>
       <c r="R60" s="32">
-        <v>512503</v>
+        <v>1349390</v>
       </c>
       <c r="S60" s="32">
-        <v>512762</v>
+        <v>1390811</v>
       </c>
       <c r="T60" s="32">
-        <v>513456</v>
+        <v>1336732</v>
       </c>
       <c r="U60" s="36">
-        <v>496795</v>
+        <v>1196609</v>
       </c>
       <c r="V60" s="36">
-        <v>516026</v>
+        <v>1233028</v>
       </c>
       <c r="W60" s="36">
-        <v>496667</v>
+        <v>1252596</v>
       </c>
       <c r="X60" s="36"/>
     </row>
@@ -22011,7 +22051,7 @@
         <v>40164072</v>
       </c>
       <c r="W63" s="33">
-        <v>9609627</v>
+        <v>12386427</v>
       </c>
       <c r="X63" s="33"/>
     </row>
@@ -22080,8 +22120,8 @@
       <c r="V64" s="46">
         <v>2.3313380602290611E-2</v>
       </c>
-      <c r="W64" s="192">
-        <v>1.387E-2</v>
+      <c r="W64" s="157">
+        <v>1.468E-2</v>
       </c>
       <c r="X64" s="33"/>
     </row>
@@ -22208,7 +22248,7 @@
         <v>1722790559</v>
       </c>
       <c r="W68" s="33">
-        <v>692849547</v>
+        <v>843934361</v>
       </c>
       <c r="X68" s="33">
         <f>IFERROR(SUM('📅 DAILY T9'!C$6:C$35)+SUM('📅 DAILY T9'!G$6:I$35),0)</f>
@@ -22216,30 +22256,30 @@
       </c>
     </row>
     <row r="69" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="157"/>
-      <c r="B69" s="158"/>
-      <c r="C69" s="158"/>
-      <c r="D69" s="158"/>
-      <c r="E69" s="158"/>
-      <c r="F69" s="158"/>
-      <c r="G69" s="158"/>
-      <c r="H69" s="158"/>
-      <c r="I69" s="158"/>
-      <c r="J69" s="158"/>
-      <c r="K69" s="158"/>
-      <c r="L69" s="158"/>
-      <c r="M69" s="158"/>
-      <c r="N69" s="158"/>
-      <c r="O69" s="158"/>
-      <c r="P69" s="158"/>
-      <c r="Q69" s="158"/>
-      <c r="R69" s="158"/>
-      <c r="S69" s="158"/>
-      <c r="T69" s="158"/>
-      <c r="U69" s="158"/>
-      <c r="V69" s="158"/>
-      <c r="W69" s="158"/>
-      <c r="X69" s="159"/>
+      <c r="A69" s="160"/>
+      <c r="B69" s="159"/>
+      <c r="C69" s="159"/>
+      <c r="D69" s="159"/>
+      <c r="E69" s="159"/>
+      <c r="F69" s="159"/>
+      <c r="G69" s="159"/>
+      <c r="H69" s="159"/>
+      <c r="I69" s="159"/>
+      <c r="J69" s="159"/>
+      <c r="K69" s="159"/>
+      <c r="L69" s="159"/>
+      <c r="M69" s="159"/>
+      <c r="N69" s="159"/>
+      <c r="O69" s="159"/>
+      <c r="P69" s="159"/>
+      <c r="Q69" s="159"/>
+      <c r="R69" s="159"/>
+      <c r="S69" s="159"/>
+      <c r="T69" s="159"/>
+      <c r="U69" s="159"/>
+      <c r="V69" s="159"/>
+      <c r="W69" s="159"/>
+      <c r="X69" s="161"/>
     </row>
     <row r="70" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="50"/>
@@ -22307,7 +22347,7 @@
         <v>2.12</v>
       </c>
       <c r="W70" s="39">
-        <v>2.17</v>
+        <v>5.4</v>
       </c>
       <c r="X70" s="39"/>
     </row>
@@ -22377,7 +22417,7 @@
         <v>19927</v>
       </c>
       <c r="W71" s="36">
-        <v>19225</v>
+        <v>19442</v>
       </c>
       <c r="X71" s="36"/>
     </row>
@@ -22447,7 +22487,7 @@
         <v>1493</v>
       </c>
       <c r="W72" s="36">
-        <v>593</v>
+        <v>715</v>
       </c>
       <c r="X72" s="36"/>
     </row>
@@ -22517,7 +22557,7 @@
         <v>101</v>
       </c>
       <c r="W73" s="53">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="X73" s="53"/>
     </row>
@@ -22583,7 +22623,7 @@
         <v>105</v>
       </c>
       <c r="W74">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="75" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -22648,7 +22688,7 @@
         <v>112</v>
       </c>
       <c r="W75">
-        <v>110</v>
+        <v>100</v>
       </c>
     </row>
     <row r="76" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -22688,64 +22728,64 @@
         <v>58</v>
       </c>
       <c r="D77" s="32">
-        <v>854166</v>
+        <v>1682420</v>
       </c>
       <c r="E77" s="32">
-        <v>867740</v>
+        <v>1697971</v>
       </c>
       <c r="F77" s="32">
-        <v>885205</v>
+        <v>1647813</v>
       </c>
       <c r="G77" s="32">
-        <v>896218</v>
+        <v>1590798</v>
       </c>
       <c r="H77" s="32">
-        <v>906167</v>
+        <v>1567974</v>
       </c>
       <c r="I77" s="32">
-        <v>913413</v>
+        <v>1502827</v>
       </c>
       <c r="J77" s="32">
-        <v>921336</v>
+        <v>1560559</v>
       </c>
       <c r="K77" s="32">
-        <v>930073</v>
+        <v>1457531</v>
       </c>
       <c r="L77" s="32">
-        <v>935217</v>
+        <v>1416398</v>
       </c>
       <c r="M77" s="32">
-        <v>938756</v>
+        <v>1385887</v>
       </c>
       <c r="N77" s="32">
-        <v>944689</v>
+        <v>1367706</v>
       </c>
       <c r="O77" s="32">
-        <v>954722</v>
+        <v>1433049</v>
       </c>
       <c r="P77" s="32">
-        <v>964715</v>
+        <v>1484601</v>
       </c>
       <c r="Q77" s="32">
-        <v>976110</v>
+        <v>1467356</v>
       </c>
       <c r="R77" s="32">
-        <v>985971</v>
+        <v>1449002</v>
       </c>
       <c r="S77" s="32">
-        <v>997893</v>
+        <v>1490197</v>
       </c>
       <c r="T77" s="32">
-        <v>1010217</v>
+        <v>1463010</v>
       </c>
       <c r="U77" s="36">
-        <v>1014219</v>
+        <v>1243436</v>
       </c>
       <c r="V77" s="36">
-        <v>990553</v>
+        <v>1296094</v>
       </c>
       <c r="W77" s="36">
-        <v>1027501</v>
+        <v>1287658</v>
       </c>
       <c r="X77" s="36"/>
     </row>
@@ -22758,64 +22798,64 @@
         <v>58</v>
       </c>
       <c r="D78" s="32">
-        <v>649776</v>
+        <v>1207160</v>
       </c>
       <c r="E78" s="32">
-        <v>653034</v>
+        <v>1186307</v>
       </c>
       <c r="F78" s="32">
-        <v>656527</v>
+        <v>1174552</v>
       </c>
       <c r="G78" s="32">
-        <v>656372</v>
+        <v>1090490</v>
       </c>
       <c r="H78" s="32">
-        <v>654539</v>
+        <v>1037129</v>
       </c>
       <c r="I78" s="32">
-        <v>655579</v>
+        <v>996932</v>
       </c>
       <c r="J78" s="32">
-        <v>656930</v>
+        <v>1008976</v>
       </c>
       <c r="K78" s="32">
-        <v>657134</v>
+        <v>918780</v>
       </c>
       <c r="L78" s="32">
-        <v>654379</v>
+        <v>937082</v>
       </c>
       <c r="M78" s="32">
-        <v>649380</v>
+        <v>849447</v>
       </c>
       <c r="N78" s="32">
-        <v>643032</v>
+        <v>813700</v>
       </c>
       <c r="O78" s="32">
-        <v>643077</v>
+        <v>904830</v>
       </c>
       <c r="P78" s="32">
-        <v>643489</v>
+        <v>940509</v>
       </c>
       <c r="Q78" s="32">
-        <v>647444</v>
+        <v>966748</v>
       </c>
       <c r="R78" s="32">
-        <v>648524</v>
+        <v>887825</v>
       </c>
       <c r="S78" s="32">
-        <v>652853</v>
+        <v>915077</v>
       </c>
       <c r="T78" s="32">
-        <v>656021</v>
+        <v>879497</v>
       </c>
       <c r="U78" s="36">
-        <v>647229</v>
+        <v>787303</v>
       </c>
       <c r="V78" s="36">
-        <v>569362</v>
+        <v>811265</v>
       </c>
       <c r="W78" s="36">
-        <v>652732</v>
+        <v>824140</v>
       </c>
       <c r="X78" s="36"/>
     </row>
@@ -22828,64 +22868,64 @@
         <v>58</v>
       </c>
       <c r="D79" s="32">
-        <v>854166</v>
+        <v>2063244</v>
       </c>
       <c r="E79" s="32">
-        <v>867740</v>
+        <v>2082315</v>
       </c>
       <c r="F79" s="32">
-        <v>885205</v>
+        <v>2020803</v>
       </c>
       <c r="G79" s="32">
-        <v>896218</v>
+        <v>1950883</v>
       </c>
       <c r="H79" s="32">
-        <v>906167</v>
+        <v>1922893</v>
       </c>
       <c r="I79" s="32">
-        <v>880436</v>
+        <v>1843000</v>
       </c>
       <c r="J79" s="32">
-        <v>858858</v>
+        <v>1913799</v>
       </c>
       <c r="K79" s="32">
-        <v>834925</v>
+        <v>1787450</v>
       </c>
       <c r="L79" s="32">
-        <v>815142</v>
+        <v>1737007</v>
       </c>
       <c r="M79" s="32">
-        <v>798971</v>
+        <v>1699589</v>
       </c>
       <c r="N79" s="32">
-        <v>787161</v>
+        <v>1677293</v>
       </c>
       <c r="O79" s="32">
-        <v>781719</v>
+        <v>1757426</v>
       </c>
       <c r="P79" s="32">
-        <v>777311</v>
+        <v>1820648</v>
       </c>
       <c r="Q79" s="32">
-        <v>781068</v>
+        <v>1799499</v>
       </c>
       <c r="R79" s="32">
-        <v>778576</v>
+        <v>1776990</v>
       </c>
       <c r="S79" s="32">
-        <v>785070</v>
+        <v>1827510</v>
       </c>
       <c r="T79" s="32">
-        <v>793187</v>
+        <v>1794170</v>
       </c>
       <c r="U79" s="36">
-        <v>804514</v>
+        <v>1524894</v>
       </c>
       <c r="V79" s="36">
-        <v>988687</v>
+        <v>1589471</v>
       </c>
       <c r="W79" s="36">
-        <v>810188</v>
+        <v>1579126</v>
       </c>
       <c r="X79" s="36"/>
     </row>
@@ -22898,94 +22938,94 @@
         <v>58</v>
       </c>
       <c r="D80" s="32">
-        <v>649776</v>
+        <v>1834742</v>
       </c>
       <c r="E80" s="32">
-        <v>653034</v>
+        <v>1803049</v>
       </c>
       <c r="F80" s="32">
-        <v>656527</v>
+        <v>1785182</v>
       </c>
       <c r="G80" s="32">
-        <v>656372</v>
+        <v>1657418</v>
       </c>
       <c r="H80" s="32">
-        <v>654539</v>
+        <v>1576315</v>
       </c>
       <c r="I80" s="32">
-        <v>634626</v>
+        <v>1515221</v>
       </c>
       <c r="J80" s="32">
-        <v>617933</v>
+        <v>1533526</v>
       </c>
       <c r="K80" s="32">
-        <v>599967</v>
+        <v>1396439</v>
       </c>
       <c r="L80" s="32">
-        <v>584496</v>
+        <v>1424256</v>
       </c>
       <c r="M80" s="32">
-        <v>565801</v>
+        <v>1291060</v>
       </c>
       <c r="N80" s="32">
-        <v>544704</v>
+        <v>1236730</v>
       </c>
       <c r="O80" s="32">
-        <v>531895</v>
+        <v>1375236</v>
       </c>
       <c r="P80" s="32">
-        <v>516683</v>
+        <v>1429464</v>
       </c>
       <c r="Q80" s="32">
-        <v>518311</v>
+        <v>1469344</v>
       </c>
       <c r="R80" s="32">
-        <v>512897</v>
+        <v>1349390</v>
       </c>
       <c r="S80" s="32">
-        <v>514213</v>
+        <v>1390811</v>
       </c>
       <c r="T80" s="32">
-        <v>514850</v>
+        <v>1336732</v>
       </c>
       <c r="U80" s="36">
-        <v>496795</v>
+        <v>1196609</v>
       </c>
       <c r="V80" s="36">
-        <v>516026</v>
+        <v>1233028</v>
       </c>
       <c r="W80" s="36">
-        <v>496667</v>
+        <v>1252596</v>
       </c>
       <c r="X80" s="36"/>
     </row>
     <row r="81" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="163" t="s">
+      <c r="A81" s="164" t="s">
         <v>93</v>
       </c>
-      <c r="B81" s="158"/>
-      <c r="C81" s="158"/>
-      <c r="D81" s="158"/>
-      <c r="E81" s="158"/>
-      <c r="F81" s="158"/>
-      <c r="G81" s="158"/>
-      <c r="H81" s="158"/>
-      <c r="I81" s="158"/>
-      <c r="J81" s="158"/>
-      <c r="K81" s="158"/>
-      <c r="L81" s="158"/>
-      <c r="M81" s="158"/>
-      <c r="N81" s="158"/>
-      <c r="O81" s="158"/>
-      <c r="P81" s="158"/>
-      <c r="Q81" s="158"/>
-      <c r="R81" s="158"/>
-      <c r="S81" s="158"/>
-      <c r="T81" s="158"/>
-      <c r="U81" s="158"/>
-      <c r="V81" s="158"/>
-      <c r="W81" s="158"/>
-      <c r="X81" s="158"/>
+      <c r="B81" s="159"/>
+      <c r="C81" s="159"/>
+      <c r="D81" s="159"/>
+      <c r="E81" s="159"/>
+      <c r="F81" s="159"/>
+      <c r="G81" s="159"/>
+      <c r="H81" s="159"/>
+      <c r="I81" s="159"/>
+      <c r="J81" s="159"/>
+      <c r="K81" s="159"/>
+      <c r="L81" s="159"/>
+      <c r="M81" s="159"/>
+      <c r="N81" s="159"/>
+      <c r="O81" s="159"/>
+      <c r="P81" s="159"/>
+      <c r="Q81" s="159"/>
+      <c r="R81" s="159"/>
+      <c r="S81" s="159"/>
+      <c r="T81" s="159"/>
+      <c r="U81" s="159"/>
+      <c r="V81" s="159"/>
+      <c r="W81" s="159"/>
+      <c r="X81" s="159"/>
     </row>
     <row r="82" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="54"/>
@@ -23286,6 +23326,7 @@
   </sheetData>
   <mergeCells count="16">
     <mergeCell ref="A1:X1"/>
+    <mergeCell ref="A5:X5"/>
     <mergeCell ref="A13:X13"/>
     <mergeCell ref="A14:X14"/>
     <mergeCell ref="A2:X2"/>
@@ -23293,9 +23334,8 @@
     <mergeCell ref="A41:X41"/>
     <mergeCell ref="A19:X19"/>
     <mergeCell ref="A33:X33"/>
-    <mergeCell ref="A5:X5"/>
+    <mergeCell ref="A34:X34"/>
     <mergeCell ref="A69:X69"/>
-    <mergeCell ref="A34:X34"/>
     <mergeCell ref="A29:X29"/>
     <mergeCell ref="A4:X4"/>
     <mergeCell ref="A81:X81"/>
@@ -23331,80 +23371,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="177" t="s">
+      <c r="A1" s="178" t="s">
         <v>482</v>
       </c>
-      <c r="B1" s="158"/>
-      <c r="C1" s="158"/>
-      <c r="D1" s="158"/>
-      <c r="E1" s="158"/>
-      <c r="F1" s="158"/>
-      <c r="G1" s="158"/>
-      <c r="H1" s="158"/>
-      <c r="I1" s="158"/>
-      <c r="J1" s="158"/>
-      <c r="K1" s="158"/>
-      <c r="L1" s="158"/>
-      <c r="M1" s="158"/>
-      <c r="N1" s="158"/>
-      <c r="O1" s="158"/>
-      <c r="P1" s="158"/>
-      <c r="Q1" s="158"/>
+      <c r="B1" s="159"/>
+      <c r="C1" s="159"/>
+      <c r="D1" s="159"/>
+      <c r="E1" s="159"/>
+      <c r="F1" s="159"/>
+      <c r="G1" s="159"/>
+      <c r="H1" s="159"/>
+      <c r="I1" s="159"/>
+      <c r="J1" s="159"/>
+      <c r="K1" s="159"/>
+      <c r="L1" s="159"/>
+      <c r="M1" s="159"/>
+      <c r="N1" s="159"/>
+      <c r="O1" s="159"/>
+      <c r="P1" s="159"/>
+      <c r="Q1" s="159"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="164" t="s">
+      <c r="A2" s="165" t="s">
         <v>360</v>
       </c>
-      <c r="B2" s="158"/>
-      <c r="C2" s="158"/>
-      <c r="D2" s="158"/>
-      <c r="E2" s="158"/>
-      <c r="F2" s="158"/>
-      <c r="G2" s="158"/>
-      <c r="H2" s="158"/>
-      <c r="I2" s="158"/>
-      <c r="J2" s="158"/>
-      <c r="K2" s="158"/>
-      <c r="L2" s="158"/>
-      <c r="M2" s="158"/>
-      <c r="N2" s="158"/>
-      <c r="O2" s="158"/>
-      <c r="P2" s="158"/>
-      <c r="Q2" s="158"/>
+      <c r="B2" s="159"/>
+      <c r="C2" s="159"/>
+      <c r="D2" s="159"/>
+      <c r="E2" s="159"/>
+      <c r="F2" s="159"/>
+      <c r="G2" s="159"/>
+      <c r="H2" s="159"/>
+      <c r="I2" s="159"/>
+      <c r="J2" s="159"/>
+      <c r="K2" s="159"/>
+      <c r="L2" s="159"/>
+      <c r="M2" s="159"/>
+      <c r="N2" s="159"/>
+      <c r="O2" s="159"/>
+      <c r="P2" s="159"/>
+      <c r="Q2" s="159"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="176" t="s">
+      <c r="A3" s="177" t="s">
         <v>361</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="175" t="s">
+      <c r="B3" s="159"/>
+      <c r="C3" s="176" t="s">
         <v>362</v>
       </c>
-      <c r="D3" s="158"/>
-      <c r="E3" s="178" t="s">
+      <c r="D3" s="159"/>
+      <c r="E3" s="179" t="s">
         <v>363</v>
       </c>
-      <c r="F3" s="158"/>
-      <c r="G3" s="173" t="s">
+      <c r="F3" s="159"/>
+      <c r="G3" s="174" t="s">
         <v>364</v>
       </c>
-      <c r="H3" s="158"/>
-      <c r="I3" s="158"/>
-      <c r="J3" s="158"/>
+      <c r="H3" s="159"/>
+      <c r="I3" s="159"/>
+      <c r="J3" s="159"/>
       <c r="K3" s="56" t="s">
         <v>365</v>
       </c>
       <c r="L3" s="57" t="s">
         <v>366</v>
       </c>
-      <c r="M3" s="172" t="s">
+      <c r="M3" s="173" t="s">
         <v>367</v>
       </c>
-      <c r="N3" s="158"/>
-      <c r="O3" s="172" t="s">
+      <c r="N3" s="159"/>
+      <c r="O3" s="173" t="s">
         <v>367</v>
       </c>
-      <c r="P3" s="158"/>
+      <c r="P3" s="159"/>
       <c r="Q3" s="58" t="s">
         <v>368</v>
       </c>
@@ -23463,10 +23503,10 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="174" t="s">
+      <c r="A5" s="175" t="s">
         <v>386</v>
       </c>
-      <c r="B5" s="158"/>
+      <c r="B5" s="159"/>
       <c r="C5" s="66">
         <v>1258798314</v>
       </c>
@@ -24868,40 +24908,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="185" t="s">
         <v>483</v>
       </c>
-      <c r="B1" s="170"/>
-      <c r="C1" s="170"/>
-      <c r="D1" s="170"/>
-      <c r="E1" s="170"/>
-      <c r="F1" s="170"/>
-      <c r="G1" s="170"/>
-      <c r="H1" s="170"/>
-      <c r="I1" s="170"/>
-      <c r="J1" s="170"/>
-      <c r="K1" s="170"/>
-      <c r="L1" s="170"/>
-      <c r="M1" s="170"/>
-      <c r="N1" s="170"/>
+      <c r="B1" s="171"/>
+      <c r="C1" s="171"/>
+      <c r="D1" s="171"/>
+      <c r="E1" s="171"/>
+      <c r="F1" s="171"/>
+      <c r="G1" s="171"/>
+      <c r="H1" s="171"/>
+      <c r="I1" s="171"/>
+      <c r="J1" s="171"/>
+      <c r="K1" s="171"/>
+      <c r="L1" s="171"/>
+      <c r="M1" s="171"/>
+      <c r="N1" s="171"/>
     </row>
     <row r="2" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="183" t="s">
+      <c r="A2" s="184" t="s">
         <v>404</v>
       </c>
-      <c r="B2" s="170"/>
-      <c r="C2" s="170"/>
-      <c r="D2" s="170"/>
-      <c r="E2" s="170"/>
-      <c r="F2" s="170"/>
-      <c r="G2" s="170"/>
-      <c r="H2" s="170"/>
-      <c r="I2" s="170"/>
-      <c r="J2" s="170"/>
-      <c r="K2" s="170"/>
-      <c r="L2" s="170"/>
-      <c r="M2" s="170"/>
-      <c r="N2" s="170"/>
+      <c r="B2" s="171"/>
+      <c r="C2" s="171"/>
+      <c r="D2" s="171"/>
+      <c r="E2" s="171"/>
+      <c r="F2" s="171"/>
+      <c r="G2" s="171"/>
+      <c r="H2" s="171"/>
+      <c r="I2" s="171"/>
+      <c r="J2" s="171"/>
+      <c r="K2" s="171"/>
+      <c r="L2" s="171"/>
+      <c r="M2" s="171"/>
+      <c r="N2" s="171"/>
     </row>
     <row r="3" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="141" t="s">
@@ -25235,80 +25275,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="177" t="s">
+      <c r="A1" s="178" t="s">
         <v>489</v>
       </c>
-      <c r="B1" s="158"/>
-      <c r="C1" s="158"/>
-      <c r="D1" s="158"/>
-      <c r="E1" s="158"/>
-      <c r="F1" s="158"/>
-      <c r="G1" s="158"/>
-      <c r="H1" s="158"/>
-      <c r="I1" s="158"/>
-      <c r="J1" s="158"/>
-      <c r="K1" s="158"/>
-      <c r="L1" s="158"/>
-      <c r="M1" s="158"/>
-      <c r="N1" s="158"/>
-      <c r="O1" s="158"/>
-      <c r="P1" s="158"/>
-      <c r="Q1" s="158"/>
+      <c r="B1" s="159"/>
+      <c r="C1" s="159"/>
+      <c r="D1" s="159"/>
+      <c r="E1" s="159"/>
+      <c r="F1" s="159"/>
+      <c r="G1" s="159"/>
+      <c r="H1" s="159"/>
+      <c r="I1" s="159"/>
+      <c r="J1" s="159"/>
+      <c r="K1" s="159"/>
+      <c r="L1" s="159"/>
+      <c r="M1" s="159"/>
+      <c r="N1" s="159"/>
+      <c r="O1" s="159"/>
+      <c r="P1" s="159"/>
+      <c r="Q1" s="159"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="164" t="s">
+      <c r="A2" s="165" t="s">
         <v>360</v>
       </c>
-      <c r="B2" s="158"/>
-      <c r="C2" s="158"/>
-      <c r="D2" s="158"/>
-      <c r="E2" s="158"/>
-      <c r="F2" s="158"/>
-      <c r="G2" s="158"/>
-      <c r="H2" s="158"/>
-      <c r="I2" s="158"/>
-      <c r="J2" s="158"/>
-      <c r="K2" s="158"/>
-      <c r="L2" s="158"/>
-      <c r="M2" s="158"/>
-      <c r="N2" s="158"/>
-      <c r="O2" s="158"/>
-      <c r="P2" s="158"/>
-      <c r="Q2" s="158"/>
+      <c r="B2" s="159"/>
+      <c r="C2" s="159"/>
+      <c r="D2" s="159"/>
+      <c r="E2" s="159"/>
+      <c r="F2" s="159"/>
+      <c r="G2" s="159"/>
+      <c r="H2" s="159"/>
+      <c r="I2" s="159"/>
+      <c r="J2" s="159"/>
+      <c r="K2" s="159"/>
+      <c r="L2" s="159"/>
+      <c r="M2" s="159"/>
+      <c r="N2" s="159"/>
+      <c r="O2" s="159"/>
+      <c r="P2" s="159"/>
+      <c r="Q2" s="159"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="176" t="s">
+      <c r="A3" s="177" t="s">
         <v>361</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="175" t="s">
+      <c r="B3" s="159"/>
+      <c r="C3" s="176" t="s">
         <v>362</v>
       </c>
-      <c r="D3" s="158"/>
-      <c r="E3" s="178" t="s">
+      <c r="D3" s="159"/>
+      <c r="E3" s="179" t="s">
         <v>363</v>
       </c>
-      <c r="F3" s="158"/>
-      <c r="G3" s="173" t="s">
+      <c r="F3" s="159"/>
+      <c r="G3" s="174" t="s">
         <v>364</v>
       </c>
-      <c r="H3" s="158"/>
-      <c r="I3" s="158"/>
-      <c r="J3" s="158"/>
+      <c r="H3" s="159"/>
+      <c r="I3" s="159"/>
+      <c r="J3" s="159"/>
       <c r="K3" s="56" t="s">
         <v>365</v>
       </c>
       <c r="L3" s="57" t="s">
         <v>366</v>
       </c>
-      <c r="M3" s="172" t="s">
+      <c r="M3" s="173" t="s">
         <v>367</v>
       </c>
-      <c r="N3" s="158"/>
-      <c r="O3" s="172" t="s">
+      <c r="N3" s="159"/>
+      <c r="O3" s="173" t="s">
         <v>367</v>
       </c>
-      <c r="P3" s="158"/>
+      <c r="P3" s="159"/>
       <c r="Q3" s="58" t="s">
         <v>368</v>
       </c>
@@ -25367,10 +25407,10 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="174" t="s">
+      <c r="A5" s="175" t="s">
         <v>386</v>
       </c>
-      <c r="B5" s="158"/>
+      <c r="B5" s="159"/>
       <c r="C5" s="66">
         <v>1625138977</v>
       </c>
@@ -26745,40 +26785,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="185" t="s">
         <v>490</v>
       </c>
-      <c r="B1" s="170"/>
-      <c r="C1" s="170"/>
-      <c r="D1" s="170"/>
-      <c r="E1" s="170"/>
-      <c r="F1" s="170"/>
-      <c r="G1" s="170"/>
-      <c r="H1" s="170"/>
-      <c r="I1" s="170"/>
-      <c r="J1" s="170"/>
-      <c r="K1" s="170"/>
-      <c r="L1" s="170"/>
-      <c r="M1" s="170"/>
-      <c r="N1" s="170"/>
+      <c r="B1" s="171"/>
+      <c r="C1" s="171"/>
+      <c r="D1" s="171"/>
+      <c r="E1" s="171"/>
+      <c r="F1" s="171"/>
+      <c r="G1" s="171"/>
+      <c r="H1" s="171"/>
+      <c r="I1" s="171"/>
+      <c r="J1" s="171"/>
+      <c r="K1" s="171"/>
+      <c r="L1" s="171"/>
+      <c r="M1" s="171"/>
+      <c r="N1" s="171"/>
     </row>
     <row r="2" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="183" t="s">
+      <c r="A2" s="184" t="s">
         <v>404</v>
       </c>
-      <c r="B2" s="170"/>
-      <c r="C2" s="170"/>
-      <c r="D2" s="170"/>
-      <c r="E2" s="170"/>
-      <c r="F2" s="170"/>
-      <c r="G2" s="170"/>
-      <c r="H2" s="170"/>
-      <c r="I2" s="170"/>
-      <c r="J2" s="170"/>
-      <c r="K2" s="170"/>
-      <c r="L2" s="170"/>
-      <c r="M2" s="170"/>
-      <c r="N2" s="170"/>
+      <c r="B2" s="171"/>
+      <c r="C2" s="171"/>
+      <c r="D2" s="171"/>
+      <c r="E2" s="171"/>
+      <c r="F2" s="171"/>
+      <c r="G2" s="171"/>
+      <c r="H2" s="171"/>
+      <c r="I2" s="171"/>
+      <c r="J2" s="171"/>
+      <c r="K2" s="171"/>
+      <c r="L2" s="171"/>
+      <c r="M2" s="171"/>
+      <c r="N2" s="171"/>
     </row>
     <row r="3" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="141" t="s">
@@ -27163,80 +27203,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="177" t="s">
+      <c r="A1" s="178" t="s">
         <v>497</v>
       </c>
-      <c r="B1" s="158"/>
-      <c r="C1" s="158"/>
-      <c r="D1" s="158"/>
-      <c r="E1" s="158"/>
-      <c r="F1" s="158"/>
-      <c r="G1" s="158"/>
-      <c r="H1" s="158"/>
-      <c r="I1" s="158"/>
-      <c r="J1" s="158"/>
-      <c r="K1" s="158"/>
-      <c r="L1" s="158"/>
-      <c r="M1" s="158"/>
-      <c r="N1" s="158"/>
-      <c r="O1" s="158"/>
-      <c r="P1" s="158"/>
-      <c r="Q1" s="158"/>
+      <c r="B1" s="159"/>
+      <c r="C1" s="159"/>
+      <c r="D1" s="159"/>
+      <c r="E1" s="159"/>
+      <c r="F1" s="159"/>
+      <c r="G1" s="159"/>
+      <c r="H1" s="159"/>
+      <c r="I1" s="159"/>
+      <c r="J1" s="159"/>
+      <c r="K1" s="159"/>
+      <c r="L1" s="159"/>
+      <c r="M1" s="159"/>
+      <c r="N1" s="159"/>
+      <c r="O1" s="159"/>
+      <c r="P1" s="159"/>
+      <c r="Q1" s="159"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="164" t="s">
+      <c r="A2" s="165" t="s">
         <v>360</v>
       </c>
-      <c r="B2" s="158"/>
-      <c r="C2" s="158"/>
-      <c r="D2" s="158"/>
-      <c r="E2" s="158"/>
-      <c r="F2" s="158"/>
-      <c r="G2" s="158"/>
-      <c r="H2" s="158"/>
-      <c r="I2" s="158"/>
-      <c r="J2" s="158"/>
-      <c r="K2" s="158"/>
-      <c r="L2" s="158"/>
-      <c r="M2" s="158"/>
-      <c r="N2" s="158"/>
-      <c r="O2" s="158"/>
-      <c r="P2" s="158"/>
-      <c r="Q2" s="158"/>
+      <c r="B2" s="159"/>
+      <c r="C2" s="159"/>
+      <c r="D2" s="159"/>
+      <c r="E2" s="159"/>
+      <c r="F2" s="159"/>
+      <c r="G2" s="159"/>
+      <c r="H2" s="159"/>
+      <c r="I2" s="159"/>
+      <c r="J2" s="159"/>
+      <c r="K2" s="159"/>
+      <c r="L2" s="159"/>
+      <c r="M2" s="159"/>
+      <c r="N2" s="159"/>
+      <c r="O2" s="159"/>
+      <c r="P2" s="159"/>
+      <c r="Q2" s="159"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="176" t="s">
+      <c r="A3" s="177" t="s">
         <v>361</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="175" t="s">
+      <c r="B3" s="159"/>
+      <c r="C3" s="176" t="s">
         <v>362</v>
       </c>
-      <c r="D3" s="158"/>
-      <c r="E3" s="178" t="s">
+      <c r="D3" s="159"/>
+      <c r="E3" s="179" t="s">
         <v>363</v>
       </c>
-      <c r="F3" s="158"/>
-      <c r="G3" s="173" t="s">
+      <c r="F3" s="159"/>
+      <c r="G3" s="174" t="s">
         <v>364</v>
       </c>
-      <c r="H3" s="158"/>
-      <c r="I3" s="158"/>
-      <c r="J3" s="158"/>
+      <c r="H3" s="159"/>
+      <c r="I3" s="159"/>
+      <c r="J3" s="159"/>
       <c r="K3" s="56" t="s">
         <v>365</v>
       </c>
       <c r="L3" s="57" t="s">
         <v>366</v>
       </c>
-      <c r="M3" s="172" t="s">
+      <c r="M3" s="173" t="s">
         <v>367</v>
       </c>
-      <c r="N3" s="158"/>
-      <c r="O3" s="172" t="s">
+      <c r="N3" s="159"/>
+      <c r="O3" s="173" t="s">
         <v>367</v>
       </c>
-      <c r="P3" s="158"/>
+      <c r="P3" s="159"/>
       <c r="Q3" s="58" t="s">
         <v>368</v>
       </c>
@@ -27295,10 +27335,10 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="174" t="s">
+      <c r="A5" s="175" t="s">
         <v>386</v>
       </c>
-      <c r="B5" s="158"/>
+      <c r="B5" s="159"/>
       <c r="C5" s="66">
         <v>1965067740</v>
       </c>
@@ -28700,40 +28740,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="185" t="s">
         <v>498</v>
       </c>
-      <c r="B1" s="170"/>
-      <c r="C1" s="170"/>
-      <c r="D1" s="170"/>
-      <c r="E1" s="170"/>
-      <c r="F1" s="170"/>
-      <c r="G1" s="170"/>
-      <c r="H1" s="170"/>
-      <c r="I1" s="170"/>
-      <c r="J1" s="170"/>
-      <c r="K1" s="170"/>
-      <c r="L1" s="170"/>
-      <c r="M1" s="170"/>
-      <c r="N1" s="170"/>
+      <c r="B1" s="171"/>
+      <c r="C1" s="171"/>
+      <c r="D1" s="171"/>
+      <c r="E1" s="171"/>
+      <c r="F1" s="171"/>
+      <c r="G1" s="171"/>
+      <c r="H1" s="171"/>
+      <c r="I1" s="171"/>
+      <c r="J1" s="171"/>
+      <c r="K1" s="171"/>
+      <c r="L1" s="171"/>
+      <c r="M1" s="171"/>
+      <c r="N1" s="171"/>
     </row>
     <row r="2" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="183" t="s">
+      <c r="A2" s="184" t="s">
         <v>404</v>
       </c>
-      <c r="B2" s="170"/>
-      <c r="C2" s="170"/>
-      <c r="D2" s="170"/>
-      <c r="E2" s="170"/>
-      <c r="F2" s="170"/>
-      <c r="G2" s="170"/>
-      <c r="H2" s="170"/>
-      <c r="I2" s="170"/>
-      <c r="J2" s="170"/>
-      <c r="K2" s="170"/>
-      <c r="L2" s="170"/>
-      <c r="M2" s="170"/>
-      <c r="N2" s="170"/>
+      <c r="B2" s="171"/>
+      <c r="C2" s="171"/>
+      <c r="D2" s="171"/>
+      <c r="E2" s="171"/>
+      <c r="F2" s="171"/>
+      <c r="G2" s="171"/>
+      <c r="H2" s="171"/>
+      <c r="I2" s="171"/>
+      <c r="J2" s="171"/>
+      <c r="K2" s="171"/>
+      <c r="L2" s="171"/>
+      <c r="M2" s="171"/>
+      <c r="N2" s="171"/>
     </row>
     <row r="3" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="141" t="s">
@@ -29058,19 +29098,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="177" t="s">
+      <c r="A1" s="178" t="s">
         <v>504</v>
       </c>
-      <c r="B1" s="158"/>
-      <c r="C1" s="158"/>
+      <c r="B1" s="159"/>
+      <c r="C1" s="159"/>
     </row>
     <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="187" t="s">
+      <c r="A3" s="188" t="s">
         <v>505</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="158"/>
+      <c r="B3" s="159"/>
+      <c r="C3" s="159"/>
     </row>
     <row r="4" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="111"/>
@@ -29128,11 +29168,11 @@
     </row>
     <row r="10" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="11" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="185" t="s">
+      <c r="A11" s="186" t="s">
         <v>518</v>
       </c>
-      <c r="B11" s="158"/>
-      <c r="C11" s="158"/>
+      <c r="B11" s="159"/>
+      <c r="C11" s="159"/>
     </row>
     <row r="12" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="115"/>
@@ -29172,11 +29212,11 @@
     </row>
     <row r="16" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="17" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="186" t="s">
+      <c r="A17" s="187" t="s">
         <v>527</v>
       </c>
-      <c r="B17" s="158"/>
-      <c r="C17" s="158"/>
+      <c r="B17" s="159"/>
+      <c r="C17" s="159"/>
     </row>
     <row r="18" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="118"/>
@@ -29225,11 +29265,11 @@
     </row>
     <row r="23" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="24" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="188" t="s">
+      <c r="A24" s="189" t="s">
         <v>538</v>
       </c>
-      <c r="B24" s="158"/>
-      <c r="C24" s="158"/>
+      <c r="B24" s="159"/>
+      <c r="C24" s="159"/>
     </row>
     <row r="25" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="121"/>
@@ -29517,40 +29557,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="191" t="s">
+      <c r="A1" s="192" t="s">
         <v>556</v>
       </c>
-      <c r="B1" s="170"/>
-      <c r="C1" s="170"/>
-      <c r="D1" s="170"/>
-      <c r="E1" s="170"/>
-      <c r="F1" s="170"/>
-      <c r="G1" s="170"/>
-      <c r="H1" s="170"/>
-      <c r="I1" s="170"/>
-      <c r="J1" s="170"/>
-      <c r="K1" s="170"/>
-      <c r="L1" s="170"/>
-      <c r="M1" s="170"/>
-      <c r="N1" s="170"/>
+      <c r="B1" s="171"/>
+      <c r="C1" s="171"/>
+      <c r="D1" s="171"/>
+      <c r="E1" s="171"/>
+      <c r="F1" s="171"/>
+      <c r="G1" s="171"/>
+      <c r="H1" s="171"/>
+      <c r="I1" s="171"/>
+      <c r="J1" s="171"/>
+      <c r="K1" s="171"/>
+      <c r="L1" s="171"/>
+      <c r="M1" s="171"/>
+      <c r="N1" s="171"/>
     </row>
     <row r="2" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="190" t="s">
+      <c r="A2" s="191" t="s">
         <v>557</v>
       </c>
-      <c r="B2" s="170"/>
-      <c r="C2" s="170"/>
-      <c r="D2" s="170"/>
-      <c r="E2" s="170"/>
-      <c r="F2" s="170"/>
-      <c r="G2" s="170"/>
-      <c r="H2" s="170"/>
-      <c r="I2" s="170"/>
-      <c r="J2" s="170"/>
-      <c r="K2" s="170"/>
-      <c r="L2" s="170"/>
-      <c r="M2" s="170"/>
-      <c r="N2" s="170"/>
+      <c r="B2" s="171"/>
+      <c r="C2" s="171"/>
+      <c r="D2" s="171"/>
+      <c r="E2" s="171"/>
+      <c r="F2" s="171"/>
+      <c r="G2" s="171"/>
+      <c r="H2" s="171"/>
+      <c r="I2" s="171"/>
+      <c r="J2" s="171"/>
+      <c r="K2" s="171"/>
+      <c r="L2" s="171"/>
+      <c r="M2" s="171"/>
+      <c r="N2" s="171"/>
     </row>
     <row r="3" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="124" t="s">
@@ -29597,22 +29637,22 @@
       </c>
     </row>
     <row r="4" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="189" t="s">
+      <c r="A4" s="190" t="s">
         <v>572</v>
       </c>
-      <c r="B4" s="170"/>
-      <c r="C4" s="170"/>
-      <c r="D4" s="170"/>
-      <c r="E4" s="170"/>
-      <c r="F4" s="170"/>
-      <c r="G4" s="170"/>
-      <c r="H4" s="170"/>
-      <c r="I4" s="170"/>
-      <c r="J4" s="170"/>
-      <c r="K4" s="170"/>
-      <c r="L4" s="170"/>
-      <c r="M4" s="170"/>
-      <c r="N4" s="170"/>
+      <c r="B4" s="171"/>
+      <c r="C4" s="171"/>
+      <c r="D4" s="171"/>
+      <c r="E4" s="171"/>
+      <c r="F4" s="171"/>
+      <c r="G4" s="171"/>
+      <c r="H4" s="171"/>
+      <c r="I4" s="171"/>
+      <c r="J4" s="171"/>
+      <c r="K4" s="171"/>
+      <c r="L4" s="171"/>
+      <c r="M4" s="171"/>
+      <c r="N4" s="171"/>
     </row>
     <row r="5" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="125" t="s">
@@ -32418,40 +32458,40 @@
         <v>594</v>
       </c>
       <c r="C80" s="133">
-        <v>363</v>
+        <v>438</v>
       </c>
       <c r="D80" s="133">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="E80" s="133">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="F80" s="133">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="G80" s="133">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H80" s="133">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="I80" s="133">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="J80" s="133">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K80" s="133">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L80" s="133">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="M80" s="133">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N80" s="133">
-        <v>135</v>
+        <v>198</v>
       </c>
     </row>
     <row r="81" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -32462,22 +32502,22 @@
         <v>595</v>
       </c>
       <c r="C81">
-        <v>504</v>
+        <v>605</v>
       </c>
       <c r="D81">
-        <v>370</v>
+        <v>442</v>
       </c>
       <c r="E81">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="F81">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="G81">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H81">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I81">
         <v>3</v>
@@ -32486,16 +32526,16 @@
         <v>0</v>
       </c>
       <c r="K81">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="L81">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="M81">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="N81">
-        <v>42</v>
+        <v>104</v>
       </c>
     </row>
     <row r="82" spans="1:14" ht="4.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -32506,22 +32546,22 @@
         <v>596</v>
       </c>
       <c r="C82" s="127">
-        <v>267</v>
+        <v>322</v>
       </c>
       <c r="D82" s="128">
-        <v>224</v>
+        <v>269</v>
       </c>
       <c r="E82" s="128">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F82" s="128">
         <v>6</v>
       </c>
       <c r="G82" s="128">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H82" s="128">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I82" s="128">
         <v>0</v>
@@ -32530,16 +32570,16 @@
         <v>0</v>
       </c>
       <c r="K82" s="130">
+        <v>78</v>
+      </c>
+      <c r="L82" s="130">
+        <v>23</v>
+      </c>
+      <c r="M82" s="130">
+        <v>32</v>
+      </c>
+      <c r="N82" s="130">
         <v>63</v>
-      </c>
-      <c r="L82" s="130">
-        <v>15</v>
-      </c>
-      <c r="M82" s="130">
-        <v>27</v>
-      </c>
-      <c r="N82" s="130">
-        <v>39</v>
       </c>
     </row>
     <row r="83" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -35302,40 +35342,40 @@
         <v>594</v>
       </c>
       <c r="C157">
-        <v>304</v>
+        <v>382</v>
       </c>
       <c r="D157">
-        <v>165</v>
+        <v>207</v>
       </c>
       <c r="E157">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F157">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="G157">
+        <v>13</v>
+      </c>
+      <c r="H157">
+        <v>32</v>
+      </c>
+      <c r="I157">
         <v>10</v>
-      </c>
-      <c r="H157">
-        <v>26</v>
-      </c>
-      <c r="I157">
-        <v>7</v>
       </c>
       <c r="J157">
         <v>0</v>
       </c>
       <c r="K157">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L157">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="M157">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N157">
-        <v>103</v>
+        <v>156</v>
       </c>
     </row>
     <row r="158" spans="1:14" x14ac:dyDescent="0.2">
@@ -35346,16 +35386,16 @@
         <v>595</v>
       </c>
       <c r="C158">
-        <v>255</v>
+        <v>306</v>
       </c>
       <c r="D158">
-        <v>228</v>
+        <v>273</v>
       </c>
       <c r="E158">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F158">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G158">
         <v>1</v>
@@ -35370,16 +35410,16 @@
         <v>0</v>
       </c>
       <c r="K158">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="L158">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="M158">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="N158">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="159" spans="1:14" x14ac:dyDescent="0.2">
@@ -35390,13 +35430,13 @@
         <v>596</v>
       </c>
       <c r="C159">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="D159">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="E159">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F159">
         <v>1</v>
@@ -35414,16 +35454,16 @@
         <v>0</v>
       </c>
       <c r="K159">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="L159">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M159">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N159">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -35461,80 +35501,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="177" t="s">
+      <c r="A1" s="178" t="s">
         <v>359</v>
       </c>
-      <c r="B1" s="158"/>
-      <c r="C1" s="158"/>
-      <c r="D1" s="158"/>
-      <c r="E1" s="158"/>
-      <c r="F1" s="158"/>
-      <c r="G1" s="158"/>
-      <c r="H1" s="158"/>
-      <c r="I1" s="158"/>
-      <c r="J1" s="158"/>
-      <c r="K1" s="158"/>
-      <c r="L1" s="158"/>
-      <c r="M1" s="158"/>
-      <c r="N1" s="158"/>
-      <c r="O1" s="158"/>
-      <c r="P1" s="158"/>
-      <c r="Q1" s="158"/>
+      <c r="B1" s="159"/>
+      <c r="C1" s="159"/>
+      <c r="D1" s="159"/>
+      <c r="E1" s="159"/>
+      <c r="F1" s="159"/>
+      <c r="G1" s="159"/>
+      <c r="H1" s="159"/>
+      <c r="I1" s="159"/>
+      <c r="J1" s="159"/>
+      <c r="K1" s="159"/>
+      <c r="L1" s="159"/>
+      <c r="M1" s="159"/>
+      <c r="N1" s="159"/>
+      <c r="O1" s="159"/>
+      <c r="P1" s="159"/>
+      <c r="Q1" s="159"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="164" t="s">
+      <c r="A2" s="165" t="s">
         <v>360</v>
       </c>
-      <c r="B2" s="158"/>
-      <c r="C2" s="158"/>
-      <c r="D2" s="158"/>
-      <c r="E2" s="158"/>
-      <c r="F2" s="158"/>
-      <c r="G2" s="158"/>
-      <c r="H2" s="158"/>
-      <c r="I2" s="158"/>
-      <c r="J2" s="158"/>
-      <c r="K2" s="158"/>
-      <c r="L2" s="158"/>
-      <c r="M2" s="158"/>
-      <c r="N2" s="158"/>
-      <c r="O2" s="158"/>
-      <c r="P2" s="158"/>
-      <c r="Q2" s="158"/>
+      <c r="B2" s="159"/>
+      <c r="C2" s="159"/>
+      <c r="D2" s="159"/>
+      <c r="E2" s="159"/>
+      <c r="F2" s="159"/>
+      <c r="G2" s="159"/>
+      <c r="H2" s="159"/>
+      <c r="I2" s="159"/>
+      <c r="J2" s="159"/>
+      <c r="K2" s="159"/>
+      <c r="L2" s="159"/>
+      <c r="M2" s="159"/>
+      <c r="N2" s="159"/>
+      <c r="O2" s="159"/>
+      <c r="P2" s="159"/>
+      <c r="Q2" s="159"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="176" t="s">
+      <c r="A3" s="177" t="s">
         <v>361</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="175" t="s">
+      <c r="B3" s="159"/>
+      <c r="C3" s="176" t="s">
         <v>362</v>
       </c>
-      <c r="D3" s="158"/>
-      <c r="E3" s="178" t="s">
+      <c r="D3" s="159"/>
+      <c r="E3" s="179" t="s">
         <v>363</v>
       </c>
-      <c r="F3" s="158"/>
-      <c r="G3" s="173" t="s">
+      <c r="F3" s="159"/>
+      <c r="G3" s="174" t="s">
         <v>364</v>
       </c>
-      <c r="H3" s="158"/>
-      <c r="I3" s="158"/>
-      <c r="J3" s="158"/>
+      <c r="H3" s="159"/>
+      <c r="I3" s="159"/>
+      <c r="J3" s="159"/>
       <c r="K3" s="56" t="s">
         <v>365</v>
       </c>
       <c r="L3" s="57" t="s">
         <v>366</v>
       </c>
-      <c r="M3" s="172" t="s">
+      <c r="M3" s="173" t="s">
         <v>367</v>
       </c>
-      <c r="N3" s="158"/>
-      <c r="O3" s="172" t="s">
+      <c r="N3" s="159"/>
+      <c r="O3" s="173" t="s">
         <v>367</v>
       </c>
-      <c r="P3" s="158"/>
+      <c r="P3" s="159"/>
       <c r="Q3" s="58" t="s">
         <v>368</v>
       </c>
@@ -35593,10 +35633,10 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="174" t="s">
+      <c r="A5" s="175" t="s">
         <v>386</v>
       </c>
-      <c r="B5" s="158"/>
+      <c r="B5" s="159"/>
       <c r="C5" s="66"/>
       <c r="D5" s="67"/>
       <c r="E5" s="67"/>
@@ -37351,80 +37391,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="177" t="s">
+      <c r="A1" s="178" t="s">
         <v>394</v>
       </c>
-      <c r="B1" s="158"/>
-      <c r="C1" s="158"/>
-      <c r="D1" s="158"/>
-      <c r="E1" s="158"/>
-      <c r="F1" s="158"/>
-      <c r="G1" s="158"/>
-      <c r="H1" s="158"/>
-      <c r="I1" s="158"/>
-      <c r="J1" s="158"/>
-      <c r="K1" s="158"/>
-      <c r="L1" s="158"/>
-      <c r="M1" s="158"/>
-      <c r="N1" s="158"/>
-      <c r="O1" s="158"/>
-      <c r="P1" s="158"/>
-      <c r="Q1" s="158"/>
+      <c r="B1" s="159"/>
+      <c r="C1" s="159"/>
+      <c r="D1" s="159"/>
+      <c r="E1" s="159"/>
+      <c r="F1" s="159"/>
+      <c r="G1" s="159"/>
+      <c r="H1" s="159"/>
+      <c r="I1" s="159"/>
+      <c r="J1" s="159"/>
+      <c r="K1" s="159"/>
+      <c r="L1" s="159"/>
+      <c r="M1" s="159"/>
+      <c r="N1" s="159"/>
+      <c r="O1" s="159"/>
+      <c r="P1" s="159"/>
+      <c r="Q1" s="159"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="164" t="s">
+      <c r="A2" s="165" t="s">
         <v>360</v>
       </c>
-      <c r="B2" s="158"/>
-      <c r="C2" s="158"/>
-      <c r="D2" s="158"/>
-      <c r="E2" s="158"/>
-      <c r="F2" s="158"/>
-      <c r="G2" s="158"/>
-      <c r="H2" s="158"/>
-      <c r="I2" s="158"/>
-      <c r="J2" s="158"/>
-      <c r="K2" s="158"/>
-      <c r="L2" s="158"/>
-      <c r="M2" s="158"/>
-      <c r="N2" s="158"/>
-      <c r="O2" s="158"/>
-      <c r="P2" s="158"/>
-      <c r="Q2" s="158"/>
+      <c r="B2" s="159"/>
+      <c r="C2" s="159"/>
+      <c r="D2" s="159"/>
+      <c r="E2" s="159"/>
+      <c r="F2" s="159"/>
+      <c r="G2" s="159"/>
+      <c r="H2" s="159"/>
+      <c r="I2" s="159"/>
+      <c r="J2" s="159"/>
+      <c r="K2" s="159"/>
+      <c r="L2" s="159"/>
+      <c r="M2" s="159"/>
+      <c r="N2" s="159"/>
+      <c r="O2" s="159"/>
+      <c r="P2" s="159"/>
+      <c r="Q2" s="159"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="176" t="s">
+      <c r="A3" s="177" t="s">
         <v>361</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="175" t="s">
+      <c r="B3" s="159"/>
+      <c r="C3" s="176" t="s">
         <v>362</v>
       </c>
-      <c r="D3" s="158"/>
-      <c r="E3" s="178" t="s">
+      <c r="D3" s="159"/>
+      <c r="E3" s="179" t="s">
         <v>363</v>
       </c>
-      <c r="F3" s="158"/>
-      <c r="G3" s="173" t="s">
+      <c r="F3" s="159"/>
+      <c r="G3" s="174" t="s">
         <v>364</v>
       </c>
-      <c r="H3" s="158"/>
-      <c r="I3" s="158"/>
-      <c r="J3" s="158"/>
+      <c r="H3" s="159"/>
+      <c r="I3" s="159"/>
+      <c r="J3" s="159"/>
       <c r="K3" s="56" t="s">
         <v>365</v>
       </c>
       <c r="L3" s="57" t="s">
         <v>366</v>
       </c>
-      <c r="M3" s="172" t="s">
+      <c r="M3" s="173" t="s">
         <v>367</v>
       </c>
-      <c r="N3" s="158"/>
-      <c r="O3" s="172" t="s">
+      <c r="N3" s="159"/>
+      <c r="O3" s="173" t="s">
         <v>367</v>
       </c>
-      <c r="P3" s="158"/>
+      <c r="P3" s="159"/>
       <c r="Q3" s="58" t="s">
         <v>368</v>
       </c>
@@ -37483,10 +37523,10 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="174" t="s">
+      <c r="A5" s="175" t="s">
         <v>386</v>
       </c>
-      <c r="B5" s="158"/>
+      <c r="B5" s="159"/>
       <c r="C5" s="66"/>
       <c r="D5" s="67"/>
       <c r="E5" s="67"/>
@@ -39309,80 +39349,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="177" t="s">
+      <c r="A1" s="178" t="s">
         <v>395</v>
       </c>
-      <c r="B1" s="158"/>
-      <c r="C1" s="158"/>
-      <c r="D1" s="158"/>
-      <c r="E1" s="158"/>
-      <c r="F1" s="158"/>
-      <c r="G1" s="158"/>
-      <c r="H1" s="158"/>
-      <c r="I1" s="158"/>
-      <c r="J1" s="158"/>
-      <c r="K1" s="158"/>
-      <c r="L1" s="158"/>
-      <c r="M1" s="158"/>
-      <c r="N1" s="158"/>
-      <c r="O1" s="158"/>
-      <c r="P1" s="158"/>
-      <c r="Q1" s="158"/>
+      <c r="B1" s="159"/>
+      <c r="C1" s="159"/>
+      <c r="D1" s="159"/>
+      <c r="E1" s="159"/>
+      <c r="F1" s="159"/>
+      <c r="G1" s="159"/>
+      <c r="H1" s="159"/>
+      <c r="I1" s="159"/>
+      <c r="J1" s="159"/>
+      <c r="K1" s="159"/>
+      <c r="L1" s="159"/>
+      <c r="M1" s="159"/>
+      <c r="N1" s="159"/>
+      <c r="O1" s="159"/>
+      <c r="P1" s="159"/>
+      <c r="Q1" s="159"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="164" t="s">
+      <c r="A2" s="165" t="s">
         <v>360</v>
       </c>
-      <c r="B2" s="158"/>
-      <c r="C2" s="158"/>
-      <c r="D2" s="158"/>
-      <c r="E2" s="158"/>
-      <c r="F2" s="158"/>
-      <c r="G2" s="158"/>
-      <c r="H2" s="158"/>
-      <c r="I2" s="158"/>
-      <c r="J2" s="158"/>
-      <c r="K2" s="158"/>
-      <c r="L2" s="158"/>
-      <c r="M2" s="158"/>
-      <c r="N2" s="158"/>
-      <c r="O2" s="158"/>
-      <c r="P2" s="158"/>
-      <c r="Q2" s="158"/>
+      <c r="B2" s="159"/>
+      <c r="C2" s="159"/>
+      <c r="D2" s="159"/>
+      <c r="E2" s="159"/>
+      <c r="F2" s="159"/>
+      <c r="G2" s="159"/>
+      <c r="H2" s="159"/>
+      <c r="I2" s="159"/>
+      <c r="J2" s="159"/>
+      <c r="K2" s="159"/>
+      <c r="L2" s="159"/>
+      <c r="M2" s="159"/>
+      <c r="N2" s="159"/>
+      <c r="O2" s="159"/>
+      <c r="P2" s="159"/>
+      <c r="Q2" s="159"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="176" t="s">
+      <c r="A3" s="177" t="s">
         <v>361</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="175" t="s">
+      <c r="B3" s="159"/>
+      <c r="C3" s="176" t="s">
         <v>362</v>
       </c>
-      <c r="D3" s="158"/>
-      <c r="E3" s="178" t="s">
+      <c r="D3" s="159"/>
+      <c r="E3" s="179" t="s">
         <v>363</v>
       </c>
-      <c r="F3" s="158"/>
-      <c r="G3" s="173" t="s">
+      <c r="F3" s="159"/>
+      <c r="G3" s="174" t="s">
         <v>364</v>
       </c>
-      <c r="H3" s="158"/>
-      <c r="I3" s="158"/>
-      <c r="J3" s="158"/>
+      <c r="H3" s="159"/>
+      <c r="I3" s="159"/>
+      <c r="J3" s="159"/>
       <c r="K3" s="56" t="s">
         <v>365</v>
       </c>
       <c r="L3" s="57" t="s">
         <v>366</v>
       </c>
-      <c r="M3" s="172" t="s">
+      <c r="M3" s="173" t="s">
         <v>367</v>
       </c>
-      <c r="N3" s="158"/>
-      <c r="O3" s="172" t="s">
+      <c r="N3" s="159"/>
+      <c r="O3" s="173" t="s">
         <v>367</v>
       </c>
-      <c r="P3" s="158"/>
+      <c r="P3" s="159"/>
       <c r="Q3" s="58" t="s">
         <v>368</v>
       </c>
@@ -39441,10 +39481,10 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="174" t="s">
+      <c r="A5" s="175" t="s">
         <v>386</v>
       </c>
-      <c r="B5" s="158"/>
+      <c r="B5" s="159"/>
       <c r="C5" s="66"/>
       <c r="D5" s="67"/>
       <c r="E5" s="67"/>
@@ -41225,80 +41265,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="177" t="s">
+      <c r="A1" s="178" t="s">
         <v>396</v>
       </c>
-      <c r="B1" s="158"/>
-      <c r="C1" s="158"/>
-      <c r="D1" s="158"/>
-      <c r="E1" s="158"/>
-      <c r="F1" s="158"/>
-      <c r="G1" s="158"/>
-      <c r="H1" s="158"/>
-      <c r="I1" s="158"/>
-      <c r="J1" s="158"/>
-      <c r="K1" s="158"/>
-      <c r="L1" s="158"/>
-      <c r="M1" s="158"/>
-      <c r="N1" s="158"/>
-      <c r="O1" s="158"/>
-      <c r="P1" s="158"/>
-      <c r="Q1" s="158"/>
+      <c r="B1" s="159"/>
+      <c r="C1" s="159"/>
+      <c r="D1" s="159"/>
+      <c r="E1" s="159"/>
+      <c r="F1" s="159"/>
+      <c r="G1" s="159"/>
+      <c r="H1" s="159"/>
+      <c r="I1" s="159"/>
+      <c r="J1" s="159"/>
+      <c r="K1" s="159"/>
+      <c r="L1" s="159"/>
+      <c r="M1" s="159"/>
+      <c r="N1" s="159"/>
+      <c r="O1" s="159"/>
+      <c r="P1" s="159"/>
+      <c r="Q1" s="159"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="164" t="s">
+      <c r="A2" s="165" t="s">
         <v>360</v>
       </c>
-      <c r="B2" s="158"/>
-      <c r="C2" s="158"/>
-      <c r="D2" s="158"/>
-      <c r="E2" s="158"/>
-      <c r="F2" s="158"/>
-      <c r="G2" s="158"/>
-      <c r="H2" s="158"/>
-      <c r="I2" s="158"/>
-      <c r="J2" s="158"/>
-      <c r="K2" s="158"/>
-      <c r="L2" s="158"/>
-      <c r="M2" s="158"/>
-      <c r="N2" s="158"/>
-      <c r="O2" s="158"/>
-      <c r="P2" s="158"/>
-      <c r="Q2" s="158"/>
+      <c r="B2" s="159"/>
+      <c r="C2" s="159"/>
+      <c r="D2" s="159"/>
+      <c r="E2" s="159"/>
+      <c r="F2" s="159"/>
+      <c r="G2" s="159"/>
+      <c r="H2" s="159"/>
+      <c r="I2" s="159"/>
+      <c r="J2" s="159"/>
+      <c r="K2" s="159"/>
+      <c r="L2" s="159"/>
+      <c r="M2" s="159"/>
+      <c r="N2" s="159"/>
+      <c r="O2" s="159"/>
+      <c r="P2" s="159"/>
+      <c r="Q2" s="159"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="176" t="s">
+      <c r="A3" s="177" t="s">
         <v>361</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="175" t="s">
+      <c r="B3" s="159"/>
+      <c r="C3" s="176" t="s">
         <v>362</v>
       </c>
-      <c r="D3" s="158"/>
-      <c r="E3" s="178" t="s">
+      <c r="D3" s="159"/>
+      <c r="E3" s="179" t="s">
         <v>363</v>
       </c>
-      <c r="F3" s="158"/>
-      <c r="G3" s="173" t="s">
+      <c r="F3" s="159"/>
+      <c r="G3" s="174" t="s">
         <v>364</v>
       </c>
-      <c r="H3" s="158"/>
-      <c r="I3" s="158"/>
-      <c r="J3" s="158"/>
+      <c r="H3" s="159"/>
+      <c r="I3" s="159"/>
+      <c r="J3" s="159"/>
       <c r="K3" s="56" t="s">
         <v>365</v>
       </c>
       <c r="L3" s="57" t="s">
         <v>366</v>
       </c>
-      <c r="M3" s="172" t="s">
+      <c r="M3" s="173" t="s">
         <v>367</v>
       </c>
-      <c r="N3" s="158"/>
-      <c r="O3" s="172" t="s">
+      <c r="N3" s="159"/>
+      <c r="O3" s="173" t="s">
         <v>367</v>
       </c>
-      <c r="P3" s="158"/>
+      <c r="P3" s="159"/>
       <c r="Q3" s="58" t="s">
         <v>368</v>
       </c>
@@ -41357,10 +41397,10 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="174" t="s">
+      <c r="A5" s="175" t="s">
         <v>386</v>
       </c>
-      <c r="B5" s="158"/>
+      <c r="B5" s="159"/>
       <c r="C5" s="66"/>
       <c r="D5" s="67"/>
       <c r="E5" s="67"/>
@@ -43189,80 +43229,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="177" t="s">
+      <c r="A1" s="178" t="s">
         <v>397</v>
       </c>
-      <c r="B1" s="158"/>
-      <c r="C1" s="158"/>
-      <c r="D1" s="158"/>
-      <c r="E1" s="158"/>
-      <c r="F1" s="158"/>
-      <c r="G1" s="158"/>
-      <c r="H1" s="158"/>
-      <c r="I1" s="158"/>
-      <c r="J1" s="158"/>
-      <c r="K1" s="158"/>
-      <c r="L1" s="158"/>
-      <c r="M1" s="158"/>
-      <c r="N1" s="158"/>
-      <c r="O1" s="158"/>
-      <c r="P1" s="158"/>
-      <c r="Q1" s="158"/>
+      <c r="B1" s="159"/>
+      <c r="C1" s="159"/>
+      <c r="D1" s="159"/>
+      <c r="E1" s="159"/>
+      <c r="F1" s="159"/>
+      <c r="G1" s="159"/>
+      <c r="H1" s="159"/>
+      <c r="I1" s="159"/>
+      <c r="J1" s="159"/>
+      <c r="K1" s="159"/>
+      <c r="L1" s="159"/>
+      <c r="M1" s="159"/>
+      <c r="N1" s="159"/>
+      <c r="O1" s="159"/>
+      <c r="P1" s="159"/>
+      <c r="Q1" s="159"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="164" t="s">
+      <c r="A2" s="165" t="s">
         <v>360</v>
       </c>
-      <c r="B2" s="158"/>
-      <c r="C2" s="158"/>
-      <c r="D2" s="158"/>
-      <c r="E2" s="158"/>
-      <c r="F2" s="158"/>
-      <c r="G2" s="158"/>
-      <c r="H2" s="158"/>
-      <c r="I2" s="158"/>
-      <c r="J2" s="158"/>
-      <c r="K2" s="158"/>
-      <c r="L2" s="158"/>
-      <c r="M2" s="158"/>
-      <c r="N2" s="158"/>
-      <c r="O2" s="158"/>
-      <c r="P2" s="158"/>
-      <c r="Q2" s="158"/>
+      <c r="B2" s="159"/>
+      <c r="C2" s="159"/>
+      <c r="D2" s="159"/>
+      <c r="E2" s="159"/>
+      <c r="F2" s="159"/>
+      <c r="G2" s="159"/>
+      <c r="H2" s="159"/>
+      <c r="I2" s="159"/>
+      <c r="J2" s="159"/>
+      <c r="K2" s="159"/>
+      <c r="L2" s="159"/>
+      <c r="M2" s="159"/>
+      <c r="N2" s="159"/>
+      <c r="O2" s="159"/>
+      <c r="P2" s="159"/>
+      <c r="Q2" s="159"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="176" t="s">
+      <c r="A3" s="177" t="s">
         <v>361</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="175" t="s">
+      <c r="B3" s="159"/>
+      <c r="C3" s="176" t="s">
         <v>362</v>
       </c>
-      <c r="D3" s="158"/>
-      <c r="E3" s="178" t="s">
+      <c r="D3" s="159"/>
+      <c r="E3" s="179" t="s">
         <v>363</v>
       </c>
-      <c r="F3" s="158"/>
-      <c r="G3" s="173" t="s">
+      <c r="F3" s="159"/>
+      <c r="G3" s="174" t="s">
         <v>364</v>
       </c>
-      <c r="H3" s="158"/>
-      <c r="I3" s="158"/>
-      <c r="J3" s="158"/>
+      <c r="H3" s="159"/>
+      <c r="I3" s="159"/>
+      <c r="J3" s="159"/>
       <c r="K3" s="56" t="s">
         <v>365</v>
       </c>
       <c r="L3" s="57" t="s">
         <v>366</v>
       </c>
-      <c r="M3" s="172" t="s">
+      <c r="M3" s="173" t="s">
         <v>367</v>
       </c>
-      <c r="N3" s="158"/>
-      <c r="O3" s="172" t="s">
+      <c r="N3" s="159"/>
+      <c r="O3" s="173" t="s">
         <v>367</v>
       </c>
-      <c r="P3" s="158"/>
+      <c r="P3" s="159"/>
       <c r="Q3" s="58" t="s">
         <v>368</v>
       </c>
@@ -43321,10 +43361,10 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="174" t="s">
+      <c r="A5" s="175" t="s">
         <v>386</v>
       </c>
-      <c r="B5" s="158"/>
+      <c r="B5" s="159"/>
       <c r="C5" s="66"/>
       <c r="D5" s="67"/>
       <c r="E5" s="67"/>
@@ -45141,80 +45181,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="177" t="s">
+      <c r="A1" s="178" t="s">
         <v>398</v>
       </c>
-      <c r="B1" s="158"/>
-      <c r="C1" s="158"/>
-      <c r="D1" s="158"/>
-      <c r="E1" s="158"/>
-      <c r="F1" s="158"/>
-      <c r="G1" s="158"/>
-      <c r="H1" s="158"/>
-      <c r="I1" s="158"/>
-      <c r="J1" s="158"/>
-      <c r="K1" s="158"/>
-      <c r="L1" s="158"/>
-      <c r="M1" s="158"/>
-      <c r="N1" s="158"/>
-      <c r="O1" s="158"/>
-      <c r="P1" s="158"/>
-      <c r="Q1" s="158"/>
+      <c r="B1" s="159"/>
+      <c r="C1" s="159"/>
+      <c r="D1" s="159"/>
+      <c r="E1" s="159"/>
+      <c r="F1" s="159"/>
+      <c r="G1" s="159"/>
+      <c r="H1" s="159"/>
+      <c r="I1" s="159"/>
+      <c r="J1" s="159"/>
+      <c r="K1" s="159"/>
+      <c r="L1" s="159"/>
+      <c r="M1" s="159"/>
+      <c r="N1" s="159"/>
+      <c r="O1" s="159"/>
+      <c r="P1" s="159"/>
+      <c r="Q1" s="159"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="164" t="s">
+      <c r="A2" s="165" t="s">
         <v>360</v>
       </c>
-      <c r="B2" s="158"/>
-      <c r="C2" s="158"/>
-      <c r="D2" s="158"/>
-      <c r="E2" s="158"/>
-      <c r="F2" s="158"/>
-      <c r="G2" s="158"/>
-      <c r="H2" s="158"/>
-      <c r="I2" s="158"/>
-      <c r="J2" s="158"/>
-      <c r="K2" s="158"/>
-      <c r="L2" s="158"/>
-      <c r="M2" s="158"/>
-      <c r="N2" s="158"/>
-      <c r="O2" s="158"/>
-      <c r="P2" s="158"/>
-      <c r="Q2" s="158"/>
+      <c r="B2" s="159"/>
+      <c r="C2" s="159"/>
+      <c r="D2" s="159"/>
+      <c r="E2" s="159"/>
+      <c r="F2" s="159"/>
+      <c r="G2" s="159"/>
+      <c r="H2" s="159"/>
+      <c r="I2" s="159"/>
+      <c r="J2" s="159"/>
+      <c r="K2" s="159"/>
+      <c r="L2" s="159"/>
+      <c r="M2" s="159"/>
+      <c r="N2" s="159"/>
+      <c r="O2" s="159"/>
+      <c r="P2" s="159"/>
+      <c r="Q2" s="159"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="176" t="s">
+      <c r="A3" s="177" t="s">
         <v>361</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="175" t="s">
+      <c r="B3" s="159"/>
+      <c r="C3" s="176" t="s">
         <v>362</v>
       </c>
-      <c r="D3" s="158"/>
-      <c r="E3" s="178" t="s">
+      <c r="D3" s="159"/>
+      <c r="E3" s="179" t="s">
         <v>363</v>
       </c>
-      <c r="F3" s="158"/>
-      <c r="G3" s="173" t="s">
+      <c r="F3" s="159"/>
+      <c r="G3" s="174" t="s">
         <v>364</v>
       </c>
-      <c r="H3" s="158"/>
-      <c r="I3" s="158"/>
-      <c r="J3" s="158"/>
+      <c r="H3" s="159"/>
+      <c r="I3" s="159"/>
+      <c r="J3" s="159"/>
       <c r="K3" s="56" t="s">
         <v>365</v>
       </c>
       <c r="L3" s="57" t="s">
         <v>366</v>
       </c>
-      <c r="M3" s="172" t="s">
+      <c r="M3" s="173" t="s">
         <v>367</v>
       </c>
-      <c r="N3" s="158"/>
-      <c r="O3" s="172" t="s">
+      <c r="N3" s="159"/>
+      <c r="O3" s="173" t="s">
         <v>367</v>
       </c>
-      <c r="P3" s="158"/>
+      <c r="P3" s="159"/>
       <c r="Q3" s="58" t="s">
         <v>368</v>
       </c>
@@ -45273,10 +45313,10 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="174" t="s">
+      <c r="A5" s="175" t="s">
         <v>386</v>
       </c>
-      <c r="B5" s="158"/>
+      <c r="B5" s="159"/>
       <c r="C5" s="66"/>
       <c r="D5" s="67"/>
       <c r="E5" s="67"/>
@@ -46929,80 +46969,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="177" t="s">
+      <c r="A1" s="178" t="s">
         <v>399</v>
       </c>
-      <c r="B1" s="158"/>
-      <c r="C1" s="158"/>
-      <c r="D1" s="158"/>
-      <c r="E1" s="158"/>
-      <c r="F1" s="158"/>
-      <c r="G1" s="158"/>
-      <c r="H1" s="158"/>
-      <c r="I1" s="158"/>
-      <c r="J1" s="158"/>
-      <c r="K1" s="158"/>
-      <c r="L1" s="158"/>
-      <c r="M1" s="158"/>
-      <c r="N1" s="158"/>
-      <c r="O1" s="158"/>
-      <c r="P1" s="158"/>
-      <c r="Q1" s="158"/>
+      <c r="B1" s="159"/>
+      <c r="C1" s="159"/>
+      <c r="D1" s="159"/>
+      <c r="E1" s="159"/>
+      <c r="F1" s="159"/>
+      <c r="G1" s="159"/>
+      <c r="H1" s="159"/>
+      <c r="I1" s="159"/>
+      <c r="J1" s="159"/>
+      <c r="K1" s="159"/>
+      <c r="L1" s="159"/>
+      <c r="M1" s="159"/>
+      <c r="N1" s="159"/>
+      <c r="O1" s="159"/>
+      <c r="P1" s="159"/>
+      <c r="Q1" s="159"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="164" t="s">
+      <c r="A2" s="165" t="s">
         <v>360</v>
       </c>
-      <c r="B2" s="158"/>
-      <c r="C2" s="158"/>
-      <c r="D2" s="158"/>
-      <c r="E2" s="158"/>
-      <c r="F2" s="158"/>
-      <c r="G2" s="158"/>
-      <c r="H2" s="158"/>
-      <c r="I2" s="158"/>
-      <c r="J2" s="158"/>
-      <c r="K2" s="158"/>
-      <c r="L2" s="158"/>
-      <c r="M2" s="158"/>
-      <c r="N2" s="158"/>
-      <c r="O2" s="158"/>
-      <c r="P2" s="158"/>
-      <c r="Q2" s="158"/>
+      <c r="B2" s="159"/>
+      <c r="C2" s="159"/>
+      <c r="D2" s="159"/>
+      <c r="E2" s="159"/>
+      <c r="F2" s="159"/>
+      <c r="G2" s="159"/>
+      <c r="H2" s="159"/>
+      <c r="I2" s="159"/>
+      <c r="J2" s="159"/>
+      <c r="K2" s="159"/>
+      <c r="L2" s="159"/>
+      <c r="M2" s="159"/>
+      <c r="N2" s="159"/>
+      <c r="O2" s="159"/>
+      <c r="P2" s="159"/>
+      <c r="Q2" s="159"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="176" t="s">
+      <c r="A3" s="177" t="s">
         <v>361</v>
       </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="175" t="s">
+      <c r="B3" s="159"/>
+      <c r="C3" s="176" t="s">
         <v>362</v>
       </c>
-      <c r="D3" s="158"/>
-      <c r="E3" s="178" t="s">
+      <c r="D3" s="159"/>
+      <c r="E3" s="179" t="s">
         <v>363</v>
       </c>
-      <c r="F3" s="158"/>
-      <c r="G3" s="173" t="s">
+      <c r="F3" s="159"/>
+      <c r="G3" s="174" t="s">
         <v>364</v>
       </c>
-      <c r="H3" s="158"/>
-      <c r="I3" s="158"/>
-      <c r="J3" s="158"/>
+      <c r="H3" s="159"/>
+      <c r="I3" s="159"/>
+      <c r="J3" s="159"/>
       <c r="K3" s="56" t="s">
         <v>365</v>
       </c>
       <c r="L3" s="57" t="s">
         <v>366</v>
       </c>
-      <c r="M3" s="172" t="s">
+      <c r="M3" s="173" t="s">
         <v>367</v>
       </c>
-      <c r="N3" s="158"/>
-      <c r="O3" s="172" t="s">
+      <c r="N3" s="159"/>
+      <c r="O3" s="173" t="s">
         <v>367</v>
       </c>
-      <c r="P3" s="158"/>
+      <c r="P3" s="159"/>
       <c r="Q3" s="58" t="s">
         <v>368</v>
       </c>
@@ -47061,10 +47101,10 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="174" t="s">
+      <c r="A5" s="175" t="s">
         <v>386</v>
       </c>
-      <c r="B5" s="158"/>
+      <c r="B5" s="159"/>
       <c r="C5" s="66"/>
       <c r="D5" s="67"/>
       <c r="E5" s="67"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macos/REPORT FB&amp;STORE/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macos/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2815A711-2357-6D4A-8B8F-408B7D7CFC2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9670C4E-6329-D345-B6B3-2D0DC192514C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="80" yWindow="660" windowWidth="29320" windowHeight="18460" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,6 @@
     <sheet name="HÀNH VI SP" sheetId="27" r:id="rId27"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -2888,7 +2887,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="49" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="184">
+  <cellXfs count="183">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3296,13 +3295,35 @@
     <xf numFmtId="0" fontId="54" fillId="53" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="11" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3310,19 +3331,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="50" fillId="46" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3336,6 +3344,12 @@
     </xf>
     <xf numFmtId="0" fontId="51" fillId="47" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3352,22 +3366,16 @@
     <xf numFmtId="0" fontId="15" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="45" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3394,18 +3402,6 @@
     </xf>
     <xf numFmtId="0" fontId="34" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3682,40 +3678,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="155" t="s">
+      <c r="A1" s="158" t="s">
         <v>95</v>
       </c>
-      <c r="B1" s="156"/>
-      <c r="C1" s="156"/>
-      <c r="D1" s="156"/>
-      <c r="E1" s="156"/>
-      <c r="F1" s="156"/>
-      <c r="G1" s="156"/>
-      <c r="H1" s="156"/>
+      <c r="B1" s="159"/>
+      <c r="C1" s="159"/>
+      <c r="D1" s="159"/>
+      <c r="E1" s="159"/>
+      <c r="F1" s="159"/>
+      <c r="G1" s="159"/>
+      <c r="H1" s="159"/>
     </row>
     <row r="2" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="159" t="s">
+      <c r="A2" s="162" t="s">
         <v>96</v>
       </c>
-      <c r="B2" s="156"/>
-      <c r="C2" s="156"/>
-      <c r="D2" s="156"/>
-      <c r="E2" s="156"/>
-      <c r="F2" s="156"/>
-      <c r="G2" s="156"/>
-      <c r="H2" s="156"/>
+      <c r="B2" s="159"/>
+      <c r="C2" s="159"/>
+      <c r="D2" s="159"/>
+      <c r="E2" s="159"/>
+      <c r="F2" s="159"/>
+      <c r="G2" s="159"/>
+      <c r="H2" s="159"/>
     </row>
     <row r="3" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="157" t="s">
+      <c r="A3" s="160" t="s">
         <v>97</v>
       </c>
-      <c r="B3" s="156"/>
-      <c r="C3" s="156"/>
-      <c r="D3" s="156"/>
-      <c r="E3" s="156"/>
-      <c r="F3" s="156"/>
-      <c r="G3" s="156"/>
-      <c r="H3" s="156"/>
+      <c r="B3" s="159"/>
+      <c r="C3" s="159"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="159"/>
+      <c r="G3" s="159"/>
+      <c r="H3" s="159"/>
     </row>
     <row r="4" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="133" t="s">
@@ -3744,16 +3740,16 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="158" t="s">
+      <c r="A5" s="161" t="s">
         <v>106</v>
       </c>
-      <c r="B5" s="156"/>
-      <c r="C5" s="156"/>
-      <c r="D5" s="156"/>
-      <c r="E5" s="156"/>
-      <c r="F5" s="156"/>
-      <c r="G5" s="156"/>
-      <c r="H5" s="156"/>
+      <c r="B5" s="159"/>
+      <c r="C5" s="159"/>
+      <c r="D5" s="159"/>
+      <c r="E5" s="159"/>
+      <c r="F5" s="159"/>
+      <c r="G5" s="159"/>
+      <c r="H5" s="159"/>
     </row>
     <row r="6" spans="1:8" ht="68" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="134" t="s">
@@ -3884,16 +3880,16 @@
       <c r="H10" s="136"/>
     </row>
     <row r="11" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="158" t="s">
+      <c r="A11" s="161" t="s">
         <v>137</v>
       </c>
-      <c r="B11" s="156"/>
-      <c r="C11" s="156"/>
-      <c r="D11" s="156"/>
-      <c r="E11" s="156"/>
-      <c r="F11" s="156"/>
-      <c r="G11" s="156"/>
-      <c r="H11" s="156"/>
+      <c r="B11" s="159"/>
+      <c r="C11" s="159"/>
+      <c r="D11" s="159"/>
+      <c r="E11" s="159"/>
+      <c r="F11" s="159"/>
+      <c r="G11" s="159"/>
+      <c r="H11" s="159"/>
     </row>
     <row r="12" spans="1:8" ht="68" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="134" t="s">
@@ -4202,16 +4198,16 @@
       </c>
     </row>
     <row r="24" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="158" t="s">
+      <c r="A24" s="161" t="s">
         <v>207</v>
       </c>
-      <c r="B24" s="156"/>
-      <c r="C24" s="156"/>
-      <c r="D24" s="156"/>
-      <c r="E24" s="156"/>
-      <c r="F24" s="156"/>
-      <c r="G24" s="156"/>
-      <c r="H24" s="156"/>
+      <c r="B24" s="159"/>
+      <c r="C24" s="159"/>
+      <c r="D24" s="159"/>
+      <c r="E24" s="159"/>
+      <c r="F24" s="159"/>
+      <c r="G24" s="159"/>
+      <c r="H24" s="159"/>
     </row>
     <row r="25" spans="1:8" ht="68" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="134" t="s">
@@ -4356,16 +4352,16 @@
       <c r="H30" s="140"/>
     </row>
     <row r="31" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="158" t="s">
+      <c r="A31" s="161" t="s">
         <v>237</v>
       </c>
-      <c r="B31" s="156"/>
-      <c r="C31" s="156"/>
-      <c r="D31" s="156"/>
-      <c r="E31" s="156"/>
-      <c r="F31" s="156"/>
-      <c r="G31" s="156"/>
-      <c r="H31" s="156"/>
+      <c r="B31" s="159"/>
+      <c r="C31" s="159"/>
+      <c r="D31" s="159"/>
+      <c r="E31" s="159"/>
+      <c r="F31" s="159"/>
+      <c r="G31" s="159"/>
+      <c r="H31" s="159"/>
     </row>
     <row r="32" spans="1:8" ht="68" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="134" t="s">
@@ -4650,16 +4646,16 @@
       </c>
     </row>
     <row r="44" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="158" t="s">
+      <c r="A44" s="161" t="s">
         <v>293</v>
       </c>
-      <c r="B44" s="156"/>
-      <c r="C44" s="156"/>
-      <c r="D44" s="156"/>
-      <c r="E44" s="156"/>
-      <c r="F44" s="156"/>
-      <c r="G44" s="156"/>
-      <c r="H44" s="156"/>
+      <c r="B44" s="159"/>
+      <c r="C44" s="159"/>
+      <c r="D44" s="159"/>
+      <c r="E44" s="159"/>
+      <c r="F44" s="159"/>
+      <c r="G44" s="159"/>
+      <c r="H44" s="159"/>
     </row>
     <row r="45" spans="1:8" ht="68" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="134" t="s">
@@ -4816,16 +4812,16 @@
       </c>
     </row>
     <row r="51" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="158" t="s">
+      <c r="A51" s="161" t="s">
         <v>331</v>
       </c>
-      <c r="B51" s="156"/>
-      <c r="C51" s="156"/>
-      <c r="D51" s="156"/>
-      <c r="E51" s="156"/>
-      <c r="F51" s="156"/>
-      <c r="G51" s="156"/>
-      <c r="H51" s="156"/>
+      <c r="B51" s="159"/>
+      <c r="C51" s="159"/>
+      <c r="D51" s="159"/>
+      <c r="E51" s="159"/>
+      <c r="F51" s="159"/>
+      <c r="G51" s="159"/>
+      <c r="H51" s="159"/>
     </row>
     <row r="52" spans="1:8" ht="68" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="134" t="s">
@@ -5039,80 +5035,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="165" t="s">
+      <c r="A1" s="163" t="s">
         <v>413</v>
       </c>
-      <c r="B1" s="144"/>
-      <c r="C1" s="144"/>
-      <c r="D1" s="144"/>
-      <c r="E1" s="144"/>
-      <c r="F1" s="144"/>
-      <c r="G1" s="144"/>
-      <c r="H1" s="144"/>
-      <c r="I1" s="144"/>
-      <c r="J1" s="144"/>
-      <c r="K1" s="144"/>
-      <c r="L1" s="144"/>
-      <c r="M1" s="144"/>
-      <c r="N1" s="144"/>
-      <c r="O1" s="144"/>
-      <c r="P1" s="144"/>
-      <c r="Q1" s="144"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="147"/>
+      <c r="M1" s="147"/>
+      <c r="N1" s="147"/>
+      <c r="O1" s="147"/>
+      <c r="P1" s="147"/>
+      <c r="Q1" s="147"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="150" t="s">
         <v>373</v>
       </c>
-      <c r="B2" s="144"/>
-      <c r="C2" s="144"/>
-      <c r="D2" s="144"/>
-      <c r="E2" s="144"/>
-      <c r="F2" s="144"/>
-      <c r="G2" s="144"/>
-      <c r="H2" s="144"/>
-      <c r="I2" s="144"/>
-      <c r="J2" s="144"/>
-      <c r="K2" s="144"/>
-      <c r="L2" s="144"/>
-      <c r="M2" s="144"/>
-      <c r="N2" s="144"/>
-      <c r="O2" s="144"/>
-      <c r="P2" s="144"/>
-      <c r="Q2" s="144"/>
+      <c r="B2" s="147"/>
+      <c r="C2" s="147"/>
+      <c r="D2" s="147"/>
+      <c r="E2" s="147"/>
+      <c r="F2" s="147"/>
+      <c r="G2" s="147"/>
+      <c r="H2" s="147"/>
+      <c r="I2" s="147"/>
+      <c r="J2" s="147"/>
+      <c r="K2" s="147"/>
+      <c r="L2" s="147"/>
+      <c r="M2" s="147"/>
+      <c r="N2" s="147"/>
+      <c r="O2" s="147"/>
+      <c r="P2" s="147"/>
+      <c r="Q2" s="147"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="164" t="s">
+      <c r="A3" s="169" t="s">
         <v>374</v>
       </c>
-      <c r="B3" s="144"/>
-      <c r="C3" s="163" t="s">
+      <c r="B3" s="147"/>
+      <c r="C3" s="168" t="s">
         <v>375</v>
       </c>
-      <c r="D3" s="144"/>
-      <c r="E3" s="166" t="s">
+      <c r="D3" s="147"/>
+      <c r="E3" s="164" t="s">
         <v>376</v>
       </c>
-      <c r="F3" s="144"/>
-      <c r="G3" s="161" t="s">
+      <c r="F3" s="147"/>
+      <c r="G3" s="166" t="s">
         <v>377</v>
       </c>
-      <c r="H3" s="144"/>
-      <c r="I3" s="144"/>
-      <c r="J3" s="144"/>
+      <c r="H3" s="147"/>
+      <c r="I3" s="147"/>
+      <c r="J3" s="147"/>
       <c r="K3" s="31" t="s">
         <v>378</v>
       </c>
       <c r="L3" s="32" t="s">
         <v>379</v>
       </c>
-      <c r="M3" s="160" t="s">
+      <c r="M3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="N3" s="144"/>
-      <c r="O3" s="160" t="s">
+      <c r="N3" s="147"/>
+      <c r="O3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="P3" s="144"/>
+      <c r="P3" s="147"/>
       <c r="Q3" s="33" t="s">
         <v>381</v>
       </c>
@@ -5171,10 +5167,10 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="162" t="s">
+      <c r="A5" s="167" t="s">
         <v>399</v>
       </c>
-      <c r="B5" s="144"/>
+      <c r="B5" s="147"/>
       <c r="C5" s="41"/>
       <c r="D5" s="42"/>
       <c r="E5" s="42"/>
@@ -6937,80 +6933,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="165" t="s">
+      <c r="A1" s="163" t="s">
         <v>414</v>
       </c>
-      <c r="B1" s="144"/>
-      <c r="C1" s="144"/>
-      <c r="D1" s="144"/>
-      <c r="E1" s="144"/>
-      <c r="F1" s="144"/>
-      <c r="G1" s="144"/>
-      <c r="H1" s="144"/>
-      <c r="I1" s="144"/>
-      <c r="J1" s="144"/>
-      <c r="K1" s="144"/>
-      <c r="L1" s="144"/>
-      <c r="M1" s="144"/>
-      <c r="N1" s="144"/>
-      <c r="O1" s="144"/>
-      <c r="P1" s="144"/>
-      <c r="Q1" s="144"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="147"/>
+      <c r="M1" s="147"/>
+      <c r="N1" s="147"/>
+      <c r="O1" s="147"/>
+      <c r="P1" s="147"/>
+      <c r="Q1" s="147"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="150" t="s">
         <v>373</v>
       </c>
-      <c r="B2" s="144"/>
-      <c r="C2" s="144"/>
-      <c r="D2" s="144"/>
-      <c r="E2" s="144"/>
-      <c r="F2" s="144"/>
-      <c r="G2" s="144"/>
-      <c r="H2" s="144"/>
-      <c r="I2" s="144"/>
-      <c r="J2" s="144"/>
-      <c r="K2" s="144"/>
-      <c r="L2" s="144"/>
-      <c r="M2" s="144"/>
-      <c r="N2" s="144"/>
-      <c r="O2" s="144"/>
-      <c r="P2" s="144"/>
-      <c r="Q2" s="144"/>
+      <c r="B2" s="147"/>
+      <c r="C2" s="147"/>
+      <c r="D2" s="147"/>
+      <c r="E2" s="147"/>
+      <c r="F2" s="147"/>
+      <c r="G2" s="147"/>
+      <c r="H2" s="147"/>
+      <c r="I2" s="147"/>
+      <c r="J2" s="147"/>
+      <c r="K2" s="147"/>
+      <c r="L2" s="147"/>
+      <c r="M2" s="147"/>
+      <c r="N2" s="147"/>
+      <c r="O2" s="147"/>
+      <c r="P2" s="147"/>
+      <c r="Q2" s="147"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="164" t="s">
+      <c r="A3" s="169" t="s">
         <v>374</v>
       </c>
-      <c r="B3" s="144"/>
-      <c r="C3" s="163" t="s">
+      <c r="B3" s="147"/>
+      <c r="C3" s="168" t="s">
         <v>375</v>
       </c>
-      <c r="D3" s="144"/>
-      <c r="E3" s="166" t="s">
+      <c r="D3" s="147"/>
+      <c r="E3" s="164" t="s">
         <v>376</v>
       </c>
-      <c r="F3" s="144"/>
-      <c r="G3" s="161" t="s">
+      <c r="F3" s="147"/>
+      <c r="G3" s="166" t="s">
         <v>377</v>
       </c>
-      <c r="H3" s="144"/>
-      <c r="I3" s="144"/>
-      <c r="J3" s="144"/>
+      <c r="H3" s="147"/>
+      <c r="I3" s="147"/>
+      <c r="J3" s="147"/>
       <c r="K3" s="31" t="s">
         <v>378</v>
       </c>
       <c r="L3" s="32" t="s">
         <v>379</v>
       </c>
-      <c r="M3" s="160" t="s">
+      <c r="M3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="N3" s="144"/>
-      <c r="O3" s="160" t="s">
+      <c r="N3" s="147"/>
+      <c r="O3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="P3" s="144"/>
+      <c r="P3" s="147"/>
       <c r="Q3" s="33" t="s">
         <v>381</v>
       </c>
@@ -7069,10 +7065,10 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="162" t="s">
+      <c r="A5" s="167" t="s">
         <v>399</v>
       </c>
-      <c r="B5" s="144"/>
+      <c r="B5" s="147"/>
       <c r="C5" s="41"/>
       <c r="D5" s="42"/>
       <c r="E5" s="42"/>
@@ -8876,80 +8872,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="165" t="s">
+      <c r="A1" s="163" t="s">
         <v>415</v>
       </c>
-      <c r="B1" s="144"/>
-      <c r="C1" s="144"/>
-      <c r="D1" s="144"/>
-      <c r="E1" s="144"/>
-      <c r="F1" s="144"/>
-      <c r="G1" s="144"/>
-      <c r="H1" s="144"/>
-      <c r="I1" s="144"/>
-      <c r="J1" s="144"/>
-      <c r="K1" s="144"/>
-      <c r="L1" s="144"/>
-      <c r="M1" s="144"/>
-      <c r="N1" s="144"/>
-      <c r="O1" s="144"/>
-      <c r="P1" s="144"/>
-      <c r="Q1" s="144"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="147"/>
+      <c r="M1" s="147"/>
+      <c r="N1" s="147"/>
+      <c r="O1" s="147"/>
+      <c r="P1" s="147"/>
+      <c r="Q1" s="147"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="150" t="s">
         <v>373</v>
       </c>
-      <c r="B2" s="144"/>
-      <c r="C2" s="144"/>
-      <c r="D2" s="144"/>
-      <c r="E2" s="144"/>
-      <c r="F2" s="144"/>
-      <c r="G2" s="144"/>
-      <c r="H2" s="144"/>
-      <c r="I2" s="144"/>
-      <c r="J2" s="144"/>
-      <c r="K2" s="144"/>
-      <c r="L2" s="144"/>
-      <c r="M2" s="144"/>
-      <c r="N2" s="144"/>
-      <c r="O2" s="144"/>
-      <c r="P2" s="144"/>
-      <c r="Q2" s="144"/>
+      <c r="B2" s="147"/>
+      <c r="C2" s="147"/>
+      <c r="D2" s="147"/>
+      <c r="E2" s="147"/>
+      <c r="F2" s="147"/>
+      <c r="G2" s="147"/>
+      <c r="H2" s="147"/>
+      <c r="I2" s="147"/>
+      <c r="J2" s="147"/>
+      <c r="K2" s="147"/>
+      <c r="L2" s="147"/>
+      <c r="M2" s="147"/>
+      <c r="N2" s="147"/>
+      <c r="O2" s="147"/>
+      <c r="P2" s="147"/>
+      <c r="Q2" s="147"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="164" t="s">
+      <c r="A3" s="169" t="s">
         <v>374</v>
       </c>
-      <c r="B3" s="144"/>
-      <c r="C3" s="163" t="s">
+      <c r="B3" s="147"/>
+      <c r="C3" s="168" t="s">
         <v>375</v>
       </c>
-      <c r="D3" s="144"/>
-      <c r="E3" s="166" t="s">
+      <c r="D3" s="147"/>
+      <c r="E3" s="164" t="s">
         <v>376</v>
       </c>
-      <c r="F3" s="144"/>
-      <c r="G3" s="161" t="s">
+      <c r="F3" s="147"/>
+      <c r="G3" s="166" t="s">
         <v>377</v>
       </c>
-      <c r="H3" s="144"/>
-      <c r="I3" s="144"/>
-      <c r="J3" s="144"/>
+      <c r="H3" s="147"/>
+      <c r="I3" s="147"/>
+      <c r="J3" s="147"/>
       <c r="K3" s="31" t="s">
         <v>378</v>
       </c>
       <c r="L3" s="32" t="s">
         <v>379</v>
       </c>
-      <c r="M3" s="160" t="s">
+      <c r="M3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="N3" s="144"/>
-      <c r="O3" s="160" t="s">
+      <c r="N3" s="147"/>
+      <c r="O3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="P3" s="144"/>
+      <c r="P3" s="147"/>
       <c r="Q3" s="33" t="s">
         <v>381</v>
       </c>
@@ -9008,10 +9004,10 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="162" t="s">
+      <c r="A5" s="167" t="s">
         <v>399</v>
       </c>
-      <c r="B5" s="144"/>
+      <c r="B5" s="147"/>
       <c r="C5" s="41">
         <v>1149763530</v>
       </c>
@@ -10789,36 +10785,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="165" t="s">
+      <c r="A1" s="163" t="s">
         <v>416</v>
       </c>
-      <c r="B1" s="144"/>
-      <c r="C1" s="144"/>
-      <c r="D1" s="144"/>
-      <c r="E1" s="144"/>
-      <c r="F1" s="144"/>
-      <c r="G1" s="144"/>
-      <c r="H1" s="144"/>
-      <c r="I1" s="144"/>
-      <c r="J1" s="144"/>
-      <c r="K1" s="144"/>
-      <c r="L1" s="144"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="147"/>
     </row>
     <row r="2" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="150" t="s">
         <v>417</v>
       </c>
-      <c r="B2" s="144"/>
-      <c r="C2" s="144"/>
-      <c r="D2" s="144"/>
-      <c r="E2" s="144"/>
-      <c r="F2" s="144"/>
-      <c r="G2" s="144"/>
-      <c r="H2" s="144"/>
-      <c r="I2" s="144"/>
-      <c r="J2" s="144"/>
-      <c r="K2" s="144"/>
-      <c r="L2" s="144"/>
+      <c r="B2" s="147"/>
+      <c r="C2" s="147"/>
+      <c r="D2" s="147"/>
+      <c r="E2" s="147"/>
+      <c r="F2" s="147"/>
+      <c r="G2" s="147"/>
+      <c r="H2" s="147"/>
+      <c r="I2" s="147"/>
+      <c r="J2" s="147"/>
+      <c r="K2" s="147"/>
+      <c r="L2" s="147"/>
     </row>
     <row r="3" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="35" t="s">
@@ -11088,10 +11084,10 @@
     </row>
     <row r="22" spans="1:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="23" spans="1:20" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="168" t="s">
+      <c r="A23" s="173" t="s">
         <v>437</v>
       </c>
-      <c r="B23" s="144"/>
+      <c r="B23" s="147"/>
       <c r="C23" s="76">
         <v>1221140305</v>
       </c>
@@ -11111,37 +11107,37 @@
     </row>
     <row r="24" spans="1:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="25" spans="1:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="167" t="s">
+      <c r="A25" s="172" t="s">
         <v>438</v>
       </c>
-      <c r="B25" s="144"/>
-      <c r="C25" s="144"/>
-      <c r="D25" s="144"/>
-      <c r="E25" s="144"/>
-      <c r="F25" s="144"/>
-      <c r="G25" s="144"/>
-      <c r="H25" s="144"/>
-      <c r="I25" s="144"/>
-      <c r="J25" s="144"/>
-      <c r="K25" s="144"/>
-      <c r="L25" s="144"/>
+      <c r="B25" s="147"/>
+      <c r="C25" s="147"/>
+      <c r="D25" s="147"/>
+      <c r="E25" s="147"/>
+      <c r="F25" s="147"/>
+      <c r="G25" s="147"/>
+      <c r="H25" s="147"/>
+      <c r="I25" s="147"/>
+      <c r="J25" s="147"/>
+      <c r="K25" s="147"/>
+      <c r="L25" s="147"/>
     </row>
     <row r="26" spans="1:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="27" spans="1:20" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="169" t="s">
+      <c r="A27" s="170" t="s">
         <v>439</v>
       </c>
-      <c r="B27" s="144"/>
-      <c r="C27" s="144"/>
-      <c r="D27" s="144"/>
-      <c r="E27" s="144"/>
-      <c r="F27" s="144"/>
-      <c r="G27" s="144"/>
-      <c r="H27" s="144"/>
-      <c r="I27" s="144"/>
-      <c r="J27" s="144"/>
-      <c r="K27" s="144"/>
-      <c r="L27" s="170"/>
+      <c r="B27" s="147"/>
+      <c r="C27" s="147"/>
+      <c r="D27" s="147"/>
+      <c r="E27" s="147"/>
+      <c r="F27" s="147"/>
+      <c r="G27" s="147"/>
+      <c r="H27" s="147"/>
+      <c r="I27" s="147"/>
+      <c r="J27" s="147"/>
+      <c r="K27" s="147"/>
+      <c r="L27" s="171"/>
       <c r="M27" s="79"/>
       <c r="N27" s="79"/>
       <c r="O27" s="79"/>
@@ -11374,20 +11370,20 @@
       <c r="T34" s="84"/>
     </row>
     <row r="35" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="169" t="s">
+      <c r="A35" s="170" t="s">
         <v>463</v>
       </c>
-      <c r="B35" s="144"/>
-      <c r="C35" s="144"/>
-      <c r="D35" s="144"/>
-      <c r="E35" s="144"/>
-      <c r="F35" s="144"/>
-      <c r="G35" s="144"/>
-      <c r="H35" s="144"/>
-      <c r="I35" s="144"/>
-      <c r="J35" s="144"/>
-      <c r="K35" s="144"/>
-      <c r="L35" s="170"/>
+      <c r="B35" s="147"/>
+      <c r="C35" s="147"/>
+      <c r="D35" s="147"/>
+      <c r="E35" s="147"/>
+      <c r="F35" s="147"/>
+      <c r="G35" s="147"/>
+      <c r="H35" s="147"/>
+      <c r="I35" s="147"/>
+      <c r="J35" s="147"/>
+      <c r="K35" s="147"/>
+      <c r="L35" s="171"/>
       <c r="M35" s="84"/>
       <c r="N35" s="84"/>
       <c r="O35" s="84"/>
@@ -11698,80 +11694,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="165" t="s">
+      <c r="A1" s="163" t="s">
         <v>467</v>
       </c>
-      <c r="B1" s="144"/>
-      <c r="C1" s="144"/>
-      <c r="D1" s="144"/>
-      <c r="E1" s="144"/>
-      <c r="F1" s="144"/>
-      <c r="G1" s="144"/>
-      <c r="H1" s="144"/>
-      <c r="I1" s="144"/>
-      <c r="J1" s="144"/>
-      <c r="K1" s="144"/>
-      <c r="L1" s="144"/>
-      <c r="M1" s="144"/>
-      <c r="N1" s="144"/>
-      <c r="O1" s="144"/>
-      <c r="P1" s="144"/>
-      <c r="Q1" s="144"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="147"/>
+      <c r="M1" s="147"/>
+      <c r="N1" s="147"/>
+      <c r="O1" s="147"/>
+      <c r="P1" s="147"/>
+      <c r="Q1" s="147"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="150" t="s">
         <v>373</v>
       </c>
-      <c r="B2" s="144"/>
-      <c r="C2" s="144"/>
-      <c r="D2" s="144"/>
-      <c r="E2" s="144"/>
-      <c r="F2" s="144"/>
-      <c r="G2" s="144"/>
-      <c r="H2" s="144"/>
-      <c r="I2" s="144"/>
-      <c r="J2" s="144"/>
-      <c r="K2" s="144"/>
-      <c r="L2" s="144"/>
-      <c r="M2" s="144"/>
-      <c r="N2" s="144"/>
-      <c r="O2" s="144"/>
-      <c r="P2" s="144"/>
-      <c r="Q2" s="144"/>
+      <c r="B2" s="147"/>
+      <c r="C2" s="147"/>
+      <c r="D2" s="147"/>
+      <c r="E2" s="147"/>
+      <c r="F2" s="147"/>
+      <c r="G2" s="147"/>
+      <c r="H2" s="147"/>
+      <c r="I2" s="147"/>
+      <c r="J2" s="147"/>
+      <c r="K2" s="147"/>
+      <c r="L2" s="147"/>
+      <c r="M2" s="147"/>
+      <c r="N2" s="147"/>
+      <c r="O2" s="147"/>
+      <c r="P2" s="147"/>
+      <c r="Q2" s="147"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="164" t="s">
+      <c r="A3" s="169" t="s">
         <v>374</v>
       </c>
-      <c r="B3" s="144"/>
-      <c r="C3" s="163" t="s">
+      <c r="B3" s="147"/>
+      <c r="C3" s="168" t="s">
         <v>375</v>
       </c>
-      <c r="D3" s="144"/>
-      <c r="E3" s="166" t="s">
+      <c r="D3" s="147"/>
+      <c r="E3" s="164" t="s">
         <v>376</v>
       </c>
-      <c r="F3" s="144"/>
-      <c r="G3" s="161" t="s">
+      <c r="F3" s="147"/>
+      <c r="G3" s="166" t="s">
         <v>377</v>
       </c>
-      <c r="H3" s="144"/>
-      <c r="I3" s="144"/>
-      <c r="J3" s="144"/>
+      <c r="H3" s="147"/>
+      <c r="I3" s="147"/>
+      <c r="J3" s="147"/>
       <c r="K3" s="31" t="s">
         <v>378</v>
       </c>
       <c r="L3" s="32" t="s">
         <v>379</v>
       </c>
-      <c r="M3" s="160" t="s">
+      <c r="M3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="N3" s="144"/>
-      <c r="O3" s="160" t="s">
+      <c r="N3" s="147"/>
+      <c r="O3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="P3" s="144"/>
+      <c r="P3" s="147"/>
       <c r="Q3" s="33" t="s">
         <v>381</v>
       </c>
@@ -11830,10 +11826,10 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="162" t="s">
+      <c r="A5" s="167" t="s">
         <v>399</v>
       </c>
-      <c r="B5" s="144"/>
+      <c r="B5" s="147"/>
       <c r="C5" s="41">
         <v>1214990084</v>
       </c>
@@ -13664,36 +13660,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="165" t="s">
+      <c r="A1" s="163" t="s">
         <v>468</v>
       </c>
-      <c r="B1" s="144"/>
-      <c r="C1" s="144"/>
-      <c r="D1" s="144"/>
-      <c r="E1" s="144"/>
-      <c r="F1" s="144"/>
-      <c r="G1" s="144"/>
-      <c r="H1" s="144"/>
-      <c r="I1" s="144"/>
-      <c r="J1" s="144"/>
-      <c r="K1" s="144"/>
-      <c r="L1" s="144"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="147"/>
     </row>
     <row r="2" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="150" t="s">
         <v>417</v>
       </c>
-      <c r="B2" s="144"/>
-      <c r="C2" s="144"/>
-      <c r="D2" s="144"/>
-      <c r="E2" s="144"/>
-      <c r="F2" s="144"/>
-      <c r="G2" s="144"/>
-      <c r="H2" s="144"/>
-      <c r="I2" s="144"/>
-      <c r="J2" s="144"/>
-      <c r="K2" s="144"/>
-      <c r="L2" s="144"/>
+      <c r="B2" s="147"/>
+      <c r="C2" s="147"/>
+      <c r="D2" s="147"/>
+      <c r="E2" s="147"/>
+      <c r="F2" s="147"/>
+      <c r="G2" s="147"/>
+      <c r="H2" s="147"/>
+      <c r="I2" s="147"/>
+      <c r="J2" s="147"/>
+      <c r="K2" s="147"/>
+      <c r="L2" s="147"/>
     </row>
     <row r="3" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="35" t="s">
@@ -14041,10 +14037,10 @@
     </row>
     <row r="22" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="23" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="168" t="s">
+      <c r="A23" s="173" t="s">
         <v>437</v>
       </c>
-      <c r="B23" s="144"/>
+      <c r="B23" s="147"/>
       <c r="C23" s="76">
         <v>1214990084</v>
       </c>
@@ -14064,20 +14060,20 @@
     </row>
     <row r="24" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="25" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="167" t="s">
+      <c r="A25" s="172" t="s">
         <v>438</v>
       </c>
-      <c r="B25" s="144"/>
-      <c r="C25" s="144"/>
-      <c r="D25" s="144"/>
-      <c r="E25" s="144"/>
-      <c r="F25" s="144"/>
-      <c r="G25" s="144"/>
-      <c r="H25" s="144"/>
-      <c r="I25" s="144"/>
-      <c r="J25" s="144"/>
-      <c r="K25" s="144"/>
-      <c r="L25" s="144"/>
+      <c r="B25" s="147"/>
+      <c r="C25" s="147"/>
+      <c r="D25" s="147"/>
+      <c r="E25" s="147"/>
+      <c r="F25" s="147"/>
+      <c r="G25" s="147"/>
+      <c r="H25" s="147"/>
+      <c r="I25" s="147"/>
+      <c r="J25" s="147"/>
+      <c r="K25" s="147"/>
+      <c r="L25" s="147"/>
     </row>
     <row r="26" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="27" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -14290,80 +14286,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="165" t="s">
+      <c r="A1" s="163" t="s">
         <v>475</v>
       </c>
-      <c r="B1" s="144"/>
-      <c r="C1" s="144"/>
-      <c r="D1" s="144"/>
-      <c r="E1" s="144"/>
-      <c r="F1" s="144"/>
-      <c r="G1" s="144"/>
-      <c r="H1" s="144"/>
-      <c r="I1" s="144"/>
-      <c r="J1" s="144"/>
-      <c r="K1" s="144"/>
-      <c r="L1" s="144"/>
-      <c r="M1" s="144"/>
-      <c r="N1" s="144"/>
-      <c r="O1" s="144"/>
-      <c r="P1" s="144"/>
-      <c r="Q1" s="144"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="147"/>
+      <c r="M1" s="147"/>
+      <c r="N1" s="147"/>
+      <c r="O1" s="147"/>
+      <c r="P1" s="147"/>
+      <c r="Q1" s="147"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="150" t="s">
         <v>373</v>
       </c>
-      <c r="B2" s="144"/>
-      <c r="C2" s="144"/>
-      <c r="D2" s="144"/>
-      <c r="E2" s="144"/>
-      <c r="F2" s="144"/>
-      <c r="G2" s="144"/>
-      <c r="H2" s="144"/>
-      <c r="I2" s="144"/>
-      <c r="J2" s="144"/>
-      <c r="K2" s="144"/>
-      <c r="L2" s="144"/>
-      <c r="M2" s="144"/>
-      <c r="N2" s="144"/>
-      <c r="O2" s="144"/>
-      <c r="P2" s="144"/>
-      <c r="Q2" s="144"/>
+      <c r="B2" s="147"/>
+      <c r="C2" s="147"/>
+      <c r="D2" s="147"/>
+      <c r="E2" s="147"/>
+      <c r="F2" s="147"/>
+      <c r="G2" s="147"/>
+      <c r="H2" s="147"/>
+      <c r="I2" s="147"/>
+      <c r="J2" s="147"/>
+      <c r="K2" s="147"/>
+      <c r="L2" s="147"/>
+      <c r="M2" s="147"/>
+      <c r="N2" s="147"/>
+      <c r="O2" s="147"/>
+      <c r="P2" s="147"/>
+      <c r="Q2" s="147"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="164" t="s">
+      <c r="A3" s="169" t="s">
         <v>374</v>
       </c>
-      <c r="B3" s="144"/>
-      <c r="C3" s="163" t="s">
+      <c r="B3" s="147"/>
+      <c r="C3" s="168" t="s">
         <v>375</v>
       </c>
-      <c r="D3" s="144"/>
-      <c r="E3" s="166" t="s">
+      <c r="D3" s="147"/>
+      <c r="E3" s="164" t="s">
         <v>376</v>
       </c>
-      <c r="F3" s="144"/>
-      <c r="G3" s="161" t="s">
+      <c r="F3" s="147"/>
+      <c r="G3" s="166" t="s">
         <v>377</v>
       </c>
-      <c r="H3" s="144"/>
-      <c r="I3" s="144"/>
-      <c r="J3" s="144"/>
+      <c r="H3" s="147"/>
+      <c r="I3" s="147"/>
+      <c r="J3" s="147"/>
       <c r="K3" s="31" t="s">
         <v>378</v>
       </c>
       <c r="L3" s="32" t="s">
         <v>379</v>
       </c>
-      <c r="M3" s="160" t="s">
+      <c r="M3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="N3" s="144"/>
-      <c r="O3" s="160" t="s">
+      <c r="N3" s="147"/>
+      <c r="O3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="P3" s="144"/>
+      <c r="P3" s="147"/>
       <c r="Q3" s="33" t="s">
         <v>381</v>
       </c>
@@ -14422,10 +14418,10 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="162" t="s">
+      <c r="A5" s="167" t="s">
         <v>399</v>
       </c>
-      <c r="B5" s="144"/>
+      <c r="B5" s="147"/>
       <c r="C5" s="41">
         <v>1221751028</v>
       </c>
@@ -16052,36 +16048,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="165" t="s">
+      <c r="A1" s="163" t="s">
         <v>476</v>
       </c>
-      <c r="B1" s="144"/>
-      <c r="C1" s="144"/>
-      <c r="D1" s="144"/>
-      <c r="E1" s="144"/>
-      <c r="F1" s="144"/>
-      <c r="G1" s="144"/>
-      <c r="H1" s="144"/>
-      <c r="I1" s="144"/>
-      <c r="J1" s="144"/>
-      <c r="K1" s="144"/>
-      <c r="L1" s="144"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="147"/>
     </row>
     <row r="2" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="150" t="s">
         <v>417</v>
       </c>
-      <c r="B2" s="144"/>
-      <c r="C2" s="144"/>
-      <c r="D2" s="144"/>
-      <c r="E2" s="144"/>
-      <c r="F2" s="144"/>
-      <c r="G2" s="144"/>
-      <c r="H2" s="144"/>
-      <c r="I2" s="144"/>
-      <c r="J2" s="144"/>
-      <c r="K2" s="144"/>
-      <c r="L2" s="144"/>
+      <c r="B2" s="147"/>
+      <c r="C2" s="147"/>
+      <c r="D2" s="147"/>
+      <c r="E2" s="147"/>
+      <c r="F2" s="147"/>
+      <c r="G2" s="147"/>
+      <c r="H2" s="147"/>
+      <c r="I2" s="147"/>
+      <c r="J2" s="147"/>
+      <c r="K2" s="147"/>
+      <c r="L2" s="147"/>
     </row>
     <row r="3" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="35" t="s">
@@ -16468,10 +16464,10 @@
     </row>
     <row r="23" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="24" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="168" t="s">
+      <c r="A24" s="173" t="s">
         <v>437</v>
       </c>
-      <c r="B24" s="144"/>
+      <c r="B24" s="147"/>
       <c r="C24" s="76">
         <v>1221751028</v>
       </c>
@@ -16491,20 +16487,20 @@
     </row>
     <row r="25" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="26" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="167" t="s">
+      <c r="A26" s="172" t="s">
         <v>438</v>
       </c>
-      <c r="B26" s="144"/>
-      <c r="C26" s="144"/>
-      <c r="D26" s="144"/>
-      <c r="E26" s="144"/>
-      <c r="F26" s="144"/>
-      <c r="G26" s="144"/>
-      <c r="H26" s="144"/>
-      <c r="I26" s="144"/>
-      <c r="J26" s="144"/>
-      <c r="K26" s="144"/>
-      <c r="L26" s="144"/>
+      <c r="B26" s="147"/>
+      <c r="C26" s="147"/>
+      <c r="D26" s="147"/>
+      <c r="E26" s="147"/>
+      <c r="F26" s="147"/>
+      <c r="G26" s="147"/>
+      <c r="H26" s="147"/>
+      <c r="I26" s="147"/>
+      <c r="J26" s="147"/>
+      <c r="K26" s="147"/>
+      <c r="L26" s="147"/>
     </row>
     <row r="27" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="28" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -16717,80 +16713,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="165" t="s">
+      <c r="A1" s="163" t="s">
         <v>484</v>
       </c>
-      <c r="B1" s="144"/>
-      <c r="C1" s="144"/>
-      <c r="D1" s="144"/>
-      <c r="E1" s="144"/>
-      <c r="F1" s="144"/>
-      <c r="G1" s="144"/>
-      <c r="H1" s="144"/>
-      <c r="I1" s="144"/>
-      <c r="J1" s="144"/>
-      <c r="K1" s="144"/>
-      <c r="L1" s="144"/>
-      <c r="M1" s="144"/>
-      <c r="N1" s="144"/>
-      <c r="O1" s="144"/>
-      <c r="P1" s="144"/>
-      <c r="Q1" s="144"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="147"/>
+      <c r="M1" s="147"/>
+      <c r="N1" s="147"/>
+      <c r="O1" s="147"/>
+      <c r="P1" s="147"/>
+      <c r="Q1" s="147"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="150" t="s">
         <v>373</v>
       </c>
-      <c r="B2" s="144"/>
-      <c r="C2" s="144"/>
-      <c r="D2" s="144"/>
-      <c r="E2" s="144"/>
-      <c r="F2" s="144"/>
-      <c r="G2" s="144"/>
-      <c r="H2" s="144"/>
-      <c r="I2" s="144"/>
-      <c r="J2" s="144"/>
-      <c r="K2" s="144"/>
-      <c r="L2" s="144"/>
-      <c r="M2" s="144"/>
-      <c r="N2" s="144"/>
-      <c r="O2" s="144"/>
-      <c r="P2" s="144"/>
-      <c r="Q2" s="144"/>
+      <c r="B2" s="147"/>
+      <c r="C2" s="147"/>
+      <c r="D2" s="147"/>
+      <c r="E2" s="147"/>
+      <c r="F2" s="147"/>
+      <c r="G2" s="147"/>
+      <c r="H2" s="147"/>
+      <c r="I2" s="147"/>
+      <c r="J2" s="147"/>
+      <c r="K2" s="147"/>
+      <c r="L2" s="147"/>
+      <c r="M2" s="147"/>
+      <c r="N2" s="147"/>
+      <c r="O2" s="147"/>
+      <c r="P2" s="147"/>
+      <c r="Q2" s="147"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="164" t="s">
+      <c r="A3" s="169" t="s">
         <v>374</v>
       </c>
-      <c r="B3" s="144"/>
-      <c r="C3" s="163" t="s">
+      <c r="B3" s="147"/>
+      <c r="C3" s="168" t="s">
         <v>375</v>
       </c>
-      <c r="D3" s="144"/>
-      <c r="E3" s="166" t="s">
+      <c r="D3" s="147"/>
+      <c r="E3" s="164" t="s">
         <v>376</v>
       </c>
-      <c r="F3" s="144"/>
-      <c r="G3" s="161" t="s">
+      <c r="F3" s="147"/>
+      <c r="G3" s="166" t="s">
         <v>377</v>
       </c>
-      <c r="H3" s="144"/>
-      <c r="I3" s="144"/>
-      <c r="J3" s="144"/>
+      <c r="H3" s="147"/>
+      <c r="I3" s="147"/>
+      <c r="J3" s="147"/>
       <c r="K3" s="31" t="s">
         <v>378</v>
       </c>
       <c r="L3" s="32" t="s">
         <v>379</v>
       </c>
-      <c r="M3" s="160" t="s">
+      <c r="M3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="N3" s="144"/>
-      <c r="O3" s="160" t="s">
+      <c r="N3" s="147"/>
+      <c r="O3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="P3" s="144"/>
+      <c r="P3" s="147"/>
       <c r="Q3" s="33" t="s">
         <v>381</v>
       </c>
@@ -16849,10 +16845,10 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="162" t="s">
+      <c r="A5" s="167" t="s">
         <v>399</v>
       </c>
-      <c r="B5" s="144"/>
+      <c r="B5" s="147"/>
       <c r="C5" s="41">
         <v>1009097583</v>
       </c>
@@ -18227,40 +18223,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="172" t="s">
+      <c r="A1" s="175" t="s">
         <v>485</v>
       </c>
-      <c r="B1" s="156"/>
-      <c r="C1" s="156"/>
-      <c r="D1" s="156"/>
-      <c r="E1" s="156"/>
-      <c r="F1" s="156"/>
-      <c r="G1" s="156"/>
-      <c r="H1" s="156"/>
-      <c r="I1" s="156"/>
-      <c r="J1" s="156"/>
-      <c r="K1" s="156"/>
-      <c r="L1" s="156"/>
-      <c r="M1" s="156"/>
-      <c r="N1" s="156"/>
+      <c r="B1" s="159"/>
+      <c r="C1" s="159"/>
+      <c r="D1" s="159"/>
+      <c r="E1" s="159"/>
+      <c r="F1" s="159"/>
+      <c r="G1" s="159"/>
+      <c r="H1" s="159"/>
+      <c r="I1" s="159"/>
+      <c r="J1" s="159"/>
+      <c r="K1" s="159"/>
+      <c r="L1" s="159"/>
+      <c r="M1" s="159"/>
+      <c r="N1" s="159"/>
     </row>
     <row r="2" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="171" t="s">
+      <c r="A2" s="174" t="s">
         <v>417</v>
       </c>
-      <c r="B2" s="156"/>
-      <c r="C2" s="156"/>
-      <c r="D2" s="156"/>
-      <c r="E2" s="156"/>
-      <c r="F2" s="156"/>
-      <c r="G2" s="156"/>
-      <c r="H2" s="156"/>
-      <c r="I2" s="156"/>
-      <c r="J2" s="156"/>
-      <c r="K2" s="156"/>
-      <c r="L2" s="156"/>
-      <c r="M2" s="156"/>
-      <c r="N2" s="156"/>
+      <c r="B2" s="159"/>
+      <c r="C2" s="159"/>
+      <c r="D2" s="159"/>
+      <c r="E2" s="159"/>
+      <c r="F2" s="159"/>
+      <c r="G2" s="159"/>
+      <c r="H2" s="159"/>
+      <c r="I2" s="159"/>
+      <c r="J2" s="159"/>
+      <c r="K2" s="159"/>
+      <c r="L2" s="159"/>
+      <c r="M2" s="159"/>
+      <c r="N2" s="159"/>
     </row>
     <row r="3" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="116" t="s">
@@ -18587,60 +18583,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="154" t="s">
+      <c r="A1" s="146" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="144"/>
-      <c r="C1" s="144"/>
-      <c r="D1" s="144"/>
-      <c r="E1" s="144"/>
-      <c r="F1" s="144"/>
-      <c r="G1" s="144"/>
-      <c r="H1" s="144"/>
-      <c r="I1" s="144"/>
-      <c r="J1" s="144"/>
-      <c r="K1" s="144"/>
-      <c r="L1" s="144"/>
-      <c r="M1" s="144"/>
-      <c r="N1" s="144"/>
-      <c r="O1" s="144"/>
-      <c r="P1" s="144"/>
-      <c r="Q1" s="144"/>
-      <c r="R1" s="144"/>
-      <c r="S1" s="144"/>
-      <c r="T1" s="144"/>
-      <c r="U1" s="144"/>
-      <c r="V1" s="144"/>
-      <c r="W1" s="144"/>
-      <c r="X1" s="144"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="147"/>
+      <c r="M1" s="147"/>
+      <c r="N1" s="147"/>
+      <c r="O1" s="147"/>
+      <c r="P1" s="147"/>
+      <c r="Q1" s="147"/>
+      <c r="R1" s="147"/>
+      <c r="S1" s="147"/>
+      <c r="T1" s="147"/>
+      <c r="U1" s="147"/>
+      <c r="V1" s="147"/>
+      <c r="W1" s="147"/>
+      <c r="X1" s="147"/>
     </row>
     <row r="2" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="150" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="144"/>
-      <c r="C2" s="144"/>
-      <c r="D2" s="144"/>
-      <c r="E2" s="144"/>
-      <c r="F2" s="144"/>
-      <c r="G2" s="144"/>
-      <c r="H2" s="144"/>
-      <c r="I2" s="144"/>
-      <c r="J2" s="144"/>
-      <c r="K2" s="144"/>
-      <c r="L2" s="144"/>
-      <c r="M2" s="144"/>
-      <c r="N2" s="144"/>
-      <c r="O2" s="144"/>
-      <c r="P2" s="144"/>
-      <c r="Q2" s="144"/>
-      <c r="R2" s="144"/>
-      <c r="S2" s="144"/>
-      <c r="T2" s="144"/>
-      <c r="U2" s="144"/>
-      <c r="V2" s="144"/>
-      <c r="W2" s="144"/>
-      <c r="X2" s="144"/>
+      <c r="B2" s="147"/>
+      <c r="C2" s="147"/>
+      <c r="D2" s="147"/>
+      <c r="E2" s="147"/>
+      <c r="F2" s="147"/>
+      <c r="G2" s="147"/>
+      <c r="H2" s="147"/>
+      <c r="I2" s="147"/>
+      <c r="J2" s="147"/>
+      <c r="K2" s="147"/>
+      <c r="L2" s="147"/>
+      <c r="M2" s="147"/>
+      <c r="N2" s="147"/>
+      <c r="O2" s="147"/>
+      <c r="P2" s="147"/>
+      <c r="Q2" s="147"/>
+      <c r="R2" s="147"/>
+      <c r="S2" s="147"/>
+      <c r="T2" s="147"/>
+      <c r="U2" s="147"/>
+      <c r="V2" s="147"/>
+      <c r="W2" s="147"/>
+      <c r="X2" s="147"/>
     </row>
     <row r="3" spans="1:24" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -18717,60 +18713,60 @@
       </c>
     </row>
     <row r="4" spans="1:24" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="148" t="s">
+      <c r="A4" s="156" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="144"/>
-      <c r="C4" s="144"/>
-      <c r="D4" s="144"/>
-      <c r="E4" s="144"/>
-      <c r="F4" s="144"/>
-      <c r="G4" s="144"/>
-      <c r="H4" s="144"/>
-      <c r="I4" s="144"/>
-      <c r="J4" s="144"/>
-      <c r="K4" s="144"/>
-      <c r="L4" s="144"/>
-      <c r="M4" s="144"/>
-      <c r="N4" s="144"/>
-      <c r="O4" s="144"/>
-      <c r="P4" s="144"/>
-      <c r="Q4" s="144"/>
-      <c r="R4" s="144"/>
-      <c r="S4" s="144"/>
-      <c r="T4" s="144"/>
-      <c r="U4" s="144"/>
-      <c r="V4" s="144"/>
-      <c r="W4" s="144"/>
-      <c r="X4" s="144"/>
+      <c r="B4" s="147"/>
+      <c r="C4" s="147"/>
+      <c r="D4" s="147"/>
+      <c r="E4" s="147"/>
+      <c r="F4" s="147"/>
+      <c r="G4" s="147"/>
+      <c r="H4" s="147"/>
+      <c r="I4" s="147"/>
+      <c r="J4" s="147"/>
+      <c r="K4" s="147"/>
+      <c r="L4" s="147"/>
+      <c r="M4" s="147"/>
+      <c r="N4" s="147"/>
+      <c r="O4" s="147"/>
+      <c r="P4" s="147"/>
+      <c r="Q4" s="147"/>
+      <c r="R4" s="147"/>
+      <c r="S4" s="147"/>
+      <c r="T4" s="147"/>
+      <c r="U4" s="147"/>
+      <c r="V4" s="147"/>
+      <c r="W4" s="147"/>
+      <c r="X4" s="147"/>
     </row>
     <row r="5" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="153" t="s">
+      <c r="A5" s="148" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="144"/>
-      <c r="C5" s="144"/>
-      <c r="D5" s="144"/>
-      <c r="E5" s="144"/>
-      <c r="F5" s="144"/>
-      <c r="G5" s="144"/>
-      <c r="H5" s="144"/>
-      <c r="I5" s="144"/>
-      <c r="J5" s="144"/>
-      <c r="K5" s="144"/>
-      <c r="L5" s="144"/>
-      <c r="M5" s="144"/>
-      <c r="N5" s="144"/>
-      <c r="O5" s="144"/>
-      <c r="P5" s="144"/>
-      <c r="Q5" s="144"/>
-      <c r="R5" s="144"/>
-      <c r="S5" s="144"/>
-      <c r="T5" s="144"/>
-      <c r="U5" s="144"/>
-      <c r="V5" s="144"/>
-      <c r="W5" s="144"/>
-      <c r="X5" s="144"/>
+      <c r="B5" s="147"/>
+      <c r="C5" s="147"/>
+      <c r="D5" s="147"/>
+      <c r="E5" s="147"/>
+      <c r="F5" s="147"/>
+      <c r="G5" s="147"/>
+      <c r="H5" s="147"/>
+      <c r="I5" s="147"/>
+      <c r="J5" s="147"/>
+      <c r="K5" s="147"/>
+      <c r="L5" s="147"/>
+      <c r="M5" s="147"/>
+      <c r="N5" s="147"/>
+      <c r="O5" s="147"/>
+      <c r="P5" s="147"/>
+      <c r="Q5" s="147"/>
+      <c r="R5" s="147"/>
+      <c r="S5" s="147"/>
+      <c r="T5" s="147"/>
+      <c r="U5" s="147"/>
+      <c r="V5" s="147"/>
+      <c r="W5" s="147"/>
+      <c r="X5" s="147"/>
     </row>
     <row r="6" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4"/>
@@ -19208,60 +19204,60 @@
       <c r="X12" s="14"/>
     </row>
     <row r="13" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="153" t="s">
+      <c r="A13" s="148" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="144"/>
-      <c r="C13" s="144"/>
-      <c r="D13" s="144"/>
-      <c r="E13" s="144"/>
-      <c r="F13" s="144"/>
-      <c r="G13" s="144"/>
-      <c r="H13" s="144"/>
-      <c r="I13" s="144"/>
-      <c r="J13" s="144"/>
-      <c r="K13" s="144"/>
-      <c r="L13" s="144"/>
-      <c r="M13" s="144"/>
-      <c r="N13" s="144"/>
-      <c r="O13" s="144"/>
-      <c r="P13" s="144"/>
-      <c r="Q13" s="144"/>
-      <c r="R13" s="144"/>
-      <c r="S13" s="144"/>
-      <c r="T13" s="144"/>
-      <c r="U13" s="144"/>
-      <c r="V13" s="144"/>
-      <c r="W13" s="144"/>
-      <c r="X13" s="144"/>
+      <c r="B13" s="147"/>
+      <c r="C13" s="147"/>
+      <c r="D13" s="147"/>
+      <c r="E13" s="147"/>
+      <c r="F13" s="147"/>
+      <c r="G13" s="147"/>
+      <c r="H13" s="147"/>
+      <c r="I13" s="147"/>
+      <c r="J13" s="147"/>
+      <c r="K13" s="147"/>
+      <c r="L13" s="147"/>
+      <c r="M13" s="147"/>
+      <c r="N13" s="147"/>
+      <c r="O13" s="147"/>
+      <c r="P13" s="147"/>
+      <c r="Q13" s="147"/>
+      <c r="R13" s="147"/>
+      <c r="S13" s="147"/>
+      <c r="T13" s="147"/>
+      <c r="U13" s="147"/>
+      <c r="V13" s="147"/>
+      <c r="W13" s="147"/>
+      <c r="X13" s="147"/>
     </row>
     <row r="14" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="147" t="s">
+      <c r="A14" s="149" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="144"/>
-      <c r="C14" s="144"/>
-      <c r="D14" s="144"/>
-      <c r="E14" s="144"/>
-      <c r="F14" s="144"/>
-      <c r="G14" s="144"/>
-      <c r="H14" s="144"/>
-      <c r="I14" s="144"/>
-      <c r="J14" s="144"/>
-      <c r="K14" s="144"/>
-      <c r="L14" s="144"/>
-      <c r="M14" s="144"/>
-      <c r="N14" s="144"/>
-      <c r="O14" s="144"/>
-      <c r="P14" s="144"/>
-      <c r="Q14" s="144"/>
-      <c r="R14" s="144"/>
-      <c r="S14" s="144"/>
-      <c r="T14" s="144"/>
-      <c r="U14" s="144"/>
-      <c r="V14" s="144"/>
-      <c r="W14" s="144"/>
-      <c r="X14" s="144"/>
+      <c r="B14" s="147"/>
+      <c r="C14" s="147"/>
+      <c r="D14" s="147"/>
+      <c r="E14" s="147"/>
+      <c r="F14" s="147"/>
+      <c r="G14" s="147"/>
+      <c r="H14" s="147"/>
+      <c r="I14" s="147"/>
+      <c r="J14" s="147"/>
+      <c r="K14" s="147"/>
+      <c r="L14" s="147"/>
+      <c r="M14" s="147"/>
+      <c r="N14" s="147"/>
+      <c r="O14" s="147"/>
+      <c r="P14" s="147"/>
+      <c r="Q14" s="147"/>
+      <c r="R14" s="147"/>
+      <c r="S14" s="147"/>
+      <c r="T14" s="147"/>
+      <c r="U14" s="147"/>
+      <c r="V14" s="147"/>
+      <c r="W14" s="147"/>
+      <c r="X14" s="147"/>
     </row>
     <row r="15" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4"/>
@@ -19409,66 +19405,66 @@
         <v>44</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D17" s="180">
+        <v>42</v>
+      </c>
+      <c r="D17" s="143">
         <v>525</v>
       </c>
-      <c r="E17" s="180">
+      <c r="E17" s="143">
         <v>400</v>
       </c>
-      <c r="F17" s="180">
+      <c r="F17" s="143">
         <v>306</v>
       </c>
-      <c r="G17" s="180">
+      <c r="G17" s="143">
         <v>221</v>
       </c>
-      <c r="H17" s="180">
+      <c r="H17" s="143">
         <v>134</v>
       </c>
-      <c r="I17" s="180">
+      <c r="I17" s="143">
         <v>161</v>
       </c>
-      <c r="J17" s="180">
+      <c r="J17" s="143">
         <v>131</v>
       </c>
-      <c r="K17" s="180">
+      <c r="K17" s="143">
         <v>138</v>
       </c>
-      <c r="L17" s="180">
+      <c r="L17" s="143">
         <v>111</v>
       </c>
-      <c r="M17" s="180">
+      <c r="M17" s="143">
         <v>130</v>
       </c>
-      <c r="N17" s="180">
+      <c r="N17" s="143">
         <v>156</v>
       </c>
-      <c r="O17" s="180">
+      <c r="O17" s="143">
         <v>145</v>
       </c>
-      <c r="P17" s="180">
+      <c r="P17" s="143">
         <v>234</v>
       </c>
-      <c r="Q17" s="180">
+      <c r="Q17" s="143">
         <v>271</v>
       </c>
-      <c r="R17" s="180">
+      <c r="R17" s="143">
         <v>244</v>
       </c>
-      <c r="S17" s="180">
+      <c r="S17" s="143">
         <v>247</v>
       </c>
-      <c r="T17" s="180">
+      <c r="T17" s="143">
         <v>145</v>
       </c>
-      <c r="U17" s="181">
+      <c r="U17" s="144">
         <v>156</v>
       </c>
-      <c r="V17" s="181">
+      <c r="V17" s="144">
         <v>135</v>
       </c>
-      <c r="W17" s="181">
+      <c r="W17" s="144">
         <v>125</v>
       </c>
       <c r="X17" s="13"/>
@@ -19479,97 +19475,97 @@
         <v>45</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D18" s="180">
+        <v>42</v>
+      </c>
+      <c r="D18" s="143">
         <v>118</v>
       </c>
-      <c r="E18" s="180">
+      <c r="E18" s="143">
         <v>79</v>
       </c>
-      <c r="F18" s="180">
+      <c r="F18" s="143">
         <v>55</v>
       </c>
-      <c r="G18" s="180">
+      <c r="G18" s="143">
         <v>60</v>
       </c>
-      <c r="H18" s="180">
+      <c r="H18" s="143">
         <v>59</v>
       </c>
-      <c r="I18" s="180">
+      <c r="I18" s="143">
         <v>51</v>
       </c>
-      <c r="J18" s="180">
+      <c r="J18" s="143">
         <v>39</v>
       </c>
-      <c r="K18" s="180">
+      <c r="K18" s="143">
         <v>48</v>
       </c>
-      <c r="L18" s="180">
+      <c r="L18" s="143">
         <v>52</v>
       </c>
-      <c r="M18" s="180">
+      <c r="M18" s="143">
         <v>58</v>
       </c>
-      <c r="N18" s="180">
+      <c r="N18" s="143">
         <v>82</v>
       </c>
-      <c r="O18" s="180">
+      <c r="O18" s="143">
         <v>110</v>
       </c>
-      <c r="P18" s="180">
+      <c r="P18" s="143">
         <v>98</v>
       </c>
-      <c r="Q18" s="180">
+      <c r="Q18" s="143">
         <v>86</v>
       </c>
-      <c r="R18" s="180">
+      <c r="R18" s="143">
         <v>57</v>
       </c>
-      <c r="S18" s="180">
+      <c r="S18" s="143">
         <v>62</v>
       </c>
-      <c r="T18" s="180">
+      <c r="T18" s="143">
         <v>52</v>
       </c>
-      <c r="U18" s="181">
+      <c r="U18" s="144">
         <v>54</v>
       </c>
-      <c r="V18" s="181">
+      <c r="V18" s="144">
         <v>69</v>
       </c>
-      <c r="W18" s="181">
+      <c r="W18" s="144">
         <v>44</v>
       </c>
       <c r="X18" s="13"/>
     </row>
     <row r="19" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="147" t="s">
+      <c r="A19" s="149" t="s">
         <v>46</v>
       </c>
-      <c r="B19" s="144"/>
-      <c r="C19" s="144"/>
-      <c r="D19" s="144"/>
-      <c r="E19" s="144"/>
-      <c r="F19" s="144"/>
-      <c r="G19" s="144"/>
-      <c r="H19" s="144"/>
-      <c r="I19" s="144"/>
-      <c r="J19" s="144"/>
-      <c r="K19" s="144"/>
-      <c r="L19" s="144"/>
-      <c r="M19" s="144"/>
-      <c r="N19" s="144"/>
-      <c r="O19" s="144"/>
-      <c r="P19" s="144"/>
-      <c r="Q19" s="144"/>
-      <c r="R19" s="144"/>
-      <c r="S19" s="144"/>
-      <c r="T19" s="144"/>
-      <c r="U19" s="144"/>
-      <c r="V19" s="144"/>
-      <c r="W19" s="144"/>
-      <c r="X19" s="144"/>
+      <c r="B19" s="147"/>
+      <c r="C19" s="147"/>
+      <c r="D19" s="147"/>
+      <c r="E19" s="147"/>
+      <c r="F19" s="147"/>
+      <c r="G19" s="147"/>
+      <c r="H19" s="147"/>
+      <c r="I19" s="147"/>
+      <c r="J19" s="147"/>
+      <c r="K19" s="147"/>
+      <c r="L19" s="147"/>
+      <c r="M19" s="147"/>
+      <c r="N19" s="147"/>
+      <c r="O19" s="147"/>
+      <c r="P19" s="147"/>
+      <c r="Q19" s="147"/>
+      <c r="R19" s="147"/>
+      <c r="S19" s="147"/>
+      <c r="T19" s="147"/>
+      <c r="U19" s="147"/>
+      <c r="V19" s="147"/>
+      <c r="W19" s="147"/>
+      <c r="X19" s="147"/>
     </row>
     <row r="20" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4"/>
@@ -20202,32 +20198,32 @@
       <c r="X28" s="11"/>
     </row>
     <row r="29" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="147" t="s">
+      <c r="A29" s="149" t="s">
         <v>54</v>
       </c>
-      <c r="B29" s="144"/>
-      <c r="C29" s="144"/>
-      <c r="D29" s="144"/>
-      <c r="E29" s="144"/>
-      <c r="F29" s="144"/>
-      <c r="G29" s="144"/>
-      <c r="H29" s="144"/>
-      <c r="I29" s="144"/>
-      <c r="J29" s="144"/>
-      <c r="K29" s="144"/>
-      <c r="L29" s="144"/>
-      <c r="M29" s="144"/>
-      <c r="N29" s="144"/>
-      <c r="O29" s="144"/>
-      <c r="P29" s="144"/>
-      <c r="Q29" s="144"/>
-      <c r="R29" s="144"/>
-      <c r="S29" s="144"/>
-      <c r="T29" s="144"/>
-      <c r="U29" s="144"/>
-      <c r="V29" s="144"/>
-      <c r="W29" s="144"/>
-      <c r="X29" s="144"/>
+      <c r="B29" s="147"/>
+      <c r="C29" s="147"/>
+      <c r="D29" s="147"/>
+      <c r="E29" s="147"/>
+      <c r="F29" s="147"/>
+      <c r="G29" s="147"/>
+      <c r="H29" s="147"/>
+      <c r="I29" s="147"/>
+      <c r="J29" s="147"/>
+      <c r="K29" s="147"/>
+      <c r="L29" s="147"/>
+      <c r="M29" s="147"/>
+      <c r="N29" s="147"/>
+      <c r="O29" s="147"/>
+      <c r="P29" s="147"/>
+      <c r="Q29" s="147"/>
+      <c r="R29" s="147"/>
+      <c r="S29" s="147"/>
+      <c r="T29" s="147"/>
+      <c r="U29" s="147"/>
+      <c r="V29" s="147"/>
+      <c r="W29" s="147"/>
+      <c r="X29" s="147"/>
     </row>
     <row r="30" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4"/>
@@ -20440,60 +20436,60 @@
       <c r="X32" s="11"/>
     </row>
     <row r="33" spans="1:24" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="152" t="s">
+      <c r="A33" s="153" t="s">
         <v>59</v>
       </c>
-      <c r="B33" s="144"/>
-      <c r="C33" s="144"/>
-      <c r="D33" s="144"/>
-      <c r="E33" s="144"/>
-      <c r="F33" s="144"/>
-      <c r="G33" s="144"/>
-      <c r="H33" s="144"/>
-      <c r="I33" s="144"/>
-      <c r="J33" s="144"/>
-      <c r="K33" s="144"/>
-      <c r="L33" s="144"/>
-      <c r="M33" s="144"/>
-      <c r="N33" s="144"/>
-      <c r="O33" s="144"/>
-      <c r="P33" s="144"/>
-      <c r="Q33" s="144"/>
-      <c r="R33" s="144"/>
-      <c r="S33" s="144"/>
-      <c r="T33" s="144"/>
-      <c r="U33" s="144"/>
-      <c r="V33" s="144"/>
-      <c r="W33" s="144"/>
-      <c r="X33" s="144"/>
+      <c r="B33" s="147"/>
+      <c r="C33" s="147"/>
+      <c r="D33" s="147"/>
+      <c r="E33" s="147"/>
+      <c r="F33" s="147"/>
+      <c r="G33" s="147"/>
+      <c r="H33" s="147"/>
+      <c r="I33" s="147"/>
+      <c r="J33" s="147"/>
+      <c r="K33" s="147"/>
+      <c r="L33" s="147"/>
+      <c r="M33" s="147"/>
+      <c r="N33" s="147"/>
+      <c r="O33" s="147"/>
+      <c r="P33" s="147"/>
+      <c r="Q33" s="147"/>
+      <c r="R33" s="147"/>
+      <c r="S33" s="147"/>
+      <c r="T33" s="147"/>
+      <c r="U33" s="147"/>
+      <c r="V33" s="147"/>
+      <c r="W33" s="147"/>
+      <c r="X33" s="147"/>
     </row>
     <row r="34" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="146" t="s">
+      <c r="A34" s="155" t="s">
         <v>60</v>
       </c>
-      <c r="B34" s="144"/>
-      <c r="C34" s="144"/>
-      <c r="D34" s="144"/>
-      <c r="E34" s="144"/>
-      <c r="F34" s="144"/>
-      <c r="G34" s="144"/>
-      <c r="H34" s="144"/>
-      <c r="I34" s="144"/>
-      <c r="J34" s="144"/>
-      <c r="K34" s="144"/>
-      <c r="L34" s="144"/>
-      <c r="M34" s="144"/>
-      <c r="N34" s="144"/>
-      <c r="O34" s="144"/>
-      <c r="P34" s="144"/>
-      <c r="Q34" s="144"/>
-      <c r="R34" s="144"/>
-      <c r="S34" s="144"/>
-      <c r="T34" s="144"/>
-      <c r="U34" s="144"/>
-      <c r="V34" s="144"/>
-      <c r="W34" s="144"/>
-      <c r="X34" s="144"/>
+      <c r="B34" s="147"/>
+      <c r="C34" s="147"/>
+      <c r="D34" s="147"/>
+      <c r="E34" s="147"/>
+      <c r="F34" s="147"/>
+      <c r="G34" s="147"/>
+      <c r="H34" s="147"/>
+      <c r="I34" s="147"/>
+      <c r="J34" s="147"/>
+      <c r="K34" s="147"/>
+      <c r="L34" s="147"/>
+      <c r="M34" s="147"/>
+      <c r="N34" s="147"/>
+      <c r="O34" s="147"/>
+      <c r="P34" s="147"/>
+      <c r="Q34" s="147"/>
+      <c r="R34" s="147"/>
+      <c r="S34" s="147"/>
+      <c r="T34" s="147"/>
+      <c r="U34" s="147"/>
+      <c r="V34" s="147"/>
+      <c r="W34" s="147"/>
+      <c r="X34" s="147"/>
     </row>
     <row r="35" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="20"/>
@@ -20935,55 +20931,55 @@
     </row>
     <row r="41" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="151"/>
-      <c r="B41" s="144"/>
-      <c r="C41" s="144"/>
-      <c r="D41" s="144"/>
-      <c r="E41" s="144"/>
-      <c r="F41" s="144"/>
-      <c r="G41" s="144"/>
-      <c r="H41" s="144"/>
-      <c r="I41" s="144"/>
-      <c r="J41" s="144"/>
-      <c r="K41" s="144"/>
-      <c r="L41" s="144"/>
-      <c r="M41" s="144"/>
-      <c r="N41" s="144"/>
-      <c r="O41" s="144"/>
-      <c r="P41" s="144"/>
-      <c r="Q41" s="144"/>
-      <c r="R41" s="144"/>
-      <c r="S41" s="144"/>
-      <c r="T41" s="144"/>
-      <c r="U41" s="144"/>
-      <c r="V41" s="144"/>
-      <c r="W41" s="144"/>
-      <c r="X41" s="145"/>
+      <c r="B41" s="147"/>
+      <c r="C41" s="147"/>
+      <c r="D41" s="147"/>
+      <c r="E41" s="147"/>
+      <c r="F41" s="147"/>
+      <c r="G41" s="147"/>
+      <c r="H41" s="147"/>
+      <c r="I41" s="147"/>
+      <c r="J41" s="147"/>
+      <c r="K41" s="147"/>
+      <c r="L41" s="147"/>
+      <c r="M41" s="147"/>
+      <c r="N41" s="147"/>
+      <c r="O41" s="147"/>
+      <c r="P41" s="147"/>
+      <c r="Q41" s="147"/>
+      <c r="R41" s="147"/>
+      <c r="S41" s="147"/>
+      <c r="T41" s="147"/>
+      <c r="U41" s="147"/>
+      <c r="V41" s="147"/>
+      <c r="W41" s="147"/>
+      <c r="X41" s="152"/>
     </row>
     <row r="42" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="151"/>
-      <c r="B42" s="144"/>
-      <c r="C42" s="144"/>
-      <c r="D42" s="144"/>
-      <c r="E42" s="144"/>
-      <c r="F42" s="144"/>
-      <c r="G42" s="144"/>
-      <c r="H42" s="144"/>
-      <c r="I42" s="144"/>
-      <c r="J42" s="144"/>
-      <c r="K42" s="144"/>
-      <c r="L42" s="144"/>
-      <c r="M42" s="144"/>
-      <c r="N42" s="144"/>
-      <c r="O42" s="144"/>
-      <c r="P42" s="144"/>
-      <c r="Q42" s="144"/>
-      <c r="R42" s="144"/>
-      <c r="S42" s="144"/>
-      <c r="T42" s="144"/>
-      <c r="U42" s="144"/>
-      <c r="V42" s="144"/>
-      <c r="W42" s="144"/>
-      <c r="X42" s="145"/>
+      <c r="B42" s="147"/>
+      <c r="C42" s="147"/>
+      <c r="D42" s="147"/>
+      <c r="E42" s="147"/>
+      <c r="F42" s="147"/>
+      <c r="G42" s="147"/>
+      <c r="H42" s="147"/>
+      <c r="I42" s="147"/>
+      <c r="J42" s="147"/>
+      <c r="K42" s="147"/>
+      <c r="L42" s="147"/>
+      <c r="M42" s="147"/>
+      <c r="N42" s="147"/>
+      <c r="O42" s="147"/>
+      <c r="P42" s="147"/>
+      <c r="Q42" s="147"/>
+      <c r="R42" s="147"/>
+      <c r="S42" s="147"/>
+      <c r="T42" s="147"/>
+      <c r="U42" s="147"/>
+      <c r="V42" s="147"/>
+      <c r="W42" s="147"/>
+      <c r="X42" s="152"/>
     </row>
     <row r="43" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="20"/>
@@ -21131,66 +21127,66 @@
         <v>44</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D45" s="182">
+        <v>42</v>
+      </c>
+      <c r="D45" s="145">
         <v>167</v>
       </c>
-      <c r="E45" s="182">
+      <c r="E45" s="145">
         <v>149</v>
       </c>
-      <c r="F45" s="182">
+      <c r="F45" s="145">
         <v>150</v>
       </c>
-      <c r="G45" s="182">
+      <c r="G45" s="145">
         <v>179</v>
       </c>
-      <c r="H45" s="182">
+      <c r="H45" s="145">
         <v>89</v>
       </c>
-      <c r="I45" s="182">
+      <c r="I45" s="145">
         <v>120</v>
       </c>
-      <c r="J45" s="182">
+      <c r="J45" s="145">
         <v>123</v>
       </c>
-      <c r="K45" s="182">
+      <c r="K45" s="145">
         <v>135</v>
       </c>
-      <c r="L45" s="182">
+      <c r="L45" s="145">
         <v>143</v>
       </c>
-      <c r="M45" s="182">
+      <c r="M45" s="145">
         <v>144</v>
       </c>
-      <c r="N45" s="182">
+      <c r="N45" s="145">
         <v>151</v>
       </c>
-      <c r="O45" s="182">
+      <c r="O45" s="145">
         <v>184</v>
       </c>
-      <c r="P45" s="182">
+      <c r="P45" s="145">
         <v>210</v>
       </c>
-      <c r="Q45" s="182">
+      <c r="Q45" s="145">
         <v>272</v>
       </c>
-      <c r="R45" s="182">
+      <c r="R45" s="145">
         <v>273</v>
       </c>
-      <c r="S45" s="182">
+      <c r="S45" s="145">
         <v>222</v>
       </c>
-      <c r="T45" s="182">
+      <c r="T45" s="145">
         <v>185</v>
       </c>
-      <c r="U45" s="183">
+      <c r="U45" s="49">
         <v>142</v>
       </c>
-      <c r="V45" s="183">
+      <c r="V45" s="49">
         <v>130</v>
       </c>
-      <c r="W45" s="183">
+      <c r="W45" s="49">
         <v>111</v>
       </c>
       <c r="X45" s="13"/>
@@ -21201,97 +21197,97 @@
         <v>45</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D46" s="182">
+        <v>42</v>
+      </c>
+      <c r="D46" s="145">
         <v>72</v>
       </c>
-      <c r="E46" s="182">
+      <c r="E46" s="145">
         <v>51</v>
       </c>
-      <c r="F46" s="182">
+      <c r="F46" s="145">
         <v>39</v>
       </c>
-      <c r="G46" s="182">
+      <c r="G46" s="145">
         <v>46</v>
       </c>
-      <c r="H46" s="182">
+      <c r="H46" s="145">
         <v>39</v>
       </c>
-      <c r="I46" s="182">
+      <c r="I46" s="145">
         <v>53</v>
       </c>
-      <c r="J46" s="182">
+      <c r="J46" s="145">
         <v>59</v>
       </c>
-      <c r="K46" s="182">
+      <c r="K46" s="145">
         <v>68</v>
       </c>
-      <c r="L46" s="182">
+      <c r="L46" s="145">
         <v>56</v>
       </c>
-      <c r="M46" s="182">
+      <c r="M46" s="145">
         <v>71</v>
       </c>
-      <c r="N46" s="182">
+      <c r="N46" s="145">
         <v>82</v>
       </c>
-      <c r="O46" s="182">
+      <c r="O46" s="145">
         <v>97</v>
       </c>
-      <c r="P46" s="182">
+      <c r="P46" s="145">
         <v>113</v>
       </c>
-      <c r="Q46" s="182">
+      <c r="Q46" s="145">
         <v>79</v>
       </c>
-      <c r="R46" s="182">
+      <c r="R46" s="145">
         <v>64</v>
       </c>
-      <c r="S46" s="182">
+      <c r="S46" s="145">
         <v>69</v>
       </c>
-      <c r="T46" s="182">
+      <c r="T46" s="145">
         <v>56</v>
       </c>
-      <c r="U46" s="183">
+      <c r="U46" s="49">
         <v>42</v>
       </c>
-      <c r="V46" s="183">
+      <c r="V46" s="49">
         <v>35</v>
       </c>
-      <c r="W46" s="183">
+      <c r="W46" s="49">
         <v>23</v>
       </c>
       <c r="X46" s="13"/>
     </row>
     <row r="47" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="147" t="s">
+      <c r="A47" s="149" t="s">
         <v>46</v>
       </c>
-      <c r="B47" s="144"/>
-      <c r="C47" s="144"/>
-      <c r="D47" s="144"/>
-      <c r="E47" s="144"/>
-      <c r="F47" s="144"/>
-      <c r="G47" s="144"/>
-      <c r="H47" s="144"/>
-      <c r="I47" s="144"/>
-      <c r="J47" s="144"/>
-      <c r="K47" s="144"/>
-      <c r="L47" s="144"/>
-      <c r="M47" s="144"/>
-      <c r="N47" s="144"/>
-      <c r="O47" s="144"/>
-      <c r="P47" s="144"/>
-      <c r="Q47" s="144"/>
-      <c r="R47" s="144"/>
-      <c r="S47" s="144"/>
-      <c r="T47" s="144"/>
-      <c r="U47" s="144"/>
-      <c r="V47" s="144"/>
-      <c r="W47" s="144"/>
-      <c r="X47" s="144"/>
+      <c r="B47" s="147"/>
+      <c r="C47" s="147"/>
+      <c r="D47" s="147"/>
+      <c r="E47" s="147"/>
+      <c r="F47" s="147"/>
+      <c r="G47" s="147"/>
+      <c r="H47" s="147"/>
+      <c r="I47" s="147"/>
+      <c r="J47" s="147"/>
+      <c r="K47" s="147"/>
+      <c r="L47" s="147"/>
+      <c r="M47" s="147"/>
+      <c r="N47" s="147"/>
+      <c r="O47" s="147"/>
+      <c r="P47" s="147"/>
+      <c r="Q47" s="147"/>
+      <c r="R47" s="147"/>
+      <c r="S47" s="147"/>
+      <c r="T47" s="147"/>
+      <c r="U47" s="147"/>
+      <c r="V47" s="147"/>
+      <c r="W47" s="147"/>
+      <c r="X47" s="147"/>
     </row>
     <row r="48" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="20"/>
@@ -21924,32 +21920,32 @@
       <c r="X56" s="11"/>
     </row>
     <row r="57" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="147" t="s">
+      <c r="A57" s="149" t="s">
         <v>54</v>
       </c>
-      <c r="B57" s="144"/>
-      <c r="C57" s="144"/>
-      <c r="D57" s="144"/>
-      <c r="E57" s="144"/>
-      <c r="F57" s="144"/>
-      <c r="G57" s="144"/>
-      <c r="H57" s="144"/>
-      <c r="I57" s="144"/>
-      <c r="J57" s="144"/>
-      <c r="K57" s="144"/>
-      <c r="L57" s="144"/>
-      <c r="M57" s="144"/>
-      <c r="N57" s="144"/>
-      <c r="O57" s="144"/>
-      <c r="P57" s="144"/>
-      <c r="Q57" s="144"/>
-      <c r="R57" s="144"/>
-      <c r="S57" s="144"/>
-      <c r="T57" s="144"/>
-      <c r="U57" s="144"/>
-      <c r="V57" s="144"/>
-      <c r="W57" s="144"/>
-      <c r="X57" s="144"/>
+      <c r="B57" s="147"/>
+      <c r="C57" s="147"/>
+      <c r="D57" s="147"/>
+      <c r="E57" s="147"/>
+      <c r="F57" s="147"/>
+      <c r="G57" s="147"/>
+      <c r="H57" s="147"/>
+      <c r="I57" s="147"/>
+      <c r="J57" s="147"/>
+      <c r="K57" s="147"/>
+      <c r="L57" s="147"/>
+      <c r="M57" s="147"/>
+      <c r="N57" s="147"/>
+      <c r="O57" s="147"/>
+      <c r="P57" s="147"/>
+      <c r="Q57" s="147"/>
+      <c r="R57" s="147"/>
+      <c r="S57" s="147"/>
+      <c r="T57" s="147"/>
+      <c r="U57" s="147"/>
+      <c r="V57" s="147"/>
+      <c r="W57" s="147"/>
+      <c r="X57" s="147"/>
     </row>
     <row r="58" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="20"/>
@@ -22442,30 +22438,30 @@
       </c>
     </row>
     <row r="69" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="143"/>
-      <c r="B69" s="144"/>
-      <c r="C69" s="144"/>
-      <c r="D69" s="144"/>
-      <c r="E69" s="144"/>
-      <c r="F69" s="144"/>
-      <c r="G69" s="144"/>
-      <c r="H69" s="144"/>
-      <c r="I69" s="144"/>
-      <c r="J69" s="144"/>
-      <c r="K69" s="144"/>
-      <c r="L69" s="144"/>
-      <c r="M69" s="144"/>
-      <c r="N69" s="144"/>
-      <c r="O69" s="144"/>
-      <c r="P69" s="144"/>
-      <c r="Q69" s="144"/>
-      <c r="R69" s="144"/>
-      <c r="S69" s="144"/>
-      <c r="T69" s="144"/>
-      <c r="U69" s="144"/>
-      <c r="V69" s="144"/>
-      <c r="W69" s="144"/>
-      <c r="X69" s="145"/>
+      <c r="A69" s="154"/>
+      <c r="B69" s="147"/>
+      <c r="C69" s="147"/>
+      <c r="D69" s="147"/>
+      <c r="E69" s="147"/>
+      <c r="F69" s="147"/>
+      <c r="G69" s="147"/>
+      <c r="H69" s="147"/>
+      <c r="I69" s="147"/>
+      <c r="J69" s="147"/>
+      <c r="K69" s="147"/>
+      <c r="L69" s="147"/>
+      <c r="M69" s="147"/>
+      <c r="N69" s="147"/>
+      <c r="O69" s="147"/>
+      <c r="P69" s="147"/>
+      <c r="Q69" s="147"/>
+      <c r="R69" s="147"/>
+      <c r="S69" s="147"/>
+      <c r="T69" s="147"/>
+      <c r="U69" s="147"/>
+      <c r="V69" s="147"/>
+      <c r="W69" s="147"/>
+      <c r="X69" s="152"/>
     </row>
     <row r="70" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="25"/>
@@ -23194,32 +23190,32 @@
       <c r="X80" s="11"/>
     </row>
     <row r="81" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="149" t="s">
+      <c r="A81" s="157" t="s">
         <v>93</v>
       </c>
-      <c r="B81" s="144"/>
-      <c r="C81" s="144"/>
-      <c r="D81" s="144"/>
-      <c r="E81" s="144"/>
-      <c r="F81" s="144"/>
-      <c r="G81" s="144"/>
-      <c r="H81" s="144"/>
-      <c r="I81" s="144"/>
-      <c r="J81" s="144"/>
-      <c r="K81" s="144"/>
-      <c r="L81" s="144"/>
-      <c r="M81" s="144"/>
-      <c r="N81" s="144"/>
-      <c r="O81" s="144"/>
-      <c r="P81" s="144"/>
-      <c r="Q81" s="144"/>
-      <c r="R81" s="144"/>
-      <c r="S81" s="144"/>
-      <c r="T81" s="144"/>
-      <c r="U81" s="144"/>
-      <c r="V81" s="144"/>
-      <c r="W81" s="144"/>
-      <c r="X81" s="144"/>
+      <c r="B81" s="147"/>
+      <c r="C81" s="147"/>
+      <c r="D81" s="147"/>
+      <c r="E81" s="147"/>
+      <c r="F81" s="147"/>
+      <c r="G81" s="147"/>
+      <c r="H81" s="147"/>
+      <c r="I81" s="147"/>
+      <c r="J81" s="147"/>
+      <c r="K81" s="147"/>
+      <c r="L81" s="147"/>
+      <c r="M81" s="147"/>
+      <c r="N81" s="147"/>
+      <c r="O81" s="147"/>
+      <c r="P81" s="147"/>
+      <c r="Q81" s="147"/>
+      <c r="R81" s="147"/>
+      <c r="S81" s="147"/>
+      <c r="T81" s="147"/>
+      <c r="U81" s="147"/>
+      <c r="V81" s="147"/>
+      <c r="W81" s="147"/>
+      <c r="X81" s="147"/>
     </row>
     <row r="82" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="29"/>
@@ -23519,6 +23515,13 @@
     <row r="200" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A69:X69"/>
+    <mergeCell ref="A34:X34"/>
+    <mergeCell ref="A29:X29"/>
+    <mergeCell ref="A4:X4"/>
+    <mergeCell ref="A81:X81"/>
+    <mergeCell ref="A57:X57"/>
+    <mergeCell ref="A47:X47"/>
     <mergeCell ref="A1:X1"/>
     <mergeCell ref="A13:X13"/>
     <mergeCell ref="A14:X14"/>
@@ -23528,13 +23531,6 @@
     <mergeCell ref="A19:X19"/>
     <mergeCell ref="A33:X33"/>
     <mergeCell ref="A5:X5"/>
-    <mergeCell ref="A69:X69"/>
-    <mergeCell ref="A34:X34"/>
-    <mergeCell ref="A29:X29"/>
-    <mergeCell ref="A4:X4"/>
-    <mergeCell ref="A81:X81"/>
-    <mergeCell ref="A57:X57"/>
-    <mergeCell ref="A47:X47"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -23565,80 +23561,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="165" t="s">
+      <c r="A1" s="163" t="s">
         <v>495</v>
       </c>
-      <c r="B1" s="144"/>
-      <c r="C1" s="144"/>
-      <c r="D1" s="144"/>
-      <c r="E1" s="144"/>
-      <c r="F1" s="144"/>
-      <c r="G1" s="144"/>
-      <c r="H1" s="144"/>
-      <c r="I1" s="144"/>
-      <c r="J1" s="144"/>
-      <c r="K1" s="144"/>
-      <c r="L1" s="144"/>
-      <c r="M1" s="144"/>
-      <c r="N1" s="144"/>
-      <c r="O1" s="144"/>
-      <c r="P1" s="144"/>
-      <c r="Q1" s="144"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="147"/>
+      <c r="M1" s="147"/>
+      <c r="N1" s="147"/>
+      <c r="O1" s="147"/>
+      <c r="P1" s="147"/>
+      <c r="Q1" s="147"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="150" t="s">
         <v>373</v>
       </c>
-      <c r="B2" s="144"/>
-      <c r="C2" s="144"/>
-      <c r="D2" s="144"/>
-      <c r="E2" s="144"/>
-      <c r="F2" s="144"/>
-      <c r="G2" s="144"/>
-      <c r="H2" s="144"/>
-      <c r="I2" s="144"/>
-      <c r="J2" s="144"/>
-      <c r="K2" s="144"/>
-      <c r="L2" s="144"/>
-      <c r="M2" s="144"/>
-      <c r="N2" s="144"/>
-      <c r="O2" s="144"/>
-      <c r="P2" s="144"/>
-      <c r="Q2" s="144"/>
+      <c r="B2" s="147"/>
+      <c r="C2" s="147"/>
+      <c r="D2" s="147"/>
+      <c r="E2" s="147"/>
+      <c r="F2" s="147"/>
+      <c r="G2" s="147"/>
+      <c r="H2" s="147"/>
+      <c r="I2" s="147"/>
+      <c r="J2" s="147"/>
+      <c r="K2" s="147"/>
+      <c r="L2" s="147"/>
+      <c r="M2" s="147"/>
+      <c r="N2" s="147"/>
+      <c r="O2" s="147"/>
+      <c r="P2" s="147"/>
+      <c r="Q2" s="147"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="164" t="s">
+      <c r="A3" s="169" t="s">
         <v>374</v>
       </c>
-      <c r="B3" s="144"/>
-      <c r="C3" s="163" t="s">
+      <c r="B3" s="147"/>
+      <c r="C3" s="168" t="s">
         <v>375</v>
       </c>
-      <c r="D3" s="144"/>
-      <c r="E3" s="166" t="s">
+      <c r="D3" s="147"/>
+      <c r="E3" s="164" t="s">
         <v>376</v>
       </c>
-      <c r="F3" s="144"/>
-      <c r="G3" s="161" t="s">
+      <c r="F3" s="147"/>
+      <c r="G3" s="166" t="s">
         <v>377</v>
       </c>
-      <c r="H3" s="144"/>
-      <c r="I3" s="144"/>
-      <c r="J3" s="144"/>
+      <c r="H3" s="147"/>
+      <c r="I3" s="147"/>
+      <c r="J3" s="147"/>
       <c r="K3" s="31" t="s">
         <v>378</v>
       </c>
       <c r="L3" s="32" t="s">
         <v>379</v>
       </c>
-      <c r="M3" s="160" t="s">
+      <c r="M3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="N3" s="144"/>
-      <c r="O3" s="160" t="s">
+      <c r="N3" s="147"/>
+      <c r="O3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="P3" s="144"/>
+      <c r="P3" s="147"/>
       <c r="Q3" s="33" t="s">
         <v>381</v>
       </c>
@@ -23697,10 +23693,10 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="162" t="s">
+      <c r="A5" s="167" t="s">
         <v>399</v>
       </c>
-      <c r="B5" s="144"/>
+      <c r="B5" s="147"/>
       <c r="C5" s="41">
         <v>1258798314</v>
       </c>
@@ -25102,40 +25098,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="172" t="s">
+      <c r="A1" s="175" t="s">
         <v>496</v>
       </c>
-      <c r="B1" s="156"/>
-      <c r="C1" s="156"/>
-      <c r="D1" s="156"/>
-      <c r="E1" s="156"/>
-      <c r="F1" s="156"/>
-      <c r="G1" s="156"/>
-      <c r="H1" s="156"/>
-      <c r="I1" s="156"/>
-      <c r="J1" s="156"/>
-      <c r="K1" s="156"/>
-      <c r="L1" s="156"/>
-      <c r="M1" s="156"/>
-      <c r="N1" s="156"/>
+      <c r="B1" s="159"/>
+      <c r="C1" s="159"/>
+      <c r="D1" s="159"/>
+      <c r="E1" s="159"/>
+      <c r="F1" s="159"/>
+      <c r="G1" s="159"/>
+      <c r="H1" s="159"/>
+      <c r="I1" s="159"/>
+      <c r="J1" s="159"/>
+      <c r="K1" s="159"/>
+      <c r="L1" s="159"/>
+      <c r="M1" s="159"/>
+      <c r="N1" s="159"/>
     </row>
     <row r="2" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="171" t="s">
+      <c r="A2" s="174" t="s">
         <v>417</v>
       </c>
-      <c r="B2" s="156"/>
-      <c r="C2" s="156"/>
-      <c r="D2" s="156"/>
-      <c r="E2" s="156"/>
-      <c r="F2" s="156"/>
-      <c r="G2" s="156"/>
-      <c r="H2" s="156"/>
-      <c r="I2" s="156"/>
-      <c r="J2" s="156"/>
-      <c r="K2" s="156"/>
-      <c r="L2" s="156"/>
-      <c r="M2" s="156"/>
-      <c r="N2" s="156"/>
+      <c r="B2" s="159"/>
+      <c r="C2" s="159"/>
+      <c r="D2" s="159"/>
+      <c r="E2" s="159"/>
+      <c r="F2" s="159"/>
+      <c r="G2" s="159"/>
+      <c r="H2" s="159"/>
+      <c r="I2" s="159"/>
+      <c r="J2" s="159"/>
+      <c r="K2" s="159"/>
+      <c r="L2" s="159"/>
+      <c r="M2" s="159"/>
+      <c r="N2" s="159"/>
     </row>
     <row r="3" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="116" t="s">
@@ -25469,80 +25465,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="165" t="s">
+      <c r="A1" s="163" t="s">
         <v>502</v>
       </c>
-      <c r="B1" s="144"/>
-      <c r="C1" s="144"/>
-      <c r="D1" s="144"/>
-      <c r="E1" s="144"/>
-      <c r="F1" s="144"/>
-      <c r="G1" s="144"/>
-      <c r="H1" s="144"/>
-      <c r="I1" s="144"/>
-      <c r="J1" s="144"/>
-      <c r="K1" s="144"/>
-      <c r="L1" s="144"/>
-      <c r="M1" s="144"/>
-      <c r="N1" s="144"/>
-      <c r="O1" s="144"/>
-      <c r="P1" s="144"/>
-      <c r="Q1" s="144"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="147"/>
+      <c r="M1" s="147"/>
+      <c r="N1" s="147"/>
+      <c r="O1" s="147"/>
+      <c r="P1" s="147"/>
+      <c r="Q1" s="147"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="150" t="s">
         <v>373</v>
       </c>
-      <c r="B2" s="144"/>
-      <c r="C2" s="144"/>
-      <c r="D2" s="144"/>
-      <c r="E2" s="144"/>
-      <c r="F2" s="144"/>
-      <c r="G2" s="144"/>
-      <c r="H2" s="144"/>
-      <c r="I2" s="144"/>
-      <c r="J2" s="144"/>
-      <c r="K2" s="144"/>
-      <c r="L2" s="144"/>
-      <c r="M2" s="144"/>
-      <c r="N2" s="144"/>
-      <c r="O2" s="144"/>
-      <c r="P2" s="144"/>
-      <c r="Q2" s="144"/>
+      <c r="B2" s="147"/>
+      <c r="C2" s="147"/>
+      <c r="D2" s="147"/>
+      <c r="E2" s="147"/>
+      <c r="F2" s="147"/>
+      <c r="G2" s="147"/>
+      <c r="H2" s="147"/>
+      <c r="I2" s="147"/>
+      <c r="J2" s="147"/>
+      <c r="K2" s="147"/>
+      <c r="L2" s="147"/>
+      <c r="M2" s="147"/>
+      <c r="N2" s="147"/>
+      <c r="O2" s="147"/>
+      <c r="P2" s="147"/>
+      <c r="Q2" s="147"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="164" t="s">
+      <c r="A3" s="169" t="s">
         <v>374</v>
       </c>
-      <c r="B3" s="144"/>
-      <c r="C3" s="163" t="s">
+      <c r="B3" s="147"/>
+      <c r="C3" s="168" t="s">
         <v>375</v>
       </c>
-      <c r="D3" s="144"/>
-      <c r="E3" s="166" t="s">
+      <c r="D3" s="147"/>
+      <c r="E3" s="164" t="s">
         <v>376</v>
       </c>
-      <c r="F3" s="144"/>
-      <c r="G3" s="161" t="s">
+      <c r="F3" s="147"/>
+      <c r="G3" s="166" t="s">
         <v>377</v>
       </c>
-      <c r="H3" s="144"/>
-      <c r="I3" s="144"/>
-      <c r="J3" s="144"/>
+      <c r="H3" s="147"/>
+      <c r="I3" s="147"/>
+      <c r="J3" s="147"/>
       <c r="K3" s="31" t="s">
         <v>378</v>
       </c>
       <c r="L3" s="32" t="s">
         <v>379</v>
       </c>
-      <c r="M3" s="160" t="s">
+      <c r="M3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="N3" s="144"/>
-      <c r="O3" s="160" t="s">
+      <c r="N3" s="147"/>
+      <c r="O3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="P3" s="144"/>
+      <c r="P3" s="147"/>
       <c r="Q3" s="33" t="s">
         <v>381</v>
       </c>
@@ -25601,10 +25597,10 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="162" t="s">
+      <c r="A5" s="167" t="s">
         <v>399</v>
       </c>
-      <c r="B5" s="144"/>
+      <c r="B5" s="147"/>
       <c r="C5" s="41">
         <v>1625138977</v>
       </c>
@@ -26979,40 +26975,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="172" t="s">
+      <c r="A1" s="175" t="s">
         <v>503</v>
       </c>
-      <c r="B1" s="156"/>
-      <c r="C1" s="156"/>
-      <c r="D1" s="156"/>
-      <c r="E1" s="156"/>
-      <c r="F1" s="156"/>
-      <c r="G1" s="156"/>
-      <c r="H1" s="156"/>
-      <c r="I1" s="156"/>
-      <c r="J1" s="156"/>
-      <c r="K1" s="156"/>
-      <c r="L1" s="156"/>
-      <c r="M1" s="156"/>
-      <c r="N1" s="156"/>
+      <c r="B1" s="159"/>
+      <c r="C1" s="159"/>
+      <c r="D1" s="159"/>
+      <c r="E1" s="159"/>
+      <c r="F1" s="159"/>
+      <c r="G1" s="159"/>
+      <c r="H1" s="159"/>
+      <c r="I1" s="159"/>
+      <c r="J1" s="159"/>
+      <c r="K1" s="159"/>
+      <c r="L1" s="159"/>
+      <c r="M1" s="159"/>
+      <c r="N1" s="159"/>
     </row>
     <row r="2" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="171" t="s">
+      <c r="A2" s="174" t="s">
         <v>417</v>
       </c>
-      <c r="B2" s="156"/>
-      <c r="C2" s="156"/>
-      <c r="D2" s="156"/>
-      <c r="E2" s="156"/>
-      <c r="F2" s="156"/>
-      <c r="G2" s="156"/>
-      <c r="H2" s="156"/>
-      <c r="I2" s="156"/>
-      <c r="J2" s="156"/>
-      <c r="K2" s="156"/>
-      <c r="L2" s="156"/>
-      <c r="M2" s="156"/>
-      <c r="N2" s="156"/>
+      <c r="B2" s="159"/>
+      <c r="C2" s="159"/>
+      <c r="D2" s="159"/>
+      <c r="E2" s="159"/>
+      <c r="F2" s="159"/>
+      <c r="G2" s="159"/>
+      <c r="H2" s="159"/>
+      <c r="I2" s="159"/>
+      <c r="J2" s="159"/>
+      <c r="K2" s="159"/>
+      <c r="L2" s="159"/>
+      <c r="M2" s="159"/>
+      <c r="N2" s="159"/>
     </row>
     <row r="3" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="116" t="s">
@@ -27397,80 +27393,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="165" t="s">
+      <c r="A1" s="163" t="s">
         <v>510</v>
       </c>
-      <c r="B1" s="144"/>
-      <c r="C1" s="144"/>
-      <c r="D1" s="144"/>
-      <c r="E1" s="144"/>
-      <c r="F1" s="144"/>
-      <c r="G1" s="144"/>
-      <c r="H1" s="144"/>
-      <c r="I1" s="144"/>
-      <c r="J1" s="144"/>
-      <c r="K1" s="144"/>
-      <c r="L1" s="144"/>
-      <c r="M1" s="144"/>
-      <c r="N1" s="144"/>
-      <c r="O1" s="144"/>
-      <c r="P1" s="144"/>
-      <c r="Q1" s="144"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="147"/>
+      <c r="M1" s="147"/>
+      <c r="N1" s="147"/>
+      <c r="O1" s="147"/>
+      <c r="P1" s="147"/>
+      <c r="Q1" s="147"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="150" t="s">
         <v>373</v>
       </c>
-      <c r="B2" s="144"/>
-      <c r="C2" s="144"/>
-      <c r="D2" s="144"/>
-      <c r="E2" s="144"/>
-      <c r="F2" s="144"/>
-      <c r="G2" s="144"/>
-      <c r="H2" s="144"/>
-      <c r="I2" s="144"/>
-      <c r="J2" s="144"/>
-      <c r="K2" s="144"/>
-      <c r="L2" s="144"/>
-      <c r="M2" s="144"/>
-      <c r="N2" s="144"/>
-      <c r="O2" s="144"/>
-      <c r="P2" s="144"/>
-      <c r="Q2" s="144"/>
+      <c r="B2" s="147"/>
+      <c r="C2" s="147"/>
+      <c r="D2" s="147"/>
+      <c r="E2" s="147"/>
+      <c r="F2" s="147"/>
+      <c r="G2" s="147"/>
+      <c r="H2" s="147"/>
+      <c r="I2" s="147"/>
+      <c r="J2" s="147"/>
+      <c r="K2" s="147"/>
+      <c r="L2" s="147"/>
+      <c r="M2" s="147"/>
+      <c r="N2" s="147"/>
+      <c r="O2" s="147"/>
+      <c r="P2" s="147"/>
+      <c r="Q2" s="147"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="164" t="s">
+      <c r="A3" s="169" t="s">
         <v>374</v>
       </c>
-      <c r="B3" s="144"/>
-      <c r="C3" s="163" t="s">
+      <c r="B3" s="147"/>
+      <c r="C3" s="168" t="s">
         <v>375</v>
       </c>
-      <c r="D3" s="144"/>
-      <c r="E3" s="166" t="s">
+      <c r="D3" s="147"/>
+      <c r="E3" s="164" t="s">
         <v>376</v>
       </c>
-      <c r="F3" s="144"/>
-      <c r="G3" s="161" t="s">
+      <c r="F3" s="147"/>
+      <c r="G3" s="166" t="s">
         <v>377</v>
       </c>
-      <c r="H3" s="144"/>
-      <c r="I3" s="144"/>
-      <c r="J3" s="144"/>
+      <c r="H3" s="147"/>
+      <c r="I3" s="147"/>
+      <c r="J3" s="147"/>
       <c r="K3" s="31" t="s">
         <v>378</v>
       </c>
       <c r="L3" s="32" t="s">
         <v>379</v>
       </c>
-      <c r="M3" s="160" t="s">
+      <c r="M3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="N3" s="144"/>
-      <c r="O3" s="160" t="s">
+      <c r="N3" s="147"/>
+      <c r="O3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="P3" s="144"/>
+      <c r="P3" s="147"/>
       <c r="Q3" s="33" t="s">
         <v>381</v>
       </c>
@@ -27529,10 +27525,10 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="162" t="s">
+      <c r="A5" s="167" t="s">
         <v>399</v>
       </c>
-      <c r="B5" s="144"/>
+      <c r="B5" s="147"/>
       <c r="C5" s="41">
         <v>1965067740</v>
       </c>
@@ -28934,40 +28930,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="172" t="s">
+      <c r="A1" s="175" t="s">
         <v>511</v>
       </c>
-      <c r="B1" s="156"/>
-      <c r="C1" s="156"/>
-      <c r="D1" s="156"/>
-      <c r="E1" s="156"/>
-      <c r="F1" s="156"/>
-      <c r="G1" s="156"/>
-      <c r="H1" s="156"/>
-      <c r="I1" s="156"/>
-      <c r="J1" s="156"/>
-      <c r="K1" s="156"/>
-      <c r="L1" s="156"/>
-      <c r="M1" s="156"/>
-      <c r="N1" s="156"/>
+      <c r="B1" s="159"/>
+      <c r="C1" s="159"/>
+      <c r="D1" s="159"/>
+      <c r="E1" s="159"/>
+      <c r="F1" s="159"/>
+      <c r="G1" s="159"/>
+      <c r="H1" s="159"/>
+      <c r="I1" s="159"/>
+      <c r="J1" s="159"/>
+      <c r="K1" s="159"/>
+      <c r="L1" s="159"/>
+      <c r="M1" s="159"/>
+      <c r="N1" s="159"/>
     </row>
     <row r="2" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="171" t="s">
+      <c r="A2" s="174" t="s">
         <v>417</v>
       </c>
-      <c r="B2" s="156"/>
-      <c r="C2" s="156"/>
-      <c r="D2" s="156"/>
-      <c r="E2" s="156"/>
-      <c r="F2" s="156"/>
-      <c r="G2" s="156"/>
-      <c r="H2" s="156"/>
-      <c r="I2" s="156"/>
-      <c r="J2" s="156"/>
-      <c r="K2" s="156"/>
-      <c r="L2" s="156"/>
-      <c r="M2" s="156"/>
-      <c r="N2" s="156"/>
+      <c r="B2" s="159"/>
+      <c r="C2" s="159"/>
+      <c r="D2" s="159"/>
+      <c r="E2" s="159"/>
+      <c r="F2" s="159"/>
+      <c r="G2" s="159"/>
+      <c r="H2" s="159"/>
+      <c r="I2" s="159"/>
+      <c r="J2" s="159"/>
+      <c r="K2" s="159"/>
+      <c r="L2" s="159"/>
+      <c r="M2" s="159"/>
+      <c r="N2" s="159"/>
     </row>
     <row r="3" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="116" t="s">
@@ -29292,19 +29288,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="165" t="s">
+      <c r="A1" s="163" t="s">
         <v>517</v>
       </c>
-      <c r="B1" s="144"/>
-      <c r="C1" s="144"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
     </row>
     <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="175" t="s">
+      <c r="A3" s="178" t="s">
         <v>518</v>
       </c>
-      <c r="B3" s="144"/>
-      <c r="C3" s="144"/>
+      <c r="B3" s="147"/>
+      <c r="C3" s="147"/>
     </row>
     <row r="4" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
@@ -29362,11 +29358,11 @@
     </row>
     <row r="10" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="11" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="173" t="s">
+      <c r="A11" s="176" t="s">
         <v>531</v>
       </c>
-      <c r="B11" s="144"/>
-      <c r="C11" s="144"/>
+      <c r="B11" s="147"/>
+      <c r="C11" s="147"/>
     </row>
     <row r="12" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="90"/>
@@ -29406,11 +29402,11 @@
     </row>
     <row r="16" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="17" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="174" t="s">
+      <c r="A17" s="177" t="s">
         <v>540</v>
       </c>
-      <c r="B17" s="144"/>
-      <c r="C17" s="144"/>
+      <c r="B17" s="147"/>
+      <c r="C17" s="147"/>
     </row>
     <row r="18" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="93"/>
@@ -29459,11 +29455,11 @@
     </row>
     <row r="23" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="24" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="176" t="s">
+      <c r="A24" s="179" t="s">
         <v>551</v>
       </c>
-      <c r="B24" s="144"/>
-      <c r="C24" s="144"/>
+      <c r="B24" s="147"/>
+      <c r="C24" s="147"/>
     </row>
     <row r="25" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="96"/>
@@ -29751,40 +29747,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="179" t="s">
+      <c r="A1" s="182" t="s">
         <v>572</v>
       </c>
-      <c r="B1" s="156"/>
-      <c r="C1" s="156"/>
-      <c r="D1" s="156"/>
-      <c r="E1" s="156"/>
-      <c r="F1" s="156"/>
-      <c r="G1" s="156"/>
-      <c r="H1" s="156"/>
-      <c r="I1" s="156"/>
-      <c r="J1" s="156"/>
-      <c r="K1" s="156"/>
-      <c r="L1" s="156"/>
-      <c r="M1" s="156"/>
-      <c r="N1" s="156"/>
+      <c r="B1" s="159"/>
+      <c r="C1" s="159"/>
+      <c r="D1" s="159"/>
+      <c r="E1" s="159"/>
+      <c r="F1" s="159"/>
+      <c r="G1" s="159"/>
+      <c r="H1" s="159"/>
+      <c r="I1" s="159"/>
+      <c r="J1" s="159"/>
+      <c r="K1" s="159"/>
+      <c r="L1" s="159"/>
+      <c r="M1" s="159"/>
+      <c r="N1" s="159"/>
     </row>
     <row r="2" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="178" t="s">
+      <c r="A2" s="181" t="s">
         <v>573</v>
       </c>
-      <c r="B2" s="156"/>
-      <c r="C2" s="156"/>
-      <c r="D2" s="156"/>
-      <c r="E2" s="156"/>
-      <c r="F2" s="156"/>
-      <c r="G2" s="156"/>
-      <c r="H2" s="156"/>
-      <c r="I2" s="156"/>
-      <c r="J2" s="156"/>
-      <c r="K2" s="156"/>
-      <c r="L2" s="156"/>
-      <c r="M2" s="156"/>
-      <c r="N2" s="156"/>
+      <c r="B2" s="159"/>
+      <c r="C2" s="159"/>
+      <c r="D2" s="159"/>
+      <c r="E2" s="159"/>
+      <c r="F2" s="159"/>
+      <c r="G2" s="159"/>
+      <c r="H2" s="159"/>
+      <c r="I2" s="159"/>
+      <c r="J2" s="159"/>
+      <c r="K2" s="159"/>
+      <c r="L2" s="159"/>
+      <c r="M2" s="159"/>
+      <c r="N2" s="159"/>
     </row>
     <row r="3" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="99" t="s">
@@ -29831,22 +29827,22 @@
       </c>
     </row>
     <row r="4" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="177" t="s">
+      <c r="A4" s="180" t="s">
         <v>588</v>
       </c>
-      <c r="B4" s="156"/>
-      <c r="C4" s="156"/>
-      <c r="D4" s="156"/>
-      <c r="E4" s="156"/>
-      <c r="F4" s="156"/>
-      <c r="G4" s="156"/>
-      <c r="H4" s="156"/>
-      <c r="I4" s="156"/>
-      <c r="J4" s="156"/>
-      <c r="K4" s="156"/>
-      <c r="L4" s="156"/>
-      <c r="M4" s="156"/>
-      <c r="N4" s="156"/>
+      <c r="B4" s="159"/>
+      <c r="C4" s="159"/>
+      <c r="D4" s="159"/>
+      <c r="E4" s="159"/>
+      <c r="F4" s="159"/>
+      <c r="G4" s="159"/>
+      <c r="H4" s="159"/>
+      <c r="I4" s="159"/>
+      <c r="J4" s="159"/>
+      <c r="K4" s="159"/>
+      <c r="L4" s="159"/>
+      <c r="M4" s="159"/>
+      <c r="N4" s="159"/>
     </row>
     <row r="5" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="100" t="s">
@@ -35695,80 +35691,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="165" t="s">
+      <c r="A1" s="163" t="s">
         <v>372</v>
       </c>
-      <c r="B1" s="144"/>
-      <c r="C1" s="144"/>
-      <c r="D1" s="144"/>
-      <c r="E1" s="144"/>
-      <c r="F1" s="144"/>
-      <c r="G1" s="144"/>
-      <c r="H1" s="144"/>
-      <c r="I1" s="144"/>
-      <c r="J1" s="144"/>
-      <c r="K1" s="144"/>
-      <c r="L1" s="144"/>
-      <c r="M1" s="144"/>
-      <c r="N1" s="144"/>
-      <c r="O1" s="144"/>
-      <c r="P1" s="144"/>
-      <c r="Q1" s="144"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="147"/>
+      <c r="M1" s="147"/>
+      <c r="N1" s="147"/>
+      <c r="O1" s="147"/>
+      <c r="P1" s="147"/>
+      <c r="Q1" s="147"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="150" t="s">
         <v>373</v>
       </c>
-      <c r="B2" s="144"/>
-      <c r="C2" s="144"/>
-      <c r="D2" s="144"/>
-      <c r="E2" s="144"/>
-      <c r="F2" s="144"/>
-      <c r="G2" s="144"/>
-      <c r="H2" s="144"/>
-      <c r="I2" s="144"/>
-      <c r="J2" s="144"/>
-      <c r="K2" s="144"/>
-      <c r="L2" s="144"/>
-      <c r="M2" s="144"/>
-      <c r="N2" s="144"/>
-      <c r="O2" s="144"/>
-      <c r="P2" s="144"/>
-      <c r="Q2" s="144"/>
+      <c r="B2" s="147"/>
+      <c r="C2" s="147"/>
+      <c r="D2" s="147"/>
+      <c r="E2" s="147"/>
+      <c r="F2" s="147"/>
+      <c r="G2" s="147"/>
+      <c r="H2" s="147"/>
+      <c r="I2" s="147"/>
+      <c r="J2" s="147"/>
+      <c r="K2" s="147"/>
+      <c r="L2" s="147"/>
+      <c r="M2" s="147"/>
+      <c r="N2" s="147"/>
+      <c r="O2" s="147"/>
+      <c r="P2" s="147"/>
+      <c r="Q2" s="147"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="164" t="s">
+      <c r="A3" s="169" t="s">
         <v>374</v>
       </c>
-      <c r="B3" s="144"/>
-      <c r="C3" s="163" t="s">
+      <c r="B3" s="147"/>
+      <c r="C3" s="168" t="s">
         <v>375</v>
       </c>
-      <c r="D3" s="144"/>
-      <c r="E3" s="166" t="s">
+      <c r="D3" s="147"/>
+      <c r="E3" s="164" t="s">
         <v>376</v>
       </c>
-      <c r="F3" s="144"/>
-      <c r="G3" s="161" t="s">
+      <c r="F3" s="147"/>
+      <c r="G3" s="166" t="s">
         <v>377</v>
       </c>
-      <c r="H3" s="144"/>
-      <c r="I3" s="144"/>
-      <c r="J3" s="144"/>
+      <c r="H3" s="147"/>
+      <c r="I3" s="147"/>
+      <c r="J3" s="147"/>
       <c r="K3" s="31" t="s">
         <v>378</v>
       </c>
       <c r="L3" s="32" t="s">
         <v>379</v>
       </c>
-      <c r="M3" s="160" t="s">
+      <c r="M3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="N3" s="144"/>
-      <c r="O3" s="160" t="s">
+      <c r="N3" s="147"/>
+      <c r="O3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="P3" s="144"/>
+      <c r="P3" s="147"/>
       <c r="Q3" s="33" t="s">
         <v>381</v>
       </c>
@@ -35827,10 +35823,10 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="162" t="s">
+      <c r="A5" s="167" t="s">
         <v>399</v>
       </c>
-      <c r="B5" s="144"/>
+      <c r="B5" s="147"/>
       <c r="C5" s="41"/>
       <c r="D5" s="42"/>
       <c r="E5" s="42"/>
@@ -37585,80 +37581,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="165" t="s">
+      <c r="A1" s="163" t="s">
         <v>407</v>
       </c>
-      <c r="B1" s="144"/>
-      <c r="C1" s="144"/>
-      <c r="D1" s="144"/>
-      <c r="E1" s="144"/>
-      <c r="F1" s="144"/>
-      <c r="G1" s="144"/>
-      <c r="H1" s="144"/>
-      <c r="I1" s="144"/>
-      <c r="J1" s="144"/>
-      <c r="K1" s="144"/>
-      <c r="L1" s="144"/>
-      <c r="M1" s="144"/>
-      <c r="N1" s="144"/>
-      <c r="O1" s="144"/>
-      <c r="P1" s="144"/>
-      <c r="Q1" s="144"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="147"/>
+      <c r="M1" s="147"/>
+      <c r="N1" s="147"/>
+      <c r="O1" s="147"/>
+      <c r="P1" s="147"/>
+      <c r="Q1" s="147"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="150" t="s">
         <v>373</v>
       </c>
-      <c r="B2" s="144"/>
-      <c r="C2" s="144"/>
-      <c r="D2" s="144"/>
-      <c r="E2" s="144"/>
-      <c r="F2" s="144"/>
-      <c r="G2" s="144"/>
-      <c r="H2" s="144"/>
-      <c r="I2" s="144"/>
-      <c r="J2" s="144"/>
-      <c r="K2" s="144"/>
-      <c r="L2" s="144"/>
-      <c r="M2" s="144"/>
-      <c r="N2" s="144"/>
-      <c r="O2" s="144"/>
-      <c r="P2" s="144"/>
-      <c r="Q2" s="144"/>
+      <c r="B2" s="147"/>
+      <c r="C2" s="147"/>
+      <c r="D2" s="147"/>
+      <c r="E2" s="147"/>
+      <c r="F2" s="147"/>
+      <c r="G2" s="147"/>
+      <c r="H2" s="147"/>
+      <c r="I2" s="147"/>
+      <c r="J2" s="147"/>
+      <c r="K2" s="147"/>
+      <c r="L2" s="147"/>
+      <c r="M2" s="147"/>
+      <c r="N2" s="147"/>
+      <c r="O2" s="147"/>
+      <c r="P2" s="147"/>
+      <c r="Q2" s="147"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="164" t="s">
+      <c r="A3" s="169" t="s">
         <v>374</v>
       </c>
-      <c r="B3" s="144"/>
-      <c r="C3" s="163" t="s">
+      <c r="B3" s="147"/>
+      <c r="C3" s="168" t="s">
         <v>375</v>
       </c>
-      <c r="D3" s="144"/>
-      <c r="E3" s="166" t="s">
+      <c r="D3" s="147"/>
+      <c r="E3" s="164" t="s">
         <v>376</v>
       </c>
-      <c r="F3" s="144"/>
-      <c r="G3" s="161" t="s">
+      <c r="F3" s="147"/>
+      <c r="G3" s="166" t="s">
         <v>377</v>
       </c>
-      <c r="H3" s="144"/>
-      <c r="I3" s="144"/>
-      <c r="J3" s="144"/>
+      <c r="H3" s="147"/>
+      <c r="I3" s="147"/>
+      <c r="J3" s="147"/>
       <c r="K3" s="31" t="s">
         <v>378</v>
       </c>
       <c r="L3" s="32" t="s">
         <v>379</v>
       </c>
-      <c r="M3" s="160" t="s">
+      <c r="M3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="N3" s="144"/>
-      <c r="O3" s="160" t="s">
+      <c r="N3" s="147"/>
+      <c r="O3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="P3" s="144"/>
+      <c r="P3" s="147"/>
       <c r="Q3" s="33" t="s">
         <v>381</v>
       </c>
@@ -37717,10 +37713,10 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="162" t="s">
+      <c r="A5" s="167" t="s">
         <v>399</v>
       </c>
-      <c r="B5" s="144"/>
+      <c r="B5" s="147"/>
       <c r="C5" s="41"/>
       <c r="D5" s="42"/>
       <c r="E5" s="42"/>
@@ -39543,80 +39539,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="165" t="s">
+      <c r="A1" s="163" t="s">
         <v>408</v>
       </c>
-      <c r="B1" s="144"/>
-      <c r="C1" s="144"/>
-      <c r="D1" s="144"/>
-      <c r="E1" s="144"/>
-      <c r="F1" s="144"/>
-      <c r="G1" s="144"/>
-      <c r="H1" s="144"/>
-      <c r="I1" s="144"/>
-      <c r="J1" s="144"/>
-      <c r="K1" s="144"/>
-      <c r="L1" s="144"/>
-      <c r="M1" s="144"/>
-      <c r="N1" s="144"/>
-      <c r="O1" s="144"/>
-      <c r="P1" s="144"/>
-      <c r="Q1" s="144"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="147"/>
+      <c r="M1" s="147"/>
+      <c r="N1" s="147"/>
+      <c r="O1" s="147"/>
+      <c r="P1" s="147"/>
+      <c r="Q1" s="147"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="150" t="s">
         <v>373</v>
       </c>
-      <c r="B2" s="144"/>
-      <c r="C2" s="144"/>
-      <c r="D2" s="144"/>
-      <c r="E2" s="144"/>
-      <c r="F2" s="144"/>
-      <c r="G2" s="144"/>
-      <c r="H2" s="144"/>
-      <c r="I2" s="144"/>
-      <c r="J2" s="144"/>
-      <c r="K2" s="144"/>
-      <c r="L2" s="144"/>
-      <c r="M2" s="144"/>
-      <c r="N2" s="144"/>
-      <c r="O2" s="144"/>
-      <c r="P2" s="144"/>
-      <c r="Q2" s="144"/>
+      <c r="B2" s="147"/>
+      <c r="C2" s="147"/>
+      <c r="D2" s="147"/>
+      <c r="E2" s="147"/>
+      <c r="F2" s="147"/>
+      <c r="G2" s="147"/>
+      <c r="H2" s="147"/>
+      <c r="I2" s="147"/>
+      <c r="J2" s="147"/>
+      <c r="K2" s="147"/>
+      <c r="L2" s="147"/>
+      <c r="M2" s="147"/>
+      <c r="N2" s="147"/>
+      <c r="O2" s="147"/>
+      <c r="P2" s="147"/>
+      <c r="Q2" s="147"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="164" t="s">
+      <c r="A3" s="169" t="s">
         <v>374</v>
       </c>
-      <c r="B3" s="144"/>
-      <c r="C3" s="163" t="s">
+      <c r="B3" s="147"/>
+      <c r="C3" s="168" t="s">
         <v>375</v>
       </c>
-      <c r="D3" s="144"/>
-      <c r="E3" s="166" t="s">
+      <c r="D3" s="147"/>
+      <c r="E3" s="164" t="s">
         <v>376</v>
       </c>
-      <c r="F3" s="144"/>
-      <c r="G3" s="161" t="s">
+      <c r="F3" s="147"/>
+      <c r="G3" s="166" t="s">
         <v>377</v>
       </c>
-      <c r="H3" s="144"/>
-      <c r="I3" s="144"/>
-      <c r="J3" s="144"/>
+      <c r="H3" s="147"/>
+      <c r="I3" s="147"/>
+      <c r="J3" s="147"/>
       <c r="K3" s="31" t="s">
         <v>378</v>
       </c>
       <c r="L3" s="32" t="s">
         <v>379</v>
       </c>
-      <c r="M3" s="160" t="s">
+      <c r="M3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="N3" s="144"/>
-      <c r="O3" s="160" t="s">
+      <c r="N3" s="147"/>
+      <c r="O3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="P3" s="144"/>
+      <c r="P3" s="147"/>
       <c r="Q3" s="33" t="s">
         <v>381</v>
       </c>
@@ -39675,10 +39671,10 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="162" t="s">
+      <c r="A5" s="167" t="s">
         <v>399</v>
       </c>
-      <c r="B5" s="144"/>
+      <c r="B5" s="147"/>
       <c r="C5" s="41"/>
       <c r="D5" s="42"/>
       <c r="E5" s="42"/>
@@ -41459,80 +41455,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="165" t="s">
+      <c r="A1" s="163" t="s">
         <v>409</v>
       </c>
-      <c r="B1" s="144"/>
-      <c r="C1" s="144"/>
-      <c r="D1" s="144"/>
-      <c r="E1" s="144"/>
-      <c r="F1" s="144"/>
-      <c r="G1" s="144"/>
-      <c r="H1" s="144"/>
-      <c r="I1" s="144"/>
-      <c r="J1" s="144"/>
-      <c r="K1" s="144"/>
-      <c r="L1" s="144"/>
-      <c r="M1" s="144"/>
-      <c r="N1" s="144"/>
-      <c r="O1" s="144"/>
-      <c r="P1" s="144"/>
-      <c r="Q1" s="144"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="147"/>
+      <c r="M1" s="147"/>
+      <c r="N1" s="147"/>
+      <c r="O1" s="147"/>
+      <c r="P1" s="147"/>
+      <c r="Q1" s="147"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="150" t="s">
         <v>373</v>
       </c>
-      <c r="B2" s="144"/>
-      <c r="C2" s="144"/>
-      <c r="D2" s="144"/>
-      <c r="E2" s="144"/>
-      <c r="F2" s="144"/>
-      <c r="G2" s="144"/>
-      <c r="H2" s="144"/>
-      <c r="I2" s="144"/>
-      <c r="J2" s="144"/>
-      <c r="K2" s="144"/>
-      <c r="L2" s="144"/>
-      <c r="M2" s="144"/>
-      <c r="N2" s="144"/>
-      <c r="O2" s="144"/>
-      <c r="P2" s="144"/>
-      <c r="Q2" s="144"/>
+      <c r="B2" s="147"/>
+      <c r="C2" s="147"/>
+      <c r="D2" s="147"/>
+      <c r="E2" s="147"/>
+      <c r="F2" s="147"/>
+      <c r="G2" s="147"/>
+      <c r="H2" s="147"/>
+      <c r="I2" s="147"/>
+      <c r="J2" s="147"/>
+      <c r="K2" s="147"/>
+      <c r="L2" s="147"/>
+      <c r="M2" s="147"/>
+      <c r="N2" s="147"/>
+      <c r="O2" s="147"/>
+      <c r="P2" s="147"/>
+      <c r="Q2" s="147"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="164" t="s">
+      <c r="A3" s="169" t="s">
         <v>374</v>
       </c>
-      <c r="B3" s="144"/>
-      <c r="C3" s="163" t="s">
+      <c r="B3" s="147"/>
+      <c r="C3" s="168" t="s">
         <v>375</v>
       </c>
-      <c r="D3" s="144"/>
-      <c r="E3" s="166" t="s">
+      <c r="D3" s="147"/>
+      <c r="E3" s="164" t="s">
         <v>376</v>
       </c>
-      <c r="F3" s="144"/>
-      <c r="G3" s="161" t="s">
+      <c r="F3" s="147"/>
+      <c r="G3" s="166" t="s">
         <v>377</v>
       </c>
-      <c r="H3" s="144"/>
-      <c r="I3" s="144"/>
-      <c r="J3" s="144"/>
+      <c r="H3" s="147"/>
+      <c r="I3" s="147"/>
+      <c r="J3" s="147"/>
       <c r="K3" s="31" t="s">
         <v>378</v>
       </c>
       <c r="L3" s="32" t="s">
         <v>379</v>
       </c>
-      <c r="M3" s="160" t="s">
+      <c r="M3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="N3" s="144"/>
-      <c r="O3" s="160" t="s">
+      <c r="N3" s="147"/>
+      <c r="O3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="P3" s="144"/>
+      <c r="P3" s="147"/>
       <c r="Q3" s="33" t="s">
         <v>381</v>
       </c>
@@ -41591,10 +41587,10 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="162" t="s">
+      <c r="A5" s="167" t="s">
         <v>399</v>
       </c>
-      <c r="B5" s="144"/>
+      <c r="B5" s="147"/>
       <c r="C5" s="41"/>
       <c r="D5" s="42"/>
       <c r="E5" s="42"/>
@@ -43423,80 +43419,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="165" t="s">
+      <c r="A1" s="163" t="s">
         <v>410</v>
       </c>
-      <c r="B1" s="144"/>
-      <c r="C1" s="144"/>
-      <c r="D1" s="144"/>
-      <c r="E1" s="144"/>
-      <c r="F1" s="144"/>
-      <c r="G1" s="144"/>
-      <c r="H1" s="144"/>
-      <c r="I1" s="144"/>
-      <c r="J1" s="144"/>
-      <c r="K1" s="144"/>
-      <c r="L1" s="144"/>
-      <c r="M1" s="144"/>
-      <c r="N1" s="144"/>
-      <c r="O1" s="144"/>
-      <c r="P1" s="144"/>
-      <c r="Q1" s="144"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="147"/>
+      <c r="M1" s="147"/>
+      <c r="N1" s="147"/>
+      <c r="O1" s="147"/>
+      <c r="P1" s="147"/>
+      <c r="Q1" s="147"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="150" t="s">
         <v>373</v>
       </c>
-      <c r="B2" s="144"/>
-      <c r="C2" s="144"/>
-      <c r="D2" s="144"/>
-      <c r="E2" s="144"/>
-      <c r="F2" s="144"/>
-      <c r="G2" s="144"/>
-      <c r="H2" s="144"/>
-      <c r="I2" s="144"/>
-      <c r="J2" s="144"/>
-      <c r="K2" s="144"/>
-      <c r="L2" s="144"/>
-      <c r="M2" s="144"/>
-      <c r="N2" s="144"/>
-      <c r="O2" s="144"/>
-      <c r="P2" s="144"/>
-      <c r="Q2" s="144"/>
+      <c r="B2" s="147"/>
+      <c r="C2" s="147"/>
+      <c r="D2" s="147"/>
+      <c r="E2" s="147"/>
+      <c r="F2" s="147"/>
+      <c r="G2" s="147"/>
+      <c r="H2" s="147"/>
+      <c r="I2" s="147"/>
+      <c r="J2" s="147"/>
+      <c r="K2" s="147"/>
+      <c r="L2" s="147"/>
+      <c r="M2" s="147"/>
+      <c r="N2" s="147"/>
+      <c r="O2" s="147"/>
+      <c r="P2" s="147"/>
+      <c r="Q2" s="147"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="164" t="s">
+      <c r="A3" s="169" t="s">
         <v>374</v>
       </c>
-      <c r="B3" s="144"/>
-      <c r="C3" s="163" t="s">
+      <c r="B3" s="147"/>
+      <c r="C3" s="168" t="s">
         <v>375</v>
       </c>
-      <c r="D3" s="144"/>
-      <c r="E3" s="166" t="s">
+      <c r="D3" s="147"/>
+      <c r="E3" s="164" t="s">
         <v>376</v>
       </c>
-      <c r="F3" s="144"/>
-      <c r="G3" s="161" t="s">
+      <c r="F3" s="147"/>
+      <c r="G3" s="166" t="s">
         <v>377</v>
       </c>
-      <c r="H3" s="144"/>
-      <c r="I3" s="144"/>
-      <c r="J3" s="144"/>
+      <c r="H3" s="147"/>
+      <c r="I3" s="147"/>
+      <c r="J3" s="147"/>
       <c r="K3" s="31" t="s">
         <v>378</v>
       </c>
       <c r="L3" s="32" t="s">
         <v>379</v>
       </c>
-      <c r="M3" s="160" t="s">
+      <c r="M3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="N3" s="144"/>
-      <c r="O3" s="160" t="s">
+      <c r="N3" s="147"/>
+      <c r="O3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="P3" s="144"/>
+      <c r="P3" s="147"/>
       <c r="Q3" s="33" t="s">
         <v>381</v>
       </c>
@@ -43555,10 +43551,10 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="162" t="s">
+      <c r="A5" s="167" t="s">
         <v>399</v>
       </c>
-      <c r="B5" s="144"/>
+      <c r="B5" s="147"/>
       <c r="C5" s="41"/>
       <c r="D5" s="42"/>
       <c r="E5" s="42"/>
@@ -45375,80 +45371,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="165" t="s">
+      <c r="A1" s="163" t="s">
         <v>411</v>
       </c>
-      <c r="B1" s="144"/>
-      <c r="C1" s="144"/>
-      <c r="D1" s="144"/>
-      <c r="E1" s="144"/>
-      <c r="F1" s="144"/>
-      <c r="G1" s="144"/>
-      <c r="H1" s="144"/>
-      <c r="I1" s="144"/>
-      <c r="J1" s="144"/>
-      <c r="K1" s="144"/>
-      <c r="L1" s="144"/>
-      <c r="M1" s="144"/>
-      <c r="N1" s="144"/>
-      <c r="O1" s="144"/>
-      <c r="P1" s="144"/>
-      <c r="Q1" s="144"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="147"/>
+      <c r="M1" s="147"/>
+      <c r="N1" s="147"/>
+      <c r="O1" s="147"/>
+      <c r="P1" s="147"/>
+      <c r="Q1" s="147"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="150" t="s">
         <v>373</v>
       </c>
-      <c r="B2" s="144"/>
-      <c r="C2" s="144"/>
-      <c r="D2" s="144"/>
-      <c r="E2" s="144"/>
-      <c r="F2" s="144"/>
-      <c r="G2" s="144"/>
-      <c r="H2" s="144"/>
-      <c r="I2" s="144"/>
-      <c r="J2" s="144"/>
-      <c r="K2" s="144"/>
-      <c r="L2" s="144"/>
-      <c r="M2" s="144"/>
-      <c r="N2" s="144"/>
-      <c r="O2" s="144"/>
-      <c r="P2" s="144"/>
-      <c r="Q2" s="144"/>
+      <c r="B2" s="147"/>
+      <c r="C2" s="147"/>
+      <c r="D2" s="147"/>
+      <c r="E2" s="147"/>
+      <c r="F2" s="147"/>
+      <c r="G2" s="147"/>
+      <c r="H2" s="147"/>
+      <c r="I2" s="147"/>
+      <c r="J2" s="147"/>
+      <c r="K2" s="147"/>
+      <c r="L2" s="147"/>
+      <c r="M2" s="147"/>
+      <c r="N2" s="147"/>
+      <c r="O2" s="147"/>
+      <c r="P2" s="147"/>
+      <c r="Q2" s="147"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="164" t="s">
+      <c r="A3" s="169" t="s">
         <v>374</v>
       </c>
-      <c r="B3" s="144"/>
-      <c r="C3" s="163" t="s">
+      <c r="B3" s="147"/>
+      <c r="C3" s="168" t="s">
         <v>375</v>
       </c>
-      <c r="D3" s="144"/>
-      <c r="E3" s="166" t="s">
+      <c r="D3" s="147"/>
+      <c r="E3" s="164" t="s">
         <v>376</v>
       </c>
-      <c r="F3" s="144"/>
-      <c r="G3" s="161" t="s">
+      <c r="F3" s="147"/>
+      <c r="G3" s="166" t="s">
         <v>377</v>
       </c>
-      <c r="H3" s="144"/>
-      <c r="I3" s="144"/>
-      <c r="J3" s="144"/>
+      <c r="H3" s="147"/>
+      <c r="I3" s="147"/>
+      <c r="J3" s="147"/>
       <c r="K3" s="31" t="s">
         <v>378</v>
       </c>
       <c r="L3" s="32" t="s">
         <v>379</v>
       </c>
-      <c r="M3" s="160" t="s">
+      <c r="M3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="N3" s="144"/>
-      <c r="O3" s="160" t="s">
+      <c r="N3" s="147"/>
+      <c r="O3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="P3" s="144"/>
+      <c r="P3" s="147"/>
       <c r="Q3" s="33" t="s">
         <v>381</v>
       </c>
@@ -45507,10 +45503,10 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="162" t="s">
+      <c r="A5" s="167" t="s">
         <v>399</v>
       </c>
-      <c r="B5" s="144"/>
+      <c r="B5" s="147"/>
       <c r="C5" s="41"/>
       <c r="D5" s="42"/>
       <c r="E5" s="42"/>
@@ -47163,80 +47159,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="165" t="s">
+      <c r="A1" s="163" t="s">
         <v>412</v>
       </c>
-      <c r="B1" s="144"/>
-      <c r="C1" s="144"/>
-      <c r="D1" s="144"/>
-      <c r="E1" s="144"/>
-      <c r="F1" s="144"/>
-      <c r="G1" s="144"/>
-      <c r="H1" s="144"/>
-      <c r="I1" s="144"/>
-      <c r="J1" s="144"/>
-      <c r="K1" s="144"/>
-      <c r="L1" s="144"/>
-      <c r="M1" s="144"/>
-      <c r="N1" s="144"/>
-      <c r="O1" s="144"/>
-      <c r="P1" s="144"/>
-      <c r="Q1" s="144"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="147"/>
+      <c r="M1" s="147"/>
+      <c r="N1" s="147"/>
+      <c r="O1" s="147"/>
+      <c r="P1" s="147"/>
+      <c r="Q1" s="147"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="150" t="s">
         <v>373</v>
       </c>
-      <c r="B2" s="144"/>
-      <c r="C2" s="144"/>
-      <c r="D2" s="144"/>
-      <c r="E2" s="144"/>
-      <c r="F2" s="144"/>
-      <c r="G2" s="144"/>
-      <c r="H2" s="144"/>
-      <c r="I2" s="144"/>
-      <c r="J2" s="144"/>
-      <c r="K2" s="144"/>
-      <c r="L2" s="144"/>
-      <c r="M2" s="144"/>
-      <c r="N2" s="144"/>
-      <c r="O2" s="144"/>
-      <c r="P2" s="144"/>
-      <c r="Q2" s="144"/>
+      <c r="B2" s="147"/>
+      <c r="C2" s="147"/>
+      <c r="D2" s="147"/>
+      <c r="E2" s="147"/>
+      <c r="F2" s="147"/>
+      <c r="G2" s="147"/>
+      <c r="H2" s="147"/>
+      <c r="I2" s="147"/>
+      <c r="J2" s="147"/>
+      <c r="K2" s="147"/>
+      <c r="L2" s="147"/>
+      <c r="M2" s="147"/>
+      <c r="N2" s="147"/>
+      <c r="O2" s="147"/>
+      <c r="P2" s="147"/>
+      <c r="Q2" s="147"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="164" t="s">
+      <c r="A3" s="169" t="s">
         <v>374</v>
       </c>
-      <c r="B3" s="144"/>
-      <c r="C3" s="163" t="s">
+      <c r="B3" s="147"/>
+      <c r="C3" s="168" t="s">
         <v>375</v>
       </c>
-      <c r="D3" s="144"/>
-      <c r="E3" s="166" t="s">
+      <c r="D3" s="147"/>
+      <c r="E3" s="164" t="s">
         <v>376</v>
       </c>
-      <c r="F3" s="144"/>
-      <c r="G3" s="161" t="s">
+      <c r="F3" s="147"/>
+      <c r="G3" s="166" t="s">
         <v>377</v>
       </c>
-      <c r="H3" s="144"/>
-      <c r="I3" s="144"/>
-      <c r="J3" s="144"/>
+      <c r="H3" s="147"/>
+      <c r="I3" s="147"/>
+      <c r="J3" s="147"/>
       <c r="K3" s="31" t="s">
         <v>378</v>
       </c>
       <c r="L3" s="32" t="s">
         <v>379</v>
       </c>
-      <c r="M3" s="160" t="s">
+      <c r="M3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="N3" s="144"/>
-      <c r="O3" s="160" t="s">
+      <c r="N3" s="147"/>
+      <c r="O3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="P3" s="144"/>
+      <c r="P3" s="147"/>
       <c r="Q3" s="33" t="s">
         <v>381</v>
       </c>
@@ -47295,10 +47291,10 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="162" t="s">
+      <c r="A5" s="167" t="s">
         <v>399</v>
       </c>
-      <c r="B5" s="144"/>
+      <c r="B5" s="147"/>
       <c r="C5" s="41"/>
       <c r="D5" s="42"/>
       <c r="E5" s="42"/>
